--- a/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
+++ b/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.02.2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.03.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B61422-5F20-4ECF-9C40-0EAE326EFF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7D54E7-686B-4240-B9D0-5B85758199FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mensual" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="48">
   <si>
     <t>FLUJOS DE LA CUENTA FINANCIERA DE BALANZA DE PAGOS</t>
   </si>
@@ -254,7 +254,7 @@
       <name val="Helvetica"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,6 +271,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -717,7 +723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -862,40 +868,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -923,6 +896,45 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:JQ54"/>
+  <dimension ref="A1:JR54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1125,891 +1137,897 @@
     <col min="275" max="275" width="7.42578125" style="1" customWidth="1"/>
     <col min="276" max="276" width="7.28515625" style="1" customWidth="1"/>
     <col min="277" max="277" width="7.28515625" style="47" customWidth="1"/>
-    <col min="278" max="16384" width="11.42578125" style="1"/>
+    <col min="278" max="278" width="7.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="279" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:277" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AO1" s="57"/>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="57"/>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57"/>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AW1" s="57"/>
-      <c r="AX1" s="57"/>
-      <c r="AY1" s="57"/>
-      <c r="AZ1" s="57"/>
-      <c r="BA1" s="57"/>
-      <c r="BB1" s="57"/>
-      <c r="BC1" s="57"/>
-      <c r="BD1" s="57"/>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="57"/>
-      <c r="BG1" s="57"/>
-      <c r="BH1" s="57"/>
-      <c r="BI1" s="57"/>
-      <c r="BJ1" s="57"/>
-      <c r="BK1" s="57"/>
-      <c r="BL1" s="57"/>
-      <c r="BM1" s="57"/>
-      <c r="BN1" s="57"/>
-      <c r="BO1" s="57"/>
-      <c r="BP1" s="57"/>
-      <c r="BQ1" s="57"/>
-      <c r="BR1" s="57"/>
-      <c r="BS1" s="57"/>
-      <c r="BT1" s="57"/>
-      <c r="BU1" s="57"/>
-      <c r="BV1" s="57"/>
-      <c r="BW1" s="57"/>
-      <c r="BX1" s="57"/>
-      <c r="BY1" s="57"/>
-      <c r="BZ1" s="57"/>
-      <c r="CA1" s="57"/>
-      <c r="CB1" s="57"/>
-      <c r="CC1" s="57"/>
-      <c r="CD1" s="57"/>
-      <c r="CE1" s="57"/>
-      <c r="CF1" s="57"/>
-      <c r="CG1" s="57"/>
-      <c r="CH1" s="57"/>
-      <c r="CI1" s="57"/>
-      <c r="CJ1" s="57"/>
-      <c r="CK1" s="57"/>
-      <c r="CL1" s="57"/>
-      <c r="CM1" s="57"/>
-      <c r="CN1" s="57"/>
-      <c r="CO1" s="57"/>
-      <c r="CP1" s="57"/>
-      <c r="CQ1" s="57"/>
-      <c r="CR1" s="57"/>
-      <c r="CS1" s="57"/>
-      <c r="CT1" s="57"/>
-      <c r="CU1" s="57"/>
-      <c r="CV1" s="57"/>
-      <c r="CW1" s="57"/>
-      <c r="CX1" s="57"/>
-      <c r="CY1" s="57"/>
-      <c r="CZ1" s="57"/>
-      <c r="DA1" s="57"/>
-      <c r="DB1" s="57"/>
-      <c r="DC1" s="57"/>
-      <c r="DD1" s="57"/>
-      <c r="DE1" s="57"/>
-      <c r="DF1" s="57"/>
-      <c r="DG1" s="57"/>
-      <c r="DH1" s="57"/>
-      <c r="DI1" s="57"/>
-      <c r="DJ1" s="57"/>
-      <c r="DK1" s="57"/>
-      <c r="DL1" s="57"/>
-      <c r="DM1" s="57"/>
-      <c r="DN1" s="57"/>
-      <c r="DO1" s="57"/>
-      <c r="DP1" s="57"/>
-      <c r="DQ1" s="57"/>
-      <c r="DR1" s="57"/>
-      <c r="DS1" s="57"/>
-      <c r="DT1" s="57"/>
-      <c r="DU1" s="57"/>
-      <c r="DV1" s="57"/>
-      <c r="DW1" s="57"/>
-      <c r="DX1" s="57"/>
-      <c r="DY1" s="57"/>
-      <c r="DZ1" s="57"/>
-      <c r="EA1" s="57"/>
-      <c r="EB1" s="57"/>
-      <c r="EC1" s="57"/>
-      <c r="ED1" s="57"/>
-      <c r="EE1" s="57"/>
-      <c r="EF1" s="57"/>
-      <c r="EG1" s="57"/>
-      <c r="EH1" s="57"/>
-      <c r="EI1" s="57"/>
-      <c r="EJ1" s="57"/>
-      <c r="EK1" s="57"/>
-      <c r="EL1" s="57"/>
-      <c r="EM1" s="57"/>
-      <c r="EN1" s="57"/>
-      <c r="EO1" s="57"/>
-      <c r="EP1" s="57"/>
-      <c r="EQ1" s="57"/>
-      <c r="ER1" s="57"/>
-      <c r="ES1" s="57"/>
-      <c r="ET1" s="57"/>
-      <c r="EU1" s="57"/>
-      <c r="EV1" s="57"/>
-      <c r="EW1" s="57"/>
-      <c r="EX1" s="57"/>
-      <c r="EY1" s="57"/>
-      <c r="EZ1" s="57"/>
-      <c r="FA1" s="57"/>
-      <c r="FB1" s="57"/>
-      <c r="FC1" s="57"/>
-      <c r="FD1" s="57"/>
-      <c r="FE1" s="57"/>
-      <c r="FF1" s="57"/>
-      <c r="FG1" s="57"/>
-      <c r="FH1" s="57"/>
-      <c r="FI1" s="57"/>
-      <c r="FJ1" s="57"/>
-      <c r="FK1" s="57"/>
-      <c r="FL1" s="57"/>
-      <c r="FM1" s="57"/>
-      <c r="FN1" s="57"/>
-      <c r="FO1" s="57"/>
-      <c r="FP1" s="57"/>
-      <c r="FQ1" s="57"/>
-      <c r="FR1" s="57"/>
-      <c r="FS1" s="57"/>
-      <c r="FT1" s="57"/>
-      <c r="FU1" s="57"/>
-      <c r="FV1" s="57"/>
-      <c r="FW1" s="57"/>
-      <c r="FX1" s="57"/>
-      <c r="FY1" s="57"/>
-      <c r="FZ1" s="57"/>
-      <c r="GA1" s="57"/>
-      <c r="GB1" s="57"/>
-      <c r="GC1" s="57"/>
-      <c r="GD1" s="57"/>
-      <c r="GE1" s="57"/>
-      <c r="GF1" s="57"/>
-      <c r="GG1" s="57"/>
-      <c r="GH1" s="57"/>
-      <c r="GI1" s="57"/>
-      <c r="GJ1" s="57"/>
-      <c r="GK1" s="57"/>
-      <c r="GL1" s="57"/>
-      <c r="GM1" s="57"/>
-      <c r="GN1" s="57"/>
-      <c r="GO1" s="57"/>
-      <c r="GP1" s="57"/>
-      <c r="GQ1" s="57"/>
-      <c r="GR1" s="57"/>
-      <c r="GS1" s="57"/>
-      <c r="GT1" s="57"/>
-      <c r="GU1" s="57"/>
-      <c r="GV1" s="57"/>
-      <c r="GW1" s="57"/>
-      <c r="GX1" s="57"/>
-      <c r="GY1" s="57"/>
-      <c r="GZ1" s="57"/>
-      <c r="HA1" s="57"/>
-      <c r="HB1" s="57"/>
-      <c r="HC1" s="57"/>
-      <c r="HD1" s="57"/>
-      <c r="HE1" s="57"/>
-      <c r="HF1" s="57"/>
-      <c r="HG1" s="57"/>
-      <c r="HH1" s="57"/>
-      <c r="HI1" s="57"/>
-      <c r="HJ1" s="57"/>
-      <c r="HK1" s="57"/>
-      <c r="HL1" s="57"/>
-      <c r="HM1" s="57"/>
-      <c r="HN1" s="57"/>
-      <c r="HO1" s="57"/>
-      <c r="HP1" s="57"/>
-      <c r="HQ1" s="57"/>
-      <c r="HR1" s="57"/>
-      <c r="HS1" s="57"/>
-      <c r="HT1" s="57"/>
-      <c r="HU1" s="57"/>
-      <c r="HV1" s="57"/>
-      <c r="HW1" s="57"/>
-      <c r="HX1" s="57"/>
-      <c r="HY1" s="57"/>
-      <c r="HZ1" s="57"/>
-      <c r="IA1" s="57"/>
-      <c r="IB1" s="57"/>
-      <c r="IC1" s="57"/>
-      <c r="ID1" s="57"/>
-      <c r="IE1" s="57"/>
-      <c r="IF1" s="57"/>
-      <c r="IG1" s="57"/>
-      <c r="IH1" s="57"/>
-      <c r="II1" s="57"/>
-      <c r="IJ1" s="57"/>
-      <c r="IK1" s="57"/>
-      <c r="IL1" s="57"/>
-      <c r="IM1" s="57"/>
-      <c r="IN1" s="57"/>
-      <c r="IO1" s="57"/>
-      <c r="IP1" s="57"/>
-      <c r="IQ1" s="57"/>
-      <c r="IR1" s="57"/>
-      <c r="IS1" s="57"/>
-      <c r="IT1" s="57"/>
-      <c r="IU1" s="57"/>
-      <c r="IV1" s="57"/>
-      <c r="IW1" s="57"/>
-      <c r="IX1" s="57"/>
-      <c r="IY1" s="57"/>
-      <c r="IZ1" s="57"/>
-      <c r="JA1" s="57"/>
-      <c r="JB1" s="57"/>
-      <c r="JC1" s="57"/>
-      <c r="JD1" s="57"/>
-      <c r="JE1" s="57"/>
-      <c r="JF1" s="57"/>
-      <c r="JG1" s="57"/>
-      <c r="JH1" s="57"/>
+    <row r="1" spans="1:278" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="59"/>
+      <c r="Z1" s="59"/>
+      <c r="AA1" s="59"/>
+      <c r="AB1" s="59"/>
+      <c r="AC1" s="59"/>
+      <c r="AD1" s="59"/>
+      <c r="AE1" s="59"/>
+      <c r="AF1" s="59"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="59"/>
+      <c r="AI1" s="59"/>
+      <c r="AJ1" s="59"/>
+      <c r="AK1" s="59"/>
+      <c r="AL1" s="59"/>
+      <c r="AM1" s="59"/>
+      <c r="AN1" s="59"/>
+      <c r="AO1" s="59"/>
+      <c r="AP1" s="59"/>
+      <c r="AQ1" s="59"/>
+      <c r="AR1" s="59"/>
+      <c r="AS1" s="59"/>
+      <c r="AT1" s="59"/>
+      <c r="AU1" s="59"/>
+      <c r="AV1" s="59"/>
+      <c r="AW1" s="59"/>
+      <c r="AX1" s="59"/>
+      <c r="AY1" s="59"/>
+      <c r="AZ1" s="59"/>
+      <c r="BA1" s="59"/>
+      <c r="BB1" s="59"/>
+      <c r="BC1" s="59"/>
+      <c r="BD1" s="59"/>
+      <c r="BE1" s="59"/>
+      <c r="BF1" s="59"/>
+      <c r="BG1" s="59"/>
+      <c r="BH1" s="59"/>
+      <c r="BI1" s="59"/>
+      <c r="BJ1" s="59"/>
+      <c r="BK1" s="59"/>
+      <c r="BL1" s="59"/>
+      <c r="BM1" s="59"/>
+      <c r="BN1" s="59"/>
+      <c r="BO1" s="59"/>
+      <c r="BP1" s="59"/>
+      <c r="BQ1" s="59"/>
+      <c r="BR1" s="59"/>
+      <c r="BS1" s="59"/>
+      <c r="BT1" s="59"/>
+      <c r="BU1" s="59"/>
+      <c r="BV1" s="59"/>
+      <c r="BW1" s="59"/>
+      <c r="BX1" s="59"/>
+      <c r="BY1" s="59"/>
+      <c r="BZ1" s="59"/>
+      <c r="CA1" s="59"/>
+      <c r="CB1" s="59"/>
+      <c r="CC1" s="59"/>
+      <c r="CD1" s="59"/>
+      <c r="CE1" s="59"/>
+      <c r="CF1" s="59"/>
+      <c r="CG1" s="59"/>
+      <c r="CH1" s="59"/>
+      <c r="CI1" s="59"/>
+      <c r="CJ1" s="59"/>
+      <c r="CK1" s="59"/>
+      <c r="CL1" s="59"/>
+      <c r="CM1" s="59"/>
+      <c r="CN1" s="59"/>
+      <c r="CO1" s="59"/>
+      <c r="CP1" s="59"/>
+      <c r="CQ1" s="59"/>
+      <c r="CR1" s="59"/>
+      <c r="CS1" s="59"/>
+      <c r="CT1" s="59"/>
+      <c r="CU1" s="59"/>
+      <c r="CV1" s="59"/>
+      <c r="CW1" s="59"/>
+      <c r="CX1" s="59"/>
+      <c r="CY1" s="59"/>
+      <c r="CZ1" s="59"/>
+      <c r="DA1" s="59"/>
+      <c r="DB1" s="59"/>
+      <c r="DC1" s="59"/>
+      <c r="DD1" s="59"/>
+      <c r="DE1" s="59"/>
+      <c r="DF1" s="59"/>
+      <c r="DG1" s="59"/>
+      <c r="DH1" s="59"/>
+      <c r="DI1" s="59"/>
+      <c r="DJ1" s="59"/>
+      <c r="DK1" s="59"/>
+      <c r="DL1" s="59"/>
+      <c r="DM1" s="59"/>
+      <c r="DN1" s="59"/>
+      <c r="DO1" s="59"/>
+      <c r="DP1" s="59"/>
+      <c r="DQ1" s="59"/>
+      <c r="DR1" s="59"/>
+      <c r="DS1" s="59"/>
+      <c r="DT1" s="59"/>
+      <c r="DU1" s="59"/>
+      <c r="DV1" s="59"/>
+      <c r="DW1" s="59"/>
+      <c r="DX1" s="59"/>
+      <c r="DY1" s="59"/>
+      <c r="DZ1" s="59"/>
+      <c r="EA1" s="59"/>
+      <c r="EB1" s="59"/>
+      <c r="EC1" s="59"/>
+      <c r="ED1" s="59"/>
+      <c r="EE1" s="59"/>
+      <c r="EF1" s="59"/>
+      <c r="EG1" s="59"/>
+      <c r="EH1" s="59"/>
+      <c r="EI1" s="59"/>
+      <c r="EJ1" s="59"/>
+      <c r="EK1" s="59"/>
+      <c r="EL1" s="59"/>
+      <c r="EM1" s="59"/>
+      <c r="EN1" s="59"/>
+      <c r="EO1" s="59"/>
+      <c r="EP1" s="59"/>
+      <c r="EQ1" s="59"/>
+      <c r="ER1" s="59"/>
+      <c r="ES1" s="59"/>
+      <c r="ET1" s="59"/>
+      <c r="EU1" s="59"/>
+      <c r="EV1" s="59"/>
+      <c r="EW1" s="59"/>
+      <c r="EX1" s="59"/>
+      <c r="EY1" s="59"/>
+      <c r="EZ1" s="59"/>
+      <c r="FA1" s="59"/>
+      <c r="FB1" s="59"/>
+      <c r="FC1" s="59"/>
+      <c r="FD1" s="59"/>
+      <c r="FE1" s="59"/>
+      <c r="FF1" s="59"/>
+      <c r="FG1" s="59"/>
+      <c r="FH1" s="59"/>
+      <c r="FI1" s="59"/>
+      <c r="FJ1" s="59"/>
+      <c r="FK1" s="59"/>
+      <c r="FL1" s="59"/>
+      <c r="FM1" s="59"/>
+      <c r="FN1" s="59"/>
+      <c r="FO1" s="59"/>
+      <c r="FP1" s="59"/>
+      <c r="FQ1" s="59"/>
+      <c r="FR1" s="59"/>
+      <c r="FS1" s="59"/>
+      <c r="FT1" s="59"/>
+      <c r="FU1" s="59"/>
+      <c r="FV1" s="59"/>
+      <c r="FW1" s="59"/>
+      <c r="FX1" s="59"/>
+      <c r="FY1" s="59"/>
+      <c r="FZ1" s="59"/>
+      <c r="GA1" s="59"/>
+      <c r="GB1" s="59"/>
+      <c r="GC1" s="59"/>
+      <c r="GD1" s="59"/>
+      <c r="GE1" s="59"/>
+      <c r="GF1" s="59"/>
+      <c r="GG1" s="59"/>
+      <c r="GH1" s="59"/>
+      <c r="GI1" s="59"/>
+      <c r="GJ1" s="59"/>
+      <c r="GK1" s="59"/>
+      <c r="GL1" s="59"/>
+      <c r="GM1" s="59"/>
+      <c r="GN1" s="59"/>
+      <c r="GO1" s="59"/>
+      <c r="GP1" s="59"/>
+      <c r="GQ1" s="59"/>
+      <c r="GR1" s="59"/>
+      <c r="GS1" s="59"/>
+      <c r="GT1" s="59"/>
+      <c r="GU1" s="59"/>
+      <c r="GV1" s="59"/>
+      <c r="GW1" s="59"/>
+      <c r="GX1" s="59"/>
+      <c r="GY1" s="59"/>
+      <c r="GZ1" s="59"/>
+      <c r="HA1" s="59"/>
+      <c r="HB1" s="59"/>
+      <c r="HC1" s="59"/>
+      <c r="HD1" s="59"/>
+      <c r="HE1" s="59"/>
+      <c r="HF1" s="59"/>
+      <c r="HG1" s="59"/>
+      <c r="HH1" s="59"/>
+      <c r="HI1" s="59"/>
+      <c r="HJ1" s="59"/>
+      <c r="HK1" s="59"/>
+      <c r="HL1" s="59"/>
+      <c r="HM1" s="59"/>
+      <c r="HN1" s="59"/>
+      <c r="HO1" s="59"/>
+      <c r="HP1" s="59"/>
+      <c r="HQ1" s="59"/>
+      <c r="HR1" s="59"/>
+      <c r="HS1" s="59"/>
+      <c r="HT1" s="59"/>
+      <c r="HU1" s="59"/>
+      <c r="HV1" s="59"/>
+      <c r="HW1" s="59"/>
+      <c r="HX1" s="59"/>
+      <c r="HY1" s="59"/>
+      <c r="HZ1" s="59"/>
+      <c r="IA1" s="59"/>
+      <c r="IB1" s="59"/>
+      <c r="IC1" s="59"/>
+      <c r="ID1" s="59"/>
+      <c r="IE1" s="59"/>
+      <c r="IF1" s="59"/>
+      <c r="IG1" s="59"/>
+      <c r="IH1" s="59"/>
+      <c r="II1" s="59"/>
+      <c r="IJ1" s="59"/>
+      <c r="IK1" s="59"/>
+      <c r="IL1" s="59"/>
+      <c r="IM1" s="59"/>
+      <c r="IN1" s="59"/>
+      <c r="IO1" s="59"/>
+      <c r="IP1" s="59"/>
+      <c r="IQ1" s="59"/>
+      <c r="IR1" s="59"/>
+      <c r="IS1" s="59"/>
+      <c r="IT1" s="59"/>
+      <c r="IU1" s="59"/>
+      <c r="IV1" s="59"/>
+      <c r="IW1" s="59"/>
+      <c r="IX1" s="59"/>
+      <c r="IY1" s="59"/>
+      <c r="IZ1" s="59"/>
+      <c r="JA1" s="59"/>
+      <c r="JB1" s="59"/>
+      <c r="JC1" s="59"/>
+      <c r="JD1" s="59"/>
+      <c r="JE1" s="59"/>
+      <c r="JF1" s="59"/>
+      <c r="JG1" s="59"/>
+      <c r="JH1" s="59"/>
       <c r="JI1" s="1"/>
       <c r="JJ1" s="1"/>
       <c r="JK1" s="1"/>
       <c r="JL1" s="1"/>
       <c r="JM1" s="1"/>
       <c r="JN1" s="1"/>
+      <c r="JR1" s="1"/>
     </row>
-    <row r="2" spans="1:277" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
+    <row r="2" spans="1:278" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
-      <c r="Z2" s="57"/>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="57"/>
-      <c r="AC2" s="57"/>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="57"/>
-      <c r="AH2" s="57"/>
-      <c r="AI2" s="57"/>
-      <c r="AJ2" s="57"/>
-      <c r="AK2" s="57"/>
-      <c r="AL2" s="57"/>
-      <c r="AM2" s="57"/>
-      <c r="AN2" s="57"/>
-      <c r="AO2" s="57"/>
-      <c r="AP2" s="57"/>
-      <c r="AQ2" s="57"/>
-      <c r="AR2" s="57"/>
-      <c r="AS2" s="57"/>
-      <c r="AT2" s="57"/>
-      <c r="AU2" s="57"/>
-      <c r="AV2" s="57"/>
-      <c r="AW2" s="57"/>
-      <c r="AX2" s="57"/>
-      <c r="AY2" s="57"/>
-      <c r="AZ2" s="57"/>
-      <c r="BA2" s="57"/>
-      <c r="BB2" s="57"/>
-      <c r="BC2" s="57"/>
-      <c r="BD2" s="57"/>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="57"/>
-      <c r="BG2" s="57"/>
-      <c r="BH2" s="57"/>
-      <c r="BI2" s="57"/>
-      <c r="BJ2" s="57"/>
-      <c r="BK2" s="57"/>
-      <c r="BL2" s="57"/>
-      <c r="BM2" s="57"/>
-      <c r="BN2" s="57"/>
-      <c r="BO2" s="57"/>
-      <c r="BP2" s="57"/>
-      <c r="BQ2" s="57"/>
-      <c r="BR2" s="57"/>
-      <c r="BS2" s="57"/>
-      <c r="BT2" s="57"/>
-      <c r="BU2" s="57"/>
-      <c r="BV2" s="57"/>
-      <c r="BW2" s="57"/>
-      <c r="BX2" s="57"/>
-      <c r="BY2" s="57"/>
-      <c r="BZ2" s="57"/>
-      <c r="CA2" s="57"/>
-      <c r="CB2" s="57"/>
-      <c r="CC2" s="57"/>
-      <c r="CD2" s="57"/>
-      <c r="CE2" s="57"/>
-      <c r="CF2" s="57"/>
-      <c r="CG2" s="57"/>
-      <c r="CH2" s="57"/>
-      <c r="CI2" s="57"/>
-      <c r="CJ2" s="57"/>
-      <c r="CK2" s="57"/>
-      <c r="CL2" s="57"/>
-      <c r="CM2" s="57"/>
-      <c r="CN2" s="57"/>
-      <c r="CO2" s="57"/>
-      <c r="CP2" s="57"/>
-      <c r="CQ2" s="57"/>
-      <c r="CR2" s="57"/>
-      <c r="CS2" s="57"/>
-      <c r="CT2" s="57"/>
-      <c r="CU2" s="57"/>
-      <c r="CV2" s="57"/>
-      <c r="CW2" s="57"/>
-      <c r="CX2" s="57"/>
-      <c r="CY2" s="57"/>
-      <c r="CZ2" s="57"/>
-      <c r="DA2" s="57"/>
-      <c r="DB2" s="57"/>
-      <c r="DC2" s="57"/>
-      <c r="DD2" s="57"/>
-      <c r="DE2" s="57"/>
-      <c r="DF2" s="57"/>
-      <c r="DG2" s="57"/>
-      <c r="DH2" s="57"/>
-      <c r="DI2" s="57"/>
-      <c r="DJ2" s="57"/>
-      <c r="DK2" s="57"/>
-      <c r="DL2" s="57"/>
-      <c r="DM2" s="57"/>
-      <c r="DN2" s="57"/>
-      <c r="DO2" s="57"/>
-      <c r="DP2" s="57"/>
-      <c r="DQ2" s="57"/>
-      <c r="DR2" s="57"/>
-      <c r="DS2" s="57"/>
-      <c r="DT2" s="57"/>
-      <c r="DU2" s="57"/>
-      <c r="DV2" s="57"/>
-      <c r="DW2" s="57"/>
-      <c r="DX2" s="57"/>
-      <c r="DY2" s="57"/>
-      <c r="DZ2" s="57"/>
-      <c r="EA2" s="57"/>
-      <c r="EB2" s="57"/>
-      <c r="EC2" s="57"/>
-      <c r="ED2" s="57"/>
-      <c r="EE2" s="57"/>
-      <c r="EF2" s="57"/>
-      <c r="EG2" s="57"/>
-      <c r="EH2" s="57"/>
-      <c r="EI2" s="57"/>
-      <c r="EJ2" s="57"/>
-      <c r="EK2" s="57"/>
-      <c r="EL2" s="57"/>
-      <c r="EM2" s="57"/>
-      <c r="EN2" s="57"/>
-      <c r="EO2" s="57"/>
-      <c r="EP2" s="57"/>
-      <c r="EQ2" s="57"/>
-      <c r="ER2" s="57"/>
-      <c r="ES2" s="57"/>
-      <c r="ET2" s="57"/>
-      <c r="EU2" s="57"/>
-      <c r="EV2" s="57"/>
-      <c r="EW2" s="57"/>
-      <c r="EX2" s="57"/>
-      <c r="EY2" s="57"/>
-      <c r="EZ2" s="57"/>
-      <c r="FA2" s="57"/>
-      <c r="FB2" s="57"/>
-      <c r="FC2" s="57"/>
-      <c r="FD2" s="57"/>
-      <c r="FE2" s="57"/>
-      <c r="FF2" s="57"/>
-      <c r="FG2" s="57"/>
-      <c r="FH2" s="57"/>
-      <c r="FI2" s="57"/>
-      <c r="FJ2" s="57"/>
-      <c r="FK2" s="57"/>
-      <c r="FL2" s="57"/>
-      <c r="FM2" s="57"/>
-      <c r="FN2" s="57"/>
-      <c r="FO2" s="57"/>
-      <c r="FP2" s="57"/>
-      <c r="FQ2" s="57"/>
-      <c r="FR2" s="57"/>
-      <c r="FS2" s="57"/>
-      <c r="FT2" s="57"/>
-      <c r="FU2" s="57"/>
-      <c r="FV2" s="57"/>
-      <c r="FW2" s="57"/>
-      <c r="FX2" s="57"/>
-      <c r="FY2" s="57"/>
-      <c r="FZ2" s="57"/>
-      <c r="GA2" s="57"/>
-      <c r="GB2" s="57"/>
-      <c r="GC2" s="57"/>
-      <c r="GD2" s="57"/>
-      <c r="GE2" s="57"/>
-      <c r="GF2" s="57"/>
-      <c r="GG2" s="57"/>
-      <c r="GH2" s="57"/>
-      <c r="GI2" s="57"/>
-      <c r="GJ2" s="57"/>
-      <c r="GK2" s="57"/>
-      <c r="GL2" s="57"/>
-      <c r="GM2" s="57"/>
-      <c r="GN2" s="57"/>
-      <c r="GO2" s="57"/>
-      <c r="GP2" s="57"/>
-      <c r="GQ2" s="57"/>
-      <c r="GR2" s="57"/>
-      <c r="GS2" s="57"/>
-      <c r="GT2" s="57"/>
-      <c r="GU2" s="57"/>
-      <c r="GV2" s="57"/>
-      <c r="GW2" s="57"/>
-      <c r="GX2" s="57"/>
-      <c r="GY2" s="57"/>
-      <c r="GZ2" s="57"/>
-      <c r="HA2" s="57"/>
-      <c r="HB2" s="57"/>
-      <c r="HC2" s="57"/>
-      <c r="HD2" s="57"/>
-      <c r="HE2" s="57"/>
-      <c r="HF2" s="57"/>
-      <c r="HG2" s="57"/>
-      <c r="HH2" s="57"/>
-      <c r="HI2" s="57"/>
-      <c r="HJ2" s="57"/>
-      <c r="HK2" s="57"/>
-      <c r="HL2" s="57"/>
-      <c r="HM2" s="57"/>
-      <c r="HN2" s="57"/>
-      <c r="HO2" s="57"/>
-      <c r="HP2" s="57"/>
-      <c r="HQ2" s="57"/>
-      <c r="HR2" s="57"/>
-      <c r="HS2" s="57"/>
-      <c r="HT2" s="57"/>
-      <c r="HU2" s="57"/>
-      <c r="HV2" s="57"/>
-      <c r="HW2" s="57"/>
-      <c r="HX2" s="57"/>
-      <c r="HY2" s="57"/>
-      <c r="HZ2" s="57"/>
-      <c r="IA2" s="57"/>
-      <c r="IB2" s="57"/>
-      <c r="IC2" s="57"/>
-      <c r="ID2" s="57"/>
-      <c r="IE2" s="57"/>
-      <c r="IF2" s="57"/>
-      <c r="IG2" s="57"/>
-      <c r="IH2" s="57"/>
-      <c r="II2" s="57"/>
-      <c r="IJ2" s="57"/>
-      <c r="IK2" s="57"/>
-      <c r="IL2" s="57"/>
-      <c r="IM2" s="57"/>
-      <c r="IN2" s="57"/>
-      <c r="IO2" s="57"/>
-      <c r="IP2" s="57"/>
-      <c r="IQ2" s="57"/>
-      <c r="IR2" s="57"/>
-      <c r="IS2" s="57"/>
-      <c r="IT2" s="57"/>
-      <c r="IU2" s="57"/>
-      <c r="IV2" s="57"/>
-      <c r="IW2" s="57"/>
-      <c r="IX2" s="57"/>
-      <c r="IY2" s="57"/>
-      <c r="IZ2" s="57"/>
-      <c r="JA2" s="57"/>
-      <c r="JB2" s="57"/>
-      <c r="JC2" s="57"/>
-      <c r="JD2" s="57"/>
-      <c r="JE2" s="57"/>
-      <c r="JF2" s="57"/>
-      <c r="JG2" s="57"/>
-      <c r="JH2" s="57"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
+      <c r="AM2" s="59"/>
+      <c r="AN2" s="59"/>
+      <c r="AO2" s="59"/>
+      <c r="AP2" s="59"/>
+      <c r="AQ2" s="59"/>
+      <c r="AR2" s="59"/>
+      <c r="AS2" s="59"/>
+      <c r="AT2" s="59"/>
+      <c r="AU2" s="59"/>
+      <c r="AV2" s="59"/>
+      <c r="AW2" s="59"/>
+      <c r="AX2" s="59"/>
+      <c r="AY2" s="59"/>
+      <c r="AZ2" s="59"/>
+      <c r="BA2" s="59"/>
+      <c r="BB2" s="59"/>
+      <c r="BC2" s="59"/>
+      <c r="BD2" s="59"/>
+      <c r="BE2" s="59"/>
+      <c r="BF2" s="59"/>
+      <c r="BG2" s="59"/>
+      <c r="BH2" s="59"/>
+      <c r="BI2" s="59"/>
+      <c r="BJ2" s="59"/>
+      <c r="BK2" s="59"/>
+      <c r="BL2" s="59"/>
+      <c r="BM2" s="59"/>
+      <c r="BN2" s="59"/>
+      <c r="BO2" s="59"/>
+      <c r="BP2" s="59"/>
+      <c r="BQ2" s="59"/>
+      <c r="BR2" s="59"/>
+      <c r="BS2" s="59"/>
+      <c r="BT2" s="59"/>
+      <c r="BU2" s="59"/>
+      <c r="BV2" s="59"/>
+      <c r="BW2" s="59"/>
+      <c r="BX2" s="59"/>
+      <c r="BY2" s="59"/>
+      <c r="BZ2" s="59"/>
+      <c r="CA2" s="59"/>
+      <c r="CB2" s="59"/>
+      <c r="CC2" s="59"/>
+      <c r="CD2" s="59"/>
+      <c r="CE2" s="59"/>
+      <c r="CF2" s="59"/>
+      <c r="CG2" s="59"/>
+      <c r="CH2" s="59"/>
+      <c r="CI2" s="59"/>
+      <c r="CJ2" s="59"/>
+      <c r="CK2" s="59"/>
+      <c r="CL2" s="59"/>
+      <c r="CM2" s="59"/>
+      <c r="CN2" s="59"/>
+      <c r="CO2" s="59"/>
+      <c r="CP2" s="59"/>
+      <c r="CQ2" s="59"/>
+      <c r="CR2" s="59"/>
+      <c r="CS2" s="59"/>
+      <c r="CT2" s="59"/>
+      <c r="CU2" s="59"/>
+      <c r="CV2" s="59"/>
+      <c r="CW2" s="59"/>
+      <c r="CX2" s="59"/>
+      <c r="CY2" s="59"/>
+      <c r="CZ2" s="59"/>
+      <c r="DA2" s="59"/>
+      <c r="DB2" s="59"/>
+      <c r="DC2" s="59"/>
+      <c r="DD2" s="59"/>
+      <c r="DE2" s="59"/>
+      <c r="DF2" s="59"/>
+      <c r="DG2" s="59"/>
+      <c r="DH2" s="59"/>
+      <c r="DI2" s="59"/>
+      <c r="DJ2" s="59"/>
+      <c r="DK2" s="59"/>
+      <c r="DL2" s="59"/>
+      <c r="DM2" s="59"/>
+      <c r="DN2" s="59"/>
+      <c r="DO2" s="59"/>
+      <c r="DP2" s="59"/>
+      <c r="DQ2" s="59"/>
+      <c r="DR2" s="59"/>
+      <c r="DS2" s="59"/>
+      <c r="DT2" s="59"/>
+      <c r="DU2" s="59"/>
+      <c r="DV2" s="59"/>
+      <c r="DW2" s="59"/>
+      <c r="DX2" s="59"/>
+      <c r="DY2" s="59"/>
+      <c r="DZ2" s="59"/>
+      <c r="EA2" s="59"/>
+      <c r="EB2" s="59"/>
+      <c r="EC2" s="59"/>
+      <c r="ED2" s="59"/>
+      <c r="EE2" s="59"/>
+      <c r="EF2" s="59"/>
+      <c r="EG2" s="59"/>
+      <c r="EH2" s="59"/>
+      <c r="EI2" s="59"/>
+      <c r="EJ2" s="59"/>
+      <c r="EK2" s="59"/>
+      <c r="EL2" s="59"/>
+      <c r="EM2" s="59"/>
+      <c r="EN2" s="59"/>
+      <c r="EO2" s="59"/>
+      <c r="EP2" s="59"/>
+      <c r="EQ2" s="59"/>
+      <c r="ER2" s="59"/>
+      <c r="ES2" s="59"/>
+      <c r="ET2" s="59"/>
+      <c r="EU2" s="59"/>
+      <c r="EV2" s="59"/>
+      <c r="EW2" s="59"/>
+      <c r="EX2" s="59"/>
+      <c r="EY2" s="59"/>
+      <c r="EZ2" s="59"/>
+      <c r="FA2" s="59"/>
+      <c r="FB2" s="59"/>
+      <c r="FC2" s="59"/>
+      <c r="FD2" s="59"/>
+      <c r="FE2" s="59"/>
+      <c r="FF2" s="59"/>
+      <c r="FG2" s="59"/>
+      <c r="FH2" s="59"/>
+      <c r="FI2" s="59"/>
+      <c r="FJ2" s="59"/>
+      <c r="FK2" s="59"/>
+      <c r="FL2" s="59"/>
+      <c r="FM2" s="59"/>
+      <c r="FN2" s="59"/>
+      <c r="FO2" s="59"/>
+      <c r="FP2" s="59"/>
+      <c r="FQ2" s="59"/>
+      <c r="FR2" s="59"/>
+      <c r="FS2" s="59"/>
+      <c r="FT2" s="59"/>
+      <c r="FU2" s="59"/>
+      <c r="FV2" s="59"/>
+      <c r="FW2" s="59"/>
+      <c r="FX2" s="59"/>
+      <c r="FY2" s="59"/>
+      <c r="FZ2" s="59"/>
+      <c r="GA2" s="59"/>
+      <c r="GB2" s="59"/>
+      <c r="GC2" s="59"/>
+      <c r="GD2" s="59"/>
+      <c r="GE2" s="59"/>
+      <c r="GF2" s="59"/>
+      <c r="GG2" s="59"/>
+      <c r="GH2" s="59"/>
+      <c r="GI2" s="59"/>
+      <c r="GJ2" s="59"/>
+      <c r="GK2" s="59"/>
+      <c r="GL2" s="59"/>
+      <c r="GM2" s="59"/>
+      <c r="GN2" s="59"/>
+      <c r="GO2" s="59"/>
+      <c r="GP2" s="59"/>
+      <c r="GQ2" s="59"/>
+      <c r="GR2" s="59"/>
+      <c r="GS2" s="59"/>
+      <c r="GT2" s="59"/>
+      <c r="GU2" s="59"/>
+      <c r="GV2" s="59"/>
+      <c r="GW2" s="59"/>
+      <c r="GX2" s="59"/>
+      <c r="GY2" s="59"/>
+      <c r="GZ2" s="59"/>
+      <c r="HA2" s="59"/>
+      <c r="HB2" s="59"/>
+      <c r="HC2" s="59"/>
+      <c r="HD2" s="59"/>
+      <c r="HE2" s="59"/>
+      <c r="HF2" s="59"/>
+      <c r="HG2" s="59"/>
+      <c r="HH2" s="59"/>
+      <c r="HI2" s="59"/>
+      <c r="HJ2" s="59"/>
+      <c r="HK2" s="59"/>
+      <c r="HL2" s="59"/>
+      <c r="HM2" s="59"/>
+      <c r="HN2" s="59"/>
+      <c r="HO2" s="59"/>
+      <c r="HP2" s="59"/>
+      <c r="HQ2" s="59"/>
+      <c r="HR2" s="59"/>
+      <c r="HS2" s="59"/>
+      <c r="HT2" s="59"/>
+      <c r="HU2" s="59"/>
+      <c r="HV2" s="59"/>
+      <c r="HW2" s="59"/>
+      <c r="HX2" s="59"/>
+      <c r="HY2" s="59"/>
+      <c r="HZ2" s="59"/>
+      <c r="IA2" s="59"/>
+      <c r="IB2" s="59"/>
+      <c r="IC2" s="59"/>
+      <c r="ID2" s="59"/>
+      <c r="IE2" s="59"/>
+      <c r="IF2" s="59"/>
+      <c r="IG2" s="59"/>
+      <c r="IH2" s="59"/>
+      <c r="II2" s="59"/>
+      <c r="IJ2" s="59"/>
+      <c r="IK2" s="59"/>
+      <c r="IL2" s="59"/>
+      <c r="IM2" s="59"/>
+      <c r="IN2" s="59"/>
+      <c r="IO2" s="59"/>
+      <c r="IP2" s="59"/>
+      <c r="IQ2" s="59"/>
+      <c r="IR2" s="59"/>
+      <c r="IS2" s="59"/>
+      <c r="IT2" s="59"/>
+      <c r="IU2" s="59"/>
+      <c r="IV2" s="59"/>
+      <c r="IW2" s="59"/>
+      <c r="IX2" s="59"/>
+      <c r="IY2" s="59"/>
+      <c r="IZ2" s="59"/>
+      <c r="JA2" s="59"/>
+      <c r="JB2" s="59"/>
+      <c r="JC2" s="59"/>
+      <c r="JD2" s="59"/>
+      <c r="JE2" s="59"/>
+      <c r="JF2" s="59"/>
+      <c r="JG2" s="59"/>
+      <c r="JH2" s="59"/>
       <c r="JI2" s="1"/>
       <c r="JJ2" s="1"/>
       <c r="JK2" s="1"/>
       <c r="JL2" s="1"/>
       <c r="JM2" s="1"/>
       <c r="JN2" s="1"/>
+      <c r="JR2" s="1"/>
     </row>
-    <row r="4" spans="1:277" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:278" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="49">
+      <c r="B4" s="61">
         <v>2003</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49">
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61">
         <v>2004</v>
       </c>
-      <c r="O4" s="49"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="49"/>
-      <c r="W4" s="49"/>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="49">
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="61"/>
+      <c r="V4" s="61"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
+      <c r="Y4" s="61"/>
+      <c r="Z4" s="61">
         <v>2005</v>
       </c>
-      <c r="AA4" s="49"/>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="49"/>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="49"/>
-      <c r="AH4" s="49"/>
-      <c r="AI4" s="49"/>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
-      <c r="AL4" s="49">
+      <c r="AA4" s="61"/>
+      <c r="AB4" s="61"/>
+      <c r="AC4" s="61"/>
+      <c r="AD4" s="61"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="61"/>
+      <c r="AG4" s="61"/>
+      <c r="AH4" s="61"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="61"/>
+      <c r="AL4" s="61">
         <v>2006</v>
       </c>
-      <c r="AM4" s="49"/>
-      <c r="AN4" s="49"/>
-      <c r="AO4" s="49"/>
-      <c r="AP4" s="49"/>
-      <c r="AQ4" s="49"/>
-      <c r="AR4" s="49"/>
-      <c r="AS4" s="49"/>
-      <c r="AT4" s="49"/>
-      <c r="AU4" s="49"/>
-      <c r="AV4" s="49"/>
-      <c r="AW4" s="49"/>
-      <c r="AX4" s="49">
+      <c r="AM4" s="61"/>
+      <c r="AN4" s="61"/>
+      <c r="AO4" s="61"/>
+      <c r="AP4" s="61"/>
+      <c r="AQ4" s="61"/>
+      <c r="AR4" s="61"/>
+      <c r="AS4" s="61"/>
+      <c r="AT4" s="61"/>
+      <c r="AU4" s="61"/>
+      <c r="AV4" s="61"/>
+      <c r="AW4" s="61"/>
+      <c r="AX4" s="61">
         <v>2007</v>
       </c>
-      <c r="AY4" s="49"/>
-      <c r="AZ4" s="49"/>
-      <c r="BA4" s="49"/>
-      <c r="BB4" s="49"/>
-      <c r="BC4" s="49"/>
-      <c r="BD4" s="49"/>
-      <c r="BE4" s="49"/>
-      <c r="BF4" s="49"/>
-      <c r="BG4" s="49"/>
-      <c r="BH4" s="49"/>
-      <c r="BI4" s="49"/>
-      <c r="BJ4" s="49">
+      <c r="AY4" s="61"/>
+      <c r="AZ4" s="61"/>
+      <c r="BA4" s="61"/>
+      <c r="BB4" s="61"/>
+      <c r="BC4" s="61"/>
+      <c r="BD4" s="61"/>
+      <c r="BE4" s="61"/>
+      <c r="BF4" s="61"/>
+      <c r="BG4" s="61"/>
+      <c r="BH4" s="61"/>
+      <c r="BI4" s="61"/>
+      <c r="BJ4" s="61">
         <v>2008</v>
       </c>
-      <c r="BK4" s="49"/>
-      <c r="BL4" s="49"/>
-      <c r="BM4" s="49"/>
-      <c r="BN4" s="49"/>
-      <c r="BO4" s="49"/>
-      <c r="BP4" s="49"/>
-      <c r="BQ4" s="49"/>
-      <c r="BR4" s="49"/>
-      <c r="BS4" s="49"/>
-      <c r="BT4" s="49"/>
-      <c r="BU4" s="49"/>
-      <c r="BV4" s="49">
+      <c r="BK4" s="61"/>
+      <c r="BL4" s="61"/>
+      <c r="BM4" s="61"/>
+      <c r="BN4" s="61"/>
+      <c r="BO4" s="61"/>
+      <c r="BP4" s="61"/>
+      <c r="BQ4" s="61"/>
+      <c r="BR4" s="61"/>
+      <c r="BS4" s="61"/>
+      <c r="BT4" s="61"/>
+      <c r="BU4" s="61"/>
+      <c r="BV4" s="61">
         <v>2009</v>
       </c>
-      <c r="BW4" s="49"/>
-      <c r="BX4" s="49"/>
-      <c r="BY4" s="49"/>
-      <c r="BZ4" s="49"/>
-      <c r="CA4" s="49"/>
-      <c r="CB4" s="49"/>
-      <c r="CC4" s="49"/>
-      <c r="CD4" s="49"/>
-      <c r="CE4" s="49"/>
-      <c r="CF4" s="49"/>
-      <c r="CG4" s="49"/>
-      <c r="CH4" s="49">
+      <c r="BW4" s="61"/>
+      <c r="BX4" s="61"/>
+      <c r="BY4" s="61"/>
+      <c r="BZ4" s="61"/>
+      <c r="CA4" s="61"/>
+      <c r="CB4" s="61"/>
+      <c r="CC4" s="61"/>
+      <c r="CD4" s="61"/>
+      <c r="CE4" s="61"/>
+      <c r="CF4" s="61"/>
+      <c r="CG4" s="61"/>
+      <c r="CH4" s="61">
         <v>2010</v>
       </c>
-      <c r="CI4" s="49"/>
-      <c r="CJ4" s="49"/>
-      <c r="CK4" s="49"/>
-      <c r="CL4" s="49"/>
-      <c r="CM4" s="49"/>
-      <c r="CN4" s="49"/>
-      <c r="CO4" s="49"/>
-      <c r="CP4" s="49"/>
-      <c r="CQ4" s="49"/>
-      <c r="CR4" s="49"/>
-      <c r="CS4" s="49"/>
-      <c r="CT4" s="49">
+      <c r="CI4" s="61"/>
+      <c r="CJ4" s="61"/>
+      <c r="CK4" s="61"/>
+      <c r="CL4" s="61"/>
+      <c r="CM4" s="61"/>
+      <c r="CN4" s="61"/>
+      <c r="CO4" s="61"/>
+      <c r="CP4" s="61"/>
+      <c r="CQ4" s="61"/>
+      <c r="CR4" s="61"/>
+      <c r="CS4" s="61"/>
+      <c r="CT4" s="61">
         <v>2011</v>
       </c>
-      <c r="CU4" s="49"/>
-      <c r="CV4" s="49"/>
-      <c r="CW4" s="49"/>
-      <c r="CX4" s="49"/>
-      <c r="CY4" s="49"/>
-      <c r="CZ4" s="49"/>
-      <c r="DA4" s="49"/>
-      <c r="DB4" s="49"/>
-      <c r="DC4" s="49"/>
-      <c r="DD4" s="49"/>
-      <c r="DE4" s="49"/>
-      <c r="DF4" s="49">
+      <c r="CU4" s="61"/>
+      <c r="CV4" s="61"/>
+      <c r="CW4" s="61"/>
+      <c r="CX4" s="61"/>
+      <c r="CY4" s="61"/>
+      <c r="CZ4" s="61"/>
+      <c r="DA4" s="61"/>
+      <c r="DB4" s="61"/>
+      <c r="DC4" s="61"/>
+      <c r="DD4" s="61"/>
+      <c r="DE4" s="61"/>
+      <c r="DF4" s="61">
         <v>2012</v>
       </c>
-      <c r="DG4" s="49"/>
-      <c r="DH4" s="49"/>
-      <c r="DI4" s="49"/>
-      <c r="DJ4" s="49"/>
-      <c r="DK4" s="49"/>
-      <c r="DL4" s="49"/>
-      <c r="DM4" s="49"/>
-      <c r="DN4" s="49"/>
-      <c r="DO4" s="49"/>
-      <c r="DP4" s="49"/>
-      <c r="DQ4" s="49"/>
-      <c r="DR4" s="49">
+      <c r="DG4" s="61"/>
+      <c r="DH4" s="61"/>
+      <c r="DI4" s="61"/>
+      <c r="DJ4" s="61"/>
+      <c r="DK4" s="61"/>
+      <c r="DL4" s="61"/>
+      <c r="DM4" s="61"/>
+      <c r="DN4" s="61"/>
+      <c r="DO4" s="61"/>
+      <c r="DP4" s="61"/>
+      <c r="DQ4" s="61"/>
+      <c r="DR4" s="61">
         <v>2013</v>
       </c>
-      <c r="DS4" s="49"/>
-      <c r="DT4" s="49"/>
-      <c r="DU4" s="49"/>
-      <c r="DV4" s="49"/>
-      <c r="DW4" s="49"/>
-      <c r="DX4" s="49"/>
-      <c r="DY4" s="49"/>
-      <c r="DZ4" s="49"/>
-      <c r="EA4" s="49"/>
-      <c r="EB4" s="49"/>
-      <c r="EC4" s="49"/>
-      <c r="ED4" s="49">
+      <c r="DS4" s="61"/>
+      <c r="DT4" s="61"/>
+      <c r="DU4" s="61"/>
+      <c r="DV4" s="61"/>
+      <c r="DW4" s="61"/>
+      <c r="DX4" s="61"/>
+      <c r="DY4" s="61"/>
+      <c r="DZ4" s="61"/>
+      <c r="EA4" s="61"/>
+      <c r="EB4" s="61"/>
+      <c r="EC4" s="61"/>
+      <c r="ED4" s="61">
         <v>2014</v>
       </c>
-      <c r="EE4" s="49"/>
-      <c r="EF4" s="49"/>
-      <c r="EG4" s="49"/>
-      <c r="EH4" s="49"/>
-      <c r="EI4" s="49"/>
-      <c r="EJ4" s="49"/>
-      <c r="EK4" s="49"/>
-      <c r="EL4" s="49"/>
-      <c r="EM4" s="49"/>
-      <c r="EN4" s="49"/>
-      <c r="EO4" s="49"/>
-      <c r="EP4" s="49">
+      <c r="EE4" s="61"/>
+      <c r="EF4" s="61"/>
+      <c r="EG4" s="61"/>
+      <c r="EH4" s="61"/>
+      <c r="EI4" s="61"/>
+      <c r="EJ4" s="61"/>
+      <c r="EK4" s="61"/>
+      <c r="EL4" s="61"/>
+      <c r="EM4" s="61"/>
+      <c r="EN4" s="61"/>
+      <c r="EO4" s="61"/>
+      <c r="EP4" s="61">
         <v>2015</v>
       </c>
-      <c r="EQ4" s="49"/>
-      <c r="ER4" s="49"/>
-      <c r="ES4" s="49"/>
-      <c r="ET4" s="49"/>
-      <c r="EU4" s="49"/>
-      <c r="EV4" s="49"/>
-      <c r="EW4" s="49"/>
-      <c r="EX4" s="49"/>
-      <c r="EY4" s="49"/>
-      <c r="EZ4" s="49"/>
-      <c r="FA4" s="49"/>
-      <c r="FB4" s="49">
+      <c r="EQ4" s="61"/>
+      <c r="ER4" s="61"/>
+      <c r="ES4" s="61"/>
+      <c r="ET4" s="61"/>
+      <c r="EU4" s="61"/>
+      <c r="EV4" s="61"/>
+      <c r="EW4" s="61"/>
+      <c r="EX4" s="61"/>
+      <c r="EY4" s="61"/>
+      <c r="EZ4" s="61"/>
+      <c r="FA4" s="61"/>
+      <c r="FB4" s="61">
         <v>2016</v>
       </c>
-      <c r="FC4" s="49"/>
-      <c r="FD4" s="49"/>
-      <c r="FE4" s="49"/>
-      <c r="FF4" s="49"/>
-      <c r="FG4" s="49"/>
-      <c r="FH4" s="49"/>
-      <c r="FI4" s="49"/>
-      <c r="FJ4" s="49"/>
-      <c r="FK4" s="49"/>
-      <c r="FL4" s="49"/>
-      <c r="FM4" s="49"/>
-      <c r="FN4" s="49">
+      <c r="FC4" s="61"/>
+      <c r="FD4" s="61"/>
+      <c r="FE4" s="61"/>
+      <c r="FF4" s="61"/>
+      <c r="FG4" s="61"/>
+      <c r="FH4" s="61"/>
+      <c r="FI4" s="61"/>
+      <c r="FJ4" s="61"/>
+      <c r="FK4" s="61"/>
+      <c r="FL4" s="61"/>
+      <c r="FM4" s="61"/>
+      <c r="FN4" s="61">
         <v>2017</v>
       </c>
-      <c r="FO4" s="49"/>
-      <c r="FP4" s="49"/>
-      <c r="FQ4" s="49"/>
-      <c r="FR4" s="49"/>
-      <c r="FS4" s="49"/>
-      <c r="FT4" s="49"/>
-      <c r="FU4" s="49"/>
-      <c r="FV4" s="49"/>
-      <c r="FW4" s="49"/>
-      <c r="FX4" s="49"/>
-      <c r="FY4" s="49"/>
-      <c r="FZ4" s="49">
+      <c r="FO4" s="61"/>
+      <c r="FP4" s="61"/>
+      <c r="FQ4" s="61"/>
+      <c r="FR4" s="61"/>
+      <c r="FS4" s="61"/>
+      <c r="FT4" s="61"/>
+      <c r="FU4" s="61"/>
+      <c r="FV4" s="61"/>
+      <c r="FW4" s="61"/>
+      <c r="FX4" s="61"/>
+      <c r="FY4" s="61"/>
+      <c r="FZ4" s="61">
         <v>2018</v>
       </c>
-      <c r="GA4" s="49"/>
-      <c r="GB4" s="49"/>
-      <c r="GC4" s="49"/>
-      <c r="GD4" s="49"/>
-      <c r="GE4" s="49"/>
-      <c r="GF4" s="49"/>
-      <c r="GG4" s="49"/>
-      <c r="GH4" s="49"/>
-      <c r="GI4" s="49"/>
-      <c r="GJ4" s="49"/>
-      <c r="GK4" s="49"/>
-      <c r="GL4" s="49">
+      <c r="GA4" s="61"/>
+      <c r="GB4" s="61"/>
+      <c r="GC4" s="61"/>
+      <c r="GD4" s="61"/>
+      <c r="GE4" s="61"/>
+      <c r="GF4" s="61"/>
+      <c r="GG4" s="61"/>
+      <c r="GH4" s="61"/>
+      <c r="GI4" s="61"/>
+      <c r="GJ4" s="61"/>
+      <c r="GK4" s="61"/>
+      <c r="GL4" s="61">
         <v>2019</v>
       </c>
-      <c r="GM4" s="49"/>
-      <c r="GN4" s="49"/>
-      <c r="GO4" s="49"/>
-      <c r="GP4" s="49"/>
-      <c r="GQ4" s="49"/>
-      <c r="GR4" s="49"/>
-      <c r="GS4" s="49"/>
-      <c r="GT4" s="49"/>
-      <c r="GU4" s="49"/>
-      <c r="GV4" s="49"/>
-      <c r="GW4" s="49"/>
-      <c r="GX4" s="49">
+      <c r="GM4" s="61"/>
+      <c r="GN4" s="61"/>
+      <c r="GO4" s="61"/>
+      <c r="GP4" s="61"/>
+      <c r="GQ4" s="61"/>
+      <c r="GR4" s="61"/>
+      <c r="GS4" s="61"/>
+      <c r="GT4" s="61"/>
+      <c r="GU4" s="61"/>
+      <c r="GV4" s="61"/>
+      <c r="GW4" s="61"/>
+      <c r="GX4" s="61">
         <v>2020</v>
       </c>
-      <c r="GY4" s="49"/>
-      <c r="GZ4" s="49"/>
-      <c r="HA4" s="49"/>
-      <c r="HB4" s="49"/>
-      <c r="HC4" s="49"/>
-      <c r="HD4" s="49"/>
-      <c r="HE4" s="49"/>
-      <c r="HF4" s="49"/>
-      <c r="HG4" s="49"/>
-      <c r="HH4" s="49"/>
-      <c r="HI4" s="49"/>
-      <c r="HJ4" s="49">
+      <c r="GY4" s="61"/>
+      <c r="GZ4" s="61"/>
+      <c r="HA4" s="61"/>
+      <c r="HB4" s="61"/>
+      <c r="HC4" s="61"/>
+      <c r="HD4" s="61"/>
+      <c r="HE4" s="61"/>
+      <c r="HF4" s="61"/>
+      <c r="HG4" s="61"/>
+      <c r="HH4" s="61"/>
+      <c r="HI4" s="61"/>
+      <c r="HJ4" s="61">
         <v>2021</v>
       </c>
-      <c r="HK4" s="49"/>
-      <c r="HL4" s="49"/>
-      <c r="HM4" s="49"/>
-      <c r="HN4" s="49"/>
-      <c r="HO4" s="49"/>
-      <c r="HP4" s="49"/>
-      <c r="HQ4" s="49"/>
-      <c r="HR4" s="49"/>
-      <c r="HS4" s="49"/>
-      <c r="HT4" s="49"/>
-      <c r="HU4" s="49"/>
-      <c r="HV4" s="49">
+      <c r="HK4" s="61"/>
+      <c r="HL4" s="61"/>
+      <c r="HM4" s="61"/>
+      <c r="HN4" s="61"/>
+      <c r="HO4" s="61"/>
+      <c r="HP4" s="61"/>
+      <c r="HQ4" s="61"/>
+      <c r="HR4" s="61"/>
+      <c r="HS4" s="61"/>
+      <c r="HT4" s="61"/>
+      <c r="HU4" s="61"/>
+      <c r="HV4" s="61">
         <v>2022</v>
       </c>
-      <c r="HW4" s="49"/>
-      <c r="HX4" s="49"/>
-      <c r="HY4" s="49"/>
-      <c r="HZ4" s="49"/>
-      <c r="IA4" s="49"/>
-      <c r="IB4" s="49"/>
-      <c r="IC4" s="49"/>
-      <c r="ID4" s="49"/>
-      <c r="IE4" s="49"/>
-      <c r="IF4" s="49"/>
-      <c r="IG4" s="49"/>
-      <c r="IH4" s="49">
+      <c r="HW4" s="61"/>
+      <c r="HX4" s="61"/>
+      <c r="HY4" s="61"/>
+      <c r="HZ4" s="61"/>
+      <c r="IA4" s="61"/>
+      <c r="IB4" s="61"/>
+      <c r="IC4" s="61"/>
+      <c r="ID4" s="61"/>
+      <c r="IE4" s="61"/>
+      <c r="IF4" s="61"/>
+      <c r="IG4" s="61"/>
+      <c r="IH4" s="61">
         <v>2023</v>
       </c>
-      <c r="II4" s="49"/>
-      <c r="IJ4" s="49"/>
-      <c r="IK4" s="49"/>
-      <c r="IL4" s="49"/>
-      <c r="IM4" s="49"/>
-      <c r="IN4" s="49"/>
-      <c r="IO4" s="49"/>
-      <c r="IP4" s="49"/>
-      <c r="IQ4" s="49"/>
-      <c r="IR4" s="49"/>
-      <c r="IS4" s="49"/>
-      <c r="IT4" s="49">
+      <c r="II4" s="61"/>
+      <c r="IJ4" s="61"/>
+      <c r="IK4" s="61"/>
+      <c r="IL4" s="61"/>
+      <c r="IM4" s="61"/>
+      <c r="IN4" s="61"/>
+      <c r="IO4" s="61"/>
+      <c r="IP4" s="61"/>
+      <c r="IQ4" s="61"/>
+      <c r="IR4" s="61"/>
+      <c r="IS4" s="61"/>
+      <c r="IT4" s="61">
         <v>2024</v>
       </c>
-      <c r="IU4" s="49"/>
-      <c r="IV4" s="49"/>
-      <c r="IW4" s="49"/>
-      <c r="IX4" s="49"/>
-      <c r="IY4" s="49"/>
-      <c r="IZ4" s="49"/>
-      <c r="JA4" s="49"/>
-      <c r="JB4" s="49"/>
-      <c r="JC4" s="49"/>
-      <c r="JD4" s="49"/>
-      <c r="JE4" s="50"/>
-      <c r="JF4" s="53">
+      <c r="IU4" s="61"/>
+      <c r="IV4" s="61"/>
+      <c r="IW4" s="61"/>
+      <c r="IX4" s="61"/>
+      <c r="IY4" s="61"/>
+      <c r="IZ4" s="61"/>
+      <c r="JA4" s="61"/>
+      <c r="JB4" s="61"/>
+      <c r="JC4" s="61"/>
+      <c r="JD4" s="61"/>
+      <c r="JE4" s="63"/>
+      <c r="JF4" s="66">
         <v>2025</v>
       </c>
-      <c r="JG4" s="54"/>
-      <c r="JH4" s="54"/>
-      <c r="JI4" s="54"/>
-      <c r="JJ4" s="54"/>
-      <c r="JK4" s="54"/>
-      <c r="JL4" s="54"/>
-      <c r="JM4" s="54"/>
-      <c r="JN4" s="54"/>
-      <c r="JO4" s="54"/>
-      <c r="JP4" s="54"/>
-      <c r="JQ4" s="55"/>
+      <c r="JG4" s="67"/>
+      <c r="JH4" s="67"/>
+      <c r="JI4" s="67"/>
+      <c r="JJ4" s="67"/>
+      <c r="JK4" s="67"/>
+      <c r="JL4" s="67"/>
+      <c r="JM4" s="67"/>
+      <c r="JN4" s="67"/>
+      <c r="JO4" s="67"/>
+      <c r="JP4" s="67"/>
+      <c r="JQ4" s="68"/>
+      <c r="JR4" s="70">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="5" spans="1:277" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:278" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2841,8 +2859,11 @@
       <c r="JQ5" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="JR5" s="7" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
@@ -3674,8 +3695,11 @@
       <c r="JQ6" s="12">
         <v>4228.7969168391301</v>
       </c>
+      <c r="JR6" s="12">
+        <v>1590.6848722236</v>
+      </c>
     </row>
-    <row r="7" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -4507,8 +4531,11 @@
       <c r="JQ7" s="12">
         <v>2341.3583789813601</v>
       </c>
+      <c r="JR7" s="12">
+        <v>6208.30117425356</v>
+      </c>
     </row>
-    <row r="8" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>17</v>
       </c>
@@ -5340,8 +5367,11 @@
       <c r="JQ8" s="12">
         <v>-1887.4385378577999</v>
       </c>
+      <c r="JR8" s="12">
+        <v>4617.61630202996</v>
+      </c>
     </row>
-    <row r="9" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>18</v>
       </c>
@@ -6173,8 +6203,11 @@
       <c r="JQ9" s="12">
         <v>1220.97858189108</v>
       </c>
+      <c r="JR9" s="12">
+        <v>-817.87384374868998</v>
+      </c>
     </row>
-    <row r="10" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>19</v>
       </c>
@@ -7006,8 +7039,11 @@
       <c r="JQ10" s="17">
         <v>582.71755831577798</v>
       </c>
+      <c r="JR10" s="17">
+        <v>996.91297164238597</v>
+      </c>
     </row>
-    <row r="11" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>20</v>
       </c>
@@ -7839,8 +7875,11 @@
       <c r="JQ11" s="17">
         <v>300.347057857018</v>
       </c>
+      <c r="JR11" s="17">
+        <v>303.45890342688199</v>
+      </c>
     </row>
-    <row r="12" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>21</v>
       </c>
@@ -8672,8 +8711,11 @@
       <c r="JQ12" s="17">
         <v>-161.99617878958</v>
       </c>
+      <c r="JR12" s="17">
+        <v>59.205363193840597</v>
+      </c>
     </row>
-    <row r="13" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>22</v>
       </c>
@@ -9505,8 +9547,11 @@
       <c r="JQ13" s="17">
         <v>444.36667924834001</v>
       </c>
+      <c r="JR13" s="17">
+        <v>634.248705021663</v>
+      </c>
     </row>
-    <row r="14" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>23</v>
       </c>
@@ -10338,8 +10383,11 @@
       <c r="JQ14" s="17">
         <v>-638.26102357530999</v>
       </c>
+      <c r="JR14" s="17">
+        <v>1814.7868153910799</v>
+      </c>
     </row>
-    <row r="15" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>20</v>
       </c>
@@ -11171,8 +11219,11 @@
       <c r="JQ15" s="17">
         <v>533.27321182451101</v>
       </c>
+      <c r="JR15" s="17">
+        <v>272.365870470939</v>
+      </c>
     </row>
-    <row r="16" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>21</v>
       </c>
@@ -12004,8 +12055,11 @@
       <c r="JQ16" s="17">
         <v>-412.14521154213003</v>
       </c>
+      <c r="JR16" s="17">
+        <v>53.8616785100443</v>
+      </c>
     </row>
-    <row r="17" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>22</v>
       </c>
@@ -12837,8 +12891,11 @@
       <c r="JQ17" s="17">
         <v>-759.38902385768995</v>
       </c>
+      <c r="JR17" s="17">
+        <v>1488.5592664101</v>
+      </c>
     </row>
-    <row r="18" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
@@ -13670,8 +13727,11 @@
       <c r="JQ18" s="12">
         <v>434.431672953168</v>
       </c>
+      <c r="JR18" s="12">
+        <v>-3354.4657471342998</v>
+      </c>
     </row>
-    <row r="19" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>19</v>
       </c>
@@ -14503,8 +14563,11 @@
       <c r="JQ19" s="17">
         <v>1052.9335972096901</v>
       </c>
+      <c r="JR19" s="17">
+        <v>1219.2364803358</v>
+      </c>
     </row>
-    <row r="20" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>25</v>
       </c>
@@ -15336,8 +15399,11 @@
       <c r="JQ20" s="17">
         <v>1341.99770044298</v>
       </c>
+      <c r="JR20" s="17">
+        <v>1295.16391503002</v>
+      </c>
     </row>
-    <row r="21" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>26</v>
       </c>
@@ -16169,8 +16235,11 @@
       <c r="JQ21" s="17">
         <v>-289.06410323327998</v>
       </c>
+      <c r="JR21" s="17">
+        <v>-75.927434694229007</v>
+      </c>
     </row>
-    <row r="22" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>27</v>
       </c>
@@ -17002,8 +17071,11 @@
       <c r="JQ22" s="17">
         <v>-89.788852452597993</v>
       </c>
+      <c r="JR22" s="17">
+        <v>185.25839893528101</v>
+      </c>
     </row>
-    <row r="23" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>28</v>
       </c>
@@ -17835,8 +17907,11 @@
       <c r="JQ23" s="17">
         <v>-199.27525078068001</v>
       </c>
+      <c r="JR23" s="17">
+        <v>-261.18583362951</v>
+      </c>
     </row>
-    <row r="24" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>29</v>
       </c>
@@ -18668,8 +18743,11 @@
       <c r="JQ24" s="17">
         <v>618.50192425652597</v>
       </c>
+      <c r="JR24" s="17">
+        <v>4573.7022274701303</v>
+      </c>
     </row>
-    <row r="25" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>25</v>
       </c>
@@ -19501,8 +19579,11 @@
       <c r="JQ25" s="17">
         <v>-143.21190431747999</v>
       </c>
+      <c r="JR25" s="17">
+        <v>130.854396267223</v>
+      </c>
     </row>
-    <row r="26" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
         <v>26</v>
       </c>
@@ -20334,8 +20415,11 @@
       <c r="JQ26" s="17">
         <v>761.71382857400704</v>
       </c>
+      <c r="JR26" s="17">
+        <v>4442.8478312029101</v>
+      </c>
     </row>
-    <row r="27" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>27</v>
       </c>
@@ -21167,8 +21251,11 @@
       <c r="JQ27" s="17">
         <v>769.70208234903896</v>
       </c>
+      <c r="JR27" s="17">
+        <v>4782.7133550756398</v>
+      </c>
     </row>
-    <row r="28" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>28</v>
       </c>
@@ -22000,8 +22087,11 @@
       <c r="JQ28" s="17">
         <v>-7.9882537750321001</v>
       </c>
+      <c r="JR28" s="17">
+        <v>-339.86552387273002</v>
+      </c>
     </row>
-    <row r="29" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>30</v>
       </c>
@@ -22833,8 +22923,11 @@
       <c r="JQ29" s="12">
         <v>-124.71365373330001</v>
       </c>
+      <c r="JR29" s="12">
+        <v>-248.61479256209</v>
+      </c>
     </row>
-    <row r="30" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>31</v>
       </c>
@@ -23666,8 +23759,11 @@
       <c r="JQ30" s="12">
         <v>2124.62411221411</v>
       </c>
+      <c r="JR30" s="12">
+        <v>6003.8324365039298</v>
+      </c>
     </row>
-    <row r="31" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
         <v>19</v>
       </c>
@@ -24499,8 +24595,11 @@
       <c r="JQ31" s="17">
         <v>2162.1295450842499</v>
       </c>
+      <c r="JR31" s="17">
+        <v>6394.47874529814</v>
+      </c>
     </row>
-    <row r="32" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
         <v>32</v>
       </c>
@@ -25332,8 +25431,11 @@
       <c r="JQ32" s="17">
         <v>0</v>
       </c>
+      <c r="JR32" s="17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="13" t="s">
         <v>33</v>
       </c>
@@ -26165,8 +26267,11 @@
       <c r="JQ33" s="17">
         <v>1783.3577970025101</v>
       </c>
+      <c r="JR33" s="17">
+        <v>1096.01935598298</v>
+      </c>
     </row>
-    <row r="34" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="13" t="s">
         <v>34</v>
       </c>
@@ -26998,8 +27103,11 @@
       <c r="JQ34" s="17">
         <v>57.533693594552098</v>
       </c>
+      <c r="JR34" s="17">
+        <v>-298.45582954593999</v>
+      </c>
     </row>
-    <row r="35" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="13" t="s">
         <v>35</v>
       </c>
@@ -27831,8 +27939,11 @@
       <c r="JQ35" s="17">
         <v>324.21636301694002</v>
       </c>
+      <c r="JR35" s="17">
+        <v>5599.7042915846096</v>
+      </c>
     </row>
-    <row r="36" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="13" t="s">
         <v>36</v>
       </c>
@@ -28664,8 +28775,11 @@
       <c r="JQ36" s="17">
         <v>-2.9783085297472001</v>
       </c>
+      <c r="JR36" s="17">
+        <v>-2.7890727235087001</v>
+      </c>
     </row>
-    <row r="37" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="13" t="s">
         <v>23</v>
       </c>
@@ -29497,8 +29611,11 @@
       <c r="JQ37" s="17">
         <v>37.505432870144197</v>
       </c>
+      <c r="JR37" s="17">
+        <v>390.64630879420702</v>
+      </c>
     </row>
-    <row r="38" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>33</v>
       </c>
@@ -30330,8 +30447,11 @@
       <c r="JQ38" s="17">
         <v>151.45436455636101</v>
       </c>
+      <c r="JR38" s="17">
+        <v>-435.16125301766999</v>
+      </c>
     </row>
-    <row r="39" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="13" t="s">
         <v>34</v>
       </c>
@@ -31163,8 +31283,11 @@
       <c r="JQ39" s="17">
         <v>594.48588119577596</v>
       </c>
+      <c r="JR39" s="17">
+        <v>589.98780122916605</v>
+      </c>
     </row>
-    <row r="40" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="13" t="s">
         <v>35</v>
       </c>
@@ -31996,8 +32119,11 @@
       <c r="JQ40" s="17">
         <v>-716.22638999071</v>
       </c>
+      <c r="JR40" s="17">
+        <v>228.09179297682101</v>
+      </c>
     </row>
-    <row r="41" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="13" t="s">
         <v>37</v>
       </c>
@@ -32829,8 +32955,11 @@
       <c r="JQ41" s="17">
         <v>3.5733E-4</v>
       </c>
+      <c r="JR41" s="17">
+        <v>-1.04239E-3</v>
+      </c>
     </row>
-    <row r="42" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="13" t="s">
         <v>38</v>
       </c>
@@ -33662,8 +33791,11 @@
       <c r="JQ42" s="17">
         <v>7.7912197787187498</v>
       </c>
+      <c r="JR42" s="17">
+        <v>7.7290099958920999</v>
+      </c>
     </row>
-    <row r="43" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="18" t="s">
         <v>39</v>
       </c>
@@ -34495,286 +34627,290 @@
       <c r="JQ43" s="22">
         <v>573.47620351407295</v>
       </c>
+      <c r="JR43" s="22">
+        <v>7.8068191647895997</v>
+      </c>
     </row>
-    <row r="44" spans="1:277" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="51" t="s">
+    <row r="44" spans="1:278" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="52"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="52"/>
-      <c r="O44" s="52"/>
-      <c r="P44" s="52"/>
-      <c r="Q44" s="52"/>
-      <c r="R44" s="52"/>
-      <c r="S44" s="52"/>
-      <c r="T44" s="52"/>
-      <c r="U44" s="52"/>
-      <c r="V44" s="52"/>
-      <c r="W44" s="52"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="52"/>
-      <c r="Z44" s="52"/>
-      <c r="AA44" s="52"/>
-      <c r="AB44" s="52"/>
-      <c r="AC44" s="52"/>
-      <c r="AD44" s="52"/>
-      <c r="AE44" s="52"/>
-      <c r="AF44" s="52"/>
-      <c r="AG44" s="52"/>
-      <c r="AH44" s="52"/>
-      <c r="AI44" s="52"/>
-      <c r="AJ44" s="52"/>
-      <c r="AK44" s="52"/>
-      <c r="AL44" s="52"/>
-      <c r="AM44" s="52"/>
-      <c r="AN44" s="52"/>
-      <c r="AO44" s="52"/>
-      <c r="AP44" s="52"/>
-      <c r="AQ44" s="52"/>
-      <c r="AR44" s="52"/>
-      <c r="AS44" s="52"/>
-      <c r="AT44" s="52"/>
-      <c r="AU44" s="52"/>
-      <c r="AV44" s="52"/>
-      <c r="AW44" s="52"/>
-      <c r="AX44" s="52"/>
-      <c r="AY44" s="52"/>
-      <c r="AZ44" s="52"/>
-      <c r="BA44" s="52"/>
-      <c r="BB44" s="52"/>
-      <c r="BC44" s="52"/>
-      <c r="BD44" s="52"/>
-      <c r="BE44" s="52"/>
-      <c r="BF44" s="52"/>
-      <c r="BG44" s="52"/>
-      <c r="BH44" s="52"/>
-      <c r="BI44" s="52"/>
-      <c r="BJ44" s="52"/>
-      <c r="BK44" s="52"/>
-      <c r="BL44" s="52"/>
-      <c r="BM44" s="52"/>
-      <c r="BN44" s="52"/>
-      <c r="BO44" s="52"/>
-      <c r="BP44" s="52"/>
-      <c r="BQ44" s="52"/>
-      <c r="BR44" s="52"/>
-      <c r="BS44" s="52"/>
-      <c r="BT44" s="52"/>
-      <c r="BU44" s="52"/>
-      <c r="BV44" s="52"/>
-      <c r="BW44" s="52"/>
-      <c r="BX44" s="52"/>
-      <c r="BY44" s="52"/>
-      <c r="BZ44" s="52"/>
-      <c r="CA44" s="52"/>
-      <c r="CB44" s="52"/>
-      <c r="CC44" s="52"/>
-      <c r="CD44" s="52"/>
-      <c r="CE44" s="52"/>
-      <c r="CF44" s="52"/>
-      <c r="CG44" s="52"/>
-      <c r="CH44" s="52"/>
-      <c r="CI44" s="52"/>
-      <c r="CJ44" s="52"/>
-      <c r="CK44" s="52"/>
-      <c r="CL44" s="52"/>
-      <c r="CM44" s="52"/>
-      <c r="CN44" s="52"/>
-      <c r="CO44" s="52"/>
-      <c r="CP44" s="52"/>
-      <c r="CQ44" s="52"/>
-      <c r="CR44" s="52"/>
-      <c r="CS44" s="52"/>
-      <c r="CT44" s="52"/>
-      <c r="CU44" s="52"/>
-      <c r="CV44" s="52"/>
-      <c r="CW44" s="52"/>
-      <c r="CX44" s="52"/>
-      <c r="CY44" s="52"/>
-      <c r="CZ44" s="52"/>
-      <c r="DA44" s="52"/>
-      <c r="DB44" s="52"/>
-      <c r="DC44" s="52"/>
-      <c r="DD44" s="52"/>
-      <c r="DE44" s="52"/>
-      <c r="DF44" s="52"/>
-      <c r="DG44" s="52"/>
-      <c r="DH44" s="52"/>
-      <c r="DI44" s="52"/>
-      <c r="DJ44" s="52"/>
-      <c r="DK44" s="52"/>
-      <c r="DL44" s="52"/>
-      <c r="DM44" s="52"/>
-      <c r="DN44" s="52"/>
-      <c r="DO44" s="52"/>
-      <c r="DP44" s="52"/>
-      <c r="DQ44" s="52"/>
-      <c r="DR44" s="52"/>
-      <c r="DS44" s="52"/>
-      <c r="DT44" s="52"/>
-      <c r="DU44" s="52"/>
-      <c r="DV44" s="52"/>
-      <c r="DW44" s="52"/>
-      <c r="DX44" s="52"/>
-      <c r="DY44" s="52"/>
-      <c r="DZ44" s="52"/>
-      <c r="EA44" s="52"/>
-      <c r="EB44" s="52"/>
-      <c r="EC44" s="52"/>
-      <c r="ED44" s="52"/>
-      <c r="EE44" s="52"/>
-      <c r="EF44" s="52"/>
-      <c r="EG44" s="52"/>
-      <c r="EH44" s="52"/>
-      <c r="EI44" s="52"/>
-      <c r="EJ44" s="52"/>
-      <c r="EK44" s="52"/>
-      <c r="EL44" s="52"/>
-      <c r="EM44" s="52"/>
-      <c r="EN44" s="52"/>
-      <c r="EO44" s="52"/>
-      <c r="EP44" s="52"/>
-      <c r="EQ44" s="52"/>
-      <c r="ER44" s="52"/>
-      <c r="ES44" s="52"/>
-      <c r="ET44" s="52"/>
-      <c r="EU44" s="52"/>
-      <c r="EV44" s="52"/>
-      <c r="EW44" s="52"/>
-      <c r="EX44" s="52"/>
-      <c r="EY44" s="52"/>
-      <c r="EZ44" s="52"/>
-      <c r="FA44" s="52"/>
-      <c r="FB44" s="52"/>
-      <c r="FC44" s="52"/>
-      <c r="FD44" s="52"/>
-      <c r="FE44" s="52"/>
-      <c r="FF44" s="52"/>
-      <c r="FG44" s="52"/>
-      <c r="FH44" s="52"/>
-      <c r="FI44" s="52"/>
-      <c r="FJ44" s="52"/>
-      <c r="FK44" s="52"/>
-      <c r="FL44" s="52"/>
-      <c r="FM44" s="52"/>
-      <c r="FN44" s="52"/>
-      <c r="FO44" s="52"/>
-      <c r="FP44" s="52"/>
-      <c r="FQ44" s="52"/>
-      <c r="FR44" s="52"/>
-      <c r="FS44" s="52"/>
-      <c r="FT44" s="52"/>
-      <c r="FU44" s="52"/>
-      <c r="FV44" s="52"/>
-      <c r="FW44" s="52"/>
-      <c r="FX44" s="52"/>
-      <c r="FY44" s="52"/>
-      <c r="FZ44" s="52"/>
-      <c r="GA44" s="52"/>
-      <c r="GB44" s="52"/>
-      <c r="GC44" s="52"/>
-      <c r="GD44" s="52"/>
-      <c r="GE44" s="52"/>
-      <c r="GF44" s="52"/>
-      <c r="GG44" s="52"/>
-      <c r="GH44" s="52"/>
-      <c r="GI44" s="52"/>
-      <c r="GJ44" s="52"/>
-      <c r="GK44" s="52"/>
-      <c r="GL44" s="52"/>
-      <c r="GM44" s="52"/>
-      <c r="GN44" s="52"/>
-      <c r="GO44" s="52"/>
-      <c r="GP44" s="52"/>
-      <c r="GQ44" s="52"/>
-      <c r="GR44" s="52"/>
-      <c r="GS44" s="52"/>
-      <c r="GT44" s="52"/>
-      <c r="GU44" s="52"/>
-      <c r="GV44" s="52"/>
-      <c r="GW44" s="52"/>
-      <c r="GX44" s="52"/>
-      <c r="GY44" s="52"/>
-      <c r="GZ44" s="52"/>
-      <c r="HA44" s="52"/>
-      <c r="HB44" s="52"/>
-      <c r="HC44" s="52"/>
-      <c r="HD44" s="52"/>
-      <c r="HE44" s="52"/>
-      <c r="HF44" s="52"/>
-      <c r="HG44" s="52"/>
-      <c r="HH44" s="52"/>
-      <c r="HI44" s="52"/>
-      <c r="HJ44" s="52"/>
-      <c r="HK44" s="52"/>
-      <c r="HL44" s="52"/>
-      <c r="HM44" s="52"/>
-      <c r="HN44" s="52"/>
-      <c r="HO44" s="52"/>
-      <c r="HP44" s="52"/>
-      <c r="HQ44" s="52"/>
-      <c r="HR44" s="52"/>
-      <c r="HS44" s="52"/>
-      <c r="HT44" s="52"/>
-      <c r="HU44" s="52"/>
-      <c r="HV44" s="52"/>
-      <c r="HW44" s="52"/>
-      <c r="HX44" s="52"/>
-      <c r="HY44" s="52"/>
-      <c r="HZ44" s="52"/>
-      <c r="IA44" s="52"/>
-      <c r="IB44" s="52"/>
-      <c r="IC44" s="52"/>
-      <c r="ID44" s="52"/>
-      <c r="IE44" s="52"/>
-      <c r="IF44" s="52"/>
-      <c r="IG44" s="52"/>
-      <c r="IH44" s="52"/>
-      <c r="II44" s="52"/>
-      <c r="IJ44" s="52"/>
-      <c r="IK44" s="52"/>
-      <c r="IL44" s="52"/>
-      <c r="IM44" s="52"/>
-      <c r="IN44" s="52"/>
-      <c r="IO44" s="52"/>
-      <c r="IP44" s="52"/>
-      <c r="IQ44" s="52"/>
-      <c r="IR44" s="52"/>
-      <c r="IS44" s="52"/>
-      <c r="IT44" s="52"/>
-      <c r="IU44" s="52"/>
-      <c r="IV44" s="52"/>
-      <c r="IW44" s="52"/>
-      <c r="IX44" s="52"/>
-      <c r="IY44" s="52"/>
-      <c r="IZ44" s="52"/>
-      <c r="JA44" s="52"/>
-      <c r="JB44" s="52"/>
-      <c r="JC44" s="52"/>
-      <c r="JD44" s="52"/>
-      <c r="JE44" s="52"/>
-      <c r="JF44" s="52"/>
-      <c r="JG44" s="52"/>
-      <c r="JH44" s="52"/>
-      <c r="JI44" s="52"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="65"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="65"/>
+      <c r="R44" s="65"/>
+      <c r="S44" s="65"/>
+      <c r="T44" s="65"/>
+      <c r="U44" s="65"/>
+      <c r="V44" s="65"/>
+      <c r="W44" s="65"/>
+      <c r="X44" s="65"/>
+      <c r="Y44" s="65"/>
+      <c r="Z44" s="65"/>
+      <c r="AA44" s="65"/>
+      <c r="AB44" s="65"/>
+      <c r="AC44" s="65"/>
+      <c r="AD44" s="65"/>
+      <c r="AE44" s="65"/>
+      <c r="AF44" s="65"/>
+      <c r="AG44" s="65"/>
+      <c r="AH44" s="65"/>
+      <c r="AI44" s="65"/>
+      <c r="AJ44" s="65"/>
+      <c r="AK44" s="65"/>
+      <c r="AL44" s="65"/>
+      <c r="AM44" s="65"/>
+      <c r="AN44" s="65"/>
+      <c r="AO44" s="65"/>
+      <c r="AP44" s="65"/>
+      <c r="AQ44" s="65"/>
+      <c r="AR44" s="65"/>
+      <c r="AS44" s="65"/>
+      <c r="AT44" s="65"/>
+      <c r="AU44" s="65"/>
+      <c r="AV44" s="65"/>
+      <c r="AW44" s="65"/>
+      <c r="AX44" s="65"/>
+      <c r="AY44" s="65"/>
+      <c r="AZ44" s="65"/>
+      <c r="BA44" s="65"/>
+      <c r="BB44" s="65"/>
+      <c r="BC44" s="65"/>
+      <c r="BD44" s="65"/>
+      <c r="BE44" s="65"/>
+      <c r="BF44" s="65"/>
+      <c r="BG44" s="65"/>
+      <c r="BH44" s="65"/>
+      <c r="BI44" s="65"/>
+      <c r="BJ44" s="65"/>
+      <c r="BK44" s="65"/>
+      <c r="BL44" s="65"/>
+      <c r="BM44" s="65"/>
+      <c r="BN44" s="65"/>
+      <c r="BO44" s="65"/>
+      <c r="BP44" s="65"/>
+      <c r="BQ44" s="65"/>
+      <c r="BR44" s="65"/>
+      <c r="BS44" s="65"/>
+      <c r="BT44" s="65"/>
+      <c r="BU44" s="65"/>
+      <c r="BV44" s="65"/>
+      <c r="BW44" s="65"/>
+      <c r="BX44" s="65"/>
+      <c r="BY44" s="65"/>
+      <c r="BZ44" s="65"/>
+      <c r="CA44" s="65"/>
+      <c r="CB44" s="65"/>
+      <c r="CC44" s="65"/>
+      <c r="CD44" s="65"/>
+      <c r="CE44" s="65"/>
+      <c r="CF44" s="65"/>
+      <c r="CG44" s="65"/>
+      <c r="CH44" s="65"/>
+      <c r="CI44" s="65"/>
+      <c r="CJ44" s="65"/>
+      <c r="CK44" s="65"/>
+      <c r="CL44" s="65"/>
+      <c r="CM44" s="65"/>
+      <c r="CN44" s="65"/>
+      <c r="CO44" s="65"/>
+      <c r="CP44" s="65"/>
+      <c r="CQ44" s="65"/>
+      <c r="CR44" s="65"/>
+      <c r="CS44" s="65"/>
+      <c r="CT44" s="65"/>
+      <c r="CU44" s="65"/>
+      <c r="CV44" s="65"/>
+      <c r="CW44" s="65"/>
+      <c r="CX44" s="65"/>
+      <c r="CY44" s="65"/>
+      <c r="CZ44" s="65"/>
+      <c r="DA44" s="65"/>
+      <c r="DB44" s="65"/>
+      <c r="DC44" s="65"/>
+      <c r="DD44" s="65"/>
+      <c r="DE44" s="65"/>
+      <c r="DF44" s="65"/>
+      <c r="DG44" s="65"/>
+      <c r="DH44" s="65"/>
+      <c r="DI44" s="65"/>
+      <c r="DJ44" s="65"/>
+      <c r="DK44" s="65"/>
+      <c r="DL44" s="65"/>
+      <c r="DM44" s="65"/>
+      <c r="DN44" s="65"/>
+      <c r="DO44" s="65"/>
+      <c r="DP44" s="65"/>
+      <c r="DQ44" s="65"/>
+      <c r="DR44" s="65"/>
+      <c r="DS44" s="65"/>
+      <c r="DT44" s="65"/>
+      <c r="DU44" s="65"/>
+      <c r="DV44" s="65"/>
+      <c r="DW44" s="65"/>
+      <c r="DX44" s="65"/>
+      <c r="DY44" s="65"/>
+      <c r="DZ44" s="65"/>
+      <c r="EA44" s="65"/>
+      <c r="EB44" s="65"/>
+      <c r="EC44" s="65"/>
+      <c r="ED44" s="65"/>
+      <c r="EE44" s="65"/>
+      <c r="EF44" s="65"/>
+      <c r="EG44" s="65"/>
+      <c r="EH44" s="65"/>
+      <c r="EI44" s="65"/>
+      <c r="EJ44" s="65"/>
+      <c r="EK44" s="65"/>
+      <c r="EL44" s="65"/>
+      <c r="EM44" s="65"/>
+      <c r="EN44" s="65"/>
+      <c r="EO44" s="65"/>
+      <c r="EP44" s="65"/>
+      <c r="EQ44" s="65"/>
+      <c r="ER44" s="65"/>
+      <c r="ES44" s="65"/>
+      <c r="ET44" s="65"/>
+      <c r="EU44" s="65"/>
+      <c r="EV44" s="65"/>
+      <c r="EW44" s="65"/>
+      <c r="EX44" s="65"/>
+      <c r="EY44" s="65"/>
+      <c r="EZ44" s="65"/>
+      <c r="FA44" s="65"/>
+      <c r="FB44" s="65"/>
+      <c r="FC44" s="65"/>
+      <c r="FD44" s="65"/>
+      <c r="FE44" s="65"/>
+      <c r="FF44" s="65"/>
+      <c r="FG44" s="65"/>
+      <c r="FH44" s="65"/>
+      <c r="FI44" s="65"/>
+      <c r="FJ44" s="65"/>
+      <c r="FK44" s="65"/>
+      <c r="FL44" s="65"/>
+      <c r="FM44" s="65"/>
+      <c r="FN44" s="65"/>
+      <c r="FO44" s="65"/>
+      <c r="FP44" s="65"/>
+      <c r="FQ44" s="65"/>
+      <c r="FR44" s="65"/>
+      <c r="FS44" s="65"/>
+      <c r="FT44" s="65"/>
+      <c r="FU44" s="65"/>
+      <c r="FV44" s="65"/>
+      <c r="FW44" s="65"/>
+      <c r="FX44" s="65"/>
+      <c r="FY44" s="65"/>
+      <c r="FZ44" s="65"/>
+      <c r="GA44" s="65"/>
+      <c r="GB44" s="65"/>
+      <c r="GC44" s="65"/>
+      <c r="GD44" s="65"/>
+      <c r="GE44" s="65"/>
+      <c r="GF44" s="65"/>
+      <c r="GG44" s="65"/>
+      <c r="GH44" s="65"/>
+      <c r="GI44" s="65"/>
+      <c r="GJ44" s="65"/>
+      <c r="GK44" s="65"/>
+      <c r="GL44" s="65"/>
+      <c r="GM44" s="65"/>
+      <c r="GN44" s="65"/>
+      <c r="GO44" s="65"/>
+      <c r="GP44" s="65"/>
+      <c r="GQ44" s="65"/>
+      <c r="GR44" s="65"/>
+      <c r="GS44" s="65"/>
+      <c r="GT44" s="65"/>
+      <c r="GU44" s="65"/>
+      <c r="GV44" s="65"/>
+      <c r="GW44" s="65"/>
+      <c r="GX44" s="65"/>
+      <c r="GY44" s="65"/>
+      <c r="GZ44" s="65"/>
+      <c r="HA44" s="65"/>
+      <c r="HB44" s="65"/>
+      <c r="HC44" s="65"/>
+      <c r="HD44" s="65"/>
+      <c r="HE44" s="65"/>
+      <c r="HF44" s="65"/>
+      <c r="HG44" s="65"/>
+      <c r="HH44" s="65"/>
+      <c r="HI44" s="65"/>
+      <c r="HJ44" s="65"/>
+      <c r="HK44" s="65"/>
+      <c r="HL44" s="65"/>
+      <c r="HM44" s="65"/>
+      <c r="HN44" s="65"/>
+      <c r="HO44" s="65"/>
+      <c r="HP44" s="65"/>
+      <c r="HQ44" s="65"/>
+      <c r="HR44" s="65"/>
+      <c r="HS44" s="65"/>
+      <c r="HT44" s="65"/>
+      <c r="HU44" s="65"/>
+      <c r="HV44" s="65"/>
+      <c r="HW44" s="65"/>
+      <c r="HX44" s="65"/>
+      <c r="HY44" s="65"/>
+      <c r="HZ44" s="65"/>
+      <c r="IA44" s="65"/>
+      <c r="IB44" s="65"/>
+      <c r="IC44" s="65"/>
+      <c r="ID44" s="65"/>
+      <c r="IE44" s="65"/>
+      <c r="IF44" s="65"/>
+      <c r="IG44" s="65"/>
+      <c r="IH44" s="65"/>
+      <c r="II44" s="65"/>
+      <c r="IJ44" s="65"/>
+      <c r="IK44" s="65"/>
+      <c r="IL44" s="65"/>
+      <c r="IM44" s="65"/>
+      <c r="IN44" s="65"/>
+      <c r="IO44" s="65"/>
+      <c r="IP44" s="65"/>
+      <c r="IQ44" s="65"/>
+      <c r="IR44" s="65"/>
+      <c r="IS44" s="65"/>
+      <c r="IT44" s="65"/>
+      <c r="IU44" s="65"/>
+      <c r="IV44" s="65"/>
+      <c r="IW44" s="65"/>
+      <c r="IX44" s="65"/>
+      <c r="IY44" s="65"/>
+      <c r="IZ44" s="65"/>
+      <c r="JA44" s="65"/>
+      <c r="JB44" s="65"/>
+      <c r="JC44" s="65"/>
+      <c r="JD44" s="65"/>
+      <c r="JE44" s="65"/>
+      <c r="JF44" s="65"/>
+      <c r="JG44" s="65"/>
+      <c r="JH44" s="65"/>
+      <c r="JI44" s="65"/>
       <c r="JJ44" s="23"/>
       <c r="JK44" s="1"/>
       <c r="JL44" s="1"/>
       <c r="JM44" s="1"/>
       <c r="JN44" s="1"/>
+      <c r="JR44" s="48"/>
     </row>
-    <row r="45" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="24" t="s">
         <v>41</v>
       </c>
@@ -35606,8 +35742,11 @@
       <c r="JQ45" s="30">
         <v>3655.3207133250598</v>
       </c>
+      <c r="JR45" s="30">
+        <v>1582.8780530588101</v>
+      </c>
     </row>
-    <row r="46" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>42</v>
       </c>
@@ -36439,8 +36578,11 @@
       <c r="JQ46" s="17">
         <v>618.50192425652597</v>
       </c>
+      <c r="JR46" s="17">
+        <v>4573.7022274701303</v>
+      </c>
     </row>
-    <row r="47" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
         <v>26</v>
       </c>
@@ -37272,8 +37414,11 @@
       <c r="JQ47" s="17">
         <v>761.71382857400704</v>
       </c>
+      <c r="JR47" s="17">
+        <v>4442.8478312029101</v>
+      </c>
     </row>
-    <row r="48" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="13" t="s">
         <v>43</v>
       </c>
@@ -37889,8 +38034,11 @@
       <c r="JQ48" s="17">
         <v>275.21318230396298</v>
       </c>
+      <c r="JR48" s="17">
+        <v>3666.0922732930499</v>
+      </c>
     </row>
-    <row r="49" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="13" t="s">
         <v>44</v>
       </c>
@@ -38506,8 +38654,11 @@
       <c r="JQ49" s="17">
         <v>486.50064627004502</v>
       </c>
+      <c r="JR49" s="17">
+        <v>776.755557909863</v>
+      </c>
     </row>
-    <row r="50" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="13" t="s">
         <v>25</v>
       </c>
@@ -39339,8 +39490,11 @@
       <c r="JQ50" s="17">
         <v>-143.21190431747999</v>
       </c>
+      <c r="JR50" s="17">
+        <v>130.854396267223</v>
+      </c>
     </row>
-    <row r="51" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="13" t="s">
         <v>45</v>
       </c>
@@ -40172,8 +40326,11 @@
       <c r="JQ51" s="17">
         <v>-36.414830756564001</v>
       </c>
+      <c r="JR51" s="17">
+        <v>-224.26687717748001</v>
+      </c>
     </row>
-    <row r="52" spans="1:277" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:278" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="34" t="s">
         <v>46</v>
       </c>
@@ -41005,287 +41162,302 @@
       <c r="JQ52" s="39">
         <v>-106.79707356092</v>
       </c>
+      <c r="JR52" s="39">
+        <v>355.12127344470201</v>
+      </c>
     </row>
-    <row r="54" spans="1:277" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="48" t="s">
+    <row r="54" spans="1:278" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B54" s="48"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="48"/>
-      <c r="L54" s="48"/>
-      <c r="M54" s="48"/>
-      <c r="N54" s="48"/>
-      <c r="O54" s="48"/>
-      <c r="P54" s="48"/>
-      <c r="Q54" s="48"/>
-      <c r="R54" s="48"/>
-      <c r="S54" s="48"/>
-      <c r="T54" s="48"/>
-      <c r="U54" s="48"/>
-      <c r="V54" s="48"/>
-      <c r="W54" s="48"/>
-      <c r="X54" s="48"/>
-      <c r="Y54" s="48"/>
-      <c r="Z54" s="48"/>
-      <c r="AA54" s="48"/>
-      <c r="AB54" s="48"/>
-      <c r="AC54" s="48"/>
-      <c r="AD54" s="48"/>
-      <c r="AE54" s="48"/>
-      <c r="AF54" s="48"/>
-      <c r="AG54" s="48"/>
-      <c r="AH54" s="48"/>
-      <c r="AI54" s="48"/>
-      <c r="AJ54" s="48"/>
-      <c r="AK54" s="48"/>
-      <c r="AL54" s="48"/>
-      <c r="AM54" s="48"/>
-      <c r="AN54" s="48"/>
-      <c r="AO54" s="48"/>
-      <c r="AP54" s="48"/>
-      <c r="AQ54" s="48"/>
-      <c r="AR54" s="48"/>
-      <c r="AS54" s="48"/>
-      <c r="AT54" s="48"/>
-      <c r="AU54" s="48"/>
-      <c r="AV54" s="48"/>
-      <c r="AW54" s="48"/>
-      <c r="AX54" s="48"/>
-      <c r="AY54" s="48"/>
-      <c r="AZ54" s="48"/>
-      <c r="BA54" s="48"/>
-      <c r="BB54" s="48"/>
-      <c r="BC54" s="48"/>
-      <c r="BD54" s="48"/>
-      <c r="BE54" s="48"/>
-      <c r="BF54" s="48"/>
-      <c r="BG54" s="48"/>
-      <c r="BH54" s="48"/>
-      <c r="BI54" s="48"/>
-      <c r="BJ54" s="48"/>
-      <c r="BK54" s="48"/>
-      <c r="BL54" s="48"/>
-      <c r="BM54" s="48"/>
-      <c r="BN54" s="48"/>
-      <c r="BO54" s="48"/>
-      <c r="BP54" s="48"/>
-      <c r="BQ54" s="48"/>
-      <c r="BR54" s="48"/>
-      <c r="BS54" s="48"/>
-      <c r="BT54" s="48"/>
-      <c r="BU54" s="48"/>
-      <c r="BV54" s="48"/>
-      <c r="BW54" s="48"/>
-      <c r="BX54" s="48"/>
-      <c r="BY54" s="48"/>
-      <c r="BZ54" s="48"/>
-      <c r="CA54" s="48"/>
-      <c r="CB54" s="48"/>
-      <c r="CC54" s="48"/>
-      <c r="CD54" s="48"/>
-      <c r="CE54" s="48"/>
-      <c r="CF54" s="48"/>
-      <c r="CG54" s="48"/>
-      <c r="CH54" s="48"/>
-      <c r="CI54" s="48"/>
-      <c r="CJ54" s="48"/>
-      <c r="CK54" s="48"/>
-      <c r="CL54" s="48"/>
-      <c r="CM54" s="48"/>
-      <c r="CN54" s="48"/>
-      <c r="CO54" s="48"/>
-      <c r="CP54" s="48"/>
-      <c r="CQ54" s="48"/>
-      <c r="CR54" s="48"/>
-      <c r="CS54" s="48"/>
-      <c r="CT54" s="48"/>
-      <c r="CU54" s="48"/>
-      <c r="CV54" s="48"/>
-      <c r="CW54" s="48"/>
-      <c r="CX54" s="48"/>
-      <c r="CY54" s="48"/>
-      <c r="CZ54" s="48"/>
-      <c r="DA54" s="48"/>
-      <c r="DB54" s="48"/>
-      <c r="DC54" s="48"/>
-      <c r="DD54" s="48"/>
-      <c r="DE54" s="48"/>
-      <c r="DF54" s="48"/>
-      <c r="DG54" s="48"/>
-      <c r="DH54" s="48"/>
-      <c r="DI54" s="48"/>
-      <c r="DJ54" s="48"/>
-      <c r="DK54" s="48"/>
-      <c r="DL54" s="48"/>
-      <c r="DM54" s="48"/>
-      <c r="DN54" s="48"/>
-      <c r="DO54" s="48"/>
-      <c r="DP54" s="48"/>
-      <c r="DQ54" s="48"/>
-      <c r="DR54" s="48"/>
-      <c r="DS54" s="48"/>
-      <c r="DT54" s="48"/>
-      <c r="DU54" s="48"/>
-      <c r="DV54" s="48"/>
-      <c r="DW54" s="48"/>
-      <c r="DX54" s="48"/>
-      <c r="DY54" s="48"/>
-      <c r="DZ54" s="48"/>
-      <c r="EA54" s="48"/>
-      <c r="EB54" s="48"/>
-      <c r="EC54" s="48"/>
-      <c r="ED54" s="48"/>
-      <c r="EE54" s="48"/>
-      <c r="EF54" s="48"/>
-      <c r="EG54" s="48"/>
-      <c r="EH54" s="48"/>
-      <c r="EI54" s="48"/>
-      <c r="EJ54" s="48"/>
-      <c r="EK54" s="48"/>
-      <c r="EL54" s="48"/>
-      <c r="EM54" s="48"/>
-      <c r="EN54" s="48"/>
-      <c r="EO54" s="48"/>
-      <c r="EP54" s="48"/>
-      <c r="EQ54" s="48"/>
-      <c r="ER54" s="48"/>
-      <c r="ES54" s="48"/>
-      <c r="ET54" s="48"/>
-      <c r="EU54" s="48"/>
-      <c r="EV54" s="48"/>
-      <c r="EW54" s="48"/>
-      <c r="EX54" s="48"/>
-      <c r="EY54" s="48"/>
-      <c r="EZ54" s="48"/>
-      <c r="FA54" s="48"/>
-      <c r="FB54" s="48"/>
-      <c r="FC54" s="48"/>
-      <c r="FD54" s="48"/>
-      <c r="FE54" s="48"/>
-      <c r="FF54" s="48"/>
-      <c r="FG54" s="48"/>
-      <c r="FH54" s="48"/>
-      <c r="FI54" s="48"/>
-      <c r="FJ54" s="48"/>
-      <c r="FK54" s="48"/>
-      <c r="FL54" s="48"/>
-      <c r="FM54" s="48"/>
-      <c r="FN54" s="48"/>
-      <c r="FO54" s="48"/>
-      <c r="FP54" s="48"/>
-      <c r="FQ54" s="48"/>
-      <c r="FR54" s="48"/>
-      <c r="FS54" s="48"/>
-      <c r="FT54" s="48"/>
-      <c r="FU54" s="48"/>
-      <c r="FV54" s="48"/>
-      <c r="FW54" s="48"/>
-      <c r="FX54" s="48"/>
-      <c r="FY54" s="48"/>
-      <c r="FZ54" s="48"/>
-      <c r="GA54" s="48"/>
-      <c r="GB54" s="48"/>
-      <c r="GC54" s="48"/>
-      <c r="GD54" s="48"/>
-      <c r="GE54" s="48"/>
-      <c r="GF54" s="48"/>
-      <c r="GG54" s="48"/>
-      <c r="GH54" s="48"/>
-      <c r="GI54" s="48"/>
-      <c r="GJ54" s="48"/>
-      <c r="GK54" s="48"/>
-      <c r="GL54" s="48"/>
-      <c r="GM54" s="48"/>
-      <c r="GN54" s="48"/>
-      <c r="GO54" s="48"/>
-      <c r="GP54" s="48"/>
-      <c r="GQ54" s="48"/>
-      <c r="GR54" s="48"/>
-      <c r="GS54" s="48"/>
-      <c r="GT54" s="48"/>
-      <c r="GU54" s="48"/>
-      <c r="GV54" s="48"/>
-      <c r="GW54" s="48"/>
-      <c r="GX54" s="48"/>
-      <c r="GY54" s="48"/>
-      <c r="GZ54" s="48"/>
-      <c r="HA54" s="48"/>
-      <c r="HB54" s="48"/>
-      <c r="HC54" s="48"/>
-      <c r="HD54" s="48"/>
-      <c r="HE54" s="48"/>
-      <c r="HF54" s="48"/>
-      <c r="HG54" s="48"/>
-      <c r="HH54" s="48"/>
-      <c r="HI54" s="48"/>
-      <c r="HJ54" s="48"/>
-      <c r="HK54" s="48"/>
-      <c r="HL54" s="48"/>
-      <c r="HM54" s="48"/>
-      <c r="HN54" s="48"/>
-      <c r="HO54" s="48"/>
-      <c r="HP54" s="48"/>
-      <c r="HQ54" s="48"/>
-      <c r="HR54" s="48"/>
-      <c r="HS54" s="48"/>
-      <c r="HT54" s="48"/>
-      <c r="HU54" s="48"/>
-      <c r="HV54" s="48"/>
-      <c r="HW54" s="48"/>
-      <c r="HX54" s="48"/>
-      <c r="HY54" s="48"/>
-      <c r="HZ54" s="48"/>
-      <c r="IA54" s="48"/>
-      <c r="IB54" s="48"/>
-      <c r="IC54" s="48"/>
-      <c r="ID54" s="48"/>
-      <c r="IE54" s="48"/>
-      <c r="IF54" s="48"/>
-      <c r="IG54" s="48"/>
-      <c r="IH54" s="48"/>
-      <c r="II54" s="48"/>
-      <c r="IJ54" s="48"/>
-      <c r="IK54" s="48"/>
-      <c r="IL54" s="48"/>
-      <c r="IM54" s="48"/>
-      <c r="IN54" s="48"/>
-      <c r="IO54" s="48"/>
-      <c r="IP54" s="48"/>
-      <c r="IQ54" s="48"/>
-      <c r="IR54" s="48"/>
-      <c r="IS54" s="48"/>
-      <c r="IT54" s="48"/>
-      <c r="IU54" s="48"/>
-      <c r="IV54" s="48"/>
-      <c r="IW54" s="48"/>
-      <c r="IX54" s="48"/>
-      <c r="IY54" s="48"/>
-      <c r="IZ54" s="48"/>
-      <c r="JA54" s="48"/>
-      <c r="JB54" s="48"/>
-      <c r="JC54" s="48"/>
-      <c r="JD54" s="48"/>
-      <c r="JE54" s="48"/>
-      <c r="JF54" s="48"/>
-      <c r="JG54" s="48"/>
-      <c r="JH54" s="48"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="62"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="62"/>
+      <c r="J54" s="62"/>
+      <c r="K54" s="62"/>
+      <c r="L54" s="62"/>
+      <c r="M54" s="62"/>
+      <c r="N54" s="62"/>
+      <c r="O54" s="62"/>
+      <c r="P54" s="62"/>
+      <c r="Q54" s="62"/>
+      <c r="R54" s="62"/>
+      <c r="S54" s="62"/>
+      <c r="T54" s="62"/>
+      <c r="U54" s="62"/>
+      <c r="V54" s="62"/>
+      <c r="W54" s="62"/>
+      <c r="X54" s="62"/>
+      <c r="Y54" s="62"/>
+      <c r="Z54" s="62"/>
+      <c r="AA54" s="62"/>
+      <c r="AB54" s="62"/>
+      <c r="AC54" s="62"/>
+      <c r="AD54" s="62"/>
+      <c r="AE54" s="62"/>
+      <c r="AF54" s="62"/>
+      <c r="AG54" s="62"/>
+      <c r="AH54" s="62"/>
+      <c r="AI54" s="62"/>
+      <c r="AJ54" s="62"/>
+      <c r="AK54" s="62"/>
+      <c r="AL54" s="62"/>
+      <c r="AM54" s="62"/>
+      <c r="AN54" s="62"/>
+      <c r="AO54" s="62"/>
+      <c r="AP54" s="62"/>
+      <c r="AQ54" s="62"/>
+      <c r="AR54" s="62"/>
+      <c r="AS54" s="62"/>
+      <c r="AT54" s="62"/>
+      <c r="AU54" s="62"/>
+      <c r="AV54" s="62"/>
+      <c r="AW54" s="62"/>
+      <c r="AX54" s="62"/>
+      <c r="AY54" s="62"/>
+      <c r="AZ54" s="62"/>
+      <c r="BA54" s="62"/>
+      <c r="BB54" s="62"/>
+      <c r="BC54" s="62"/>
+      <c r="BD54" s="62"/>
+      <c r="BE54" s="62"/>
+      <c r="BF54" s="62"/>
+      <c r="BG54" s="62"/>
+      <c r="BH54" s="62"/>
+      <c r="BI54" s="62"/>
+      <c r="BJ54" s="62"/>
+      <c r="BK54" s="62"/>
+      <c r="BL54" s="62"/>
+      <c r="BM54" s="62"/>
+      <c r="BN54" s="62"/>
+      <c r="BO54" s="62"/>
+      <c r="BP54" s="62"/>
+      <c r="BQ54" s="62"/>
+      <c r="BR54" s="62"/>
+      <c r="BS54" s="62"/>
+      <c r="BT54" s="62"/>
+      <c r="BU54" s="62"/>
+      <c r="BV54" s="62"/>
+      <c r="BW54" s="62"/>
+      <c r="BX54" s="62"/>
+      <c r="BY54" s="62"/>
+      <c r="BZ54" s="62"/>
+      <c r="CA54" s="62"/>
+      <c r="CB54" s="62"/>
+      <c r="CC54" s="62"/>
+      <c r="CD54" s="62"/>
+      <c r="CE54" s="62"/>
+      <c r="CF54" s="62"/>
+      <c r="CG54" s="62"/>
+      <c r="CH54" s="62"/>
+      <c r="CI54" s="62"/>
+      <c r="CJ54" s="62"/>
+      <c r="CK54" s="62"/>
+      <c r="CL54" s="62"/>
+      <c r="CM54" s="62"/>
+      <c r="CN54" s="62"/>
+      <c r="CO54" s="62"/>
+      <c r="CP54" s="62"/>
+      <c r="CQ54" s="62"/>
+      <c r="CR54" s="62"/>
+      <c r="CS54" s="62"/>
+      <c r="CT54" s="62"/>
+      <c r="CU54" s="62"/>
+      <c r="CV54" s="62"/>
+      <c r="CW54" s="62"/>
+      <c r="CX54" s="62"/>
+      <c r="CY54" s="62"/>
+      <c r="CZ54" s="62"/>
+      <c r="DA54" s="62"/>
+      <c r="DB54" s="62"/>
+      <c r="DC54" s="62"/>
+      <c r="DD54" s="62"/>
+      <c r="DE54" s="62"/>
+      <c r="DF54" s="62"/>
+      <c r="DG54" s="62"/>
+      <c r="DH54" s="62"/>
+      <c r="DI54" s="62"/>
+      <c r="DJ54" s="62"/>
+      <c r="DK54" s="62"/>
+      <c r="DL54" s="62"/>
+      <c r="DM54" s="62"/>
+      <c r="DN54" s="62"/>
+      <c r="DO54" s="62"/>
+      <c r="DP54" s="62"/>
+      <c r="DQ54" s="62"/>
+      <c r="DR54" s="62"/>
+      <c r="DS54" s="62"/>
+      <c r="DT54" s="62"/>
+      <c r="DU54" s="62"/>
+      <c r="DV54" s="62"/>
+      <c r="DW54" s="62"/>
+      <c r="DX54" s="62"/>
+      <c r="DY54" s="62"/>
+      <c r="DZ54" s="62"/>
+      <c r="EA54" s="62"/>
+      <c r="EB54" s="62"/>
+      <c r="EC54" s="62"/>
+      <c r="ED54" s="62"/>
+      <c r="EE54" s="62"/>
+      <c r="EF54" s="62"/>
+      <c r="EG54" s="62"/>
+      <c r="EH54" s="62"/>
+      <c r="EI54" s="62"/>
+      <c r="EJ54" s="62"/>
+      <c r="EK54" s="62"/>
+      <c r="EL54" s="62"/>
+      <c r="EM54" s="62"/>
+      <c r="EN54" s="62"/>
+      <c r="EO54" s="62"/>
+      <c r="EP54" s="62"/>
+      <c r="EQ54" s="62"/>
+      <c r="ER54" s="62"/>
+      <c r="ES54" s="62"/>
+      <c r="ET54" s="62"/>
+      <c r="EU54" s="62"/>
+      <c r="EV54" s="62"/>
+      <c r="EW54" s="62"/>
+      <c r="EX54" s="62"/>
+      <c r="EY54" s="62"/>
+      <c r="EZ54" s="62"/>
+      <c r="FA54" s="62"/>
+      <c r="FB54" s="62"/>
+      <c r="FC54" s="62"/>
+      <c r="FD54" s="62"/>
+      <c r="FE54" s="62"/>
+      <c r="FF54" s="62"/>
+      <c r="FG54" s="62"/>
+      <c r="FH54" s="62"/>
+      <c r="FI54" s="62"/>
+      <c r="FJ54" s="62"/>
+      <c r="FK54" s="62"/>
+      <c r="FL54" s="62"/>
+      <c r="FM54" s="62"/>
+      <c r="FN54" s="62"/>
+      <c r="FO54" s="62"/>
+      <c r="FP54" s="62"/>
+      <c r="FQ54" s="62"/>
+      <c r="FR54" s="62"/>
+      <c r="FS54" s="62"/>
+      <c r="FT54" s="62"/>
+      <c r="FU54" s="62"/>
+      <c r="FV54" s="62"/>
+      <c r="FW54" s="62"/>
+      <c r="FX54" s="62"/>
+      <c r="FY54" s="62"/>
+      <c r="FZ54" s="62"/>
+      <c r="GA54" s="62"/>
+      <c r="GB54" s="62"/>
+      <c r="GC54" s="62"/>
+      <c r="GD54" s="62"/>
+      <c r="GE54" s="62"/>
+      <c r="GF54" s="62"/>
+      <c r="GG54" s="62"/>
+      <c r="GH54" s="62"/>
+      <c r="GI54" s="62"/>
+      <c r="GJ54" s="62"/>
+      <c r="GK54" s="62"/>
+      <c r="GL54" s="62"/>
+      <c r="GM54" s="62"/>
+      <c r="GN54" s="62"/>
+      <c r="GO54" s="62"/>
+      <c r="GP54" s="62"/>
+      <c r="GQ54" s="62"/>
+      <c r="GR54" s="62"/>
+      <c r="GS54" s="62"/>
+      <c r="GT54" s="62"/>
+      <c r="GU54" s="62"/>
+      <c r="GV54" s="62"/>
+      <c r="GW54" s="62"/>
+      <c r="GX54" s="62"/>
+      <c r="GY54" s="62"/>
+      <c r="GZ54" s="62"/>
+      <c r="HA54" s="62"/>
+      <c r="HB54" s="62"/>
+      <c r="HC54" s="62"/>
+      <c r="HD54" s="62"/>
+      <c r="HE54" s="62"/>
+      <c r="HF54" s="62"/>
+      <c r="HG54" s="62"/>
+      <c r="HH54" s="62"/>
+      <c r="HI54" s="62"/>
+      <c r="HJ54" s="62"/>
+      <c r="HK54" s="62"/>
+      <c r="HL54" s="62"/>
+      <c r="HM54" s="62"/>
+      <c r="HN54" s="62"/>
+      <c r="HO54" s="62"/>
+      <c r="HP54" s="62"/>
+      <c r="HQ54" s="62"/>
+      <c r="HR54" s="62"/>
+      <c r="HS54" s="62"/>
+      <c r="HT54" s="62"/>
+      <c r="HU54" s="62"/>
+      <c r="HV54" s="62"/>
+      <c r="HW54" s="62"/>
+      <c r="HX54" s="62"/>
+      <c r="HY54" s="62"/>
+      <c r="HZ54" s="62"/>
+      <c r="IA54" s="62"/>
+      <c r="IB54" s="62"/>
+      <c r="IC54" s="62"/>
+      <c r="ID54" s="62"/>
+      <c r="IE54" s="62"/>
+      <c r="IF54" s="62"/>
+      <c r="IG54" s="62"/>
+      <c r="IH54" s="62"/>
+      <c r="II54" s="62"/>
+      <c r="IJ54" s="62"/>
+      <c r="IK54" s="62"/>
+      <c r="IL54" s="62"/>
+      <c r="IM54" s="62"/>
+      <c r="IN54" s="62"/>
+      <c r="IO54" s="62"/>
+      <c r="IP54" s="62"/>
+      <c r="IQ54" s="62"/>
+      <c r="IR54" s="62"/>
+      <c r="IS54" s="62"/>
+      <c r="IT54" s="62"/>
+      <c r="IU54" s="62"/>
+      <c r="IV54" s="62"/>
+      <c r="IW54" s="62"/>
+      <c r="IX54" s="62"/>
+      <c r="IY54" s="62"/>
+      <c r="IZ54" s="62"/>
+      <c r="JA54" s="62"/>
+      <c r="JB54" s="62"/>
+      <c r="JC54" s="62"/>
+      <c r="JD54" s="62"/>
+      <c r="JE54" s="62"/>
+      <c r="JF54" s="62"/>
+      <c r="JG54" s="62"/>
+      <c r="JH54" s="62"/>
       <c r="JI54" s="1"/>
       <c r="JJ54" s="1"/>
       <c r="JK54" s="1"/>
       <c r="JL54" s="1"/>
       <c r="JM54" s="1"/>
       <c r="JN54" s="1"/>
+      <c r="JR54" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A54:JH54"/>
+    <mergeCell ref="IH4:IS4"/>
+    <mergeCell ref="IT4:JE4"/>
+    <mergeCell ref="DF4:DQ4"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="Z4:AK4"/>
+    <mergeCell ref="AL4:AW4"/>
+    <mergeCell ref="AX4:BI4"/>
+    <mergeCell ref="A44:JI44"/>
+    <mergeCell ref="JF4:JQ4"/>
     <mergeCell ref="A1:JH1"/>
     <mergeCell ref="A2:JH2"/>
     <mergeCell ref="FZ4:GK4"/>
@@ -41302,17 +41474,6 @@
     <mergeCell ref="BV4:CG4"/>
     <mergeCell ref="CH4:CS4"/>
     <mergeCell ref="CT4:DE4"/>
-    <mergeCell ref="A54:JH54"/>
-    <mergeCell ref="IH4:IS4"/>
-    <mergeCell ref="IT4:JE4"/>
-    <mergeCell ref="DF4:DQ4"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="Z4:AK4"/>
-    <mergeCell ref="AL4:AW4"/>
-    <mergeCell ref="AX4:BI4"/>
-    <mergeCell ref="A44:JI44"/>
-    <mergeCell ref="JF4:JQ4"/>
   </mergeCells>
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -41336,132 +41497,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
       <c r="X1" s="1"/>
     </row>
     <row r="2" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
       <c r="X2" s="1"/>
     </row>
     <row r="4" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="49">
         <v>2003</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="50">
         <v>2004</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="50">
         <v>2005</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="50">
         <v>2006</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="50">
         <v>2007</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="50">
         <v>2008</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="50">
         <v>2009</v>
       </c>
-      <c r="I4" s="61">
+      <c r="I4" s="50">
         <v>2010</v>
       </c>
-      <c r="J4" s="61">
+      <c r="J4" s="50">
         <v>2011</v>
       </c>
-      <c r="K4" s="61">
+      <c r="K4" s="50">
         <v>2012</v>
       </c>
-      <c r="L4" s="61">
+      <c r="L4" s="50">
         <v>2013</v>
       </c>
-      <c r="M4" s="61">
+      <c r="M4" s="50">
         <v>2014</v>
       </c>
-      <c r="N4" s="61">
+      <c r="N4" s="50">
         <v>2015</v>
       </c>
-      <c r="O4" s="61">
+      <c r="O4" s="50">
         <v>2016</v>
       </c>
-      <c r="P4" s="61">
+      <c r="P4" s="50">
         <v>2017</v>
       </c>
-      <c r="Q4" s="61">
+      <c r="Q4" s="50">
         <v>2018</v>
       </c>
-      <c r="R4" s="61">
+      <c r="R4" s="50">
         <v>2019</v>
       </c>
-      <c r="S4" s="61">
+      <c r="S4" s="50">
         <v>2020</v>
       </c>
-      <c r="T4" s="61">
+      <c r="T4" s="50">
         <v>2021</v>
       </c>
-      <c r="U4" s="61">
+      <c r="U4" s="50">
         <v>2022</v>
       </c>
-      <c r="V4" s="61">
+      <c r="V4" s="50">
         <v>2023</v>
       </c>
-      <c r="W4" s="61">
+      <c r="W4" s="50">
         <v>2024</v>
       </c>
-      <c r="X4" s="62">
+      <c r="X4" s="51">
         <v>2025</v>
       </c>
     </row>
@@ -41535,7 +41696,7 @@
       <c r="W5" s="9">
         <v>-7104.022157204</v>
       </c>
-      <c r="X5" s="63">
+      <c r="X5" s="52">
         <v>-5272.6413423156</v>
       </c>
     </row>
@@ -41609,7 +41770,7 @@
       <c r="W6" s="9">
         <v>-11930.065806917</v>
       </c>
-      <c r="X6" s="63">
+      <c r="X6" s="52">
         <v>10576.2400574812</v>
       </c>
     </row>
@@ -41683,7 +41844,7 @@
       <c r="W7" s="9">
         <v>-4826.0436497132996</v>
       </c>
-      <c r="X7" s="63">
+      <c r="X7" s="52">
         <v>15848.881399796801</v>
       </c>
     </row>
@@ -41757,7 +41918,7 @@
       <c r="W8" s="9">
         <v>-8929.5042845784992</v>
       </c>
-      <c r="X8" s="63">
+      <c r="X8" s="52">
         <v>-6576.8191210845998</v>
       </c>
     </row>
@@ -42423,7 +42584,7 @@
       <c r="W17" s="9">
         <v>1988.22708731694</v>
       </c>
-      <c r="X17" s="63">
+      <c r="X17" s="52">
         <v>7962.8421038181796</v>
       </c>
     </row>
@@ -43237,7 +43398,7 @@
       <c r="W28" s="9">
         <v>-520.50871532618999</v>
       </c>
-      <c r="X28" s="63">
+      <c r="X28" s="52">
         <v>-1728.0230622818001</v>
       </c>
     </row>
@@ -43311,7 +43472,7 @@
       <c r="W29" s="9">
         <v>2937.0969640220901</v>
       </c>
-      <c r="X29" s="63">
+      <c r="X29" s="52">
         <v>-7121.2970718625002</v>
       </c>
     </row>
@@ -44207,7 +44368,7 @@
       <c r="A42" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="64">
+      <c r="B42" s="53">
         <v>-365.6</v>
       </c>
       <c r="C42" s="20">
@@ -44273,40 +44434,40 @@
       <c r="W42" s="20">
         <v>-2579.3332086383002</v>
       </c>
-      <c r="X42" s="65">
+      <c r="X42" s="54">
         <v>2190.6558090951498</v>
       </c>
     </row>
     <row r="43" spans="1:24" s="47" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="59" t="s">
+      <c r="A43" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="59"/>
-      <c r="O43" s="59"/>
-      <c r="P43" s="59"/>
-      <c r="Q43" s="59"/>
-      <c r="R43" s="59"/>
-      <c r="S43" s="59"/>
-      <c r="T43" s="59"/>
-      <c r="U43" s="59"/>
-      <c r="V43" s="59"/>
-      <c r="W43" s="59"/>
-      <c r="X43" s="59"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
+      <c r="K43" s="69"/>
+      <c r="L43" s="69"/>
+      <c r="M43" s="69"/>
+      <c r="N43" s="69"/>
+      <c r="O43" s="69"/>
+      <c r="P43" s="69"/>
+      <c r="Q43" s="69"/>
+      <c r="R43" s="69"/>
+      <c r="S43" s="69"/>
+      <c r="T43" s="69"/>
+      <c r="U43" s="69"/>
+      <c r="V43" s="69"/>
+      <c r="W43" s="69"/>
+      <c r="X43" s="69"/>
     </row>
     <row r="44" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="66" t="s">
+      <c r="A44" s="55" t="s">
         <v>41</v>
       </c>
       <c r="B44" s="28">
@@ -44380,7 +44541,7 @@
       </c>
     </row>
     <row r="45" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="67" t="s">
+      <c r="A45" s="56" t="s">
         <v>42</v>
       </c>
       <c r="B45" s="14">
@@ -44454,7 +44615,7 @@
       </c>
     </row>
     <row r="46" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="67" t="s">
+      <c r="A46" s="56" t="s">
         <v>26</v>
       </c>
       <c r="B46" s="14">
@@ -44528,7 +44689,7 @@
       </c>
     </row>
     <row r="47" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="67" t="s">
+      <c r="A47" s="56" t="s">
         <v>43</v>
       </c>
       <c r="B47" s="14"/>
@@ -44584,7 +44745,7 @@
       </c>
     </row>
     <row r="48" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="67" t="s">
+      <c r="A48" s="56" t="s">
         <v>44</v>
       </c>
       <c r="B48" s="14"/>
@@ -44640,7 +44801,7 @@
       </c>
     </row>
     <row r="49" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="67" t="s">
+      <c r="A49" s="56" t="s">
         <v>25</v>
       </c>
       <c r="B49" s="14">
@@ -44714,7 +44875,7 @@
       </c>
     </row>
     <row r="50" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="56" t="s">
         <v>45</v>
       </c>
       <c r="B50" s="14">
@@ -44788,7 +44949,7 @@
       </c>
     </row>
     <row r="51" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="68" t="s">
+      <c r="A51" s="57" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="35">
@@ -44862,31 +45023,31 @@
       </c>
     </row>
     <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="48" t="s">
+      <c r="A53" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="48"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
-      <c r="L53" s="48"/>
-      <c r="M53" s="48"/>
-      <c r="N53" s="48"/>
-      <c r="O53" s="48"/>
-      <c r="P53" s="48"/>
-      <c r="Q53" s="48"/>
-      <c r="R53" s="48"/>
-      <c r="S53" s="48"/>
-      <c r="T53" s="48"/>
-      <c r="U53" s="48"/>
-      <c r="V53" s="48"/>
-      <c r="W53" s="48"/>
+      <c r="B53" s="62"/>
+      <c r="C53" s="62"/>
+      <c r="D53" s="62"/>
+      <c r="E53" s="62"/>
+      <c r="F53" s="62"/>
+      <c r="G53" s="62"/>
+      <c r="H53" s="62"/>
+      <c r="I53" s="62"/>
+      <c r="J53" s="62"/>
+      <c r="K53" s="62"/>
+      <c r="L53" s="62"/>
+      <c r="M53" s="62"/>
+      <c r="N53" s="62"/>
+      <c r="O53" s="62"/>
+      <c r="P53" s="62"/>
+      <c r="Q53" s="62"/>
+      <c r="R53" s="62"/>
+      <c r="S53" s="62"/>
+      <c r="T53" s="62"/>
+      <c r="U53" s="62"/>
+      <c r="V53" s="62"/>
+      <c r="W53" s="62"/>
       <c r="X53" s="1"/>
     </row>
   </sheetData>

--- a/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
+++ b/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.04.2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.05.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E905B08E-0D21-4FC5-AB55-898031944D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ABF3C5-C165-4713-B58E-100DFEDDC867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Mensual" sheetId="1" r:id="rId1"/>
     <sheet name="Anual" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="49">
   <si>
     <t>FLUJOS DE LA CUENTA FINANCIERA DE BALANZA DE PAGOS</t>
   </si>
@@ -242,7 +255,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -478,11 +491,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -540,36 +577,6 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -587,6 +594,45 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:JS54"/>
+  <dimension ref="A1:JT54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -782,906 +828,909 @@
     <col min="191" max="265" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="266" max="266" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="267" max="278" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="279" max="279" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="280" max="16384" width="11.42578125" style="1"/>
+    <col min="279" max="280" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="281" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:279" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20"/>
-      <c r="AK1" s="20"/>
-      <c r="AL1" s="20"/>
-      <c r="AM1" s="20"/>
-      <c r="AN1" s="20"/>
-      <c r="AO1" s="20"/>
-      <c r="AP1" s="20"/>
-      <c r="AQ1" s="20"/>
-      <c r="AR1" s="20"/>
-      <c r="AS1" s="20"/>
-      <c r="AT1" s="20"/>
-      <c r="AU1" s="20"/>
-      <c r="AV1" s="20"/>
-      <c r="AW1" s="20"/>
-      <c r="AX1" s="20"/>
-      <c r="AY1" s="20"/>
-      <c r="AZ1" s="20"/>
-      <c r="BA1" s="20"/>
-      <c r="BB1" s="20"/>
-      <c r="BC1" s="20"/>
-      <c r="BD1" s="20"/>
-      <c r="BE1" s="20"/>
-      <c r="BF1" s="20"/>
-      <c r="BG1" s="20"/>
-      <c r="BH1" s="20"/>
-      <c r="BI1" s="20"/>
-      <c r="BJ1" s="20"/>
-      <c r="BK1" s="20"/>
-      <c r="BL1" s="20"/>
-      <c r="BM1" s="20"/>
-      <c r="BN1" s="20"/>
-      <c r="BO1" s="20"/>
-      <c r="BP1" s="20"/>
-      <c r="BQ1" s="20"/>
-      <c r="BR1" s="20"/>
-      <c r="BS1" s="20"/>
-      <c r="BT1" s="20"/>
-      <c r="BU1" s="20"/>
-      <c r="BV1" s="20"/>
-      <c r="BW1" s="20"/>
-      <c r="BX1" s="20"/>
-      <c r="BY1" s="20"/>
-      <c r="BZ1" s="20"/>
-      <c r="CA1" s="20"/>
-      <c r="CB1" s="20"/>
-      <c r="CC1" s="20"/>
-      <c r="CD1" s="20"/>
-      <c r="CE1" s="20"/>
-      <c r="CF1" s="20"/>
-      <c r="CG1" s="20"/>
-      <c r="CH1" s="20"/>
-      <c r="CI1" s="20"/>
-      <c r="CJ1" s="20"/>
-      <c r="CK1" s="20"/>
-      <c r="CL1" s="20"/>
-      <c r="CM1" s="20"/>
-      <c r="CN1" s="20"/>
-      <c r="CO1" s="20"/>
-      <c r="CP1" s="20"/>
-      <c r="CQ1" s="20"/>
-      <c r="CR1" s="20"/>
-      <c r="CS1" s="20"/>
-      <c r="CT1" s="20"/>
-      <c r="CU1" s="20"/>
-      <c r="CV1" s="20"/>
-      <c r="CW1" s="20"/>
-      <c r="CX1" s="20"/>
-      <c r="CY1" s="20"/>
-      <c r="CZ1" s="20"/>
-      <c r="DA1" s="20"/>
-      <c r="DB1" s="20"/>
-      <c r="DC1" s="20"/>
-      <c r="DD1" s="20"/>
-      <c r="DE1" s="20"/>
-      <c r="DF1" s="20"/>
-      <c r="DG1" s="20"/>
-      <c r="DH1" s="20"/>
-      <c r="DI1" s="20"/>
-      <c r="DJ1" s="20"/>
-      <c r="DK1" s="20"/>
-      <c r="DL1" s="20"/>
-      <c r="DM1" s="20"/>
-      <c r="DN1" s="20"/>
-      <c r="DO1" s="20"/>
-      <c r="DP1" s="20"/>
-      <c r="DQ1" s="20"/>
-      <c r="DR1" s="20"/>
-      <c r="DS1" s="20"/>
-      <c r="DT1" s="20"/>
-      <c r="DU1" s="20"/>
-      <c r="DV1" s="20"/>
-      <c r="DW1" s="20"/>
-      <c r="DX1" s="20"/>
-      <c r="DY1" s="20"/>
-      <c r="DZ1" s="20"/>
-      <c r="EA1" s="20"/>
-      <c r="EB1" s="20"/>
-      <c r="EC1" s="20"/>
-      <c r="ED1" s="20"/>
-      <c r="EE1" s="20"/>
-      <c r="EF1" s="20"/>
-      <c r="EG1" s="20"/>
-      <c r="EH1" s="20"/>
-      <c r="EI1" s="20"/>
-      <c r="EJ1" s="20"/>
-      <c r="EK1" s="20"/>
-      <c r="EL1" s="20"/>
-      <c r="EM1" s="20"/>
-      <c r="EN1" s="20"/>
-      <c r="EO1" s="20"/>
-      <c r="EP1" s="20"/>
-      <c r="EQ1" s="20"/>
-      <c r="ER1" s="20"/>
-      <c r="ES1" s="20"/>
-      <c r="ET1" s="20"/>
-      <c r="EU1" s="20"/>
-      <c r="EV1" s="20"/>
-      <c r="EW1" s="20"/>
-      <c r="EX1" s="20"/>
-      <c r="EY1" s="20"/>
-      <c r="EZ1" s="20"/>
-      <c r="FA1" s="20"/>
-      <c r="FB1" s="20"/>
-      <c r="FC1" s="20"/>
-      <c r="FD1" s="20"/>
-      <c r="FE1" s="20"/>
-      <c r="FF1" s="20"/>
-      <c r="FG1" s="20"/>
-      <c r="FH1" s="20"/>
-      <c r="FI1" s="20"/>
-      <c r="FJ1" s="20"/>
-      <c r="FK1" s="20"/>
-      <c r="FL1" s="20"/>
-      <c r="FM1" s="20"/>
-      <c r="FN1" s="20"/>
-      <c r="FO1" s="20"/>
-      <c r="FP1" s="20"/>
-      <c r="FQ1" s="20"/>
-      <c r="FR1" s="20"/>
-      <c r="FS1" s="20"/>
-      <c r="FT1" s="20"/>
-      <c r="FU1" s="20"/>
-      <c r="FV1" s="20"/>
-      <c r="FW1" s="20"/>
-      <c r="FX1" s="20"/>
-      <c r="FY1" s="20"/>
-      <c r="FZ1" s="20"/>
-      <c r="GA1" s="20"/>
-      <c r="GB1" s="20"/>
-      <c r="GC1" s="20"/>
-      <c r="GD1" s="20"/>
-      <c r="GE1" s="20"/>
-      <c r="GF1" s="20"/>
-      <c r="GG1" s="20"/>
-      <c r="GH1" s="20"/>
-      <c r="GI1" s="20"/>
-      <c r="GJ1" s="20"/>
-      <c r="GK1" s="20"/>
-      <c r="GL1" s="20"/>
-      <c r="GM1" s="20"/>
-      <c r="GN1" s="20"/>
-      <c r="GO1" s="20"/>
-      <c r="GP1" s="20"/>
-      <c r="GQ1" s="20"/>
-      <c r="GR1" s="20"/>
-      <c r="GS1" s="20"/>
-      <c r="GT1" s="20"/>
-      <c r="GU1" s="20"/>
-      <c r="GV1" s="20"/>
-      <c r="GW1" s="20"/>
-      <c r="GX1" s="20"/>
-      <c r="GY1" s="20"/>
-      <c r="GZ1" s="20"/>
-      <c r="HA1" s="20"/>
-      <c r="HB1" s="20"/>
-      <c r="HC1" s="20"/>
-      <c r="HD1" s="20"/>
-      <c r="HE1" s="20"/>
-      <c r="HF1" s="20"/>
-      <c r="HG1" s="20"/>
-      <c r="HH1" s="20"/>
-      <c r="HI1" s="20"/>
-      <c r="HJ1" s="20"/>
-      <c r="HK1" s="20"/>
-      <c r="HL1" s="20"/>
-      <c r="HM1" s="20"/>
-      <c r="HN1" s="20"/>
-      <c r="HO1" s="20"/>
-      <c r="HP1" s="20"/>
-      <c r="HQ1" s="20"/>
-      <c r="HR1" s="20"/>
-      <c r="HS1" s="20"/>
-      <c r="HT1" s="20"/>
-      <c r="HU1" s="20"/>
-      <c r="HV1" s="20"/>
-      <c r="HW1" s="20"/>
-      <c r="HX1" s="20"/>
-      <c r="HY1" s="20"/>
-      <c r="HZ1" s="20"/>
-      <c r="IA1" s="20"/>
-      <c r="IB1" s="20"/>
-      <c r="IC1" s="20"/>
-      <c r="ID1" s="20"/>
-      <c r="IE1" s="20"/>
-      <c r="IF1" s="20"/>
-      <c r="IG1" s="20"/>
-      <c r="IH1" s="20"/>
-      <c r="II1" s="20"/>
-      <c r="IJ1" s="20"/>
-      <c r="IK1" s="20"/>
-      <c r="IL1" s="20"/>
-      <c r="IM1" s="20"/>
-      <c r="IN1" s="20"/>
-      <c r="IO1" s="20"/>
-      <c r="IP1" s="20"/>
-      <c r="IQ1" s="20"/>
-      <c r="IR1" s="20"/>
-      <c r="IS1" s="20"/>
-      <c r="IT1" s="20"/>
-      <c r="IU1" s="20"/>
-      <c r="IV1" s="20"/>
-      <c r="IW1" s="20"/>
-      <c r="IX1" s="20"/>
-      <c r="IY1" s="20"/>
-      <c r="IZ1" s="20"/>
-      <c r="JA1" s="20"/>
-      <c r="JB1" s="20"/>
-      <c r="JC1" s="20"/>
-      <c r="JD1" s="20"/>
-      <c r="JE1" s="20"/>
-      <c r="JF1" s="20"/>
-      <c r="JG1" s="20"/>
-      <c r="JH1" s="20"/>
-      <c r="JI1" s="20"/>
-      <c r="JJ1" s="20"/>
-      <c r="JK1" s="20"/>
-      <c r="JL1" s="20"/>
-      <c r="JM1" s="20"/>
-      <c r="JN1" s="20"/>
-      <c r="JO1" s="20"/>
-      <c r="JP1" s="20"/>
-      <c r="JQ1" s="20"/>
-      <c r="JR1" s="20"/>
+    <row r="1" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27"/>
+      <c r="AI1" s="27"/>
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="27"/>
+      <c r="AL1" s="27"/>
+      <c r="AM1" s="27"/>
+      <c r="AN1" s="27"/>
+      <c r="AO1" s="27"/>
+      <c r="AP1" s="27"/>
+      <c r="AQ1" s="27"/>
+      <c r="AR1" s="27"/>
+      <c r="AS1" s="27"/>
+      <c r="AT1" s="27"/>
+      <c r="AU1" s="27"/>
+      <c r="AV1" s="27"/>
+      <c r="AW1" s="27"/>
+      <c r="AX1" s="27"/>
+      <c r="AY1" s="27"/>
+      <c r="AZ1" s="27"/>
+      <c r="BA1" s="27"/>
+      <c r="BB1" s="27"/>
+      <c r="BC1" s="27"/>
+      <c r="BD1" s="27"/>
+      <c r="BE1" s="27"/>
+      <c r="BF1" s="27"/>
+      <c r="BG1" s="27"/>
+      <c r="BH1" s="27"/>
+      <c r="BI1" s="27"/>
+      <c r="BJ1" s="27"/>
+      <c r="BK1" s="27"/>
+      <c r="BL1" s="27"/>
+      <c r="BM1" s="27"/>
+      <c r="BN1" s="27"/>
+      <c r="BO1" s="27"/>
+      <c r="BP1" s="27"/>
+      <c r="BQ1" s="27"/>
+      <c r="BR1" s="27"/>
+      <c r="BS1" s="27"/>
+      <c r="BT1" s="27"/>
+      <c r="BU1" s="27"/>
+      <c r="BV1" s="27"/>
+      <c r="BW1" s="27"/>
+      <c r="BX1" s="27"/>
+      <c r="BY1" s="27"/>
+      <c r="BZ1" s="27"/>
+      <c r="CA1" s="27"/>
+      <c r="CB1" s="27"/>
+      <c r="CC1" s="27"/>
+      <c r="CD1" s="27"/>
+      <c r="CE1" s="27"/>
+      <c r="CF1" s="27"/>
+      <c r="CG1" s="27"/>
+      <c r="CH1" s="27"/>
+      <c r="CI1" s="27"/>
+      <c r="CJ1" s="27"/>
+      <c r="CK1" s="27"/>
+      <c r="CL1" s="27"/>
+      <c r="CM1" s="27"/>
+      <c r="CN1" s="27"/>
+      <c r="CO1" s="27"/>
+      <c r="CP1" s="27"/>
+      <c r="CQ1" s="27"/>
+      <c r="CR1" s="27"/>
+      <c r="CS1" s="27"/>
+      <c r="CT1" s="27"/>
+      <c r="CU1" s="27"/>
+      <c r="CV1" s="27"/>
+      <c r="CW1" s="27"/>
+      <c r="CX1" s="27"/>
+      <c r="CY1" s="27"/>
+      <c r="CZ1" s="27"/>
+      <c r="DA1" s="27"/>
+      <c r="DB1" s="27"/>
+      <c r="DC1" s="27"/>
+      <c r="DD1" s="27"/>
+      <c r="DE1" s="27"/>
+      <c r="DF1" s="27"/>
+      <c r="DG1" s="27"/>
+      <c r="DH1" s="27"/>
+      <c r="DI1" s="27"/>
+      <c r="DJ1" s="27"/>
+      <c r="DK1" s="27"/>
+      <c r="DL1" s="27"/>
+      <c r="DM1" s="27"/>
+      <c r="DN1" s="27"/>
+      <c r="DO1" s="27"/>
+      <c r="DP1" s="27"/>
+      <c r="DQ1" s="27"/>
+      <c r="DR1" s="27"/>
+      <c r="DS1" s="27"/>
+      <c r="DT1" s="27"/>
+      <c r="DU1" s="27"/>
+      <c r="DV1" s="27"/>
+      <c r="DW1" s="27"/>
+      <c r="DX1" s="27"/>
+      <c r="DY1" s="27"/>
+      <c r="DZ1" s="27"/>
+      <c r="EA1" s="27"/>
+      <c r="EB1" s="27"/>
+      <c r="EC1" s="27"/>
+      <c r="ED1" s="27"/>
+      <c r="EE1" s="27"/>
+      <c r="EF1" s="27"/>
+      <c r="EG1" s="27"/>
+      <c r="EH1" s="27"/>
+      <c r="EI1" s="27"/>
+      <c r="EJ1" s="27"/>
+      <c r="EK1" s="27"/>
+      <c r="EL1" s="27"/>
+      <c r="EM1" s="27"/>
+      <c r="EN1" s="27"/>
+      <c r="EO1" s="27"/>
+      <c r="EP1" s="27"/>
+      <c r="EQ1" s="27"/>
+      <c r="ER1" s="27"/>
+      <c r="ES1" s="27"/>
+      <c r="ET1" s="27"/>
+      <c r="EU1" s="27"/>
+      <c r="EV1" s="27"/>
+      <c r="EW1" s="27"/>
+      <c r="EX1" s="27"/>
+      <c r="EY1" s="27"/>
+      <c r="EZ1" s="27"/>
+      <c r="FA1" s="27"/>
+      <c r="FB1" s="27"/>
+      <c r="FC1" s="27"/>
+      <c r="FD1" s="27"/>
+      <c r="FE1" s="27"/>
+      <c r="FF1" s="27"/>
+      <c r="FG1" s="27"/>
+      <c r="FH1" s="27"/>
+      <c r="FI1" s="27"/>
+      <c r="FJ1" s="27"/>
+      <c r="FK1" s="27"/>
+      <c r="FL1" s="27"/>
+      <c r="FM1" s="27"/>
+      <c r="FN1" s="27"/>
+      <c r="FO1" s="27"/>
+      <c r="FP1" s="27"/>
+      <c r="FQ1" s="27"/>
+      <c r="FR1" s="27"/>
+      <c r="FS1" s="27"/>
+      <c r="FT1" s="27"/>
+      <c r="FU1" s="27"/>
+      <c r="FV1" s="27"/>
+      <c r="FW1" s="27"/>
+      <c r="FX1" s="27"/>
+      <c r="FY1" s="27"/>
+      <c r="FZ1" s="27"/>
+      <c r="GA1" s="27"/>
+      <c r="GB1" s="27"/>
+      <c r="GC1" s="27"/>
+      <c r="GD1" s="27"/>
+      <c r="GE1" s="27"/>
+      <c r="GF1" s="27"/>
+      <c r="GG1" s="27"/>
+      <c r="GH1" s="27"/>
+      <c r="GI1" s="27"/>
+      <c r="GJ1" s="27"/>
+      <c r="GK1" s="27"/>
+      <c r="GL1" s="27"/>
+      <c r="GM1" s="27"/>
+      <c r="GN1" s="27"/>
+      <c r="GO1" s="27"/>
+      <c r="GP1" s="27"/>
+      <c r="GQ1" s="27"/>
+      <c r="GR1" s="27"/>
+      <c r="GS1" s="27"/>
+      <c r="GT1" s="27"/>
+      <c r="GU1" s="27"/>
+      <c r="GV1" s="27"/>
+      <c r="GW1" s="27"/>
+      <c r="GX1" s="27"/>
+      <c r="GY1" s="27"/>
+      <c r="GZ1" s="27"/>
+      <c r="HA1" s="27"/>
+      <c r="HB1" s="27"/>
+      <c r="HC1" s="27"/>
+      <c r="HD1" s="27"/>
+      <c r="HE1" s="27"/>
+      <c r="HF1" s="27"/>
+      <c r="HG1" s="27"/>
+      <c r="HH1" s="27"/>
+      <c r="HI1" s="27"/>
+      <c r="HJ1" s="27"/>
+      <c r="HK1" s="27"/>
+      <c r="HL1" s="27"/>
+      <c r="HM1" s="27"/>
+      <c r="HN1" s="27"/>
+      <c r="HO1" s="27"/>
+      <c r="HP1" s="27"/>
+      <c r="HQ1" s="27"/>
+      <c r="HR1" s="27"/>
+      <c r="HS1" s="27"/>
+      <c r="HT1" s="27"/>
+      <c r="HU1" s="27"/>
+      <c r="HV1" s="27"/>
+      <c r="HW1" s="27"/>
+      <c r="HX1" s="27"/>
+      <c r="HY1" s="27"/>
+      <c r="HZ1" s="27"/>
+      <c r="IA1" s="27"/>
+      <c r="IB1" s="27"/>
+      <c r="IC1" s="27"/>
+      <c r="ID1" s="27"/>
+      <c r="IE1" s="27"/>
+      <c r="IF1" s="27"/>
+      <c r="IG1" s="27"/>
+      <c r="IH1" s="27"/>
+      <c r="II1" s="27"/>
+      <c r="IJ1" s="27"/>
+      <c r="IK1" s="27"/>
+      <c r="IL1" s="27"/>
+      <c r="IM1" s="27"/>
+      <c r="IN1" s="27"/>
+      <c r="IO1" s="27"/>
+      <c r="IP1" s="27"/>
+      <c r="IQ1" s="27"/>
+      <c r="IR1" s="27"/>
+      <c r="IS1" s="27"/>
+      <c r="IT1" s="27"/>
+      <c r="IU1" s="27"/>
+      <c r="IV1" s="27"/>
+      <c r="IW1" s="27"/>
+      <c r="IX1" s="27"/>
+      <c r="IY1" s="27"/>
+      <c r="IZ1" s="27"/>
+      <c r="JA1" s="27"/>
+      <c r="JB1" s="27"/>
+      <c r="JC1" s="27"/>
+      <c r="JD1" s="27"/>
+      <c r="JE1" s="27"/>
+      <c r="JF1" s="27"/>
+      <c r="JG1" s="27"/>
+      <c r="JH1" s="27"/>
+      <c r="JI1" s="27"/>
+      <c r="JJ1" s="27"/>
+      <c r="JK1" s="27"/>
+      <c r="JL1" s="27"/>
+      <c r="JM1" s="27"/>
+      <c r="JN1" s="27"/>
+      <c r="JO1" s="27"/>
+      <c r="JP1" s="27"/>
+      <c r="JQ1" s="27"/>
+      <c r="JR1" s="27"/>
       <c r="JS1" s="10"/>
+      <c r="JT1" s="10"/>
     </row>
-    <row r="2" spans="1:279" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
-      <c r="AM2" s="20"/>
-      <c r="AN2" s="20"/>
-      <c r="AO2" s="20"/>
-      <c r="AP2" s="20"/>
-      <c r="AQ2" s="20"/>
-      <c r="AR2" s="20"/>
-      <c r="AS2" s="20"/>
-      <c r="AT2" s="20"/>
-      <c r="AU2" s="20"/>
-      <c r="AV2" s="20"/>
-      <c r="AW2" s="20"/>
-      <c r="AX2" s="20"/>
-      <c r="AY2" s="20"/>
-      <c r="AZ2" s="20"/>
-      <c r="BA2" s="20"/>
-      <c r="BB2" s="20"/>
-      <c r="BC2" s="20"/>
-      <c r="BD2" s="20"/>
-      <c r="BE2" s="20"/>
-      <c r="BF2" s="20"/>
-      <c r="BG2" s="20"/>
-      <c r="BH2" s="20"/>
-      <c r="BI2" s="20"/>
-      <c r="BJ2" s="20"/>
-      <c r="BK2" s="20"/>
-      <c r="BL2" s="20"/>
-      <c r="BM2" s="20"/>
-      <c r="BN2" s="20"/>
-      <c r="BO2" s="20"/>
-      <c r="BP2" s="20"/>
-      <c r="BQ2" s="20"/>
-      <c r="BR2" s="20"/>
-      <c r="BS2" s="20"/>
-      <c r="BT2" s="20"/>
-      <c r="BU2" s="20"/>
-      <c r="BV2" s="20"/>
-      <c r="BW2" s="20"/>
-      <c r="BX2" s="20"/>
-      <c r="BY2" s="20"/>
-      <c r="BZ2" s="20"/>
-      <c r="CA2" s="20"/>
-      <c r="CB2" s="20"/>
-      <c r="CC2" s="20"/>
-      <c r="CD2" s="20"/>
-      <c r="CE2" s="20"/>
-      <c r="CF2" s="20"/>
-      <c r="CG2" s="20"/>
-      <c r="CH2" s="20"/>
-      <c r="CI2" s="20"/>
-      <c r="CJ2" s="20"/>
-      <c r="CK2" s="20"/>
-      <c r="CL2" s="20"/>
-      <c r="CM2" s="20"/>
-      <c r="CN2" s="20"/>
-      <c r="CO2" s="20"/>
-      <c r="CP2" s="20"/>
-      <c r="CQ2" s="20"/>
-      <c r="CR2" s="20"/>
-      <c r="CS2" s="20"/>
-      <c r="CT2" s="20"/>
-      <c r="CU2" s="20"/>
-      <c r="CV2" s="20"/>
-      <c r="CW2" s="20"/>
-      <c r="CX2" s="20"/>
-      <c r="CY2" s="20"/>
-      <c r="CZ2" s="20"/>
-      <c r="DA2" s="20"/>
-      <c r="DB2" s="20"/>
-      <c r="DC2" s="20"/>
-      <c r="DD2" s="20"/>
-      <c r="DE2" s="20"/>
-      <c r="DF2" s="20"/>
-      <c r="DG2" s="20"/>
-      <c r="DH2" s="20"/>
-      <c r="DI2" s="20"/>
-      <c r="DJ2" s="20"/>
-      <c r="DK2" s="20"/>
-      <c r="DL2" s="20"/>
-      <c r="DM2" s="20"/>
-      <c r="DN2" s="20"/>
-      <c r="DO2" s="20"/>
-      <c r="DP2" s="20"/>
-      <c r="DQ2" s="20"/>
-      <c r="DR2" s="20"/>
-      <c r="DS2" s="20"/>
-      <c r="DT2" s="20"/>
-      <c r="DU2" s="20"/>
-      <c r="DV2" s="20"/>
-      <c r="DW2" s="20"/>
-      <c r="DX2" s="20"/>
-      <c r="DY2" s="20"/>
-      <c r="DZ2" s="20"/>
-      <c r="EA2" s="20"/>
-      <c r="EB2" s="20"/>
-      <c r="EC2" s="20"/>
-      <c r="ED2" s="20"/>
-      <c r="EE2" s="20"/>
-      <c r="EF2" s="20"/>
-      <c r="EG2" s="20"/>
-      <c r="EH2" s="20"/>
-      <c r="EI2" s="20"/>
-      <c r="EJ2" s="20"/>
-      <c r="EK2" s="20"/>
-      <c r="EL2" s="20"/>
-      <c r="EM2" s="20"/>
-      <c r="EN2" s="20"/>
-      <c r="EO2" s="20"/>
-      <c r="EP2" s="20"/>
-      <c r="EQ2" s="20"/>
-      <c r="ER2" s="20"/>
-      <c r="ES2" s="20"/>
-      <c r="ET2" s="20"/>
-      <c r="EU2" s="20"/>
-      <c r="EV2" s="20"/>
-      <c r="EW2" s="20"/>
-      <c r="EX2" s="20"/>
-      <c r="EY2" s="20"/>
-      <c r="EZ2" s="20"/>
-      <c r="FA2" s="20"/>
-      <c r="FB2" s="20"/>
-      <c r="FC2" s="20"/>
-      <c r="FD2" s="20"/>
-      <c r="FE2" s="20"/>
-      <c r="FF2" s="20"/>
-      <c r="FG2" s="20"/>
-      <c r="FH2" s="20"/>
-      <c r="FI2" s="20"/>
-      <c r="FJ2" s="20"/>
-      <c r="FK2" s="20"/>
-      <c r="FL2" s="20"/>
-      <c r="FM2" s="20"/>
-      <c r="FN2" s="20"/>
-      <c r="FO2" s="20"/>
-      <c r="FP2" s="20"/>
-      <c r="FQ2" s="20"/>
-      <c r="FR2" s="20"/>
-      <c r="FS2" s="20"/>
-      <c r="FT2" s="20"/>
-      <c r="FU2" s="20"/>
-      <c r="FV2" s="20"/>
-      <c r="FW2" s="20"/>
-      <c r="FX2" s="20"/>
-      <c r="FY2" s="20"/>
-      <c r="FZ2" s="20"/>
-      <c r="GA2" s="20"/>
-      <c r="GB2" s="20"/>
-      <c r="GC2" s="20"/>
-      <c r="GD2" s="20"/>
-      <c r="GE2" s="20"/>
-      <c r="GF2" s="20"/>
-      <c r="GG2" s="20"/>
-      <c r="GH2" s="20"/>
-      <c r="GI2" s="20"/>
-      <c r="GJ2" s="20"/>
-      <c r="GK2" s="20"/>
-      <c r="GL2" s="20"/>
-      <c r="GM2" s="20"/>
-      <c r="GN2" s="20"/>
-      <c r="GO2" s="20"/>
-      <c r="GP2" s="20"/>
-      <c r="GQ2" s="20"/>
-      <c r="GR2" s="20"/>
-      <c r="GS2" s="20"/>
-      <c r="GT2" s="20"/>
-      <c r="GU2" s="20"/>
-      <c r="GV2" s="20"/>
-      <c r="GW2" s="20"/>
-      <c r="GX2" s="20"/>
-      <c r="GY2" s="20"/>
-      <c r="GZ2" s="20"/>
-      <c r="HA2" s="20"/>
-      <c r="HB2" s="20"/>
-      <c r="HC2" s="20"/>
-      <c r="HD2" s="20"/>
-      <c r="HE2" s="20"/>
-      <c r="HF2" s="20"/>
-      <c r="HG2" s="20"/>
-      <c r="HH2" s="20"/>
-      <c r="HI2" s="20"/>
-      <c r="HJ2" s="20"/>
-      <c r="HK2" s="20"/>
-      <c r="HL2" s="20"/>
-      <c r="HM2" s="20"/>
-      <c r="HN2" s="20"/>
-      <c r="HO2" s="20"/>
-      <c r="HP2" s="20"/>
-      <c r="HQ2" s="20"/>
-      <c r="HR2" s="20"/>
-      <c r="HS2" s="20"/>
-      <c r="HT2" s="20"/>
-      <c r="HU2" s="20"/>
-      <c r="HV2" s="20"/>
-      <c r="HW2" s="20"/>
-      <c r="HX2" s="20"/>
-      <c r="HY2" s="20"/>
-      <c r="HZ2" s="20"/>
-      <c r="IA2" s="20"/>
-      <c r="IB2" s="20"/>
-      <c r="IC2" s="20"/>
-      <c r="ID2" s="20"/>
-      <c r="IE2" s="20"/>
-      <c r="IF2" s="20"/>
-      <c r="IG2" s="20"/>
-      <c r="IH2" s="20"/>
-      <c r="II2" s="20"/>
-      <c r="IJ2" s="20"/>
-      <c r="IK2" s="20"/>
-      <c r="IL2" s="20"/>
-      <c r="IM2" s="20"/>
-      <c r="IN2" s="20"/>
-      <c r="IO2" s="20"/>
-      <c r="IP2" s="20"/>
-      <c r="IQ2" s="20"/>
-      <c r="IR2" s="20"/>
-      <c r="IS2" s="20"/>
-      <c r="IT2" s="20"/>
-      <c r="IU2" s="20"/>
-      <c r="IV2" s="20"/>
-      <c r="IW2" s="20"/>
-      <c r="IX2" s="20"/>
-      <c r="IY2" s="20"/>
-      <c r="IZ2" s="20"/>
-      <c r="JA2" s="20"/>
-      <c r="JB2" s="20"/>
-      <c r="JC2" s="20"/>
-      <c r="JD2" s="20"/>
-      <c r="JE2" s="20"/>
-      <c r="JF2" s="20"/>
-      <c r="JG2" s="20"/>
-      <c r="JH2" s="20"/>
-      <c r="JI2" s="20"/>
-      <c r="JJ2" s="20"/>
-      <c r="JK2" s="20"/>
-      <c r="JL2" s="20"/>
-      <c r="JM2" s="20"/>
-      <c r="JN2" s="20"/>
-      <c r="JO2" s="20"/>
-      <c r="JP2" s="20"/>
-      <c r="JQ2" s="20"/>
-      <c r="JR2" s="20"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="27"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="27"/>
+      <c r="BB2" s="27"/>
+      <c r="BC2" s="27"/>
+      <c r="BD2" s="27"/>
+      <c r="BE2" s="27"/>
+      <c r="BF2" s="27"/>
+      <c r="BG2" s="27"/>
+      <c r="BH2" s="27"/>
+      <c r="BI2" s="27"/>
+      <c r="BJ2" s="27"/>
+      <c r="BK2" s="27"/>
+      <c r="BL2" s="27"/>
+      <c r="BM2" s="27"/>
+      <c r="BN2" s="27"/>
+      <c r="BO2" s="27"/>
+      <c r="BP2" s="27"/>
+      <c r="BQ2" s="27"/>
+      <c r="BR2" s="27"/>
+      <c r="BS2" s="27"/>
+      <c r="BT2" s="27"/>
+      <c r="BU2" s="27"/>
+      <c r="BV2" s="27"/>
+      <c r="BW2" s="27"/>
+      <c r="BX2" s="27"/>
+      <c r="BY2" s="27"/>
+      <c r="BZ2" s="27"/>
+      <c r="CA2" s="27"/>
+      <c r="CB2" s="27"/>
+      <c r="CC2" s="27"/>
+      <c r="CD2" s="27"/>
+      <c r="CE2" s="27"/>
+      <c r="CF2" s="27"/>
+      <c r="CG2" s="27"/>
+      <c r="CH2" s="27"/>
+      <c r="CI2" s="27"/>
+      <c r="CJ2" s="27"/>
+      <c r="CK2" s="27"/>
+      <c r="CL2" s="27"/>
+      <c r="CM2" s="27"/>
+      <c r="CN2" s="27"/>
+      <c r="CO2" s="27"/>
+      <c r="CP2" s="27"/>
+      <c r="CQ2" s="27"/>
+      <c r="CR2" s="27"/>
+      <c r="CS2" s="27"/>
+      <c r="CT2" s="27"/>
+      <c r="CU2" s="27"/>
+      <c r="CV2" s="27"/>
+      <c r="CW2" s="27"/>
+      <c r="CX2" s="27"/>
+      <c r="CY2" s="27"/>
+      <c r="CZ2" s="27"/>
+      <c r="DA2" s="27"/>
+      <c r="DB2" s="27"/>
+      <c r="DC2" s="27"/>
+      <c r="DD2" s="27"/>
+      <c r="DE2" s="27"/>
+      <c r="DF2" s="27"/>
+      <c r="DG2" s="27"/>
+      <c r="DH2" s="27"/>
+      <c r="DI2" s="27"/>
+      <c r="DJ2" s="27"/>
+      <c r="DK2" s="27"/>
+      <c r="DL2" s="27"/>
+      <c r="DM2" s="27"/>
+      <c r="DN2" s="27"/>
+      <c r="DO2" s="27"/>
+      <c r="DP2" s="27"/>
+      <c r="DQ2" s="27"/>
+      <c r="DR2" s="27"/>
+      <c r="DS2" s="27"/>
+      <c r="DT2" s="27"/>
+      <c r="DU2" s="27"/>
+      <c r="DV2" s="27"/>
+      <c r="DW2" s="27"/>
+      <c r="DX2" s="27"/>
+      <c r="DY2" s="27"/>
+      <c r="DZ2" s="27"/>
+      <c r="EA2" s="27"/>
+      <c r="EB2" s="27"/>
+      <c r="EC2" s="27"/>
+      <c r="ED2" s="27"/>
+      <c r="EE2" s="27"/>
+      <c r="EF2" s="27"/>
+      <c r="EG2" s="27"/>
+      <c r="EH2" s="27"/>
+      <c r="EI2" s="27"/>
+      <c r="EJ2" s="27"/>
+      <c r="EK2" s="27"/>
+      <c r="EL2" s="27"/>
+      <c r="EM2" s="27"/>
+      <c r="EN2" s="27"/>
+      <c r="EO2" s="27"/>
+      <c r="EP2" s="27"/>
+      <c r="EQ2" s="27"/>
+      <c r="ER2" s="27"/>
+      <c r="ES2" s="27"/>
+      <c r="ET2" s="27"/>
+      <c r="EU2" s="27"/>
+      <c r="EV2" s="27"/>
+      <c r="EW2" s="27"/>
+      <c r="EX2" s="27"/>
+      <c r="EY2" s="27"/>
+      <c r="EZ2" s="27"/>
+      <c r="FA2" s="27"/>
+      <c r="FB2" s="27"/>
+      <c r="FC2" s="27"/>
+      <c r="FD2" s="27"/>
+      <c r="FE2" s="27"/>
+      <c r="FF2" s="27"/>
+      <c r="FG2" s="27"/>
+      <c r="FH2" s="27"/>
+      <c r="FI2" s="27"/>
+      <c r="FJ2" s="27"/>
+      <c r="FK2" s="27"/>
+      <c r="FL2" s="27"/>
+      <c r="FM2" s="27"/>
+      <c r="FN2" s="27"/>
+      <c r="FO2" s="27"/>
+      <c r="FP2" s="27"/>
+      <c r="FQ2" s="27"/>
+      <c r="FR2" s="27"/>
+      <c r="FS2" s="27"/>
+      <c r="FT2" s="27"/>
+      <c r="FU2" s="27"/>
+      <c r="FV2" s="27"/>
+      <c r="FW2" s="27"/>
+      <c r="FX2" s="27"/>
+      <c r="FY2" s="27"/>
+      <c r="FZ2" s="27"/>
+      <c r="GA2" s="27"/>
+      <c r="GB2" s="27"/>
+      <c r="GC2" s="27"/>
+      <c r="GD2" s="27"/>
+      <c r="GE2" s="27"/>
+      <c r="GF2" s="27"/>
+      <c r="GG2" s="27"/>
+      <c r="GH2" s="27"/>
+      <c r="GI2" s="27"/>
+      <c r="GJ2" s="27"/>
+      <c r="GK2" s="27"/>
+      <c r="GL2" s="27"/>
+      <c r="GM2" s="27"/>
+      <c r="GN2" s="27"/>
+      <c r="GO2" s="27"/>
+      <c r="GP2" s="27"/>
+      <c r="GQ2" s="27"/>
+      <c r="GR2" s="27"/>
+      <c r="GS2" s="27"/>
+      <c r="GT2" s="27"/>
+      <c r="GU2" s="27"/>
+      <c r="GV2" s="27"/>
+      <c r="GW2" s="27"/>
+      <c r="GX2" s="27"/>
+      <c r="GY2" s="27"/>
+      <c r="GZ2" s="27"/>
+      <c r="HA2" s="27"/>
+      <c r="HB2" s="27"/>
+      <c r="HC2" s="27"/>
+      <c r="HD2" s="27"/>
+      <c r="HE2" s="27"/>
+      <c r="HF2" s="27"/>
+      <c r="HG2" s="27"/>
+      <c r="HH2" s="27"/>
+      <c r="HI2" s="27"/>
+      <c r="HJ2" s="27"/>
+      <c r="HK2" s="27"/>
+      <c r="HL2" s="27"/>
+      <c r="HM2" s="27"/>
+      <c r="HN2" s="27"/>
+      <c r="HO2" s="27"/>
+      <c r="HP2" s="27"/>
+      <c r="HQ2" s="27"/>
+      <c r="HR2" s="27"/>
+      <c r="HS2" s="27"/>
+      <c r="HT2" s="27"/>
+      <c r="HU2" s="27"/>
+      <c r="HV2" s="27"/>
+      <c r="HW2" s="27"/>
+      <c r="HX2" s="27"/>
+      <c r="HY2" s="27"/>
+      <c r="HZ2" s="27"/>
+      <c r="IA2" s="27"/>
+      <c r="IB2" s="27"/>
+      <c r="IC2" s="27"/>
+      <c r="ID2" s="27"/>
+      <c r="IE2" s="27"/>
+      <c r="IF2" s="27"/>
+      <c r="IG2" s="27"/>
+      <c r="IH2" s="27"/>
+      <c r="II2" s="27"/>
+      <c r="IJ2" s="27"/>
+      <c r="IK2" s="27"/>
+      <c r="IL2" s="27"/>
+      <c r="IM2" s="27"/>
+      <c r="IN2" s="27"/>
+      <c r="IO2" s="27"/>
+      <c r="IP2" s="27"/>
+      <c r="IQ2" s="27"/>
+      <c r="IR2" s="27"/>
+      <c r="IS2" s="27"/>
+      <c r="IT2" s="27"/>
+      <c r="IU2" s="27"/>
+      <c r="IV2" s="27"/>
+      <c r="IW2" s="27"/>
+      <c r="IX2" s="27"/>
+      <c r="IY2" s="27"/>
+      <c r="IZ2" s="27"/>
+      <c r="JA2" s="27"/>
+      <c r="JB2" s="27"/>
+      <c r="JC2" s="27"/>
+      <c r="JD2" s="27"/>
+      <c r="JE2" s="27"/>
+      <c r="JF2" s="27"/>
+      <c r="JG2" s="27"/>
+      <c r="JH2" s="27"/>
+      <c r="JI2" s="27"/>
+      <c r="JJ2" s="27"/>
+      <c r="JK2" s="27"/>
+      <c r="JL2" s="27"/>
+      <c r="JM2" s="27"/>
+      <c r="JN2" s="27"/>
+      <c r="JO2" s="27"/>
+      <c r="JP2" s="27"/>
+      <c r="JQ2" s="27"/>
+      <c r="JR2" s="27"/>
       <c r="JS2" s="10"/>
+      <c r="JT2" s="10"/>
     </row>
-    <row r="4" spans="1:279" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="22">
+      <c r="B4" s="29">
         <v>2003</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22">
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29">
         <v>2004</v>
       </c>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
-      <c r="Z4" s="22">
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29">
         <v>2005</v>
       </c>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="22"/>
-      <c r="AC4" s="22"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="22"/>
-      <c r="AF4" s="22"/>
-      <c r="AG4" s="22"/>
-      <c r="AH4" s="22"/>
-      <c r="AI4" s="22"/>
-      <c r="AJ4" s="22"/>
-      <c r="AK4" s="22"/>
-      <c r="AL4" s="22">
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29">
         <v>2006</v>
       </c>
-      <c r="AM4" s="22"/>
-      <c r="AN4" s="22"/>
-      <c r="AO4" s="22"/>
-      <c r="AP4" s="22"/>
-      <c r="AQ4" s="22"/>
-      <c r="AR4" s="22"/>
-      <c r="AS4" s="22"/>
-      <c r="AT4" s="22"/>
-      <c r="AU4" s="22"/>
-      <c r="AV4" s="22"/>
-      <c r="AW4" s="22"/>
-      <c r="AX4" s="22">
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29">
         <v>2007</v>
       </c>
-      <c r="AY4" s="22"/>
-      <c r="AZ4" s="22"/>
-      <c r="BA4" s="22"/>
-      <c r="BB4" s="22"/>
-      <c r="BC4" s="22"/>
-      <c r="BD4" s="22"/>
-      <c r="BE4" s="22"/>
-      <c r="BF4" s="22"/>
-      <c r="BG4" s="22"/>
-      <c r="BH4" s="22"/>
-      <c r="BI4" s="22"/>
-      <c r="BJ4" s="22">
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29">
         <v>2008</v>
       </c>
-      <c r="BK4" s="22"/>
-      <c r="BL4" s="22"/>
-      <c r="BM4" s="22"/>
-      <c r="BN4" s="22"/>
-      <c r="BO4" s="22"/>
-      <c r="BP4" s="22"/>
-      <c r="BQ4" s="22"/>
-      <c r="BR4" s="22"/>
-      <c r="BS4" s="22"/>
-      <c r="BT4" s="22"/>
-      <c r="BU4" s="22"/>
-      <c r="BV4" s="22">
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29">
         <v>2009</v>
       </c>
-      <c r="BW4" s="22"/>
-      <c r="BX4" s="22"/>
-      <c r="BY4" s="22"/>
-      <c r="BZ4" s="22"/>
-      <c r="CA4" s="22"/>
-      <c r="CB4" s="22"/>
-      <c r="CC4" s="22"/>
-      <c r="CD4" s="22"/>
-      <c r="CE4" s="22"/>
-      <c r="CF4" s="22"/>
-      <c r="CG4" s="22"/>
-      <c r="CH4" s="22">
+      <c r="BW4" s="29"/>
+      <c r="BX4" s="29"/>
+      <c r="BY4" s="29"/>
+      <c r="BZ4" s="29"/>
+      <c r="CA4" s="29"/>
+      <c r="CB4" s="29"/>
+      <c r="CC4" s="29"/>
+      <c r="CD4" s="29"/>
+      <c r="CE4" s="29"/>
+      <c r="CF4" s="29"/>
+      <c r="CG4" s="29"/>
+      <c r="CH4" s="29">
         <v>2010</v>
       </c>
-      <c r="CI4" s="22"/>
-      <c r="CJ4" s="22"/>
-      <c r="CK4" s="22"/>
-      <c r="CL4" s="22"/>
-      <c r="CM4" s="22"/>
-      <c r="CN4" s="22"/>
-      <c r="CO4" s="22"/>
-      <c r="CP4" s="22"/>
-      <c r="CQ4" s="22"/>
-      <c r="CR4" s="22"/>
-      <c r="CS4" s="22"/>
-      <c r="CT4" s="22">
+      <c r="CI4" s="29"/>
+      <c r="CJ4" s="29"/>
+      <c r="CK4" s="29"/>
+      <c r="CL4" s="29"/>
+      <c r="CM4" s="29"/>
+      <c r="CN4" s="29"/>
+      <c r="CO4" s="29"/>
+      <c r="CP4" s="29"/>
+      <c r="CQ4" s="29"/>
+      <c r="CR4" s="29"/>
+      <c r="CS4" s="29"/>
+      <c r="CT4" s="29">
         <v>2011</v>
       </c>
-      <c r="CU4" s="22"/>
-      <c r="CV4" s="22"/>
-      <c r="CW4" s="22"/>
-      <c r="CX4" s="22"/>
-      <c r="CY4" s="22"/>
-      <c r="CZ4" s="22"/>
-      <c r="DA4" s="22"/>
-      <c r="DB4" s="22"/>
-      <c r="DC4" s="22"/>
-      <c r="DD4" s="22"/>
-      <c r="DE4" s="22"/>
-      <c r="DF4" s="22">
+      <c r="CU4" s="29"/>
+      <c r="CV4" s="29"/>
+      <c r="CW4" s="29"/>
+      <c r="CX4" s="29"/>
+      <c r="CY4" s="29"/>
+      <c r="CZ4" s="29"/>
+      <c r="DA4" s="29"/>
+      <c r="DB4" s="29"/>
+      <c r="DC4" s="29"/>
+      <c r="DD4" s="29"/>
+      <c r="DE4" s="29"/>
+      <c r="DF4" s="29">
         <v>2012</v>
       </c>
-      <c r="DG4" s="22"/>
-      <c r="DH4" s="22"/>
-      <c r="DI4" s="22"/>
-      <c r="DJ4" s="22"/>
-      <c r="DK4" s="22"/>
-      <c r="DL4" s="22"/>
-      <c r="DM4" s="22"/>
-      <c r="DN4" s="22"/>
-      <c r="DO4" s="22"/>
-      <c r="DP4" s="22"/>
-      <c r="DQ4" s="22"/>
-      <c r="DR4" s="22">
+      <c r="DG4" s="29"/>
+      <c r="DH4" s="29"/>
+      <c r="DI4" s="29"/>
+      <c r="DJ4" s="29"/>
+      <c r="DK4" s="29"/>
+      <c r="DL4" s="29"/>
+      <c r="DM4" s="29"/>
+      <c r="DN4" s="29"/>
+      <c r="DO4" s="29"/>
+      <c r="DP4" s="29"/>
+      <c r="DQ4" s="29"/>
+      <c r="DR4" s="29">
         <v>2013</v>
       </c>
-      <c r="DS4" s="22"/>
-      <c r="DT4" s="22"/>
-      <c r="DU4" s="22"/>
-      <c r="DV4" s="22"/>
-      <c r="DW4" s="22"/>
-      <c r="DX4" s="22"/>
-      <c r="DY4" s="22"/>
-      <c r="DZ4" s="22"/>
-      <c r="EA4" s="22"/>
-      <c r="EB4" s="22"/>
-      <c r="EC4" s="22"/>
-      <c r="ED4" s="22">
+      <c r="DS4" s="29"/>
+      <c r="DT4" s="29"/>
+      <c r="DU4" s="29"/>
+      <c r="DV4" s="29"/>
+      <c r="DW4" s="29"/>
+      <c r="DX4" s="29"/>
+      <c r="DY4" s="29"/>
+      <c r="DZ4" s="29"/>
+      <c r="EA4" s="29"/>
+      <c r="EB4" s="29"/>
+      <c r="EC4" s="29"/>
+      <c r="ED4" s="29">
         <v>2014</v>
       </c>
-      <c r="EE4" s="22"/>
-      <c r="EF4" s="22"/>
-      <c r="EG4" s="22"/>
-      <c r="EH4" s="22"/>
-      <c r="EI4" s="22"/>
-      <c r="EJ4" s="22"/>
-      <c r="EK4" s="22"/>
-      <c r="EL4" s="22"/>
-      <c r="EM4" s="22"/>
-      <c r="EN4" s="22"/>
-      <c r="EO4" s="22"/>
-      <c r="EP4" s="22">
+      <c r="EE4" s="29"/>
+      <c r="EF4" s="29"/>
+      <c r="EG4" s="29"/>
+      <c r="EH4" s="29"/>
+      <c r="EI4" s="29"/>
+      <c r="EJ4" s="29"/>
+      <c r="EK4" s="29"/>
+      <c r="EL4" s="29"/>
+      <c r="EM4" s="29"/>
+      <c r="EN4" s="29"/>
+      <c r="EO4" s="29"/>
+      <c r="EP4" s="29">
         <v>2015</v>
       </c>
-      <c r="EQ4" s="22"/>
-      <c r="ER4" s="22"/>
-      <c r="ES4" s="22"/>
-      <c r="ET4" s="22"/>
-      <c r="EU4" s="22"/>
-      <c r="EV4" s="22"/>
-      <c r="EW4" s="22"/>
-      <c r="EX4" s="22"/>
-      <c r="EY4" s="22"/>
-      <c r="EZ4" s="22"/>
-      <c r="FA4" s="22"/>
-      <c r="FB4" s="22">
+      <c r="EQ4" s="29"/>
+      <c r="ER4" s="29"/>
+      <c r="ES4" s="29"/>
+      <c r="ET4" s="29"/>
+      <c r="EU4" s="29"/>
+      <c r="EV4" s="29"/>
+      <c r="EW4" s="29"/>
+      <c r="EX4" s="29"/>
+      <c r="EY4" s="29"/>
+      <c r="EZ4" s="29"/>
+      <c r="FA4" s="29"/>
+      <c r="FB4" s="29">
         <v>2016</v>
       </c>
-      <c r="FC4" s="22"/>
-      <c r="FD4" s="22"/>
-      <c r="FE4" s="22"/>
-      <c r="FF4" s="22"/>
-      <c r="FG4" s="22"/>
-      <c r="FH4" s="22"/>
-      <c r="FI4" s="22"/>
-      <c r="FJ4" s="22"/>
-      <c r="FK4" s="22"/>
-      <c r="FL4" s="22"/>
-      <c r="FM4" s="22"/>
-      <c r="FN4" s="22">
+      <c r="FC4" s="29"/>
+      <c r="FD4" s="29"/>
+      <c r="FE4" s="29"/>
+      <c r="FF4" s="29"/>
+      <c r="FG4" s="29"/>
+      <c r="FH4" s="29"/>
+      <c r="FI4" s="29"/>
+      <c r="FJ4" s="29"/>
+      <c r="FK4" s="29"/>
+      <c r="FL4" s="29"/>
+      <c r="FM4" s="29"/>
+      <c r="FN4" s="29">
         <v>2017</v>
       </c>
-      <c r="FO4" s="22"/>
-      <c r="FP4" s="22"/>
-      <c r="FQ4" s="22"/>
-      <c r="FR4" s="22"/>
-      <c r="FS4" s="22"/>
-      <c r="FT4" s="22"/>
-      <c r="FU4" s="22"/>
-      <c r="FV4" s="22"/>
-      <c r="FW4" s="22"/>
-      <c r="FX4" s="22"/>
-      <c r="FY4" s="22"/>
-      <c r="FZ4" s="22">
+      <c r="FO4" s="29"/>
+      <c r="FP4" s="29"/>
+      <c r="FQ4" s="29"/>
+      <c r="FR4" s="29"/>
+      <c r="FS4" s="29"/>
+      <c r="FT4" s="29"/>
+      <c r="FU4" s="29"/>
+      <c r="FV4" s="29"/>
+      <c r="FW4" s="29"/>
+      <c r="FX4" s="29"/>
+      <c r="FY4" s="29"/>
+      <c r="FZ4" s="29">
         <v>2018</v>
       </c>
-      <c r="GA4" s="22"/>
-      <c r="GB4" s="22"/>
-      <c r="GC4" s="22"/>
-      <c r="GD4" s="22"/>
-      <c r="GE4" s="22"/>
-      <c r="GF4" s="22"/>
-      <c r="GG4" s="22"/>
-      <c r="GH4" s="22"/>
-      <c r="GI4" s="22"/>
-      <c r="GJ4" s="22"/>
-      <c r="GK4" s="22"/>
-      <c r="GL4" s="22">
+      <c r="GA4" s="29"/>
+      <c r="GB4" s="29"/>
+      <c r="GC4" s="29"/>
+      <c r="GD4" s="29"/>
+      <c r="GE4" s="29"/>
+      <c r="GF4" s="29"/>
+      <c r="GG4" s="29"/>
+      <c r="GH4" s="29"/>
+      <c r="GI4" s="29"/>
+      <c r="GJ4" s="29"/>
+      <c r="GK4" s="29"/>
+      <c r="GL4" s="29">
         <v>2019</v>
       </c>
-      <c r="GM4" s="22"/>
-      <c r="GN4" s="22"/>
-      <c r="GO4" s="22"/>
-      <c r="GP4" s="22"/>
-      <c r="GQ4" s="22"/>
-      <c r="GR4" s="22"/>
-      <c r="GS4" s="22"/>
-      <c r="GT4" s="22"/>
-      <c r="GU4" s="22"/>
-      <c r="GV4" s="22"/>
-      <c r="GW4" s="22"/>
-      <c r="GX4" s="22">
+      <c r="GM4" s="29"/>
+      <c r="GN4" s="29"/>
+      <c r="GO4" s="29"/>
+      <c r="GP4" s="29"/>
+      <c r="GQ4" s="29"/>
+      <c r="GR4" s="29"/>
+      <c r="GS4" s="29"/>
+      <c r="GT4" s="29"/>
+      <c r="GU4" s="29"/>
+      <c r="GV4" s="29"/>
+      <c r="GW4" s="29"/>
+      <c r="GX4" s="29">
         <v>2020</v>
       </c>
-      <c r="GY4" s="22"/>
-      <c r="GZ4" s="22"/>
-      <c r="HA4" s="22"/>
-      <c r="HB4" s="22"/>
-      <c r="HC4" s="22"/>
-      <c r="HD4" s="22"/>
-      <c r="HE4" s="22"/>
-      <c r="HF4" s="22"/>
-      <c r="HG4" s="22"/>
-      <c r="HH4" s="22"/>
-      <c r="HI4" s="22"/>
-      <c r="HJ4" s="22">
+      <c r="GY4" s="29"/>
+      <c r="GZ4" s="29"/>
+      <c r="HA4" s="29"/>
+      <c r="HB4" s="29"/>
+      <c r="HC4" s="29"/>
+      <c r="HD4" s="29"/>
+      <c r="HE4" s="29"/>
+      <c r="HF4" s="29"/>
+      <c r="HG4" s="29"/>
+      <c r="HH4" s="29"/>
+      <c r="HI4" s="29"/>
+      <c r="HJ4" s="29">
         <v>2021</v>
       </c>
-      <c r="HK4" s="22"/>
-      <c r="HL4" s="22"/>
-      <c r="HM4" s="22"/>
-      <c r="HN4" s="22"/>
-      <c r="HO4" s="22"/>
-      <c r="HP4" s="22"/>
-      <c r="HQ4" s="22"/>
-      <c r="HR4" s="22"/>
-      <c r="HS4" s="22"/>
-      <c r="HT4" s="22"/>
-      <c r="HU4" s="22"/>
-      <c r="HV4" s="22">
+      <c r="HK4" s="29"/>
+      <c r="HL4" s="29"/>
+      <c r="HM4" s="29"/>
+      <c r="HN4" s="29"/>
+      <c r="HO4" s="29"/>
+      <c r="HP4" s="29"/>
+      <c r="HQ4" s="29"/>
+      <c r="HR4" s="29"/>
+      <c r="HS4" s="29"/>
+      <c r="HT4" s="29"/>
+      <c r="HU4" s="29"/>
+      <c r="HV4" s="29">
         <v>2022</v>
       </c>
-      <c r="HW4" s="22"/>
-      <c r="HX4" s="22"/>
-      <c r="HY4" s="22"/>
-      <c r="HZ4" s="22"/>
-      <c r="IA4" s="22"/>
-      <c r="IB4" s="22"/>
-      <c r="IC4" s="22"/>
-      <c r="ID4" s="22"/>
-      <c r="IE4" s="22"/>
-      <c r="IF4" s="22"/>
-      <c r="IG4" s="22"/>
-      <c r="IH4" s="22">
+      <c r="HW4" s="29"/>
+      <c r="HX4" s="29"/>
+      <c r="HY4" s="29"/>
+      <c r="HZ4" s="29"/>
+      <c r="IA4" s="29"/>
+      <c r="IB4" s="29"/>
+      <c r="IC4" s="29"/>
+      <c r="ID4" s="29"/>
+      <c r="IE4" s="29"/>
+      <c r="IF4" s="29"/>
+      <c r="IG4" s="29"/>
+      <c r="IH4" s="29">
         <v>2023</v>
       </c>
-      <c r="II4" s="22"/>
-      <c r="IJ4" s="22"/>
-      <c r="IK4" s="22"/>
-      <c r="IL4" s="22"/>
-      <c r="IM4" s="22"/>
-      <c r="IN4" s="22"/>
-      <c r="IO4" s="22"/>
-      <c r="IP4" s="22"/>
-      <c r="IQ4" s="22"/>
-      <c r="IR4" s="22"/>
-      <c r="IS4" s="22"/>
-      <c r="IT4" s="22">
+      <c r="II4" s="29"/>
+      <c r="IJ4" s="29"/>
+      <c r="IK4" s="29"/>
+      <c r="IL4" s="29"/>
+      <c r="IM4" s="29"/>
+      <c r="IN4" s="29"/>
+      <c r="IO4" s="29"/>
+      <c r="IP4" s="29"/>
+      <c r="IQ4" s="29"/>
+      <c r="IR4" s="29"/>
+      <c r="IS4" s="29"/>
+      <c r="IT4" s="29">
         <v>2024</v>
       </c>
-      <c r="IU4" s="22"/>
-      <c r="IV4" s="22"/>
-      <c r="IW4" s="22"/>
-      <c r="IX4" s="22"/>
-      <c r="IY4" s="22"/>
-      <c r="IZ4" s="22"/>
-      <c r="JA4" s="22"/>
-      <c r="JB4" s="22"/>
-      <c r="JC4" s="22"/>
-      <c r="JD4" s="22"/>
-      <c r="JE4" s="22"/>
-      <c r="JF4" s="22">
+      <c r="IU4" s="29"/>
+      <c r="IV4" s="29"/>
+      <c r="IW4" s="29"/>
+      <c r="IX4" s="29"/>
+      <c r="IY4" s="29"/>
+      <c r="IZ4" s="29"/>
+      <c r="JA4" s="29"/>
+      <c r="JB4" s="29"/>
+      <c r="JC4" s="29"/>
+      <c r="JD4" s="29"/>
+      <c r="JE4" s="29"/>
+      <c r="JF4" s="29">
         <v>2025</v>
       </c>
-      <c r="JG4" s="22"/>
-      <c r="JH4" s="22"/>
-      <c r="JI4" s="22"/>
-      <c r="JJ4" s="22"/>
-      <c r="JK4" s="22"/>
-      <c r="JL4" s="22"/>
-      <c r="JM4" s="22"/>
-      <c r="JN4" s="22"/>
-      <c r="JO4" s="22"/>
-      <c r="JP4" s="22"/>
-      <c r="JQ4" s="22"/>
-      <c r="JR4" s="25">
+      <c r="JG4" s="29"/>
+      <c r="JH4" s="29"/>
+      <c r="JI4" s="29"/>
+      <c r="JJ4" s="29"/>
+      <c r="JK4" s="29"/>
+      <c r="JL4" s="29"/>
+      <c r="JM4" s="29"/>
+      <c r="JN4" s="29"/>
+      <c r="JO4" s="29"/>
+      <c r="JP4" s="29"/>
+      <c r="JQ4" s="31"/>
+      <c r="JR4" s="34">
         <v>2026</v>
       </c>
-      <c r="JS4" s="26"/>
+      <c r="JS4" s="35"/>
+      <c r="JT4" s="36"/>
     </row>
-    <row r="5" spans="1:279" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2513,14 +2562,17 @@
       <c r="JQ5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="JR5" s="2" t="s">
+      <c r="JR5" s="25" t="s">
         <v>3</v>
       </c>
       <c r="JS5" s="12" t="s">
         <v>4</v>
       </c>
+      <c r="JT5" s="12" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -3358,8 +3410,11 @@
       <c r="JS6" s="13">
         <v>-457.65576820684998</v>
       </c>
+      <c r="JT6" s="13">
+        <v>-1791.9971723619001</v>
+      </c>
     </row>
-    <row r="7" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -4197,8 +4252,11 @@
       <c r="JS7" s="13">
         <v>-144.26505840165001</v>
       </c>
+      <c r="JT7" s="13">
+        <v>-630.65916268001001</v>
+      </c>
     </row>
-    <row r="8" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -5036,8 +5094,11 @@
       <c r="JS8" s="13">
         <v>313.39070980519801</v>
       </c>
+      <c r="JT8" s="13">
+        <v>1161.3380096818801</v>
+      </c>
     </row>
-    <row r="9" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -5875,8 +5936,11 @@
       <c r="JS9" s="13">
         <v>-1715.9752870149</v>
       </c>
+      <c r="JT9" s="13">
+        <v>-123.21843762915</v>
+      </c>
     </row>
-    <row r="10" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
@@ -6714,8 +6778,11 @@
       <c r="JS10" s="14">
         <v>850.35542422505398</v>
       </c>
+      <c r="JT10" s="14">
+        <v>993.340014061283</v>
+      </c>
     </row>
-    <row r="11" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
@@ -7553,8 +7620,11 @@
       <c r="JS11" s="14">
         <v>172.615561669253</v>
       </c>
+      <c r="JT11" s="14">
+        <v>246.56366097202499</v>
+      </c>
     </row>
-    <row r="12" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
@@ -8392,8 +8462,11 @@
       <c r="JS12" s="14">
         <v>153.39134869341899</v>
       </c>
+      <c r="JT12" s="14">
+        <v>592.13699388596501</v>
+      </c>
     </row>
-    <row r="13" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
@@ -9231,8 +9304,11 @@
       <c r="JS13" s="14">
         <v>524.34851386238199</v>
       </c>
+      <c r="JT13" s="14">
+        <v>154.639359203293</v>
+      </c>
     </row>
-    <row r="14" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -10070,8 +10146,11 @@
       <c r="JS14" s="14">
         <v>2566.3307112399598</v>
       </c>
+      <c r="JT14" s="14">
+        <v>1116.5584516904401</v>
+      </c>
     </row>
-    <row r="15" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -10909,8 +10988,11 @@
       <c r="JS15" s="14">
         <v>175.55531654080701</v>
       </c>
+      <c r="JT15" s="14">
+        <v>215.926776724597</v>
+      </c>
     </row>
-    <row r="16" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
@@ -11748,8 +11830,11 @@
       <c r="JS16" s="14">
         <v>559.13327007328905</v>
       </c>
+      <c r="JT16" s="14">
+        <v>0.22057358829779999</v>
+      </c>
     </row>
-    <row r="17" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
@@ -12587,8 +12672,11 @@
       <c r="JS17" s="14">
         <v>1831.6421246258601</v>
       </c>
+      <c r="JT17" s="14">
+        <v>900.41110137754299</v>
+      </c>
     </row>
-    <row r="18" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -13426,8 +13514,11 @@
       <c r="JS18" s="13">
         <v>1936.88908388811</v>
       </c>
+      <c r="JT18" s="13">
+        <v>-869.06357683322005</v>
+      </c>
     </row>
-    <row r="19" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
@@ -14265,8 +14356,11 @@
       <c r="JS19" s="14">
         <v>2493.6477855128901</v>
       </c>
+      <c r="JT19" s="14">
+        <v>235.45631309248199</v>
+      </c>
     </row>
-    <row r="20" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>25</v>
       </c>
@@ -15104,8 +15198,11 @@
       <c r="JS20" s="14">
         <v>2303.8337792542002</v>
       </c>
+      <c r="JT20" s="14">
+        <v>369.39918577771198</v>
+      </c>
     </row>
-    <row r="21" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>26</v>
       </c>
@@ -15943,8 +16040,11 @@
       <c r="JS21" s="14">
         <v>189.81400625869199</v>
       </c>
+      <c r="JT21" s="14">
+        <v>-133.94287268522999</v>
+      </c>
     </row>
-    <row r="22" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>27</v>
       </c>
@@ -16782,8 +16882,11 @@
       <c r="JS22" s="14">
         <v>225.029749125206</v>
       </c>
+      <c r="JT22" s="14">
+        <v>301.71439026306598</v>
+      </c>
     </row>
-    <row r="23" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
@@ -17621,8 +17724,11 @@
       <c r="JS23" s="14">
         <v>-35.215742866513999</v>
       </c>
+      <c r="JT23" s="14">
+        <v>-435.6572629483</v>
+      </c>
     </row>
-    <row r="24" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
@@ -18460,8 +18566,11 @@
       <c r="JS24" s="14">
         <v>556.75870162478202</v>
       </c>
+      <c r="JT24" s="14">
+        <v>1104.5198899257</v>
+      </c>
     </row>
-    <row r="25" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
@@ -19299,8 +19408,11 @@
       <c r="JS25" s="14">
         <v>-435.87857536126</v>
       </c>
+      <c r="JT25" s="14">
+        <v>-154.67187124678</v>
+      </c>
     </row>
-    <row r="26" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -20138,8 +20250,11 @@
       <c r="JS26" s="14">
         <v>992.63727698604498</v>
       </c>
+      <c r="JT26" s="14">
+        <v>1259.19176117249</v>
+      </c>
     </row>
-    <row r="27" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
@@ -20977,8 +21092,11 @@
       <c r="JS27" s="14">
         <v>775.04262379891895</v>
       </c>
+      <c r="JT27" s="14">
+        <v>637.39290799523303</v>
+      </c>
     </row>
-    <row r="28" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -21816,8 +21934,11 @@
       <c r="JS28" s="14">
         <v>217.594653187126</v>
       </c>
+      <c r="JT28" s="14">
+        <v>621.79885317725302</v>
+      </c>
     </row>
-    <row r="29" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>30</v>
       </c>
@@ -22655,8 +22776,11 @@
       <c r="JS29" s="13">
         <v>-203.30924334349999</v>
       </c>
+      <c r="JT29" s="13">
+        <v>-533.71735119058997</v>
+      </c>
     </row>
-    <row r="30" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -23494,8 +23618,11 @@
       <c r="JS30" s="13">
         <v>-1454.1110346932001</v>
       </c>
+      <c r="JT30" s="13">
+        <v>-736.14305708759002</v>
+      </c>
     </row>
-    <row r="31" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>19</v>
       </c>
@@ -24333,8 +24460,11 @@
       <c r="JS31" s="14">
         <v>-1815.2766953419</v>
       </c>
+      <c r="JT31" s="14">
+        <v>423.552901234243</v>
+      </c>
     </row>
-    <row r="32" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>32</v>
       </c>
@@ -25172,8 +25302,11 @@
       <c r="JS32" s="14">
         <v>0</v>
       </c>
+      <c r="JT32" s="14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>33</v>
       </c>
@@ -26011,8 +26144,11 @@
       <c r="JS33" s="14">
         <v>-1366.8626790773999</v>
       </c>
+      <c r="JT33" s="14">
+        <v>597.18702029778694</v>
+      </c>
     </row>
-    <row r="34" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
@@ -26850,8 +26986,11 @@
       <c r="JS34" s="14">
         <v>147.80157153360599</v>
       </c>
+      <c r="JT34" s="14">
+        <v>582.63625970682403</v>
+      </c>
     </row>
-    <row r="35" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>35</v>
       </c>
@@ -27689,8 +27828,11 @@
       <c r="JS35" s="14">
         <v>-593.21475514147005</v>
       </c>
+      <c r="JT35" s="14">
+        <v>-753.29851554178003</v>
+      </c>
     </row>
-    <row r="36" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>36</v>
       </c>
@@ -28528,8 +28670,11 @@
       <c r="JS36" s="14">
         <v>-3.0008326566563999</v>
       </c>
+      <c r="JT36" s="14">
+        <v>-2.9718632285884001</v>
+      </c>
     </row>
-    <row r="37" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>23</v>
       </c>
@@ -29367,8 +29512,11 @@
       <c r="JS37" s="14">
         <v>-361.16566064873001</v>
       </c>
+      <c r="JT37" s="14">
+        <v>1159.6959583218299</v>
+      </c>
     </row>
-    <row r="38" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>33</v>
       </c>
@@ -30206,8 +30354,11 @@
       <c r="JS38" s="14">
         <v>-392.70565980050998</v>
       </c>
+      <c r="JT38" s="14">
+        <v>190.207973260139</v>
+      </c>
     </row>
-    <row r="39" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>34</v>
       </c>
@@ -31045,8 +31196,11 @@
       <c r="JS39" s="14">
         <v>17.7723565924429</v>
       </c>
+      <c r="JT39" s="14">
+        <v>928.83028183550596</v>
+      </c>
     </row>
-    <row r="40" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>35</v>
       </c>
@@ -31884,8 +32038,11 @@
       <c r="JS40" s="14">
         <v>30.095974693617102</v>
       </c>
+      <c r="JT40" s="14">
+        <v>32.827728776506</v>
+      </c>
     </row>
-    <row r="41" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>37</v>
       </c>
@@ -32723,8 +32880,11 @@
       <c r="JS41" s="14">
         <v>6.6995199999999996E-3</v>
       </c>
+      <c r="JT41" s="14">
+        <v>3.5743999999999999E-4</v>
+      </c>
     </row>
-    <row r="42" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>38</v>
       </c>
@@ -33562,1970 +33722,1980 @@
       <c r="JS42" s="14">
         <v>-16.335031654280002</v>
       </c>
+      <c r="JT42" s="14">
+        <v>7.8296170096769799</v>
+      </c>
     </row>
-    <row r="43" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29" t="s">
+    <row r="43" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="20">
         <v>905.8</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="20">
         <v>35.5</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="20">
         <v>28</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="20">
         <v>-715.9</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="20">
         <v>-312.7</v>
       </c>
-      <c r="G43" s="30">
+      <c r="G43" s="20">
         <v>-248</v>
       </c>
-      <c r="H43" s="30">
+      <c r="H43" s="20">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="I43" s="30">
+      <c r="I43" s="20">
         <v>44.7</v>
       </c>
-      <c r="J43" s="30">
+      <c r="J43" s="20">
         <v>15.6</v>
       </c>
-      <c r="K43" s="30">
+      <c r="K43" s="20">
         <v>-20.8</v>
       </c>
-      <c r="L43" s="30">
+      <c r="L43" s="20">
         <v>43.9</v>
       </c>
-      <c r="M43" s="30">
+      <c r="M43" s="20">
         <v>-137.6</v>
       </c>
-      <c r="N43" s="30">
+      <c r="N43" s="20">
         <v>139.30000000000001</v>
       </c>
-      <c r="O43" s="30">
+      <c r="O43" s="20">
         <v>10</v>
       </c>
-      <c r="P43" s="30">
+      <c r="P43" s="20">
         <v>-58</v>
       </c>
-      <c r="Q43" s="30">
+      <c r="Q43" s="20">
         <v>156.80000000000001</v>
       </c>
-      <c r="R43" s="30">
+      <c r="R43" s="20">
         <v>92.8</v>
       </c>
-      <c r="S43" s="30">
+      <c r="S43" s="20">
         <v>-225.08</v>
       </c>
-      <c r="T43" s="30">
+      <c r="T43" s="20">
         <v>-7.7</v>
       </c>
-      <c r="U43" s="30">
+      <c r="U43" s="20">
         <v>-102.9</v>
       </c>
-      <c r="V43" s="30">
+      <c r="V43" s="20">
         <v>-25.6</v>
       </c>
-      <c r="W43" s="30">
+      <c r="W43" s="20">
         <v>-270.7</v>
       </c>
-      <c r="X43" s="30">
+      <c r="X43" s="20">
         <v>170.7</v>
       </c>
-      <c r="Y43" s="30">
+      <c r="Y43" s="20">
         <v>-70.400000000000006</v>
       </c>
-      <c r="Z43" s="30">
+      <c r="Z43" s="20">
         <v>-265</v>
       </c>
-      <c r="AA43" s="30">
+      <c r="AA43" s="20">
         <v>-169.1</v>
       </c>
-      <c r="AB43" s="30">
+      <c r="AB43" s="20">
         <v>58.899999999999899</v>
       </c>
-      <c r="AC43" s="30">
+      <c r="AC43" s="20">
         <v>1582</v>
       </c>
-      <c r="AD43" s="30">
+      <c r="AD43" s="20">
         <v>577.5</v>
       </c>
-      <c r="AE43" s="30">
+      <c r="AE43" s="20">
         <v>-548.20000000000005</v>
       </c>
-      <c r="AF43" s="30">
+      <c r="AF43" s="20">
         <v>-434.3</v>
       </c>
-      <c r="AG43" s="30">
+      <c r="AG43" s="20">
         <v>2.5999999999999899</v>
       </c>
-      <c r="AH43" s="30">
+      <c r="AH43" s="20">
         <v>-531.9</v>
       </c>
-      <c r="AI43" s="30">
+      <c r="AI43" s="20">
         <v>-595.9</v>
       </c>
-      <c r="AJ43" s="30">
+      <c r="AJ43" s="20">
         <v>1138.5999999999999</v>
       </c>
-      <c r="AK43" s="30">
+      <c r="AK43" s="20">
         <v>900.5</v>
       </c>
-      <c r="AL43" s="30">
+      <c r="AL43" s="20">
         <v>-1156.8</v>
       </c>
-      <c r="AM43" s="30">
+      <c r="AM43" s="20">
         <v>316.10000000000002</v>
       </c>
-      <c r="AN43" s="30">
+      <c r="AN43" s="20">
         <v>-230.4</v>
       </c>
-      <c r="AO43" s="30">
+      <c r="AO43" s="20">
         <v>1340.9</v>
       </c>
-      <c r="AP43" s="30">
+      <c r="AP43" s="20">
         <v>554.6</v>
       </c>
-      <c r="AQ43" s="30">
+      <c r="AQ43" s="20">
         <v>-474.8</v>
       </c>
-      <c r="AR43" s="30">
+      <c r="AR43" s="20">
         <v>-602.04999999999995</v>
       </c>
-      <c r="AS43" s="30">
+      <c r="AS43" s="20">
         <v>-94.1</v>
       </c>
-      <c r="AT43" s="30">
+      <c r="AT43" s="20">
         <v>621.20000000000005</v>
       </c>
-      <c r="AU43" s="30">
+      <c r="AU43" s="20">
         <v>-63.25</v>
       </c>
-      <c r="AV43" s="30">
+      <c r="AV43" s="20">
         <v>-500.3</v>
       </c>
-      <c r="AW43" s="30">
+      <c r="AW43" s="20">
         <v>2286.349929</v>
       </c>
-      <c r="AX43" s="30">
+      <c r="AX43" s="20">
         <v>-1984.5819618702999</v>
       </c>
-      <c r="AY43" s="30">
+      <c r="AY43" s="20">
         <v>-1320.8036648673999</v>
       </c>
-      <c r="AZ43" s="30">
+      <c r="AZ43" s="20">
         <v>-816.82869184317997</v>
       </c>
-      <c r="BA43" s="30">
+      <c r="BA43" s="20">
         <v>2046.8821723224301</v>
       </c>
-      <c r="BB43" s="30">
+      <c r="BB43" s="20">
         <v>-459.73266682114001</v>
       </c>
-      <c r="BC43" s="30">
+      <c r="BC43" s="20">
         <v>950.92180220721696</v>
       </c>
-      <c r="BD43" s="30">
+      <c r="BD43" s="20">
         <v>526.45354186426505</v>
       </c>
-      <c r="BE43" s="30">
+      <c r="BE43" s="20">
         <v>-2825.6148634095998</v>
       </c>
-      <c r="BF43" s="30">
+      <c r="BF43" s="20">
         <v>347.63782526791499</v>
       </c>
-      <c r="BG43" s="30">
+      <c r="BG43" s="20">
         <v>-37.93311167121</v>
       </c>
-      <c r="BH43" s="30">
+      <c r="BH43" s="20">
         <v>-385.68128578264998</v>
       </c>
-      <c r="BI43" s="30">
+      <c r="BI43" s="20">
         <v>745.13879251755804</v>
       </c>
-      <c r="BJ43" s="30">
+      <c r="BJ43" s="20">
         <v>-178.74965394621</v>
       </c>
-      <c r="BK43" s="30">
+      <c r="BK43" s="20">
         <v>94.9822744421664</v>
       </c>
-      <c r="BL43" s="30">
+      <c r="BL43" s="20">
         <v>433.10229808624001</v>
       </c>
-      <c r="BM43" s="30">
+      <c r="BM43" s="20">
         <v>511.077306417035</v>
       </c>
-      <c r="BN43" s="30">
+      <c r="BN43" s="20">
         <v>934.71520834795604</v>
       </c>
-      <c r="BO43" s="30">
+      <c r="BO43" s="20">
         <v>973.611525330772</v>
       </c>
-      <c r="BP43" s="30">
+      <c r="BP43" s="20">
         <v>1708.1426290737299</v>
       </c>
-      <c r="BQ43" s="30">
+      <c r="BQ43" s="20">
         <v>945.13444913146202</v>
       </c>
-      <c r="BR43" s="30">
+      <c r="BR43" s="20">
         <v>1961.88342489347</v>
       </c>
-      <c r="BS43" s="30">
+      <c r="BS43" s="20">
         <v>-186.79698717632999</v>
       </c>
-      <c r="BT43" s="30">
+      <c r="BT43" s="20">
         <v>-1105.6225249404999</v>
       </c>
-      <c r="BU43" s="30">
+      <c r="BU43" s="20">
         <v>352.76588644283203</v>
       </c>
-      <c r="BV43" s="30">
+      <c r="BV43" s="20">
         <v>738.66985719165996</v>
       </c>
-      <c r="BW43" s="30">
+      <c r="BW43" s="20">
         <v>-363.56995113506002</v>
       </c>
-      <c r="BX43" s="30">
+      <c r="BX43" s="20">
         <v>84.544282215092693</v>
       </c>
-      <c r="BY43" s="30">
+      <c r="BY43" s="20">
         <v>187.50239709587399</v>
       </c>
-      <c r="BZ43" s="30">
+      <c r="BZ43" s="20">
         <v>-24.168840682945</v>
       </c>
-      <c r="CA43" s="30">
+      <c r="CA43" s="20">
         <v>-626.07936197508002</v>
       </c>
-      <c r="CB43" s="30">
+      <c r="CB43" s="20">
         <v>-1.1285624138940999</v>
       </c>
-      <c r="CC43" s="30">
+      <c r="CC43" s="20">
         <v>1379.1852882677699</v>
       </c>
-      <c r="CD43" s="30">
+      <c r="CD43" s="20">
         <v>739.24116301640299</v>
       </c>
-      <c r="CE43" s="30">
+      <c r="CE43" s="20">
         <v>-274.65101078380002</v>
       </c>
-      <c r="CF43" s="30">
+      <c r="CF43" s="20">
         <v>-24.443656701186999</v>
       </c>
-      <c r="CG43" s="30">
+      <c r="CG43" s="20">
         <v>-167.35420771413001</v>
       </c>
-      <c r="CH43" s="30">
+      <c r="CH43" s="20">
         <v>-180.02318997272999</v>
       </c>
-      <c r="CI43" s="30">
+      <c r="CI43" s="20">
         <v>276.49283350000002</v>
       </c>
-      <c r="CJ43" s="30">
+      <c r="CJ43" s="20">
         <v>759.05412273138904</v>
       </c>
-      <c r="CK43" s="30">
+      <c r="CK43" s="20">
         <v>-49.717873738686997</v>
       </c>
-      <c r="CL43" s="30">
+      <c r="CL43" s="20">
         <v>106.682191795802</v>
       </c>
-      <c r="CM43" s="30">
+      <c r="CM43" s="20">
         <v>293.09063078905899</v>
       </c>
-      <c r="CN43" s="30">
+      <c r="CN43" s="20">
         <v>-121.18838798236</v>
       </c>
-      <c r="CO43" s="30">
+      <c r="CO43" s="20">
         <v>-269.61108757984999</v>
       </c>
-      <c r="CP43" s="30">
+      <c r="CP43" s="20">
         <v>423.96148067796003</v>
       </c>
-      <c r="CQ43" s="30">
+      <c r="CQ43" s="20">
         <v>-207.17374284390999</v>
       </c>
-      <c r="CR43" s="30">
+      <c r="CR43" s="20">
         <v>231.71837538669001</v>
       </c>
-      <c r="CS43" s="30">
+      <c r="CS43" s="20">
         <v>1760.54763608957</v>
       </c>
-      <c r="CT43" s="30">
+      <c r="CT43" s="20">
         <v>-1134.6004728534001</v>
       </c>
-      <c r="CU43" s="30">
+      <c r="CU43" s="20">
         <v>1292.3416520000001</v>
       </c>
-      <c r="CV43" s="30">
+      <c r="CV43" s="20">
         <v>2750.59310234553</v>
       </c>
-      <c r="CW43" s="30">
+      <c r="CW43" s="20">
         <v>-305.7647324774</v>
       </c>
-      <c r="CX43" s="30">
+      <c r="CX43" s="20">
         <v>1248.0231814394001</v>
       </c>
-      <c r="CY43" s="30">
+      <c r="CY43" s="20">
         <v>2009.4823897998499</v>
       </c>
-      <c r="CZ43" s="30">
+      <c r="CZ43" s="20">
         <v>-548.31328345182999</v>
       </c>
-      <c r="DA43" s="30">
+      <c r="DA43" s="20">
         <v>1643.2135306983701</v>
       </c>
-      <c r="DB43" s="30">
+      <c r="DB43" s="20">
         <v>2555.4248205466602</v>
       </c>
-      <c r="DC43" s="30">
+      <c r="DC43" s="20">
         <v>5.4196477184270302</v>
       </c>
-      <c r="DD43" s="30">
+      <c r="DD43" s="20">
         <v>1190.75918456769</v>
       </c>
-      <c r="DE43" s="30">
+      <c r="DE43" s="20">
         <v>3483.5164320264898</v>
       </c>
-      <c r="DF43" s="30">
+      <c r="DF43" s="20">
         <v>-3159.2705756367</v>
       </c>
-      <c r="DG43" s="30">
+      <c r="DG43" s="20">
         <v>-242.82307978380001</v>
       </c>
-      <c r="DH43" s="30">
+      <c r="DH43" s="20">
         <v>561.374015191073</v>
       </c>
-      <c r="DI43" s="30">
+      <c r="DI43" s="20">
         <v>-939.35221488756997</v>
       </c>
-      <c r="DJ43" s="30">
+      <c r="DJ43" s="20">
         <v>731.61545672021805</v>
       </c>
-      <c r="DK43" s="30">
+      <c r="DK43" s="20">
         <v>1995.34298234887</v>
       </c>
-      <c r="DL43" s="30">
+      <c r="DL43" s="20">
         <v>-2025.7520538686999</v>
       </c>
-      <c r="DM43" s="30">
+      <c r="DM43" s="20">
         <v>-176.74973049440999</v>
       </c>
-      <c r="DN43" s="30">
+      <c r="DN43" s="20">
         <v>1283.8281479688301</v>
       </c>
-      <c r="DO43" s="30">
+      <c r="DO43" s="20">
         <v>-1037.7107047070999</v>
       </c>
-      <c r="DP43" s="30">
+      <c r="DP43" s="20">
         <v>782.58327392570698</v>
       </c>
-      <c r="DQ43" s="30">
+      <c r="DQ43" s="20">
         <v>1860.12651498747</v>
       </c>
-      <c r="DR43" s="30">
+      <c r="DR43" s="20">
         <v>-1699.0339461217</v>
       </c>
-      <c r="DS43" s="30">
+      <c r="DS43" s="20">
         <v>-200.27362063052001</v>
       </c>
-      <c r="DT43" s="30">
+      <c r="DT43" s="20">
         <v>664.99099579497602</v>
       </c>
-      <c r="DU43" s="30">
+      <c r="DU43" s="20">
         <v>1177.30439702485</v>
       </c>
-      <c r="DV43" s="30">
+      <c r="DV43" s="20">
         <v>-565.79229469810002</v>
       </c>
-      <c r="DW43" s="30">
+      <c r="DW43" s="20">
         <v>1161.30406622642</v>
       </c>
-      <c r="DX43" s="30">
+      <c r="DX43" s="20">
         <v>-1127.5413171235</v>
       </c>
-      <c r="DY43" s="30">
+      <c r="DY43" s="20">
         <v>791.26738353688495</v>
       </c>
-      <c r="DZ43" s="30">
+      <c r="DZ43" s="20">
         <v>1100.8197052312801</v>
       </c>
-      <c r="EA43" s="30">
+      <c r="EA43" s="20">
         <v>-1648.4764632797001</v>
       </c>
-      <c r="EB43" s="30">
+      <c r="EB43" s="20">
         <v>-603.28171225606002</v>
       </c>
-      <c r="EC43" s="30">
+      <c r="EC43" s="20">
         <v>1260.1280682686399</v>
       </c>
-      <c r="ED43" s="30">
+      <c r="ED43" s="20">
         <v>-856.48472860162997</v>
       </c>
-      <c r="EE43" s="30">
+      <c r="EE43" s="20">
         <v>-226.70307692929001</v>
       </c>
-      <c r="EF43" s="30">
+      <c r="EF43" s="20">
         <v>948.72297773927301</v>
       </c>
-      <c r="EG43" s="30">
+      <c r="EG43" s="20">
         <v>-796.05416632407002</v>
       </c>
-      <c r="EH43" s="30">
+      <c r="EH43" s="20">
         <v>660.506231160006</v>
       </c>
-      <c r="EI43" s="30">
+      <c r="EI43" s="20">
         <v>25.4844096841022</v>
       </c>
-      <c r="EJ43" s="30">
+      <c r="EJ43" s="20">
         <v>-406.69624237087999</v>
       </c>
-      <c r="EK43" s="30">
+      <c r="EK43" s="20">
         <v>35.408939660488301</v>
       </c>
-      <c r="EL43" s="30">
+      <c r="EL43" s="20">
         <v>550.93543200701004</v>
       </c>
-      <c r="EM43" s="30">
+      <c r="EM43" s="20">
         <v>-434.70554966664002</v>
       </c>
-      <c r="EN43" s="30">
+      <c r="EN43" s="20">
         <v>542.88068364945195</v>
       </c>
-      <c r="EO43" s="30">
+      <c r="EO43" s="20">
         <v>1013.5601578062</v>
       </c>
-      <c r="EP43" s="30">
+      <c r="EP43" s="20">
         <v>485.43062419589899</v>
       </c>
-      <c r="EQ43" s="30">
+      <c r="EQ43" s="20">
         <v>-1882.2159291336</v>
       </c>
-      <c r="ER43" s="30">
+      <c r="ER43" s="20">
         <v>792.11289604928095</v>
       </c>
-      <c r="ES43" s="30">
+      <c r="ES43" s="20">
         <v>10.1469516936262</v>
       </c>
-      <c r="ET43" s="30">
+      <c r="ET43" s="20">
         <v>264.37728101418702</v>
       </c>
-      <c r="EU43" s="30">
+      <c r="EU43" s="20">
         <v>-563.85031725044996</v>
       </c>
-      <c r="EV43" s="30">
+      <c r="EV43" s="20">
         <v>319.63516158433202</v>
       </c>
-      <c r="EW43" s="30">
+      <c r="EW43" s="20">
         <v>216.313844906811</v>
       </c>
-      <c r="EX43" s="30">
+      <c r="EX43" s="20">
         <v>-165.52362638989001</v>
       </c>
-      <c r="EY43" s="30">
+      <c r="EY43" s="20">
         <v>433.61762480784103</v>
       </c>
-      <c r="EZ43" s="30">
+      <c r="EZ43" s="20">
         <v>193.365522559585</v>
       </c>
-      <c r="FA43" s="30">
+      <c r="FA43" s="20">
         <v>107.711321826969</v>
       </c>
-      <c r="FB43" s="30">
+      <c r="FB43" s="20">
         <v>-354.10155910857998</v>
       </c>
-      <c r="FC43" s="30">
+      <c r="FC43" s="20">
         <v>-279.92025681541998</v>
       </c>
-      <c r="FD43" s="30">
+      <c r="FD43" s="20">
         <v>771.21186488427895</v>
       </c>
-      <c r="FE43" s="30">
+      <c r="FE43" s="20">
         <v>262.324057886964</v>
       </c>
-      <c r="FF43" s="30">
+      <c r="FF43" s="20">
         <v>353.50854730778502</v>
       </c>
-      <c r="FG43" s="30">
+      <c r="FG43" s="20">
         <v>-371.37311671985998</v>
       </c>
-      <c r="FH43" s="30">
+      <c r="FH43" s="20">
         <v>-221.27378346248</v>
       </c>
-      <c r="FI43" s="30">
+      <c r="FI43" s="20">
         <v>-356.02624813239999</v>
       </c>
-      <c r="FJ43" s="30">
+      <c r="FJ43" s="20">
         <v>275.53808212585</v>
       </c>
-      <c r="FK43" s="30">
+      <c r="FK43" s="20">
         <v>105.744878813178</v>
       </c>
-      <c r="FL43" s="30">
+      <c r="FL43" s="20">
         <v>286.06105216695897</v>
       </c>
-      <c r="FM43" s="30">
+      <c r="FM43" s="20">
         <v>1333.39910166957</v>
       </c>
-      <c r="FN43" s="30">
+      <c r="FN43" s="20">
         <v>-1076.7823250147001</v>
       </c>
-      <c r="FO43" s="30">
+      <c r="FO43" s="20">
         <v>-234.51037185759</v>
       </c>
-      <c r="FP43" s="30">
+      <c r="FP43" s="20">
         <v>-675.29386319022001</v>
       </c>
-      <c r="FQ43" s="30">
+      <c r="FQ43" s="20">
         <v>-127.2267261465</v>
       </c>
-      <c r="FR43" s="30">
+      <c r="FR43" s="20">
         <v>-372.58331242591998</v>
       </c>
-      <c r="FS43" s="30">
+      <c r="FS43" s="20">
         <v>-75.973642870988996</v>
       </c>
-      <c r="FT43" s="30">
+      <c r="FT43" s="20">
         <v>-876.93859704284</v>
       </c>
-      <c r="FU43" s="30">
+      <c r="FU43" s="20">
         <v>490.40634530185201</v>
       </c>
-      <c r="FV43" s="30">
+      <c r="FV43" s="20">
         <v>-1066.3613009686001</v>
       </c>
-      <c r="FW43" s="30">
+      <c r="FW43" s="20">
         <v>1739.5923016326501</v>
       </c>
-      <c r="FX43" s="30">
+      <c r="FX43" s="20">
         <v>-1481.6190044291</v>
       </c>
-      <c r="FY43" s="30">
+      <c r="FY43" s="20">
         <v>1007.68973449067</v>
       </c>
-      <c r="FZ43" s="30">
+      <c r="FZ43" s="20">
         <v>-690.80148546244004</v>
       </c>
-      <c r="GA43" s="30">
+      <c r="GA43" s="20">
         <v>-66.965017051512007</v>
       </c>
-      <c r="GB43" s="30">
+      <c r="GB43" s="20">
         <v>-385.24252914591</v>
       </c>
-      <c r="GC43" s="30">
+      <c r="GC43" s="20">
         <v>-498.56642212350999</v>
       </c>
-      <c r="GD43" s="30">
+      <c r="GD43" s="20">
         <v>192.88503463355499</v>
       </c>
-      <c r="GE43" s="30">
+      <c r="GE43" s="20">
         <v>-87.618118331282005</v>
       </c>
-      <c r="GF43" s="30">
+      <c r="GF43" s="20">
         <v>536.345549278014</v>
       </c>
-      <c r="GG43" s="30">
+      <c r="GG43" s="20">
         <v>-809.37827100876996</v>
       </c>
-      <c r="GH43" s="30">
+      <c r="GH43" s="20">
         <v>450.33618949808999</v>
       </c>
-      <c r="GI43" s="30">
+      <c r="GI43" s="20">
         <v>575.58521994704904</v>
       </c>
-      <c r="GJ43" s="30">
+      <c r="GJ43" s="20">
         <v>1953.11912032798</v>
       </c>
-      <c r="GK43" s="30">
+      <c r="GK43" s="20">
         <v>227.01556534863701</v>
       </c>
-      <c r="GL43" s="30">
+      <c r="GL43" s="20">
         <v>-1255.5593225473999</v>
       </c>
-      <c r="GM43" s="30">
+      <c r="GM43" s="20">
         <v>-85.805718117249995</v>
       </c>
-      <c r="GN43" s="30">
+      <c r="GN43" s="20">
         <v>177.73366265022301</v>
       </c>
-      <c r="GO43" s="30">
+      <c r="GO43" s="20">
         <v>-581.43734849991995</v>
       </c>
-      <c r="GP43" s="30">
+      <c r="GP43" s="20">
         <v>-65.556362512608999</v>
       </c>
-      <c r="GQ43" s="30">
+      <c r="GQ43" s="20">
         <v>763.80915151106501</v>
       </c>
-      <c r="GR43" s="30">
+      <c r="GR43" s="20">
         <v>-212.86460472195</v>
       </c>
-      <c r="GS43" s="30">
+      <c r="GS43" s="20">
         <v>-274.65763183578002</v>
       </c>
-      <c r="GT43" s="30">
+      <c r="GT43" s="20">
         <v>-250.97542234671999</v>
       </c>
-      <c r="GU43" s="30">
+      <c r="GU43" s="20">
         <v>911.98865929686895</v>
       </c>
-      <c r="GV43" s="30">
+      <c r="GV43" s="20">
         <v>-973.11593283995001</v>
       </c>
-      <c r="GW43" s="30">
+      <c r="GW43" s="20">
         <v>1693.9612745038701</v>
       </c>
-      <c r="GX43" s="30">
+      <c r="GX43" s="20">
         <v>-3114.1752898877999</v>
       </c>
-      <c r="GY43" s="30">
+      <c r="GY43" s="20">
         <v>-1297.4287019348999</v>
       </c>
-      <c r="GZ43" s="30">
+      <c r="GZ43" s="20">
         <v>2034.3552343239401</v>
       </c>
-      <c r="HA43" s="30">
+      <c r="HA43" s="20">
         <v>-1084.2572293674</v>
       </c>
-      <c r="HB43" s="30">
+      <c r="HB43" s="20">
         <v>-171.81275799513</v>
       </c>
-      <c r="HC43" s="30">
+      <c r="HC43" s="20">
         <v>-509.44791017588</v>
       </c>
-      <c r="HD43" s="30">
+      <c r="HD43" s="20">
         <v>-304.34803420076003</v>
       </c>
-      <c r="HE43" s="30">
+      <c r="HE43" s="20">
         <v>663.41562418438002</v>
       </c>
-      <c r="HF43" s="30">
+      <c r="HF43" s="20">
         <v>249.73305055440699</v>
       </c>
-      <c r="HG43" s="30">
+      <c r="HG43" s="20">
         <v>319.43763212685502</v>
       </c>
-      <c r="HH43" s="30">
+      <c r="HH43" s="20">
         <v>-790.95967515466998</v>
       </c>
-      <c r="HI43" s="30">
+      <c r="HI43" s="20">
         <v>1110.5330856324299</v>
       </c>
-      <c r="HJ43" s="30">
+      <c r="HJ43" s="20">
         <v>-111.13705406050001</v>
       </c>
-      <c r="HK43" s="30">
+      <c r="HK43" s="20">
         <v>686.06355969634603</v>
       </c>
-      <c r="HL43" s="30">
+      <c r="HL43" s="20">
         <v>880.19703620159896</v>
       </c>
-      <c r="HM43" s="30">
+      <c r="HM43" s="20">
         <v>2109.18799845176</v>
       </c>
-      <c r="HN43" s="30">
+      <c r="HN43" s="20">
         <v>4932.2983016542303</v>
       </c>
-      <c r="HO43" s="30">
+      <c r="HO43" s="20">
         <v>-2595.7859130034999</v>
       </c>
-      <c r="HP43" s="30">
+      <c r="HP43" s="20">
         <v>3598.89800382154</v>
       </c>
-      <c r="HQ43" s="30">
+      <c r="HQ43" s="20">
         <v>3367.5035551314299</v>
       </c>
-      <c r="HR43" s="30">
+      <c r="HR43" s="20">
         <v>1708.6467468130199</v>
       </c>
-      <c r="HS43" s="30">
+      <c r="HS43" s="20">
         <v>1540.62447646136</v>
       </c>
-      <c r="HT43" s="30">
+      <c r="HT43" s="20">
         <v>-1730.4196291781</v>
       </c>
-      <c r="HU43" s="30">
+      <c r="HU43" s="20">
         <v>-2174.6053083909001</v>
       </c>
-      <c r="HV43" s="30">
+      <c r="HV43" s="20">
         <v>-19.137787592942999</v>
       </c>
-      <c r="HW43" s="30">
+      <c r="HW43" s="20">
         <v>-553.77382030563001</v>
       </c>
-      <c r="HX43" s="30">
+      <c r="HX43" s="20">
         <v>-1206.3921973399999</v>
       </c>
-      <c r="HY43" s="30">
+      <c r="HY43" s="20">
         <v>1162.71617261344</v>
       </c>
-      <c r="HZ43" s="30">
+      <c r="HZ43" s="20">
         <v>-2230.2681606450001</v>
       </c>
-      <c r="IA43" s="30">
+      <c r="IA43" s="20">
         <v>93.900935784938596</v>
       </c>
-      <c r="IB43" s="30">
+      <c r="IB43" s="20">
         <v>-2045.3621032151</v>
       </c>
-      <c r="IC43" s="30">
+      <c r="IC43" s="20">
         <v>-2323.4686607311</v>
       </c>
-      <c r="ID43" s="30">
+      <c r="ID43" s="20">
         <v>-2655.0541050149</v>
       </c>
-      <c r="IE43" s="30">
+      <c r="IE43" s="20">
         <v>73.606745246315697</v>
       </c>
-      <c r="IF43" s="30">
+      <c r="IF43" s="20">
         <v>44.324407998723601</v>
       </c>
-      <c r="IG43" s="30">
+      <c r="IG43" s="20">
         <v>457.74093615687701</v>
       </c>
-      <c r="IH43" s="30">
+      <c r="IH43" s="20">
         <v>-354.12633401796</v>
       </c>
-      <c r="II43" s="30">
+      <c r="II43" s="20">
         <v>259.64047022095298</v>
       </c>
-      <c r="IJ43" s="30">
+      <c r="IJ43" s="20">
         <v>-236.17848457529999</v>
       </c>
-      <c r="IK43" s="30">
+      <c r="IK43" s="20">
         <v>142.90034315455799</v>
       </c>
-      <c r="IL43" s="30">
+      <c r="IL43" s="20">
         <v>99.026665024903195</v>
       </c>
-      <c r="IM43" s="30">
+      <c r="IM43" s="20">
         <v>218.05627308994201</v>
       </c>
-      <c r="IN43" s="30">
+      <c r="IN43" s="20">
         <v>835.69348272146794</v>
       </c>
-      <c r="IO43" s="30">
+      <c r="IO43" s="20">
         <v>571.20810051854801</v>
       </c>
-      <c r="IP43" s="30">
+      <c r="IP43" s="20">
         <v>778.83340397603297</v>
       </c>
-      <c r="IQ43" s="30">
+      <c r="IQ43" s="20">
         <v>1407.52751138095</v>
       </c>
-      <c r="IR43" s="30">
+      <c r="IR43" s="20">
         <v>-292.67782266940998</v>
       </c>
-      <c r="IS43" s="30">
+      <c r="IS43" s="20">
         <v>3357.9118272445899</v>
       </c>
-      <c r="IT43" s="30">
+      <c r="IT43" s="20">
         <v>33.705656762179203</v>
       </c>
-      <c r="IU43" s="30">
+      <c r="IU43" s="20">
         <v>24.1431511055107</v>
       </c>
-      <c r="IV43" s="30">
+      <c r="IV43" s="20">
         <v>-629.62500753250004</v>
       </c>
-      <c r="IW43" s="30">
+      <c r="IW43" s="20">
         <v>-1400.6848621898</v>
       </c>
-      <c r="IX43" s="30">
+      <c r="IX43" s="20">
         <v>1486.70038775997</v>
       </c>
-      <c r="IY43" s="30">
+      <c r="IY43" s="20">
         <v>-1955.4828270138</v>
       </c>
-      <c r="IZ43" s="30">
+      <c r="IZ43" s="20">
         <v>973.66785232147402</v>
       </c>
-      <c r="JA43" s="30">
+      <c r="JA43" s="20">
         <v>94.3431453500624</v>
       </c>
-      <c r="JB43" s="30">
+      <c r="JB43" s="20">
         <v>-1107.7323739668</v>
       </c>
-      <c r="JC43" s="30">
+      <c r="JC43" s="20">
         <v>-227.79080568742</v>
       </c>
-      <c r="JD43" s="30">
+      <c r="JD43" s="20">
         <v>290.86393915602503</v>
       </c>
-      <c r="JE43" s="30">
+      <c r="JE43" s="20">
         <v>-161.44146470314999</v>
       </c>
-      <c r="JF43" s="30">
+      <c r="JF43" s="20">
         <v>-198.08910227215</v>
       </c>
-      <c r="JG43" s="30">
+      <c r="JG43" s="20">
         <v>65.031576540631093</v>
       </c>
-      <c r="JH43" s="30">
+      <c r="JH43" s="20">
         <v>-121.94961046506999</v>
       </c>
-      <c r="JI43" s="30">
+      <c r="JI43" s="20">
         <v>-184.02737997209999</v>
       </c>
-      <c r="JJ43" s="30">
+      <c r="JJ43" s="20">
         <v>121.51046263933701</v>
       </c>
-      <c r="JK43" s="30">
+      <c r="JK43" s="20">
         <v>159.35798602934901</v>
       </c>
-      <c r="JL43" s="30">
+      <c r="JL43" s="20">
         <v>60.732082814104203</v>
       </c>
-      <c r="JM43" s="30">
+      <c r="JM43" s="20">
         <v>78.311586224415507</v>
       </c>
-      <c r="JN43" s="30">
+      <c r="JN43" s="20">
         <v>535.44764251350205</v>
       </c>
-      <c r="JO43" s="30">
+      <c r="JO43" s="20">
         <v>555.67682956506496</v>
       </c>
-      <c r="JP43" s="30">
+      <c r="JP43" s="20">
         <v>545.17753196399099</v>
       </c>
-      <c r="JQ43" s="30">
+      <c r="JQ43" s="20">
         <v>573.47620351407295</v>
       </c>
-      <c r="JR43" s="30">
+      <c r="JR43" s="20">
         <v>7.8068191647895997</v>
       </c>
       <c r="JS43" s="15">
         <v>978.85071295660396</v>
       </c>
+      <c r="JT43" s="15">
+        <v>470.14525037866002</v>
+      </c>
     </row>
-    <row r="44" spans="1:279" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="27" t="s">
+    <row r="44" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="28"/>
-      <c r="S44" s="28"/>
-      <c r="T44" s="28"/>
-      <c r="U44" s="28"/>
-      <c r="V44" s="28"/>
-      <c r="W44" s="28"/>
-      <c r="X44" s="28"/>
-      <c r="Y44" s="28"/>
-      <c r="Z44" s="28"/>
-      <c r="AA44" s="28"/>
-      <c r="AB44" s="28"/>
-      <c r="AC44" s="28"/>
-      <c r="AD44" s="28"/>
-      <c r="AE44" s="28"/>
-      <c r="AF44" s="28"/>
-      <c r="AG44" s="28"/>
-      <c r="AH44" s="28"/>
-      <c r="AI44" s="28"/>
-      <c r="AJ44" s="28"/>
-      <c r="AK44" s="28"/>
-      <c r="AL44" s="28"/>
-      <c r="AM44" s="28"/>
-      <c r="AN44" s="28"/>
-      <c r="AO44" s="28"/>
-      <c r="AP44" s="28"/>
-      <c r="AQ44" s="28"/>
-      <c r="AR44" s="28"/>
-      <c r="AS44" s="28"/>
-      <c r="AT44" s="28"/>
-      <c r="AU44" s="28"/>
-      <c r="AV44" s="28"/>
-      <c r="AW44" s="28"/>
-      <c r="AX44" s="28"/>
-      <c r="AY44" s="28"/>
-      <c r="AZ44" s="28"/>
-      <c r="BA44" s="28"/>
-      <c r="BB44" s="28"/>
-      <c r="BC44" s="28"/>
-      <c r="BD44" s="28"/>
-      <c r="BE44" s="28"/>
-      <c r="BF44" s="28"/>
-      <c r="BG44" s="28"/>
-      <c r="BH44" s="28"/>
-      <c r="BI44" s="28"/>
-      <c r="BJ44" s="28"/>
-      <c r="BK44" s="28"/>
-      <c r="BL44" s="28"/>
-      <c r="BM44" s="28"/>
-      <c r="BN44" s="28"/>
-      <c r="BO44" s="28"/>
-      <c r="BP44" s="28"/>
-      <c r="BQ44" s="28"/>
-      <c r="BR44" s="28"/>
-      <c r="BS44" s="28"/>
-      <c r="BT44" s="28"/>
-      <c r="BU44" s="28"/>
-      <c r="BV44" s="28"/>
-      <c r="BW44" s="28"/>
-      <c r="BX44" s="28"/>
-      <c r="BY44" s="28"/>
-      <c r="BZ44" s="28"/>
-      <c r="CA44" s="28"/>
-      <c r="CB44" s="28"/>
-      <c r="CC44" s="28"/>
-      <c r="CD44" s="28"/>
-      <c r="CE44" s="28"/>
-      <c r="CF44" s="28"/>
-      <c r="CG44" s="28"/>
-      <c r="CH44" s="28"/>
-      <c r="CI44" s="28"/>
-      <c r="CJ44" s="28"/>
-      <c r="CK44" s="28"/>
-      <c r="CL44" s="28"/>
-      <c r="CM44" s="28"/>
-      <c r="CN44" s="28"/>
-      <c r="CO44" s="28"/>
-      <c r="CP44" s="28"/>
-      <c r="CQ44" s="28"/>
-      <c r="CR44" s="28"/>
-      <c r="CS44" s="28"/>
-      <c r="CT44" s="28"/>
-      <c r="CU44" s="28"/>
-      <c r="CV44" s="28"/>
-      <c r="CW44" s="28"/>
-      <c r="CX44" s="28"/>
-      <c r="CY44" s="28"/>
-      <c r="CZ44" s="28"/>
-      <c r="DA44" s="28"/>
-      <c r="DB44" s="28"/>
-      <c r="DC44" s="28"/>
-      <c r="DD44" s="28"/>
-      <c r="DE44" s="28"/>
-      <c r="DF44" s="28"/>
-      <c r="DG44" s="28"/>
-      <c r="DH44" s="28"/>
-      <c r="DI44" s="28"/>
-      <c r="DJ44" s="28"/>
-      <c r="DK44" s="28"/>
-      <c r="DL44" s="28"/>
-      <c r="DM44" s="28"/>
-      <c r="DN44" s="28"/>
-      <c r="DO44" s="28"/>
-      <c r="DP44" s="28"/>
-      <c r="DQ44" s="28"/>
-      <c r="DR44" s="28"/>
-      <c r="DS44" s="28"/>
-      <c r="DT44" s="28"/>
-      <c r="DU44" s="28"/>
-      <c r="DV44" s="28"/>
-      <c r="DW44" s="28"/>
-      <c r="DX44" s="28"/>
-      <c r="DY44" s="28"/>
-      <c r="DZ44" s="28"/>
-      <c r="EA44" s="28"/>
-      <c r="EB44" s="28"/>
-      <c r="EC44" s="28"/>
-      <c r="ED44" s="28"/>
-      <c r="EE44" s="28"/>
-      <c r="EF44" s="28"/>
-      <c r="EG44" s="28"/>
-      <c r="EH44" s="28"/>
-      <c r="EI44" s="28"/>
-      <c r="EJ44" s="28"/>
-      <c r="EK44" s="28"/>
-      <c r="EL44" s="28"/>
-      <c r="EM44" s="28"/>
-      <c r="EN44" s="28"/>
-      <c r="EO44" s="28"/>
-      <c r="EP44" s="28"/>
-      <c r="EQ44" s="28"/>
-      <c r="ER44" s="28"/>
-      <c r="ES44" s="28"/>
-      <c r="ET44" s="28"/>
-      <c r="EU44" s="28"/>
-      <c r="EV44" s="28"/>
-      <c r="EW44" s="28"/>
-      <c r="EX44" s="28"/>
-      <c r="EY44" s="28"/>
-      <c r="EZ44" s="28"/>
-      <c r="FA44" s="28"/>
-      <c r="FB44" s="28"/>
-      <c r="FC44" s="28"/>
-      <c r="FD44" s="28"/>
-      <c r="FE44" s="28"/>
-      <c r="FF44" s="28"/>
-      <c r="FG44" s="28"/>
-      <c r="FH44" s="28"/>
-      <c r="FI44" s="28"/>
-      <c r="FJ44" s="28"/>
-      <c r="FK44" s="28"/>
-      <c r="FL44" s="28"/>
-      <c r="FM44" s="28"/>
-      <c r="FN44" s="28"/>
-      <c r="FO44" s="28"/>
-      <c r="FP44" s="28"/>
-      <c r="FQ44" s="28"/>
-      <c r="FR44" s="28"/>
-      <c r="FS44" s="28"/>
-      <c r="FT44" s="28"/>
-      <c r="FU44" s="28"/>
-      <c r="FV44" s="28"/>
-      <c r="FW44" s="28"/>
-      <c r="FX44" s="28"/>
-      <c r="FY44" s="28"/>
-      <c r="FZ44" s="28"/>
-      <c r="GA44" s="28"/>
-      <c r="GB44" s="28"/>
-      <c r="GC44" s="28"/>
-      <c r="GD44" s="28"/>
-      <c r="GE44" s="28"/>
-      <c r="GF44" s="28"/>
-      <c r="GG44" s="28"/>
-      <c r="GH44" s="28"/>
-      <c r="GI44" s="28"/>
-      <c r="GJ44" s="28"/>
-      <c r="GK44" s="28"/>
-      <c r="GL44" s="28"/>
-      <c r="GM44" s="28"/>
-      <c r="GN44" s="28"/>
-      <c r="GO44" s="28"/>
-      <c r="GP44" s="28"/>
-      <c r="GQ44" s="28"/>
-      <c r="GR44" s="28"/>
-      <c r="GS44" s="28"/>
-      <c r="GT44" s="28"/>
-      <c r="GU44" s="28"/>
-      <c r="GV44" s="28"/>
-      <c r="GW44" s="28"/>
-      <c r="GX44" s="28"/>
-      <c r="GY44" s="28"/>
-      <c r="GZ44" s="28"/>
-      <c r="HA44" s="28"/>
-      <c r="HB44" s="28"/>
-      <c r="HC44" s="28"/>
-      <c r="HD44" s="28"/>
-      <c r="HE44" s="28"/>
-      <c r="HF44" s="28"/>
-      <c r="HG44" s="28"/>
-      <c r="HH44" s="28"/>
-      <c r="HI44" s="28"/>
-      <c r="HJ44" s="28"/>
-      <c r="HK44" s="28"/>
-      <c r="HL44" s="28"/>
-      <c r="HM44" s="28"/>
-      <c r="HN44" s="28"/>
-      <c r="HO44" s="28"/>
-      <c r="HP44" s="28"/>
-      <c r="HQ44" s="28"/>
-      <c r="HR44" s="28"/>
-      <c r="HS44" s="28"/>
-      <c r="HT44" s="28"/>
-      <c r="HU44" s="28"/>
-      <c r="HV44" s="28"/>
-      <c r="HW44" s="28"/>
-      <c r="HX44" s="28"/>
-      <c r="HY44" s="28"/>
-      <c r="HZ44" s="28"/>
-      <c r="IA44" s="28"/>
-      <c r="IB44" s="28"/>
-      <c r="IC44" s="28"/>
-      <c r="ID44" s="28"/>
-      <c r="IE44" s="28"/>
-      <c r="IF44" s="28"/>
-      <c r="IG44" s="28"/>
-      <c r="IH44" s="28"/>
-      <c r="II44" s="28"/>
-      <c r="IJ44" s="28"/>
-      <c r="IK44" s="28"/>
-      <c r="IL44" s="28"/>
-      <c r="IM44" s="28"/>
-      <c r="IN44" s="28"/>
-      <c r="IO44" s="28"/>
-      <c r="IP44" s="28"/>
-      <c r="IQ44" s="28"/>
-      <c r="IR44" s="28"/>
-      <c r="IS44" s="28"/>
-      <c r="IT44" s="28"/>
-      <c r="IU44" s="28"/>
-      <c r="IV44" s="28"/>
-      <c r="IW44" s="28"/>
-      <c r="IX44" s="28"/>
-      <c r="IY44" s="28"/>
-      <c r="IZ44" s="28"/>
-      <c r="JA44" s="28"/>
-      <c r="JB44" s="28"/>
-      <c r="JC44" s="28"/>
-      <c r="JD44" s="28"/>
-      <c r="JE44" s="28"/>
-      <c r="JF44" s="28"/>
-      <c r="JG44" s="28"/>
-      <c r="JH44" s="28"/>
-      <c r="JI44" s="28"/>
-      <c r="JJ44" s="28"/>
-      <c r="JK44" s="28"/>
-      <c r="JL44" s="28"/>
-      <c r="JM44" s="28"/>
-      <c r="JN44" s="28"/>
-      <c r="JO44" s="28"/>
-      <c r="JP44" s="28"/>
-      <c r="JQ44" s="28"/>
-      <c r="JR44" s="28"/>
-      <c r="JS44" s="28"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="33"/>
+      <c r="N44" s="33"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="33"/>
+      <c r="V44" s="33"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="33"/>
+      <c r="Y44" s="33"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
+      <c r="AB44" s="33"/>
+      <c r="AC44" s="33"/>
+      <c r="AD44" s="33"/>
+      <c r="AE44" s="33"/>
+      <c r="AF44" s="33"/>
+      <c r="AG44" s="33"/>
+      <c r="AH44" s="33"/>
+      <c r="AI44" s="33"/>
+      <c r="AJ44" s="33"/>
+      <c r="AK44" s="33"/>
+      <c r="AL44" s="33"/>
+      <c r="AM44" s="33"/>
+      <c r="AN44" s="33"/>
+      <c r="AO44" s="33"/>
+      <c r="AP44" s="33"/>
+      <c r="AQ44" s="33"/>
+      <c r="AR44" s="33"/>
+      <c r="AS44" s="33"/>
+      <c r="AT44" s="33"/>
+      <c r="AU44" s="33"/>
+      <c r="AV44" s="33"/>
+      <c r="AW44" s="33"/>
+      <c r="AX44" s="33"/>
+      <c r="AY44" s="33"/>
+      <c r="AZ44" s="33"/>
+      <c r="BA44" s="33"/>
+      <c r="BB44" s="33"/>
+      <c r="BC44" s="33"/>
+      <c r="BD44" s="33"/>
+      <c r="BE44" s="33"/>
+      <c r="BF44" s="33"/>
+      <c r="BG44" s="33"/>
+      <c r="BH44" s="33"/>
+      <c r="BI44" s="33"/>
+      <c r="BJ44" s="33"/>
+      <c r="BK44" s="33"/>
+      <c r="BL44" s="33"/>
+      <c r="BM44" s="33"/>
+      <c r="BN44" s="33"/>
+      <c r="BO44" s="33"/>
+      <c r="BP44" s="33"/>
+      <c r="BQ44" s="33"/>
+      <c r="BR44" s="33"/>
+      <c r="BS44" s="33"/>
+      <c r="BT44" s="33"/>
+      <c r="BU44" s="33"/>
+      <c r="BV44" s="33"/>
+      <c r="BW44" s="33"/>
+      <c r="BX44" s="33"/>
+      <c r="BY44" s="33"/>
+      <c r="BZ44" s="33"/>
+      <c r="CA44" s="33"/>
+      <c r="CB44" s="33"/>
+      <c r="CC44" s="33"/>
+      <c r="CD44" s="33"/>
+      <c r="CE44" s="33"/>
+      <c r="CF44" s="33"/>
+      <c r="CG44" s="33"/>
+      <c r="CH44" s="33"/>
+      <c r="CI44" s="33"/>
+      <c r="CJ44" s="33"/>
+      <c r="CK44" s="33"/>
+      <c r="CL44" s="33"/>
+      <c r="CM44" s="33"/>
+      <c r="CN44" s="33"/>
+      <c r="CO44" s="33"/>
+      <c r="CP44" s="33"/>
+      <c r="CQ44" s="33"/>
+      <c r="CR44" s="33"/>
+      <c r="CS44" s="33"/>
+      <c r="CT44" s="33"/>
+      <c r="CU44" s="33"/>
+      <c r="CV44" s="33"/>
+      <c r="CW44" s="33"/>
+      <c r="CX44" s="33"/>
+      <c r="CY44" s="33"/>
+      <c r="CZ44" s="33"/>
+      <c r="DA44" s="33"/>
+      <c r="DB44" s="33"/>
+      <c r="DC44" s="33"/>
+      <c r="DD44" s="33"/>
+      <c r="DE44" s="33"/>
+      <c r="DF44" s="33"/>
+      <c r="DG44" s="33"/>
+      <c r="DH44" s="33"/>
+      <c r="DI44" s="33"/>
+      <c r="DJ44" s="33"/>
+      <c r="DK44" s="33"/>
+      <c r="DL44" s="33"/>
+      <c r="DM44" s="33"/>
+      <c r="DN44" s="33"/>
+      <c r="DO44" s="33"/>
+      <c r="DP44" s="33"/>
+      <c r="DQ44" s="33"/>
+      <c r="DR44" s="33"/>
+      <c r="DS44" s="33"/>
+      <c r="DT44" s="33"/>
+      <c r="DU44" s="33"/>
+      <c r="DV44" s="33"/>
+      <c r="DW44" s="33"/>
+      <c r="DX44" s="33"/>
+      <c r="DY44" s="33"/>
+      <c r="DZ44" s="33"/>
+      <c r="EA44" s="33"/>
+      <c r="EB44" s="33"/>
+      <c r="EC44" s="33"/>
+      <c r="ED44" s="33"/>
+      <c r="EE44" s="33"/>
+      <c r="EF44" s="33"/>
+      <c r="EG44" s="33"/>
+      <c r="EH44" s="33"/>
+      <c r="EI44" s="33"/>
+      <c r="EJ44" s="33"/>
+      <c r="EK44" s="33"/>
+      <c r="EL44" s="33"/>
+      <c r="EM44" s="33"/>
+      <c r="EN44" s="33"/>
+      <c r="EO44" s="33"/>
+      <c r="EP44" s="33"/>
+      <c r="EQ44" s="33"/>
+      <c r="ER44" s="33"/>
+      <c r="ES44" s="33"/>
+      <c r="ET44" s="33"/>
+      <c r="EU44" s="33"/>
+      <c r="EV44" s="33"/>
+      <c r="EW44" s="33"/>
+      <c r="EX44" s="33"/>
+      <c r="EY44" s="33"/>
+      <c r="EZ44" s="33"/>
+      <c r="FA44" s="33"/>
+      <c r="FB44" s="33"/>
+      <c r="FC44" s="33"/>
+      <c r="FD44" s="33"/>
+      <c r="FE44" s="33"/>
+      <c r="FF44" s="33"/>
+      <c r="FG44" s="33"/>
+      <c r="FH44" s="33"/>
+      <c r="FI44" s="33"/>
+      <c r="FJ44" s="33"/>
+      <c r="FK44" s="33"/>
+      <c r="FL44" s="33"/>
+      <c r="FM44" s="33"/>
+      <c r="FN44" s="33"/>
+      <c r="FO44" s="33"/>
+      <c r="FP44" s="33"/>
+      <c r="FQ44" s="33"/>
+      <c r="FR44" s="33"/>
+      <c r="FS44" s="33"/>
+      <c r="FT44" s="33"/>
+      <c r="FU44" s="33"/>
+      <c r="FV44" s="33"/>
+      <c r="FW44" s="33"/>
+      <c r="FX44" s="33"/>
+      <c r="FY44" s="33"/>
+      <c r="FZ44" s="33"/>
+      <c r="GA44" s="33"/>
+      <c r="GB44" s="33"/>
+      <c r="GC44" s="33"/>
+      <c r="GD44" s="33"/>
+      <c r="GE44" s="33"/>
+      <c r="GF44" s="33"/>
+      <c r="GG44" s="33"/>
+      <c r="GH44" s="33"/>
+      <c r="GI44" s="33"/>
+      <c r="GJ44" s="33"/>
+      <c r="GK44" s="33"/>
+      <c r="GL44" s="33"/>
+      <c r="GM44" s="33"/>
+      <c r="GN44" s="33"/>
+      <c r="GO44" s="33"/>
+      <c r="GP44" s="33"/>
+      <c r="GQ44" s="33"/>
+      <c r="GR44" s="33"/>
+      <c r="GS44" s="33"/>
+      <c r="GT44" s="33"/>
+      <c r="GU44" s="33"/>
+      <c r="GV44" s="33"/>
+      <c r="GW44" s="33"/>
+      <c r="GX44" s="33"/>
+      <c r="GY44" s="33"/>
+      <c r="GZ44" s="33"/>
+      <c r="HA44" s="33"/>
+      <c r="HB44" s="33"/>
+      <c r="HC44" s="33"/>
+      <c r="HD44" s="33"/>
+      <c r="HE44" s="33"/>
+      <c r="HF44" s="33"/>
+      <c r="HG44" s="33"/>
+      <c r="HH44" s="33"/>
+      <c r="HI44" s="33"/>
+      <c r="HJ44" s="33"/>
+      <c r="HK44" s="33"/>
+      <c r="HL44" s="33"/>
+      <c r="HM44" s="33"/>
+      <c r="HN44" s="33"/>
+      <c r="HO44" s="33"/>
+      <c r="HP44" s="33"/>
+      <c r="HQ44" s="33"/>
+      <c r="HR44" s="33"/>
+      <c r="HS44" s="33"/>
+      <c r="HT44" s="33"/>
+      <c r="HU44" s="33"/>
+      <c r="HV44" s="33"/>
+      <c r="HW44" s="33"/>
+      <c r="HX44" s="33"/>
+      <c r="HY44" s="33"/>
+      <c r="HZ44" s="33"/>
+      <c r="IA44" s="33"/>
+      <c r="IB44" s="33"/>
+      <c r="IC44" s="33"/>
+      <c r="ID44" s="33"/>
+      <c r="IE44" s="33"/>
+      <c r="IF44" s="33"/>
+      <c r="IG44" s="33"/>
+      <c r="IH44" s="33"/>
+      <c r="II44" s="33"/>
+      <c r="IJ44" s="33"/>
+      <c r="IK44" s="33"/>
+      <c r="IL44" s="33"/>
+      <c r="IM44" s="33"/>
+      <c r="IN44" s="33"/>
+      <c r="IO44" s="33"/>
+      <c r="IP44" s="33"/>
+      <c r="IQ44" s="33"/>
+      <c r="IR44" s="33"/>
+      <c r="IS44" s="33"/>
+      <c r="IT44" s="33"/>
+      <c r="IU44" s="33"/>
+      <c r="IV44" s="33"/>
+      <c r="IW44" s="33"/>
+      <c r="IX44" s="33"/>
+      <c r="IY44" s="33"/>
+      <c r="IZ44" s="33"/>
+      <c r="JA44" s="33"/>
+      <c r="JB44" s="33"/>
+      <c r="JC44" s="33"/>
+      <c r="JD44" s="33"/>
+      <c r="JE44" s="33"/>
+      <c r="JF44" s="33"/>
+      <c r="JG44" s="33"/>
+      <c r="JH44" s="33"/>
+      <c r="JI44" s="33"/>
+      <c r="JJ44" s="33"/>
+      <c r="JK44" s="33"/>
+      <c r="JL44" s="33"/>
+      <c r="JM44" s="33"/>
+      <c r="JN44" s="33"/>
+      <c r="JO44" s="33"/>
+      <c r="JP44" s="33"/>
+      <c r="JQ44" s="33"/>
+      <c r="JR44" s="33"/>
+      <c r="JS44" s="33"/>
+      <c r="JT44" s="1"/>
     </row>
-    <row r="45" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="31" t="s">
+    <row r="45" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="22">
         <v>-2135.7758514912998</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="22">
         <v>398.25612861667298</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="22">
         <v>947.27088880982399</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="22">
         <v>681.351934558327</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="22">
         <v>836.96074273269596</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="22">
         <v>476.46627794621702</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="22">
         <v>-194.84810975277</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="22">
         <v>-103.05784520947</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="22">
         <v>-394.80964874558998</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="22">
         <v>133.043229745264</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="22">
         <v>50.957260046182</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="22">
         <v>601.57816674276</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="22">
         <v>455.91244685532502</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="22">
         <v>648.51269373597097</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="22">
         <v>530.21197347140196</v>
       </c>
-      <c r="Q45" s="32">
+      <c r="Q45" s="22">
         <v>363.21654150979799</v>
       </c>
-      <c r="R45" s="32">
+      <c r="R45" s="22">
         <v>494.61950173301602</v>
       </c>
-      <c r="S45" s="32">
+      <c r="S45" s="22">
         <v>436.51474956345203</v>
       </c>
-      <c r="T45" s="32">
+      <c r="T45" s="22">
         <v>-114.02022134169</v>
       </c>
-      <c r="U45" s="32">
+      <c r="U45" s="22">
         <v>-77.795148042498994</v>
       </c>
-      <c r="V45" s="32">
+      <c r="V45" s="22">
         <v>-824.56346078334002</v>
       </c>
-      <c r="W45" s="32">
+      <c r="W45" s="22">
         <v>588.46899822024602</v>
       </c>
-      <c r="X45" s="32">
+      <c r="X45" s="22">
         <v>-178.25772814048</v>
       </c>
-      <c r="Y45" s="32">
+      <c r="Y45" s="22">
         <v>1372.29181906607</v>
       </c>
-      <c r="Z45" s="32">
+      <c r="Z45" s="22">
         <v>19.808068948841601</v>
       </c>
-      <c r="AA45" s="32">
+      <c r="AA45" s="22">
         <v>10.319023331798</v>
       </c>
-      <c r="AB45" s="32">
+      <c r="AB45" s="22">
         <v>257.70622758189501</v>
       </c>
-      <c r="AC45" s="32">
+      <c r="AC45" s="22">
         <v>-714.50273577985001</v>
       </c>
-      <c r="AD45" s="32">
+      <c r="AD45" s="22">
         <v>-1049.6481026336</v>
       </c>
-      <c r="AE45" s="32">
+      <c r="AE45" s="22">
         <v>195.894616346655</v>
       </c>
-      <c r="AF45" s="32">
+      <c r="AF45" s="22">
         <v>-85.007863330411993</v>
       </c>
-      <c r="AG45" s="32">
+      <c r="AG45" s="22">
         <v>381.23729626616699</v>
       </c>
-      <c r="AH45" s="32">
+      <c r="AH45" s="22">
         <v>780.84462529838402</v>
       </c>
-      <c r="AI45" s="32">
+      <c r="AI45" s="22">
         <v>1186.8226552082699</v>
       </c>
-      <c r="AJ45" s="32">
+      <c r="AJ45" s="22">
         <v>-769.54124507519998</v>
       </c>
-      <c r="AK45" s="32">
+      <c r="AK45" s="22">
         <v>-250.23323867504001</v>
       </c>
-      <c r="AL45" s="32">
+      <c r="AL45" s="22">
         <v>2120.64737723813</v>
       </c>
-      <c r="AM45" s="32">
+      <c r="AM45" s="22">
         <v>-846.41552423830001</v>
       </c>
-      <c r="AN45" s="32">
+      <c r="AN45" s="22">
         <v>556.57077464576003</v>
       </c>
-      <c r="AO45" s="32">
+      <c r="AO45" s="22">
         <v>-134.84717931579999</v>
       </c>
-      <c r="AP45" s="32">
+      <c r="AP45" s="22">
         <v>1657.27959351956</v>
       </c>
-      <c r="AQ45" s="32">
+      <c r="AQ45" s="22">
         <v>588.73850004644396</v>
       </c>
-      <c r="AR45" s="32">
+      <c r="AR45" s="22">
         <v>2691.2147787326498</v>
       </c>
-      <c r="AS45" s="32">
+      <c r="AS45" s="22">
         <v>-36.024774502546002</v>
       </c>
-      <c r="AT45" s="32">
+      <c r="AT45" s="22">
         <v>-494.89998704508997</v>
       </c>
-      <c r="AU45" s="32">
+      <c r="AU45" s="22">
         <v>1172.2876403975599</v>
       </c>
-      <c r="AV45" s="32">
+      <c r="AV45" s="22">
         <v>2816.4882227606199</v>
       </c>
-      <c r="AW45" s="32">
+      <c r="AW45" s="22">
         <v>-2048.6156328697998</v>
       </c>
-      <c r="AX45" s="32">
+      <c r="AX45" s="22">
         <v>5300.2941780715</v>
       </c>
-      <c r="AY45" s="32">
+      <c r="AY45" s="22">
         <v>1863.9674423808301</v>
       </c>
-      <c r="AZ45" s="32">
+      <c r="AZ45" s="22">
         <v>-689.90775470129995</v>
       </c>
-      <c r="BA45" s="32">
+      <c r="BA45" s="22">
         <v>-17.615070984037001</v>
       </c>
-      <c r="BB45" s="32">
+      <c r="BB45" s="22">
         <v>2548.7629054634199</v>
       </c>
-      <c r="BC45" s="32">
+      <c r="BC45" s="22">
         <v>-2379.3602493612998</v>
       </c>
-      <c r="BD45" s="32">
+      <c r="BD45" s="22">
         <v>1653.24861233511</v>
       </c>
-      <c r="BE45" s="32">
+      <c r="BE45" s="22">
         <v>2326.1321922654802</v>
       </c>
-      <c r="BF45" s="32">
+      <c r="BF45" s="22">
         <v>82.094573972245499</v>
       </c>
-      <c r="BG45" s="32">
+      <c r="BG45" s="22">
         <v>1999.7583393699199</v>
       </c>
-      <c r="BH45" s="32">
+      <c r="BH45" s="22">
         <v>1911.7495056612399</v>
       </c>
-      <c r="BI45" s="32">
+      <c r="BI45" s="22">
         <v>-3006.7767288847999</v>
       </c>
-      <c r="BJ45" s="32">
+      <c r="BJ45" s="22">
         <v>1756.33406947407</v>
       </c>
-      <c r="BK45" s="32">
+      <c r="BK45" s="22">
         <v>-592.79292225869995</v>
       </c>
-      <c r="BL45" s="32">
+      <c r="BL45" s="22">
         <v>953.43686872407295</v>
       </c>
-      <c r="BM45" s="32">
+      <c r="BM45" s="22">
         <v>2801.0753354668</v>
       </c>
-      <c r="BN45" s="32">
+      <c r="BN45" s="22">
         <v>-177.39018155986</v>
       </c>
-      <c r="BO45" s="32">
+      <c r="BO45" s="22">
         <v>-3928.6415145541</v>
       </c>
-      <c r="BP45" s="32">
+      <c r="BP45" s="22">
         <v>-1677.5642251593999</v>
       </c>
-      <c r="BQ45" s="32">
+      <c r="BQ45" s="22">
         <v>-1032.1330813658001</v>
       </c>
-      <c r="BR45" s="32">
+      <c r="BR45" s="22">
         <v>-5062.5634912504001</v>
       </c>
-      <c r="BS45" s="32">
+      <c r="BS45" s="22">
         <v>-1557.4942787752</v>
       </c>
-      <c r="BT45" s="32">
+      <c r="BT45" s="22">
         <v>-697.13291928860997</v>
       </c>
-      <c r="BU45" s="32">
+      <c r="BU45" s="22">
         <v>-1978.8813723998001</v>
       </c>
-      <c r="BV45" s="32">
+      <c r="BV45" s="22">
         <v>-513.13297089498997</v>
       </c>
-      <c r="BW45" s="32">
+      <c r="BW45" s="22">
         <v>695.90073066352295</v>
       </c>
-      <c r="BX45" s="32">
+      <c r="BX45" s="22">
         <v>-662.19860442920003</v>
       </c>
-      <c r="BY45" s="32">
+      <c r="BY45" s="22">
         <v>495.12900178515599</v>
       </c>
-      <c r="BZ45" s="32">
+      <c r="BZ45" s="22">
         <v>1238.7503342136699</v>
       </c>
-      <c r="CA45" s="32">
+      <c r="CA45" s="22">
         <v>278.48868788662998</v>
       </c>
-      <c r="CB45" s="32">
+      <c r="CB45" s="22">
         <v>-119.69804788795</v>
       </c>
-      <c r="CC45" s="32">
+      <c r="CC45" s="22">
         <v>-370.64065473677999</v>
       </c>
-      <c r="CD45" s="32">
+      <c r="CD45" s="22">
         <v>-1368.6919549938</v>
       </c>
-      <c r="CE45" s="32">
+      <c r="CE45" s="22">
         <v>371.91790509533598</v>
       </c>
-      <c r="CF45" s="32">
+      <c r="CF45" s="22">
         <v>727.40790939038004</v>
       </c>
-      <c r="CG45" s="32">
+      <c r="CG45" s="22">
         <v>-32.945420741969002</v>
       </c>
-      <c r="CH45" s="32">
+      <c r="CH45" s="22">
         <v>1132.7289536256001</v>
       </c>
-      <c r="CI45" s="32">
+      <c r="CI45" s="22">
         <v>7054.0230177930498</v>
       </c>
-      <c r="CJ45" s="32">
+      <c r="CJ45" s="22">
         <v>-1468.5987328951001</v>
       </c>
-      <c r="CK45" s="32">
+      <c r="CK45" s="22">
         <v>808.20157042145001</v>
       </c>
-      <c r="CL45" s="32">
+      <c r="CL45" s="22">
         <v>308.38709423052001</v>
       </c>
-      <c r="CM45" s="32">
+      <c r="CM45" s="22">
         <v>-2112.4294465103999</v>
       </c>
-      <c r="CN45" s="32">
+      <c r="CN45" s="22">
         <v>454.66684950784401</v>
       </c>
-      <c r="CO45" s="32">
+      <c r="CO45" s="22">
         <v>-29.614848898841998</v>
       </c>
-      <c r="CP45" s="32">
+      <c r="CP45" s="22">
         <v>-818.62682948583995</v>
       </c>
-      <c r="CQ45" s="32">
+      <c r="CQ45" s="22">
         <v>214.84506658752201</v>
       </c>
-      <c r="CR45" s="32">
+      <c r="CR45" s="22">
         <v>1658.5760660777601</v>
       </c>
-      <c r="CS45" s="32">
+      <c r="CS45" s="22">
         <v>-2738.5255905140002</v>
       </c>
-      <c r="CT45" s="32">
+      <c r="CT45" s="22">
         <v>1629.7050253749301</v>
       </c>
-      <c r="CU45" s="32">
+      <c r="CU45" s="22">
         <v>-1407.2164376306</v>
       </c>
-      <c r="CV45" s="32">
+      <c r="CV45" s="22">
         <v>-3084.4931398937001</v>
       </c>
-      <c r="CW45" s="32">
+      <c r="CW45" s="22">
         <v>2820.88172258646</v>
       </c>
-      <c r="CX45" s="32">
+      <c r="CX45" s="22">
         <v>-130.10058524734001</v>
       </c>
-      <c r="CY45" s="32">
+      <c r="CY45" s="22">
         <v>-6693.9297706889001</v>
       </c>
-      <c r="CZ45" s="32">
+      <c r="CZ45" s="22">
         <v>-1552.0320069649999</v>
       </c>
-      <c r="DA45" s="32">
+      <c r="DA45" s="22">
         <v>-3585.4941762829999</v>
       </c>
-      <c r="DB45" s="32">
+      <c r="DB45" s="22">
         <v>-4172.5043700140995</v>
       </c>
-      <c r="DC45" s="32">
+      <c r="DC45" s="22">
         <v>-1210.7530306358999</v>
       </c>
-      <c r="DD45" s="32">
+      <c r="DD45" s="22">
         <v>3165.2853762278</v>
       </c>
-      <c r="DE45" s="32">
+      <c r="DE45" s="22">
         <v>-9065.9540911222994</v>
       </c>
-      <c r="DF45" s="32">
+      <c r="DF45" s="22">
         <v>3030.39104417005</v>
       </c>
-      <c r="DG45" s="32">
+      <c r="DG45" s="22">
         <v>-1728.0739619408</v>
       </c>
-      <c r="DH45" s="32">
+      <c r="DH45" s="22">
         <v>234.947686302493</v>
       </c>
-      <c r="DI45" s="32">
+      <c r="DI45" s="22">
         <v>768.91164112564195</v>
       </c>
-      <c r="DJ45" s="32">
+      <c r="DJ45" s="22">
         <v>-1957.3607735200001</v>
       </c>
-      <c r="DK45" s="32">
+      <c r="DK45" s="22">
         <v>-5675.7433553250003</v>
       </c>
-      <c r="DL45" s="32">
+      <c r="DL45" s="22">
         <v>2128.69726514681</v>
       </c>
-      <c r="DM45" s="32">
+      <c r="DM45" s="22">
         <v>-6687.2948994100998</v>
       </c>
-      <c r="DN45" s="32">
+      <c r="DN45" s="22">
         <v>599.88201428780405</v>
       </c>
-      <c r="DO45" s="32">
+      <c r="DO45" s="22">
         <v>-1844.1932073738999</v>
       </c>
-      <c r="DP45" s="32">
+      <c r="DP45" s="22">
         <v>3919.6809079065501</v>
       </c>
-      <c r="DQ45" s="32">
+      <c r="DQ45" s="22">
         <v>-7630.1815224347001</v>
       </c>
-      <c r="DR45" s="32">
+      <c r="DR45" s="22">
         <v>1308.98439999738</v>
       </c>
-      <c r="DS45" s="32">
+      <c r="DS45" s="22">
         <v>-1056.0962745664001</v>
       </c>
-      <c r="DT45" s="32">
+      <c r="DT45" s="22">
         <v>-560.33997462968</v>
       </c>
-      <c r="DU45" s="32">
+      <c r="DU45" s="22">
         <v>-1445.4051883138</v>
       </c>
-      <c r="DV45" s="32">
+      <c r="DV45" s="22">
         <v>294.38083120815099</v>
       </c>
-      <c r="DW45" s="32">
+      <c r="DW45" s="22">
         <v>-4566.0397711645001</v>
       </c>
-      <c r="DX45" s="32">
+      <c r="DX45" s="22">
         <v>-3272.7940748637998</v>
       </c>
-      <c r="DY45" s="32">
+      <c r="DY45" s="22">
         <v>-2281.2972935337002</v>
       </c>
-      <c r="DZ45" s="32">
+      <c r="DZ45" s="22">
         <v>-525.46180380844999</v>
       </c>
-      <c r="EA45" s="32">
+      <c r="EA45" s="22">
         <v>2435.71097731288</v>
       </c>
-      <c r="EB45" s="32">
+      <c r="EB45" s="22">
         <v>1026.26252974095</v>
       </c>
-      <c r="EC45" s="32">
+      <c r="EC45" s="22">
         <v>-5203.9754307488001</v>
       </c>
-      <c r="ED45" s="32">
+      <c r="ED45" s="22">
         <v>-752.86175182978002</v>
       </c>
-      <c r="EE45" s="32">
+      <c r="EE45" s="22">
         <v>-2043.6101115255999</v>
       </c>
-      <c r="EF45" s="32">
+      <c r="EF45" s="22">
         <v>1190.3234697658099</v>
       </c>
-      <c r="EG45" s="32">
+      <c r="EG45" s="22">
         <v>837.92959794628996</v>
       </c>
-      <c r="EH45" s="32">
+      <c r="EH45" s="22">
         <v>-1057.0669465532001</v>
       </c>
-      <c r="EI45" s="32">
+      <c r="EI45" s="22">
         <v>-2080.3902572457</v>
       </c>
-      <c r="EJ45" s="32">
+      <c r="EJ45" s="22">
         <v>-2016.7701496088</v>
       </c>
-      <c r="EK45" s="32">
+      <c r="EK45" s="22">
         <v>-1677.443884025</v>
       </c>
-      <c r="EL45" s="32">
+      <c r="EL45" s="22">
         <v>146.426399909726</v>
       </c>
-      <c r="EM45" s="32">
+      <c r="EM45" s="22">
         <v>-185.24638300913</v>
       </c>
-      <c r="EN45" s="32">
+      <c r="EN45" s="22">
         <v>860.79139404754505</v>
       </c>
-      <c r="EO45" s="32">
+      <c r="EO45" s="22">
         <v>-3621.5281707109998</v>
       </c>
-      <c r="EP45" s="32">
+      <c r="EP45" s="22">
         <v>1448.3478027409799</v>
       </c>
-      <c r="EQ45" s="32">
+      <c r="EQ45" s="22">
         <v>1119.9004675056999</v>
       </c>
-      <c r="ER45" s="32">
+      <c r="ER45" s="22">
         <v>48.262056171193301</v>
       </c>
-      <c r="ES45" s="32">
+      <c r="ES45" s="22">
         <v>1514.0538268783801</v>
       </c>
-      <c r="ET45" s="32">
+      <c r="ET45" s="22">
         <v>-2537.3846201020001</v>
       </c>
-      <c r="EU45" s="32">
+      <c r="EU45" s="22">
         <v>359.88997345668298</v>
       </c>
-      <c r="EV45" s="32">
+      <c r="EV45" s="22">
         <v>-3108.253612645</v>
       </c>
-      <c r="EW45" s="32">
+      <c r="EW45" s="22">
         <v>-1852.1258300259001</v>
       </c>
-      <c r="EX45" s="32">
+      <c r="EX45" s="22">
         <v>1756.01466988722</v>
       </c>
-      <c r="EY45" s="32">
+      <c r="EY45" s="22">
         <v>-747.35984464513001</v>
       </c>
-      <c r="EZ45" s="32">
+      <c r="EZ45" s="22">
         <v>-1742.8835070350001</v>
       </c>
-      <c r="FA45" s="32">
+      <c r="FA45" s="22">
         <v>-386.48653812056</v>
       </c>
-      <c r="FB45" s="32">
+      <c r="FB45" s="22">
         <v>455.13124389014803</v>
       </c>
-      <c r="FC45" s="32">
+      <c r="FC45" s="22">
         <v>-548.12673332712995</v>
       </c>
-      <c r="FD45" s="32">
+      <c r="FD45" s="22">
         <v>1408.62122167439</v>
       </c>
-      <c r="FE45" s="32">
+      <c r="FE45" s="22">
         <v>631.16159195754699</v>
       </c>
-      <c r="FF45" s="32">
+      <c r="FF45" s="22">
         <v>-2778.1708573954002</v>
       </c>
-      <c r="FG45" s="32">
+      <c r="FG45" s="22">
         <v>247.90168015099701</v>
       </c>
-      <c r="FH45" s="32">
+      <c r="FH45" s="22">
         <v>-2549.2414483747002</v>
       </c>
-      <c r="FI45" s="32">
+      <c r="FI45" s="22">
         <v>-185.51564246688</v>
       </c>
-      <c r="FJ45" s="32">
+      <c r="FJ45" s="22">
         <v>-256.68708846093</v>
       </c>
-      <c r="FK45" s="32">
+      <c r="FK45" s="22">
         <v>-1670.8374102855</v>
       </c>
-      <c r="FL45" s="32">
+      <c r="FL45" s="22">
         <v>-636.37853714847995</v>
       </c>
-      <c r="FM45" s="32">
+      <c r="FM45" s="22">
         <v>-154.22513426425999</v>
       </c>
-      <c r="FN45" s="32">
+      <c r="FN45" s="22">
         <v>-1094.9966400536</v>
       </c>
-      <c r="FO45" s="32">
+      <c r="FO45" s="22">
         <v>1904.0471198166299</v>
       </c>
-      <c r="FP45" s="32">
+      <c r="FP45" s="22">
         <v>-422.35778188784002</v>
       </c>
-      <c r="FQ45" s="32">
+      <c r="FQ45" s="22">
         <v>-1205.3112977672999</v>
       </c>
-      <c r="FR45" s="32">
+      <c r="FR45" s="22">
         <v>782.45915043298805</v>
       </c>
-      <c r="FS45" s="32">
+      <c r="FS45" s="22">
         <v>575.21218264391405</v>
       </c>
-      <c r="FT45" s="32">
+      <c r="FT45" s="22">
         <v>137.016341356552</v>
       </c>
-      <c r="FU45" s="32">
+      <c r="FU45" s="22">
         <v>-1922.7631141879001</v>
       </c>
-      <c r="FV45" s="32">
+      <c r="FV45" s="22">
         <v>1352.5983647133501</v>
       </c>
-      <c r="FW45" s="32">
+      <c r="FW45" s="22">
         <v>-2465.5836184591999</v>
       </c>
-      <c r="FX45" s="32">
+      <c r="FX45" s="22">
         <v>-35.914355402303002</v>
       </c>
-      <c r="FY45" s="32">
+      <c r="FY45" s="22">
         <v>-1012.6221296602999</v>
       </c>
-      <c r="FZ45" s="32">
+      <c r="FZ45" s="22">
         <v>-3550.2133057888</v>
       </c>
-      <c r="GA45" s="32">
+      <c r="GA45" s="22">
         <v>713.61758044524095</v>
       </c>
-      <c r="GB45" s="32">
+      <c r="GB45" s="22">
         <v>2469.9817020339001</v>
       </c>
-      <c r="GC45" s="32">
+      <c r="GC45" s="22">
         <v>-1619.0870577251001</v>
       </c>
-      <c r="GD45" s="32">
+      <c r="GD45" s="22">
         <v>-941.82307009969998</v>
       </c>
-      <c r="GE45" s="32">
+      <c r="GE45" s="22">
         <v>-144.31109095702001</v>
       </c>
-      <c r="GF45" s="32">
+      <c r="GF45" s="22">
         <v>-4276.3204556763003</v>
       </c>
-      <c r="GG45" s="32">
+      <c r="GG45" s="22">
         <v>-1378.9225079149001</v>
       </c>
-      <c r="GH45" s="32">
+      <c r="GH45" s="22">
         <v>1006.00434845267</v>
       </c>
-      <c r="GI45" s="32">
+      <c r="GI45" s="22">
         <v>-5157.0480533029004</v>
       </c>
-      <c r="GJ45" s="32">
+      <c r="GJ45" s="22">
         <v>-1834.1489495631999</v>
       </c>
-      <c r="GK45" s="32">
+      <c r="GK45" s="22">
         <v>1976.9132937367699</v>
       </c>
-      <c r="GL45" s="32">
+      <c r="GL45" s="22">
         <v>2004.9812376623599</v>
       </c>
-      <c r="GM45" s="32">
+      <c r="GM45" s="22">
         <v>1018.70121129603</v>
       </c>
-      <c r="GN45" s="32">
+      <c r="GN45" s="22">
         <v>-1945.5221131236001</v>
       </c>
-      <c r="GO45" s="32">
+      <c r="GO45" s="22">
         <v>-810.48408179908995</v>
       </c>
-      <c r="GP45" s="32">
+      <c r="GP45" s="22">
         <v>-3828.7924749716999</v>
       </c>
-      <c r="GQ45" s="32">
+      <c r="GQ45" s="22">
         <v>437.83302534172901</v>
       </c>
-      <c r="GR45" s="32">
+      <c r="GR45" s="22">
         <v>-3887.5605868532002</v>
       </c>
-      <c r="GS45" s="32">
+      <c r="GS45" s="22">
         <v>963.715307452047</v>
       </c>
-      <c r="GT45" s="32">
+      <c r="GT45" s="22">
         <v>-1262.0679656550999</v>
       </c>
-      <c r="GU45" s="32">
+      <c r="GU45" s="22">
         <v>-1364.2717105833999</v>
       </c>
-      <c r="GV45" s="32">
+      <c r="GV45" s="22">
         <v>-1996.8061450166999</v>
       </c>
-      <c r="GW45" s="32">
+      <c r="GW45" s="22">
         <v>33.060238386819499</v>
       </c>
-      <c r="GX45" s="32">
+      <c r="GX45" s="22">
         <v>-447.11828097801998</v>
       </c>
-      <c r="GY45" s="32">
+      <c r="GY45" s="22">
         <v>1831.5159548886299</v>
       </c>
-      <c r="GZ45" s="32">
+      <c r="GZ45" s="22">
         <v>-1548.3446187917</v>
       </c>
-      <c r="HA45" s="32">
+      <c r="HA45" s="22">
         <v>833.94966231051501</v>
       </c>
-      <c r="HB45" s="32">
+      <c r="HB45" s="22">
         <v>-548.22688766249996</v>
       </c>
-      <c r="HC45" s="32">
+      <c r="HC45" s="22">
         <v>499.52887929965101</v>
       </c>
-      <c r="HD45" s="32">
+      <c r="HD45" s="22">
         <v>-2333.5818225437001</v>
       </c>
-      <c r="HE45" s="32">
+      <c r="HE45" s="22">
         <v>-223.65789118331</v>
       </c>
-      <c r="HF45" s="32">
+      <c r="HF45" s="22">
         <v>-2295.4803237966998</v>
       </c>
-      <c r="HG45" s="32">
+      <c r="HG45" s="22">
         <v>-184.82711743268999</v>
       </c>
-      <c r="HH45" s="32">
+      <c r="HH45" s="22">
         <v>2958.3722734994899</v>
       </c>
-      <c r="HI45" s="32">
+      <c r="HI45" s="22">
         <v>-3364.2816778640999</v>
       </c>
-      <c r="HJ45" s="32">
+      <c r="HJ45" s="22">
         <v>-1289.5063057110999</v>
       </c>
-      <c r="HK45" s="32">
+      <c r="HK45" s="22">
         <v>-1740.8195386134</v>
       </c>
-      <c r="HL45" s="32">
+      <c r="HL45" s="22">
         <v>-956.52157557646001</v>
       </c>
-      <c r="HM45" s="32">
+      <c r="HM45" s="22">
         <v>-3138.9226813557002</v>
       </c>
-      <c r="HN45" s="32">
+      <c r="HN45" s="22">
         <v>-5873.1026266654999</v>
       </c>
-      <c r="HO45" s="32">
+      <c r="HO45" s="22">
         <v>-1114.2078497412999</v>
       </c>
-      <c r="HP45" s="32">
+      <c r="HP45" s="22">
         <v>-8284.8341532376999</v>
       </c>
-      <c r="HQ45" s="32">
+      <c r="HQ45" s="22">
         <v>-4635.3755706961001</v>
       </c>
-      <c r="HR45" s="32">
+      <c r="HR45" s="22">
         <v>-5531.8907065625999</v>
       </c>
-      <c r="HS45" s="32">
+      <c r="HS45" s="22">
         <v>-7071.6276375624002</v>
       </c>
-      <c r="HT45" s="32">
+      <c r="HT45" s="22">
         <v>1288.1332714375301</v>
       </c>
-      <c r="HU45" s="32">
+      <c r="HU45" s="22">
         <v>942.26875293681496</v>
       </c>
-      <c r="HV45" s="32">
+      <c r="HV45" s="22">
         <v>21.437920135195199</v>
       </c>
-      <c r="HW45" s="32">
+      <c r="HW45" s="22">
         <v>-2571.1267401011</v>
       </c>
-      <c r="HX45" s="32">
+      <c r="HX45" s="22">
         <v>-1670.4053383728999</v>
       </c>
-      <c r="HY45" s="32">
+      <c r="HY45" s="22">
         <v>-4444.2882531139003</v>
       </c>
-      <c r="HZ45" s="32">
+      <c r="HZ45" s="22">
         <v>-458.28644092068998</v>
       </c>
-      <c r="IA45" s="32">
+      <c r="IA45" s="22">
         <v>-1315.2628423858</v>
       </c>
-      <c r="IB45" s="32">
+      <c r="IB45" s="22">
         <v>-430.59908087128002</v>
       </c>
-      <c r="IC45" s="32">
+      <c r="IC45" s="22">
         <v>-486.52890654839001</v>
       </c>
-      <c r="ID45" s="32">
+      <c r="ID45" s="22">
         <v>-331.86927357946001</v>
       </c>
-      <c r="IE45" s="32">
+      <c r="IE45" s="22">
         <v>-2322.1129545402</v>
       </c>
-      <c r="IF45" s="32">
+      <c r="IF45" s="22">
         <v>-5410.5882058649004</v>
       </c>
-      <c r="IG45" s="32">
+      <c r="IG45" s="22">
         <v>-470.01748173566</v>
       </c>
-      <c r="IH45" s="32">
+      <c r="IH45" s="22">
         <v>2321.9425612084301</v>
       </c>
-      <c r="II45" s="32">
+      <c r="II45" s="22">
         <v>1118.5458609790601</v>
       </c>
-      <c r="IJ45" s="32">
+      <c r="IJ45" s="22">
         <v>102.062700731888</v>
       </c>
-      <c r="IK45" s="32">
+      <c r="IK45" s="22">
         <v>-3818.2837016643998</v>
       </c>
-      <c r="IL45" s="32">
+      <c r="IL45" s="22">
         <v>136.82494329100601</v>
       </c>
-      <c r="IM45" s="32">
+      <c r="IM45" s="22">
         <v>-1466.1352166249001</v>
       </c>
-      <c r="IN45" s="32">
+      <c r="IN45" s="22">
         <v>-1493.4087980047</v>
       </c>
-      <c r="IO45" s="32">
+      <c r="IO45" s="22">
         <v>-4545.7452463889003</v>
       </c>
-      <c r="IP45" s="32">
+      <c r="IP45" s="22">
         <v>-2305.4483832022001</v>
       </c>
-      <c r="IQ45" s="32">
+      <c r="IQ45" s="22">
         <v>-6241.8322253706001</v>
       </c>
-      <c r="IR45" s="32">
+      <c r="IR45" s="22">
         <v>93.523040935998296</v>
       </c>
-      <c r="IS45" s="32">
+      <c r="IS45" s="22">
         <v>122.583065879552</v>
       </c>
-      <c r="IT45" s="32">
+      <c r="IT45" s="22">
         <v>-159.94808640899001</v>
       </c>
-      <c r="IU45" s="32">
+      <c r="IU45" s="22">
         <v>209.996978279252</v>
       </c>
-      <c r="IV45" s="32">
+      <c r="IV45" s="22">
         <v>1642.1519210737099</v>
       </c>
-      <c r="IW45" s="32">
+      <c r="IW45" s="22">
         <v>-2477.5294326812</v>
       </c>
-      <c r="IX45" s="32">
+      <c r="IX45" s="22">
         <v>-1670.7794896252999</v>
       </c>
-      <c r="IY45" s="32">
+      <c r="IY45" s="22">
         <v>2306.0793018061299</v>
       </c>
-      <c r="IZ45" s="32">
+      <c r="IZ45" s="22">
         <v>-4869.3847300513999</v>
       </c>
-      <c r="JA45" s="32">
+      <c r="JA45" s="22">
         <v>1532.83377637743</v>
       </c>
-      <c r="JB45" s="32">
+      <c r="JB45" s="22">
         <v>-1399.0683042971</v>
       </c>
-      <c r="JC45" s="32">
+      <c r="JC45" s="22">
         <v>3075.9126764447101</v>
       </c>
-      <c r="JD45" s="32">
+      <c r="JD45" s="22">
         <v>-518.36692842269997</v>
       </c>
-      <c r="JE45" s="32">
+      <c r="JE45" s="22">
         <v>-1411.047098216</v>
       </c>
-      <c r="JF45" s="32">
+      <c r="JF45" s="22">
         <v>1922.9062439614399</v>
       </c>
-      <c r="JG45" s="32">
+      <c r="JG45" s="22">
         <v>-1823.907273665</v>
       </c>
-      <c r="JH45" s="32">
+      <c r="JH45" s="22">
         <v>-2764.4689885922999</v>
       </c>
-      <c r="JI45" s="32">
+      <c r="JI45" s="22">
         <v>-748.76263018937004</v>
       </c>
-      <c r="JJ45" s="32">
+      <c r="JJ45" s="22">
         <v>-1545.3490956667999</v>
       </c>
-      <c r="JK45" s="32">
+      <c r="JK45" s="22">
         <v>-812.58431654398998</v>
       </c>
-      <c r="JL45" s="32">
+      <c r="JL45" s="22">
         <v>-848.61917374007999</v>
       </c>
-      <c r="JM45" s="32">
+      <c r="JM45" s="22">
         <v>-1190.5460992081</v>
       </c>
-      <c r="JN45" s="32">
+      <c r="JN45" s="22">
         <v>-2261.576974907</v>
       </c>
-      <c r="JO45" s="32">
+      <c r="JO45" s="22">
         <v>454.71489817980802</v>
       </c>
-      <c r="JP45" s="32">
+      <c r="JP45" s="22">
         <v>-2132.7038033218</v>
       </c>
-      <c r="JQ45" s="32">
+      <c r="JQ45" s="22">
         <v>3400.6974589851998</v>
       </c>
-      <c r="JR45" s="32">
+      <c r="JR45" s="22">
         <v>1029.2955078495399</v>
       </c>
       <c r="JS45" s="16">
         <v>-1436.5064811633999</v>
       </c>
+      <c r="JT45" s="16">
+        <v>-2262.1424227406001</v>
+      </c>
     </row>
-    <row r="46" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="33" t="s">
+    <row r="46" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="23" t="s">
         <v>42</v>
       </c>
       <c r="B46" s="7">
@@ -36362,9 +36532,12 @@
       <c r="JS46" s="17">
         <v>556.75870162478202</v>
       </c>
+      <c r="JT46" s="17">
+        <v>1104.5198899257</v>
+      </c>
     </row>
-    <row r="47" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="33" t="s">
+    <row r="47" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="23" t="s">
         <v>26</v>
       </c>
       <c r="B47" s="7">
@@ -37201,9 +37374,12 @@
       <c r="JS47" s="17">
         <v>992.63727698604498</v>
       </c>
+      <c r="JT47" s="17">
+        <v>1259.19176117249</v>
+      </c>
     </row>
-    <row r="48" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="33" t="s">
+    <row r="48" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="23" t="s">
         <v>43</v>
       </c>
       <c r="B48" s="7" t="s">
@@ -38040,9 +38216,12 @@
       <c r="JS48" s="17">
         <v>292.96925248142003</v>
       </c>
+      <c r="JT48" s="17">
+        <v>604.75921625866795</v>
+      </c>
     </row>
-    <row r="49" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="33" t="s">
+    <row r="49" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="23" t="s">
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
@@ -38879,9 +39058,12 @@
       <c r="JS49" s="17">
         <v>699.66802450462501</v>
       </c>
+      <c r="JT49" s="17">
+        <v>654.43254491381799</v>
+      </c>
     </row>
-    <row r="50" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="33" t="s">
+    <row r="50" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="23" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="7">
@@ -39718,9 +39900,12 @@
       <c r="JS50" s="17">
         <v>-435.87857536126</v>
       </c>
+      <c r="JT50" s="17">
+        <v>-154.67187124678</v>
+      </c>
     </row>
-    <row r="51" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="33" t="s">
+    <row r="51" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="23" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="7">
@@ -40557,9 +40742,12 @@
       <c r="JS51" s="17">
         <v>205.51759911505701</v>
       </c>
+      <c r="JT51" s="17">
+        <v>-29.708108825277002</v>
+      </c>
     </row>
-    <row r="52" spans="1:279" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="34" t="s">
+    <row r="52" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="24" t="s">
         <v>47</v>
       </c>
       <c r="B52" s="9">
@@ -41396,289 +41584,293 @@
       <c r="JS52" s="18">
         <v>-641.39617447631997</v>
       </c>
+      <c r="JT52" s="18">
+        <v>-124.96376242151</v>
+      </c>
     </row>
-    <row r="54" spans="1:279" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="23" t="s">
+    <row r="54" spans="1:280" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="23"/>
-      <c r="O54" s="23"/>
-      <c r="P54" s="23"/>
-      <c r="Q54" s="23"/>
-      <c r="R54" s="23"/>
-      <c r="S54" s="23"/>
-      <c r="T54" s="23"/>
-      <c r="U54" s="23"/>
-      <c r="V54" s="23"/>
-      <c r="W54" s="23"/>
-      <c r="X54" s="23"/>
-      <c r="Y54" s="23"/>
-      <c r="Z54" s="23"/>
-      <c r="AA54" s="23"/>
-      <c r="AB54" s="23"/>
-      <c r="AC54" s="23"/>
-      <c r="AD54" s="23"/>
-      <c r="AE54" s="23"/>
-      <c r="AF54" s="23"/>
-      <c r="AG54" s="23"/>
-      <c r="AH54" s="23"/>
-      <c r="AI54" s="23"/>
-      <c r="AJ54" s="23"/>
-      <c r="AK54" s="23"/>
-      <c r="AL54" s="23"/>
-      <c r="AM54" s="23"/>
-      <c r="AN54" s="23"/>
-      <c r="AO54" s="23"/>
-      <c r="AP54" s="23"/>
-      <c r="AQ54" s="23"/>
-      <c r="AR54" s="23"/>
-      <c r="AS54" s="23"/>
-      <c r="AT54" s="23"/>
-      <c r="AU54" s="23"/>
-      <c r="AV54" s="23"/>
-      <c r="AW54" s="23"/>
-      <c r="AX54" s="23"/>
-      <c r="AY54" s="23"/>
-      <c r="AZ54" s="23"/>
-      <c r="BA54" s="23"/>
-      <c r="BB54" s="23"/>
-      <c r="BC54" s="23"/>
-      <c r="BD54" s="23"/>
-      <c r="BE54" s="23"/>
-      <c r="BF54" s="23"/>
-      <c r="BG54" s="23"/>
-      <c r="BH54" s="23"/>
-      <c r="BI54" s="23"/>
-      <c r="BJ54" s="23"/>
-      <c r="BK54" s="23"/>
-      <c r="BL54" s="23"/>
-      <c r="BM54" s="23"/>
-      <c r="BN54" s="23"/>
-      <c r="BO54" s="23"/>
-      <c r="BP54" s="23"/>
-      <c r="BQ54" s="23"/>
-      <c r="BR54" s="23"/>
-      <c r="BS54" s="23"/>
-      <c r="BT54" s="23"/>
-      <c r="BU54" s="23"/>
-      <c r="BV54" s="23"/>
-      <c r="BW54" s="23"/>
-      <c r="BX54" s="23"/>
-      <c r="BY54" s="23"/>
-      <c r="BZ54" s="23"/>
-      <c r="CA54" s="23"/>
-      <c r="CB54" s="23"/>
-      <c r="CC54" s="23"/>
-      <c r="CD54" s="23"/>
-      <c r="CE54" s="23"/>
-      <c r="CF54" s="23"/>
-      <c r="CG54" s="23"/>
-      <c r="CH54" s="23"/>
-      <c r="CI54" s="23"/>
-      <c r="CJ54" s="23"/>
-      <c r="CK54" s="23"/>
-      <c r="CL54" s="23"/>
-      <c r="CM54" s="23"/>
-      <c r="CN54" s="23"/>
-      <c r="CO54" s="23"/>
-      <c r="CP54" s="23"/>
-      <c r="CQ54" s="23"/>
-      <c r="CR54" s="23"/>
-      <c r="CS54" s="23"/>
-      <c r="CT54" s="23"/>
-      <c r="CU54" s="23"/>
-      <c r="CV54" s="23"/>
-      <c r="CW54" s="23"/>
-      <c r="CX54" s="23"/>
-      <c r="CY54" s="23"/>
-      <c r="CZ54" s="23"/>
-      <c r="DA54" s="23"/>
-      <c r="DB54" s="23"/>
-      <c r="DC54" s="23"/>
-      <c r="DD54" s="23"/>
-      <c r="DE54" s="23"/>
-      <c r="DF54" s="23"/>
-      <c r="DG54" s="23"/>
-      <c r="DH54" s="23"/>
-      <c r="DI54" s="23"/>
-      <c r="DJ54" s="23"/>
-      <c r="DK54" s="23"/>
-      <c r="DL54" s="23"/>
-      <c r="DM54" s="23"/>
-      <c r="DN54" s="23"/>
-      <c r="DO54" s="23"/>
-      <c r="DP54" s="23"/>
-      <c r="DQ54" s="23"/>
-      <c r="DR54" s="23"/>
-      <c r="DS54" s="23"/>
-      <c r="DT54" s="23"/>
-      <c r="DU54" s="23"/>
-      <c r="DV54" s="23"/>
-      <c r="DW54" s="23"/>
-      <c r="DX54" s="23"/>
-      <c r="DY54" s="23"/>
-      <c r="DZ54" s="23"/>
-      <c r="EA54" s="23"/>
-      <c r="EB54" s="23"/>
-      <c r="EC54" s="23"/>
-      <c r="ED54" s="23"/>
-      <c r="EE54" s="23"/>
-      <c r="EF54" s="23"/>
-      <c r="EG54" s="23"/>
-      <c r="EH54" s="23"/>
-      <c r="EI54" s="23"/>
-      <c r="EJ54" s="23"/>
-      <c r="EK54" s="23"/>
-      <c r="EL54" s="23"/>
-      <c r="EM54" s="23"/>
-      <c r="EN54" s="23"/>
-      <c r="EO54" s="23"/>
-      <c r="EP54" s="23"/>
-      <c r="EQ54" s="23"/>
-      <c r="ER54" s="23"/>
-      <c r="ES54" s="23"/>
-      <c r="ET54" s="23"/>
-      <c r="EU54" s="23"/>
-      <c r="EV54" s="23"/>
-      <c r="EW54" s="23"/>
-      <c r="EX54" s="23"/>
-      <c r="EY54" s="23"/>
-      <c r="EZ54" s="23"/>
-      <c r="FA54" s="23"/>
-      <c r="FB54" s="23"/>
-      <c r="FC54" s="23"/>
-      <c r="FD54" s="23"/>
-      <c r="FE54" s="23"/>
-      <c r="FF54" s="23"/>
-      <c r="FG54" s="23"/>
-      <c r="FH54" s="23"/>
-      <c r="FI54" s="23"/>
-      <c r="FJ54" s="23"/>
-      <c r="FK54" s="23"/>
-      <c r="FL54" s="23"/>
-      <c r="FM54" s="23"/>
-      <c r="FN54" s="23"/>
-      <c r="FO54" s="23"/>
-      <c r="FP54" s="23"/>
-      <c r="FQ54" s="23"/>
-      <c r="FR54" s="23"/>
-      <c r="FS54" s="23"/>
-      <c r="FT54" s="23"/>
-      <c r="FU54" s="23"/>
-      <c r="FV54" s="23"/>
-      <c r="FW54" s="23"/>
-      <c r="FX54" s="23"/>
-      <c r="FY54" s="23"/>
-      <c r="FZ54" s="23"/>
-      <c r="GA54" s="23"/>
-      <c r="GB54" s="23"/>
-      <c r="GC54" s="23"/>
-      <c r="GD54" s="23"/>
-      <c r="GE54" s="23"/>
-      <c r="GF54" s="23"/>
-      <c r="GG54" s="23"/>
-      <c r="GH54" s="23"/>
-      <c r="GI54" s="23"/>
-      <c r="GJ54" s="23"/>
-      <c r="GK54" s="23"/>
-      <c r="GL54" s="23"/>
-      <c r="GM54" s="23"/>
-      <c r="GN54" s="23"/>
-      <c r="GO54" s="23"/>
-      <c r="GP54" s="23"/>
-      <c r="GQ54" s="23"/>
-      <c r="GR54" s="23"/>
-      <c r="GS54" s="23"/>
-      <c r="GT54" s="23"/>
-      <c r="GU54" s="23"/>
-      <c r="GV54" s="23"/>
-      <c r="GW54" s="23"/>
-      <c r="GX54" s="23"/>
-      <c r="GY54" s="23"/>
-      <c r="GZ54" s="23"/>
-      <c r="HA54" s="23"/>
-      <c r="HB54" s="23"/>
-      <c r="HC54" s="23"/>
-      <c r="HD54" s="23"/>
-      <c r="HE54" s="23"/>
-      <c r="HF54" s="23"/>
-      <c r="HG54" s="23"/>
-      <c r="HH54" s="23"/>
-      <c r="HI54" s="23"/>
-      <c r="HJ54" s="23"/>
-      <c r="HK54" s="23"/>
-      <c r="HL54" s="23"/>
-      <c r="HM54" s="23"/>
-      <c r="HN54" s="23"/>
-      <c r="HO54" s="23"/>
-      <c r="HP54" s="23"/>
-      <c r="HQ54" s="23"/>
-      <c r="HR54" s="23"/>
-      <c r="HS54" s="23"/>
-      <c r="HT54" s="23"/>
-      <c r="HU54" s="23"/>
-      <c r="HV54" s="23"/>
-      <c r="HW54" s="23"/>
-      <c r="HX54" s="23"/>
-      <c r="HY54" s="23"/>
-      <c r="HZ54" s="23"/>
-      <c r="IA54" s="23"/>
-      <c r="IB54" s="23"/>
-      <c r="IC54" s="23"/>
-      <c r="ID54" s="23"/>
-      <c r="IE54" s="23"/>
-      <c r="IF54" s="23"/>
-      <c r="IG54" s="23"/>
-      <c r="IH54" s="23"/>
-      <c r="II54" s="23"/>
-      <c r="IJ54" s="23"/>
-      <c r="IK54" s="23"/>
-      <c r="IL54" s="23"/>
-      <c r="IM54" s="23"/>
-      <c r="IN54" s="23"/>
-      <c r="IO54" s="23"/>
-      <c r="IP54" s="23"/>
-      <c r="IQ54" s="23"/>
-      <c r="IR54" s="23"/>
-      <c r="IS54" s="23"/>
-      <c r="IT54" s="23"/>
-      <c r="IU54" s="23"/>
-      <c r="IV54" s="23"/>
-      <c r="IW54" s="23"/>
-      <c r="IX54" s="23"/>
-      <c r="IY54" s="23"/>
-      <c r="IZ54" s="23"/>
-      <c r="JA54" s="23"/>
-      <c r="JB54" s="23"/>
-      <c r="JC54" s="23"/>
-      <c r="JD54" s="23"/>
-      <c r="JE54" s="23"/>
-      <c r="JF54" s="23"/>
-      <c r="JG54" s="23"/>
-      <c r="JH54" s="23"/>
-      <c r="JI54" s="23"/>
-      <c r="JJ54" s="23"/>
-      <c r="JK54" s="23"/>
-      <c r="JL54" s="23"/>
-      <c r="JM54" s="23"/>
-      <c r="JN54" s="23"/>
-      <c r="JO54" s="23"/>
-      <c r="JP54" s="23"/>
-      <c r="JQ54" s="23"/>
-      <c r="JR54" s="23"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="30"/>
+      <c r="X54" s="30"/>
+      <c r="Y54" s="30"/>
+      <c r="Z54" s="30"/>
+      <c r="AA54" s="30"/>
+      <c r="AB54" s="30"/>
+      <c r="AC54" s="30"/>
+      <c r="AD54" s="30"/>
+      <c r="AE54" s="30"/>
+      <c r="AF54" s="30"/>
+      <c r="AG54" s="30"/>
+      <c r="AH54" s="30"/>
+      <c r="AI54" s="30"/>
+      <c r="AJ54" s="30"/>
+      <c r="AK54" s="30"/>
+      <c r="AL54" s="30"/>
+      <c r="AM54" s="30"/>
+      <c r="AN54" s="30"/>
+      <c r="AO54" s="30"/>
+      <c r="AP54" s="30"/>
+      <c r="AQ54" s="30"/>
+      <c r="AR54" s="30"/>
+      <c r="AS54" s="30"/>
+      <c r="AT54" s="30"/>
+      <c r="AU54" s="30"/>
+      <c r="AV54" s="30"/>
+      <c r="AW54" s="30"/>
+      <c r="AX54" s="30"/>
+      <c r="AY54" s="30"/>
+      <c r="AZ54" s="30"/>
+      <c r="BA54" s="30"/>
+      <c r="BB54" s="30"/>
+      <c r="BC54" s="30"/>
+      <c r="BD54" s="30"/>
+      <c r="BE54" s="30"/>
+      <c r="BF54" s="30"/>
+      <c r="BG54" s="30"/>
+      <c r="BH54" s="30"/>
+      <c r="BI54" s="30"/>
+      <c r="BJ54" s="30"/>
+      <c r="BK54" s="30"/>
+      <c r="BL54" s="30"/>
+      <c r="BM54" s="30"/>
+      <c r="BN54" s="30"/>
+      <c r="BO54" s="30"/>
+      <c r="BP54" s="30"/>
+      <c r="BQ54" s="30"/>
+      <c r="BR54" s="30"/>
+      <c r="BS54" s="30"/>
+      <c r="BT54" s="30"/>
+      <c r="BU54" s="30"/>
+      <c r="BV54" s="30"/>
+      <c r="BW54" s="30"/>
+      <c r="BX54" s="30"/>
+      <c r="BY54" s="30"/>
+      <c r="BZ54" s="30"/>
+      <c r="CA54" s="30"/>
+      <c r="CB54" s="30"/>
+      <c r="CC54" s="30"/>
+      <c r="CD54" s="30"/>
+      <c r="CE54" s="30"/>
+      <c r="CF54" s="30"/>
+      <c r="CG54" s="30"/>
+      <c r="CH54" s="30"/>
+      <c r="CI54" s="30"/>
+      <c r="CJ54" s="30"/>
+      <c r="CK54" s="30"/>
+      <c r="CL54" s="30"/>
+      <c r="CM54" s="30"/>
+      <c r="CN54" s="30"/>
+      <c r="CO54" s="30"/>
+      <c r="CP54" s="30"/>
+      <c r="CQ54" s="30"/>
+      <c r="CR54" s="30"/>
+      <c r="CS54" s="30"/>
+      <c r="CT54" s="30"/>
+      <c r="CU54" s="30"/>
+      <c r="CV54" s="30"/>
+      <c r="CW54" s="30"/>
+      <c r="CX54" s="30"/>
+      <c r="CY54" s="30"/>
+      <c r="CZ54" s="30"/>
+      <c r="DA54" s="30"/>
+      <c r="DB54" s="30"/>
+      <c r="DC54" s="30"/>
+      <c r="DD54" s="30"/>
+      <c r="DE54" s="30"/>
+      <c r="DF54" s="30"/>
+      <c r="DG54" s="30"/>
+      <c r="DH54" s="30"/>
+      <c r="DI54" s="30"/>
+      <c r="DJ54" s="30"/>
+      <c r="DK54" s="30"/>
+      <c r="DL54" s="30"/>
+      <c r="DM54" s="30"/>
+      <c r="DN54" s="30"/>
+      <c r="DO54" s="30"/>
+      <c r="DP54" s="30"/>
+      <c r="DQ54" s="30"/>
+      <c r="DR54" s="30"/>
+      <c r="DS54" s="30"/>
+      <c r="DT54" s="30"/>
+      <c r="DU54" s="30"/>
+      <c r="DV54" s="30"/>
+      <c r="DW54" s="30"/>
+      <c r="DX54" s="30"/>
+      <c r="DY54" s="30"/>
+      <c r="DZ54" s="30"/>
+      <c r="EA54" s="30"/>
+      <c r="EB54" s="30"/>
+      <c r="EC54" s="30"/>
+      <c r="ED54" s="30"/>
+      <c r="EE54" s="30"/>
+      <c r="EF54" s="30"/>
+      <c r="EG54" s="30"/>
+      <c r="EH54" s="30"/>
+      <c r="EI54" s="30"/>
+      <c r="EJ54" s="30"/>
+      <c r="EK54" s="30"/>
+      <c r="EL54" s="30"/>
+      <c r="EM54" s="30"/>
+      <c r="EN54" s="30"/>
+      <c r="EO54" s="30"/>
+      <c r="EP54" s="30"/>
+      <c r="EQ54" s="30"/>
+      <c r="ER54" s="30"/>
+      <c r="ES54" s="30"/>
+      <c r="ET54" s="30"/>
+      <c r="EU54" s="30"/>
+      <c r="EV54" s="30"/>
+      <c r="EW54" s="30"/>
+      <c r="EX54" s="30"/>
+      <c r="EY54" s="30"/>
+      <c r="EZ54" s="30"/>
+      <c r="FA54" s="30"/>
+      <c r="FB54" s="30"/>
+      <c r="FC54" s="30"/>
+      <c r="FD54" s="30"/>
+      <c r="FE54" s="30"/>
+      <c r="FF54" s="30"/>
+      <c r="FG54" s="30"/>
+      <c r="FH54" s="30"/>
+      <c r="FI54" s="30"/>
+      <c r="FJ54" s="30"/>
+      <c r="FK54" s="30"/>
+      <c r="FL54" s="30"/>
+      <c r="FM54" s="30"/>
+      <c r="FN54" s="30"/>
+      <c r="FO54" s="30"/>
+      <c r="FP54" s="30"/>
+      <c r="FQ54" s="30"/>
+      <c r="FR54" s="30"/>
+      <c r="FS54" s="30"/>
+      <c r="FT54" s="30"/>
+      <c r="FU54" s="30"/>
+      <c r="FV54" s="30"/>
+      <c r="FW54" s="30"/>
+      <c r="FX54" s="30"/>
+      <c r="FY54" s="30"/>
+      <c r="FZ54" s="30"/>
+      <c r="GA54" s="30"/>
+      <c r="GB54" s="30"/>
+      <c r="GC54" s="30"/>
+      <c r="GD54" s="30"/>
+      <c r="GE54" s="30"/>
+      <c r="GF54" s="30"/>
+      <c r="GG54" s="30"/>
+      <c r="GH54" s="30"/>
+      <c r="GI54" s="30"/>
+      <c r="GJ54" s="30"/>
+      <c r="GK54" s="30"/>
+      <c r="GL54" s="30"/>
+      <c r="GM54" s="30"/>
+      <c r="GN54" s="30"/>
+      <c r="GO54" s="30"/>
+      <c r="GP54" s="30"/>
+      <c r="GQ54" s="30"/>
+      <c r="GR54" s="30"/>
+      <c r="GS54" s="30"/>
+      <c r="GT54" s="30"/>
+      <c r="GU54" s="30"/>
+      <c r="GV54" s="30"/>
+      <c r="GW54" s="30"/>
+      <c r="GX54" s="30"/>
+      <c r="GY54" s="30"/>
+      <c r="GZ54" s="30"/>
+      <c r="HA54" s="30"/>
+      <c r="HB54" s="30"/>
+      <c r="HC54" s="30"/>
+      <c r="HD54" s="30"/>
+      <c r="HE54" s="30"/>
+      <c r="HF54" s="30"/>
+      <c r="HG54" s="30"/>
+      <c r="HH54" s="30"/>
+      <c r="HI54" s="30"/>
+      <c r="HJ54" s="30"/>
+      <c r="HK54" s="30"/>
+      <c r="HL54" s="30"/>
+      <c r="HM54" s="30"/>
+      <c r="HN54" s="30"/>
+      <c r="HO54" s="30"/>
+      <c r="HP54" s="30"/>
+      <c r="HQ54" s="30"/>
+      <c r="HR54" s="30"/>
+      <c r="HS54" s="30"/>
+      <c r="HT54" s="30"/>
+      <c r="HU54" s="30"/>
+      <c r="HV54" s="30"/>
+      <c r="HW54" s="30"/>
+      <c r="HX54" s="30"/>
+      <c r="HY54" s="30"/>
+      <c r="HZ54" s="30"/>
+      <c r="IA54" s="30"/>
+      <c r="IB54" s="30"/>
+      <c r="IC54" s="30"/>
+      <c r="ID54" s="30"/>
+      <c r="IE54" s="30"/>
+      <c r="IF54" s="30"/>
+      <c r="IG54" s="30"/>
+      <c r="IH54" s="30"/>
+      <c r="II54" s="30"/>
+      <c r="IJ54" s="30"/>
+      <c r="IK54" s="30"/>
+      <c r="IL54" s="30"/>
+      <c r="IM54" s="30"/>
+      <c r="IN54" s="30"/>
+      <c r="IO54" s="30"/>
+      <c r="IP54" s="30"/>
+      <c r="IQ54" s="30"/>
+      <c r="IR54" s="30"/>
+      <c r="IS54" s="30"/>
+      <c r="IT54" s="30"/>
+      <c r="IU54" s="30"/>
+      <c r="IV54" s="30"/>
+      <c r="IW54" s="30"/>
+      <c r="IX54" s="30"/>
+      <c r="IY54" s="30"/>
+      <c r="IZ54" s="30"/>
+      <c r="JA54" s="30"/>
+      <c r="JB54" s="30"/>
+      <c r="JC54" s="30"/>
+      <c r="JD54" s="30"/>
+      <c r="JE54" s="30"/>
+      <c r="JF54" s="30"/>
+      <c r="JG54" s="30"/>
+      <c r="JH54" s="30"/>
+      <c r="JI54" s="30"/>
+      <c r="JJ54" s="30"/>
+      <c r="JK54" s="30"/>
+      <c r="JL54" s="30"/>
+      <c r="JM54" s="30"/>
+      <c r="JN54" s="30"/>
+      <c r="JO54" s="30"/>
+      <c r="JP54" s="30"/>
+      <c r="JQ54" s="30"/>
+      <c r="JR54" s="30"/>
       <c r="JS54" s="10"/>
+      <c r="JT54" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -41692,8 +41884,8 @@
     <mergeCell ref="Z4:AK4"/>
     <mergeCell ref="AL4:AW4"/>
     <mergeCell ref="AX4:BI4"/>
-    <mergeCell ref="JR4:JS4"/>
     <mergeCell ref="A44:JS44"/>
+    <mergeCell ref="JR4:JT4"/>
     <mergeCell ref="A1:JR1"/>
     <mergeCell ref="A2:JR2"/>
     <mergeCell ref="FZ4:GK4"/>
@@ -41733,60 +41925,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
     </row>
     <row r="2" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
     </row>
     <row r="4" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -44675,32 +44867,32 @@
       </c>
     </row>
     <row r="43" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="24"/>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="24"/>
-      <c r="R43" s="24"/>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
+      <c r="M43" s="37"/>
+      <c r="N43" s="37"/>
+      <c r="O43" s="37"/>
+      <c r="P43" s="37"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="37"/>
+      <c r="S43" s="37"/>
+      <c r="T43" s="37"/>
+      <c r="U43" s="37"/>
+      <c r="V43" s="37"/>
+      <c r="W43" s="37"/>
+      <c r="X43" s="37"/>
     </row>
     <row r="44" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -45295,32 +45487,32 @@
       </c>
     </row>
     <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="23"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="23"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="23"/>
-      <c r="Q53" s="23"/>
-      <c r="R53" s="23"/>
-      <c r="S53" s="23"/>
-      <c r="T53" s="23"/>
-      <c r="U53" s="23"/>
-      <c r="V53" s="23"/>
-      <c r="W53" s="23"/>
-      <c r="X53" s="23"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="30"/>
+      <c r="S53" s="30"/>
+      <c r="T53" s="30"/>
+      <c r="U53" s="30"/>
+      <c r="V53" s="30"/>
+      <c r="W53" s="30"/>
+      <c r="X53" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
+++ b/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.05.2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.18.05.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ABF3C5-C165-4713-B58E-100DFEDDC867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E731768-D490-44C0-B2B9-B3BCD172355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mensual" sheetId="1" r:id="rId1"/>
@@ -598,20 +598,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -630,6 +621,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -833,902 +833,902 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="27"/>
-      <c r="AJ1" s="27"/>
-      <c r="AK1" s="27"/>
-      <c r="AL1" s="27"/>
-      <c r="AM1" s="27"/>
-      <c r="AN1" s="27"/>
-      <c r="AO1" s="27"/>
-      <c r="AP1" s="27"/>
-      <c r="AQ1" s="27"/>
-      <c r="AR1" s="27"/>
-      <c r="AS1" s="27"/>
-      <c r="AT1" s="27"/>
-      <c r="AU1" s="27"/>
-      <c r="AV1" s="27"/>
-      <c r="AW1" s="27"/>
-      <c r="AX1" s="27"/>
-      <c r="AY1" s="27"/>
-      <c r="AZ1" s="27"/>
-      <c r="BA1" s="27"/>
-      <c r="BB1" s="27"/>
-      <c r="BC1" s="27"/>
-      <c r="BD1" s="27"/>
-      <c r="BE1" s="27"/>
-      <c r="BF1" s="27"/>
-      <c r="BG1" s="27"/>
-      <c r="BH1" s="27"/>
-      <c r="BI1" s="27"/>
-      <c r="BJ1" s="27"/>
-      <c r="BK1" s="27"/>
-      <c r="BL1" s="27"/>
-      <c r="BM1" s="27"/>
-      <c r="BN1" s="27"/>
-      <c r="BO1" s="27"/>
-      <c r="BP1" s="27"/>
-      <c r="BQ1" s="27"/>
-      <c r="BR1" s="27"/>
-      <c r="BS1" s="27"/>
-      <c r="BT1" s="27"/>
-      <c r="BU1" s="27"/>
-      <c r="BV1" s="27"/>
-      <c r="BW1" s="27"/>
-      <c r="BX1" s="27"/>
-      <c r="BY1" s="27"/>
-      <c r="BZ1" s="27"/>
-      <c r="CA1" s="27"/>
-      <c r="CB1" s="27"/>
-      <c r="CC1" s="27"/>
-      <c r="CD1" s="27"/>
-      <c r="CE1" s="27"/>
-      <c r="CF1" s="27"/>
-      <c r="CG1" s="27"/>
-      <c r="CH1" s="27"/>
-      <c r="CI1" s="27"/>
-      <c r="CJ1" s="27"/>
-      <c r="CK1" s="27"/>
-      <c r="CL1" s="27"/>
-      <c r="CM1" s="27"/>
-      <c r="CN1" s="27"/>
-      <c r="CO1" s="27"/>
-      <c r="CP1" s="27"/>
-      <c r="CQ1" s="27"/>
-      <c r="CR1" s="27"/>
-      <c r="CS1" s="27"/>
-      <c r="CT1" s="27"/>
-      <c r="CU1" s="27"/>
-      <c r="CV1" s="27"/>
-      <c r="CW1" s="27"/>
-      <c r="CX1" s="27"/>
-      <c r="CY1" s="27"/>
-      <c r="CZ1" s="27"/>
-      <c r="DA1" s="27"/>
-      <c r="DB1" s="27"/>
-      <c r="DC1" s="27"/>
-      <c r="DD1" s="27"/>
-      <c r="DE1" s="27"/>
-      <c r="DF1" s="27"/>
-      <c r="DG1" s="27"/>
-      <c r="DH1" s="27"/>
-      <c r="DI1" s="27"/>
-      <c r="DJ1" s="27"/>
-      <c r="DK1" s="27"/>
-      <c r="DL1" s="27"/>
-      <c r="DM1" s="27"/>
-      <c r="DN1" s="27"/>
-      <c r="DO1" s="27"/>
-      <c r="DP1" s="27"/>
-      <c r="DQ1" s="27"/>
-      <c r="DR1" s="27"/>
-      <c r="DS1" s="27"/>
-      <c r="DT1" s="27"/>
-      <c r="DU1" s="27"/>
-      <c r="DV1" s="27"/>
-      <c r="DW1" s="27"/>
-      <c r="DX1" s="27"/>
-      <c r="DY1" s="27"/>
-      <c r="DZ1" s="27"/>
-      <c r="EA1" s="27"/>
-      <c r="EB1" s="27"/>
-      <c r="EC1" s="27"/>
-      <c r="ED1" s="27"/>
-      <c r="EE1" s="27"/>
-      <c r="EF1" s="27"/>
-      <c r="EG1" s="27"/>
-      <c r="EH1" s="27"/>
-      <c r="EI1" s="27"/>
-      <c r="EJ1" s="27"/>
-      <c r="EK1" s="27"/>
-      <c r="EL1" s="27"/>
-      <c r="EM1" s="27"/>
-      <c r="EN1" s="27"/>
-      <c r="EO1" s="27"/>
-      <c r="EP1" s="27"/>
-      <c r="EQ1" s="27"/>
-      <c r="ER1" s="27"/>
-      <c r="ES1" s="27"/>
-      <c r="ET1" s="27"/>
-      <c r="EU1" s="27"/>
-      <c r="EV1" s="27"/>
-      <c r="EW1" s="27"/>
-      <c r="EX1" s="27"/>
-      <c r="EY1" s="27"/>
-      <c r="EZ1" s="27"/>
-      <c r="FA1" s="27"/>
-      <c r="FB1" s="27"/>
-      <c r="FC1" s="27"/>
-      <c r="FD1" s="27"/>
-      <c r="FE1" s="27"/>
-      <c r="FF1" s="27"/>
-      <c r="FG1" s="27"/>
-      <c r="FH1" s="27"/>
-      <c r="FI1" s="27"/>
-      <c r="FJ1" s="27"/>
-      <c r="FK1" s="27"/>
-      <c r="FL1" s="27"/>
-      <c r="FM1" s="27"/>
-      <c r="FN1" s="27"/>
-      <c r="FO1" s="27"/>
-      <c r="FP1" s="27"/>
-      <c r="FQ1" s="27"/>
-      <c r="FR1" s="27"/>
-      <c r="FS1" s="27"/>
-      <c r="FT1" s="27"/>
-      <c r="FU1" s="27"/>
-      <c r="FV1" s="27"/>
-      <c r="FW1" s="27"/>
-      <c r="FX1" s="27"/>
-      <c r="FY1" s="27"/>
-      <c r="FZ1" s="27"/>
-      <c r="GA1" s="27"/>
-      <c r="GB1" s="27"/>
-      <c r="GC1" s="27"/>
-      <c r="GD1" s="27"/>
-      <c r="GE1" s="27"/>
-      <c r="GF1" s="27"/>
-      <c r="GG1" s="27"/>
-      <c r="GH1" s="27"/>
-      <c r="GI1" s="27"/>
-      <c r="GJ1" s="27"/>
-      <c r="GK1" s="27"/>
-      <c r="GL1" s="27"/>
-      <c r="GM1" s="27"/>
-      <c r="GN1" s="27"/>
-      <c r="GO1" s="27"/>
-      <c r="GP1" s="27"/>
-      <c r="GQ1" s="27"/>
-      <c r="GR1" s="27"/>
-      <c r="GS1" s="27"/>
-      <c r="GT1" s="27"/>
-      <c r="GU1" s="27"/>
-      <c r="GV1" s="27"/>
-      <c r="GW1" s="27"/>
-      <c r="GX1" s="27"/>
-      <c r="GY1" s="27"/>
-      <c r="GZ1" s="27"/>
-      <c r="HA1" s="27"/>
-      <c r="HB1" s="27"/>
-      <c r="HC1" s="27"/>
-      <c r="HD1" s="27"/>
-      <c r="HE1" s="27"/>
-      <c r="HF1" s="27"/>
-      <c r="HG1" s="27"/>
-      <c r="HH1" s="27"/>
-      <c r="HI1" s="27"/>
-      <c r="HJ1" s="27"/>
-      <c r="HK1" s="27"/>
-      <c r="HL1" s="27"/>
-      <c r="HM1" s="27"/>
-      <c r="HN1" s="27"/>
-      <c r="HO1" s="27"/>
-      <c r="HP1" s="27"/>
-      <c r="HQ1" s="27"/>
-      <c r="HR1" s="27"/>
-      <c r="HS1" s="27"/>
-      <c r="HT1" s="27"/>
-      <c r="HU1" s="27"/>
-      <c r="HV1" s="27"/>
-      <c r="HW1" s="27"/>
-      <c r="HX1" s="27"/>
-      <c r="HY1" s="27"/>
-      <c r="HZ1" s="27"/>
-      <c r="IA1" s="27"/>
-      <c r="IB1" s="27"/>
-      <c r="IC1" s="27"/>
-      <c r="ID1" s="27"/>
-      <c r="IE1" s="27"/>
-      <c r="IF1" s="27"/>
-      <c r="IG1" s="27"/>
-      <c r="IH1" s="27"/>
-      <c r="II1" s="27"/>
-      <c r="IJ1" s="27"/>
-      <c r="IK1" s="27"/>
-      <c r="IL1" s="27"/>
-      <c r="IM1" s="27"/>
-      <c r="IN1" s="27"/>
-      <c r="IO1" s="27"/>
-      <c r="IP1" s="27"/>
-      <c r="IQ1" s="27"/>
-      <c r="IR1" s="27"/>
-      <c r="IS1" s="27"/>
-      <c r="IT1" s="27"/>
-      <c r="IU1" s="27"/>
-      <c r="IV1" s="27"/>
-      <c r="IW1" s="27"/>
-      <c r="IX1" s="27"/>
-      <c r="IY1" s="27"/>
-      <c r="IZ1" s="27"/>
-      <c r="JA1" s="27"/>
-      <c r="JB1" s="27"/>
-      <c r="JC1" s="27"/>
-      <c r="JD1" s="27"/>
-      <c r="JE1" s="27"/>
-      <c r="JF1" s="27"/>
-      <c r="JG1" s="27"/>
-      <c r="JH1" s="27"/>
-      <c r="JI1" s="27"/>
-      <c r="JJ1" s="27"/>
-      <c r="JK1" s="27"/>
-      <c r="JL1" s="27"/>
-      <c r="JM1" s="27"/>
-      <c r="JN1" s="27"/>
-      <c r="JO1" s="27"/>
-      <c r="JP1" s="27"/>
-      <c r="JQ1" s="27"/>
-      <c r="JR1" s="27"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
+      <c r="AQ1" s="35"/>
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="35"/>
+      <c r="AU1" s="35"/>
+      <c r="AV1" s="35"/>
+      <c r="AW1" s="35"/>
+      <c r="AX1" s="35"/>
+      <c r="AY1" s="35"/>
+      <c r="AZ1" s="35"/>
+      <c r="BA1" s="35"/>
+      <c r="BB1" s="35"/>
+      <c r="BC1" s="35"/>
+      <c r="BD1" s="35"/>
+      <c r="BE1" s="35"/>
+      <c r="BF1" s="35"/>
+      <c r="BG1" s="35"/>
+      <c r="BH1" s="35"/>
+      <c r="BI1" s="35"/>
+      <c r="BJ1" s="35"/>
+      <c r="BK1" s="35"/>
+      <c r="BL1" s="35"/>
+      <c r="BM1" s="35"/>
+      <c r="BN1" s="35"/>
+      <c r="BO1" s="35"/>
+      <c r="BP1" s="35"/>
+      <c r="BQ1" s="35"/>
+      <c r="BR1" s="35"/>
+      <c r="BS1" s="35"/>
+      <c r="BT1" s="35"/>
+      <c r="BU1" s="35"/>
+      <c r="BV1" s="35"/>
+      <c r="BW1" s="35"/>
+      <c r="BX1" s="35"/>
+      <c r="BY1" s="35"/>
+      <c r="BZ1" s="35"/>
+      <c r="CA1" s="35"/>
+      <c r="CB1" s="35"/>
+      <c r="CC1" s="35"/>
+      <c r="CD1" s="35"/>
+      <c r="CE1" s="35"/>
+      <c r="CF1" s="35"/>
+      <c r="CG1" s="35"/>
+      <c r="CH1" s="35"/>
+      <c r="CI1" s="35"/>
+      <c r="CJ1" s="35"/>
+      <c r="CK1" s="35"/>
+      <c r="CL1" s="35"/>
+      <c r="CM1" s="35"/>
+      <c r="CN1" s="35"/>
+      <c r="CO1" s="35"/>
+      <c r="CP1" s="35"/>
+      <c r="CQ1" s="35"/>
+      <c r="CR1" s="35"/>
+      <c r="CS1" s="35"/>
+      <c r="CT1" s="35"/>
+      <c r="CU1" s="35"/>
+      <c r="CV1" s="35"/>
+      <c r="CW1" s="35"/>
+      <c r="CX1" s="35"/>
+      <c r="CY1" s="35"/>
+      <c r="CZ1" s="35"/>
+      <c r="DA1" s="35"/>
+      <c r="DB1" s="35"/>
+      <c r="DC1" s="35"/>
+      <c r="DD1" s="35"/>
+      <c r="DE1" s="35"/>
+      <c r="DF1" s="35"/>
+      <c r="DG1" s="35"/>
+      <c r="DH1" s="35"/>
+      <c r="DI1" s="35"/>
+      <c r="DJ1" s="35"/>
+      <c r="DK1" s="35"/>
+      <c r="DL1" s="35"/>
+      <c r="DM1" s="35"/>
+      <c r="DN1" s="35"/>
+      <c r="DO1" s="35"/>
+      <c r="DP1" s="35"/>
+      <c r="DQ1" s="35"/>
+      <c r="DR1" s="35"/>
+      <c r="DS1" s="35"/>
+      <c r="DT1" s="35"/>
+      <c r="DU1" s="35"/>
+      <c r="DV1" s="35"/>
+      <c r="DW1" s="35"/>
+      <c r="DX1" s="35"/>
+      <c r="DY1" s="35"/>
+      <c r="DZ1" s="35"/>
+      <c r="EA1" s="35"/>
+      <c r="EB1" s="35"/>
+      <c r="EC1" s="35"/>
+      <c r="ED1" s="35"/>
+      <c r="EE1" s="35"/>
+      <c r="EF1" s="35"/>
+      <c r="EG1" s="35"/>
+      <c r="EH1" s="35"/>
+      <c r="EI1" s="35"/>
+      <c r="EJ1" s="35"/>
+      <c r="EK1" s="35"/>
+      <c r="EL1" s="35"/>
+      <c r="EM1" s="35"/>
+      <c r="EN1" s="35"/>
+      <c r="EO1" s="35"/>
+      <c r="EP1" s="35"/>
+      <c r="EQ1" s="35"/>
+      <c r="ER1" s="35"/>
+      <c r="ES1" s="35"/>
+      <c r="ET1" s="35"/>
+      <c r="EU1" s="35"/>
+      <c r="EV1" s="35"/>
+      <c r="EW1" s="35"/>
+      <c r="EX1" s="35"/>
+      <c r="EY1" s="35"/>
+      <c r="EZ1" s="35"/>
+      <c r="FA1" s="35"/>
+      <c r="FB1" s="35"/>
+      <c r="FC1" s="35"/>
+      <c r="FD1" s="35"/>
+      <c r="FE1" s="35"/>
+      <c r="FF1" s="35"/>
+      <c r="FG1" s="35"/>
+      <c r="FH1" s="35"/>
+      <c r="FI1" s="35"/>
+      <c r="FJ1" s="35"/>
+      <c r="FK1" s="35"/>
+      <c r="FL1" s="35"/>
+      <c r="FM1" s="35"/>
+      <c r="FN1" s="35"/>
+      <c r="FO1" s="35"/>
+      <c r="FP1" s="35"/>
+      <c r="FQ1" s="35"/>
+      <c r="FR1" s="35"/>
+      <c r="FS1" s="35"/>
+      <c r="FT1" s="35"/>
+      <c r="FU1" s="35"/>
+      <c r="FV1" s="35"/>
+      <c r="FW1" s="35"/>
+      <c r="FX1" s="35"/>
+      <c r="FY1" s="35"/>
+      <c r="FZ1" s="35"/>
+      <c r="GA1" s="35"/>
+      <c r="GB1" s="35"/>
+      <c r="GC1" s="35"/>
+      <c r="GD1" s="35"/>
+      <c r="GE1" s="35"/>
+      <c r="GF1" s="35"/>
+      <c r="GG1" s="35"/>
+      <c r="GH1" s="35"/>
+      <c r="GI1" s="35"/>
+      <c r="GJ1" s="35"/>
+      <c r="GK1" s="35"/>
+      <c r="GL1" s="35"/>
+      <c r="GM1" s="35"/>
+      <c r="GN1" s="35"/>
+      <c r="GO1" s="35"/>
+      <c r="GP1" s="35"/>
+      <c r="GQ1" s="35"/>
+      <c r="GR1" s="35"/>
+      <c r="GS1" s="35"/>
+      <c r="GT1" s="35"/>
+      <c r="GU1" s="35"/>
+      <c r="GV1" s="35"/>
+      <c r="GW1" s="35"/>
+      <c r="GX1" s="35"/>
+      <c r="GY1" s="35"/>
+      <c r="GZ1" s="35"/>
+      <c r="HA1" s="35"/>
+      <c r="HB1" s="35"/>
+      <c r="HC1" s="35"/>
+      <c r="HD1" s="35"/>
+      <c r="HE1" s="35"/>
+      <c r="HF1" s="35"/>
+      <c r="HG1" s="35"/>
+      <c r="HH1" s="35"/>
+      <c r="HI1" s="35"/>
+      <c r="HJ1" s="35"/>
+      <c r="HK1" s="35"/>
+      <c r="HL1" s="35"/>
+      <c r="HM1" s="35"/>
+      <c r="HN1" s="35"/>
+      <c r="HO1" s="35"/>
+      <c r="HP1" s="35"/>
+      <c r="HQ1" s="35"/>
+      <c r="HR1" s="35"/>
+      <c r="HS1" s="35"/>
+      <c r="HT1" s="35"/>
+      <c r="HU1" s="35"/>
+      <c r="HV1" s="35"/>
+      <c r="HW1" s="35"/>
+      <c r="HX1" s="35"/>
+      <c r="HY1" s="35"/>
+      <c r="HZ1" s="35"/>
+      <c r="IA1" s="35"/>
+      <c r="IB1" s="35"/>
+      <c r="IC1" s="35"/>
+      <c r="ID1" s="35"/>
+      <c r="IE1" s="35"/>
+      <c r="IF1" s="35"/>
+      <c r="IG1" s="35"/>
+      <c r="IH1" s="35"/>
+      <c r="II1" s="35"/>
+      <c r="IJ1" s="35"/>
+      <c r="IK1" s="35"/>
+      <c r="IL1" s="35"/>
+      <c r="IM1" s="35"/>
+      <c r="IN1" s="35"/>
+      <c r="IO1" s="35"/>
+      <c r="IP1" s="35"/>
+      <c r="IQ1" s="35"/>
+      <c r="IR1" s="35"/>
+      <c r="IS1" s="35"/>
+      <c r="IT1" s="35"/>
+      <c r="IU1" s="35"/>
+      <c r="IV1" s="35"/>
+      <c r="IW1" s="35"/>
+      <c r="IX1" s="35"/>
+      <c r="IY1" s="35"/>
+      <c r="IZ1" s="35"/>
+      <c r="JA1" s="35"/>
+      <c r="JB1" s="35"/>
+      <c r="JC1" s="35"/>
+      <c r="JD1" s="35"/>
+      <c r="JE1" s="35"/>
+      <c r="JF1" s="35"/>
+      <c r="JG1" s="35"/>
+      <c r="JH1" s="35"/>
+      <c r="JI1" s="35"/>
+      <c r="JJ1" s="35"/>
+      <c r="JK1" s="35"/>
+      <c r="JL1" s="35"/>
+      <c r="JM1" s="35"/>
+      <c r="JN1" s="35"/>
+      <c r="JO1" s="35"/>
+      <c r="JP1" s="35"/>
+      <c r="JQ1" s="35"/>
+      <c r="JR1" s="35"/>
       <c r="JS1" s="10"/>
       <c r="JT1" s="10"/>
     </row>
     <row r="2" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="27"/>
-      <c r="AJ2" s="27"/>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
-      <c r="AT2" s="27"/>
-      <c r="AU2" s="27"/>
-      <c r="AV2" s="27"/>
-      <c r="AW2" s="27"/>
-      <c r="AX2" s="27"/>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
-      <c r="BA2" s="27"/>
-      <c r="BB2" s="27"/>
-      <c r="BC2" s="27"/>
-      <c r="BD2" s="27"/>
-      <c r="BE2" s="27"/>
-      <c r="BF2" s="27"/>
-      <c r="BG2" s="27"/>
-      <c r="BH2" s="27"/>
-      <c r="BI2" s="27"/>
-      <c r="BJ2" s="27"/>
-      <c r="BK2" s="27"/>
-      <c r="BL2" s="27"/>
-      <c r="BM2" s="27"/>
-      <c r="BN2" s="27"/>
-      <c r="BO2" s="27"/>
-      <c r="BP2" s="27"/>
-      <c r="BQ2" s="27"/>
-      <c r="BR2" s="27"/>
-      <c r="BS2" s="27"/>
-      <c r="BT2" s="27"/>
-      <c r="BU2" s="27"/>
-      <c r="BV2" s="27"/>
-      <c r="BW2" s="27"/>
-      <c r="BX2" s="27"/>
-      <c r="BY2" s="27"/>
-      <c r="BZ2" s="27"/>
-      <c r="CA2" s="27"/>
-      <c r="CB2" s="27"/>
-      <c r="CC2" s="27"/>
-      <c r="CD2" s="27"/>
-      <c r="CE2" s="27"/>
-      <c r="CF2" s="27"/>
-      <c r="CG2" s="27"/>
-      <c r="CH2" s="27"/>
-      <c r="CI2" s="27"/>
-      <c r="CJ2" s="27"/>
-      <c r="CK2" s="27"/>
-      <c r="CL2" s="27"/>
-      <c r="CM2" s="27"/>
-      <c r="CN2" s="27"/>
-      <c r="CO2" s="27"/>
-      <c r="CP2" s="27"/>
-      <c r="CQ2" s="27"/>
-      <c r="CR2" s="27"/>
-      <c r="CS2" s="27"/>
-      <c r="CT2" s="27"/>
-      <c r="CU2" s="27"/>
-      <c r="CV2" s="27"/>
-      <c r="CW2" s="27"/>
-      <c r="CX2" s="27"/>
-      <c r="CY2" s="27"/>
-      <c r="CZ2" s="27"/>
-      <c r="DA2" s="27"/>
-      <c r="DB2" s="27"/>
-      <c r="DC2" s="27"/>
-      <c r="DD2" s="27"/>
-      <c r="DE2" s="27"/>
-      <c r="DF2" s="27"/>
-      <c r="DG2" s="27"/>
-      <c r="DH2" s="27"/>
-      <c r="DI2" s="27"/>
-      <c r="DJ2" s="27"/>
-      <c r="DK2" s="27"/>
-      <c r="DL2" s="27"/>
-      <c r="DM2" s="27"/>
-      <c r="DN2" s="27"/>
-      <c r="DO2" s="27"/>
-      <c r="DP2" s="27"/>
-      <c r="DQ2" s="27"/>
-      <c r="DR2" s="27"/>
-      <c r="DS2" s="27"/>
-      <c r="DT2" s="27"/>
-      <c r="DU2" s="27"/>
-      <c r="DV2" s="27"/>
-      <c r="DW2" s="27"/>
-      <c r="DX2" s="27"/>
-      <c r="DY2" s="27"/>
-      <c r="DZ2" s="27"/>
-      <c r="EA2" s="27"/>
-      <c r="EB2" s="27"/>
-      <c r="EC2" s="27"/>
-      <c r="ED2" s="27"/>
-      <c r="EE2" s="27"/>
-      <c r="EF2" s="27"/>
-      <c r="EG2" s="27"/>
-      <c r="EH2" s="27"/>
-      <c r="EI2" s="27"/>
-      <c r="EJ2" s="27"/>
-      <c r="EK2" s="27"/>
-      <c r="EL2" s="27"/>
-      <c r="EM2" s="27"/>
-      <c r="EN2" s="27"/>
-      <c r="EO2" s="27"/>
-      <c r="EP2" s="27"/>
-      <c r="EQ2" s="27"/>
-      <c r="ER2" s="27"/>
-      <c r="ES2" s="27"/>
-      <c r="ET2" s="27"/>
-      <c r="EU2" s="27"/>
-      <c r="EV2" s="27"/>
-      <c r="EW2" s="27"/>
-      <c r="EX2" s="27"/>
-      <c r="EY2" s="27"/>
-      <c r="EZ2" s="27"/>
-      <c r="FA2" s="27"/>
-      <c r="FB2" s="27"/>
-      <c r="FC2" s="27"/>
-      <c r="FD2" s="27"/>
-      <c r="FE2" s="27"/>
-      <c r="FF2" s="27"/>
-      <c r="FG2" s="27"/>
-      <c r="FH2" s="27"/>
-      <c r="FI2" s="27"/>
-      <c r="FJ2" s="27"/>
-      <c r="FK2" s="27"/>
-      <c r="FL2" s="27"/>
-      <c r="FM2" s="27"/>
-      <c r="FN2" s="27"/>
-      <c r="FO2" s="27"/>
-      <c r="FP2" s="27"/>
-      <c r="FQ2" s="27"/>
-      <c r="FR2" s="27"/>
-      <c r="FS2" s="27"/>
-      <c r="FT2" s="27"/>
-      <c r="FU2" s="27"/>
-      <c r="FV2" s="27"/>
-      <c r="FW2" s="27"/>
-      <c r="FX2" s="27"/>
-      <c r="FY2" s="27"/>
-      <c r="FZ2" s="27"/>
-      <c r="GA2" s="27"/>
-      <c r="GB2" s="27"/>
-      <c r="GC2" s="27"/>
-      <c r="GD2" s="27"/>
-      <c r="GE2" s="27"/>
-      <c r="GF2" s="27"/>
-      <c r="GG2" s="27"/>
-      <c r="GH2" s="27"/>
-      <c r="GI2" s="27"/>
-      <c r="GJ2" s="27"/>
-      <c r="GK2" s="27"/>
-      <c r="GL2" s="27"/>
-      <c r="GM2" s="27"/>
-      <c r="GN2" s="27"/>
-      <c r="GO2" s="27"/>
-      <c r="GP2" s="27"/>
-      <c r="GQ2" s="27"/>
-      <c r="GR2" s="27"/>
-      <c r="GS2" s="27"/>
-      <c r="GT2" s="27"/>
-      <c r="GU2" s="27"/>
-      <c r="GV2" s="27"/>
-      <c r="GW2" s="27"/>
-      <c r="GX2" s="27"/>
-      <c r="GY2" s="27"/>
-      <c r="GZ2" s="27"/>
-      <c r="HA2" s="27"/>
-      <c r="HB2" s="27"/>
-      <c r="HC2" s="27"/>
-      <c r="HD2" s="27"/>
-      <c r="HE2" s="27"/>
-      <c r="HF2" s="27"/>
-      <c r="HG2" s="27"/>
-      <c r="HH2" s="27"/>
-      <c r="HI2" s="27"/>
-      <c r="HJ2" s="27"/>
-      <c r="HK2" s="27"/>
-      <c r="HL2" s="27"/>
-      <c r="HM2" s="27"/>
-      <c r="HN2" s="27"/>
-      <c r="HO2" s="27"/>
-      <c r="HP2" s="27"/>
-      <c r="HQ2" s="27"/>
-      <c r="HR2" s="27"/>
-      <c r="HS2" s="27"/>
-      <c r="HT2" s="27"/>
-      <c r="HU2" s="27"/>
-      <c r="HV2" s="27"/>
-      <c r="HW2" s="27"/>
-      <c r="HX2" s="27"/>
-      <c r="HY2" s="27"/>
-      <c r="HZ2" s="27"/>
-      <c r="IA2" s="27"/>
-      <c r="IB2" s="27"/>
-      <c r="IC2" s="27"/>
-      <c r="ID2" s="27"/>
-      <c r="IE2" s="27"/>
-      <c r="IF2" s="27"/>
-      <c r="IG2" s="27"/>
-      <c r="IH2" s="27"/>
-      <c r="II2" s="27"/>
-      <c r="IJ2" s="27"/>
-      <c r="IK2" s="27"/>
-      <c r="IL2" s="27"/>
-      <c r="IM2" s="27"/>
-      <c r="IN2" s="27"/>
-      <c r="IO2" s="27"/>
-      <c r="IP2" s="27"/>
-      <c r="IQ2" s="27"/>
-      <c r="IR2" s="27"/>
-      <c r="IS2" s="27"/>
-      <c r="IT2" s="27"/>
-      <c r="IU2" s="27"/>
-      <c r="IV2" s="27"/>
-      <c r="IW2" s="27"/>
-      <c r="IX2" s="27"/>
-      <c r="IY2" s="27"/>
-      <c r="IZ2" s="27"/>
-      <c r="JA2" s="27"/>
-      <c r="JB2" s="27"/>
-      <c r="JC2" s="27"/>
-      <c r="JD2" s="27"/>
-      <c r="JE2" s="27"/>
-      <c r="JF2" s="27"/>
-      <c r="JG2" s="27"/>
-      <c r="JH2" s="27"/>
-      <c r="JI2" s="27"/>
-      <c r="JJ2" s="27"/>
-      <c r="JK2" s="27"/>
-      <c r="JL2" s="27"/>
-      <c r="JM2" s="27"/>
-      <c r="JN2" s="27"/>
-      <c r="JO2" s="27"/>
-      <c r="JP2" s="27"/>
-      <c r="JQ2" s="27"/>
-      <c r="JR2" s="27"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="35"/>
+      <c r="AU2" s="35"/>
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="35"/>
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="35"/>
+      <c r="BE2" s="35"/>
+      <c r="BF2" s="35"/>
+      <c r="BG2" s="35"/>
+      <c r="BH2" s="35"/>
+      <c r="BI2" s="35"/>
+      <c r="BJ2" s="35"/>
+      <c r="BK2" s="35"/>
+      <c r="BL2" s="35"/>
+      <c r="BM2" s="35"/>
+      <c r="BN2" s="35"/>
+      <c r="BO2" s="35"/>
+      <c r="BP2" s="35"/>
+      <c r="BQ2" s="35"/>
+      <c r="BR2" s="35"/>
+      <c r="BS2" s="35"/>
+      <c r="BT2" s="35"/>
+      <c r="BU2" s="35"/>
+      <c r="BV2" s="35"/>
+      <c r="BW2" s="35"/>
+      <c r="BX2" s="35"/>
+      <c r="BY2" s="35"/>
+      <c r="BZ2" s="35"/>
+      <c r="CA2" s="35"/>
+      <c r="CB2" s="35"/>
+      <c r="CC2" s="35"/>
+      <c r="CD2" s="35"/>
+      <c r="CE2" s="35"/>
+      <c r="CF2" s="35"/>
+      <c r="CG2" s="35"/>
+      <c r="CH2" s="35"/>
+      <c r="CI2" s="35"/>
+      <c r="CJ2" s="35"/>
+      <c r="CK2" s="35"/>
+      <c r="CL2" s="35"/>
+      <c r="CM2" s="35"/>
+      <c r="CN2" s="35"/>
+      <c r="CO2" s="35"/>
+      <c r="CP2" s="35"/>
+      <c r="CQ2" s="35"/>
+      <c r="CR2" s="35"/>
+      <c r="CS2" s="35"/>
+      <c r="CT2" s="35"/>
+      <c r="CU2" s="35"/>
+      <c r="CV2" s="35"/>
+      <c r="CW2" s="35"/>
+      <c r="CX2" s="35"/>
+      <c r="CY2" s="35"/>
+      <c r="CZ2" s="35"/>
+      <c r="DA2" s="35"/>
+      <c r="DB2" s="35"/>
+      <c r="DC2" s="35"/>
+      <c r="DD2" s="35"/>
+      <c r="DE2" s="35"/>
+      <c r="DF2" s="35"/>
+      <c r="DG2" s="35"/>
+      <c r="DH2" s="35"/>
+      <c r="DI2" s="35"/>
+      <c r="DJ2" s="35"/>
+      <c r="DK2" s="35"/>
+      <c r="DL2" s="35"/>
+      <c r="DM2" s="35"/>
+      <c r="DN2" s="35"/>
+      <c r="DO2" s="35"/>
+      <c r="DP2" s="35"/>
+      <c r="DQ2" s="35"/>
+      <c r="DR2" s="35"/>
+      <c r="DS2" s="35"/>
+      <c r="DT2" s="35"/>
+      <c r="DU2" s="35"/>
+      <c r="DV2" s="35"/>
+      <c r="DW2" s="35"/>
+      <c r="DX2" s="35"/>
+      <c r="DY2" s="35"/>
+      <c r="DZ2" s="35"/>
+      <c r="EA2" s="35"/>
+      <c r="EB2" s="35"/>
+      <c r="EC2" s="35"/>
+      <c r="ED2" s="35"/>
+      <c r="EE2" s="35"/>
+      <c r="EF2" s="35"/>
+      <c r="EG2" s="35"/>
+      <c r="EH2" s="35"/>
+      <c r="EI2" s="35"/>
+      <c r="EJ2" s="35"/>
+      <c r="EK2" s="35"/>
+      <c r="EL2" s="35"/>
+      <c r="EM2" s="35"/>
+      <c r="EN2" s="35"/>
+      <c r="EO2" s="35"/>
+      <c r="EP2" s="35"/>
+      <c r="EQ2" s="35"/>
+      <c r="ER2" s="35"/>
+      <c r="ES2" s="35"/>
+      <c r="ET2" s="35"/>
+      <c r="EU2" s="35"/>
+      <c r="EV2" s="35"/>
+      <c r="EW2" s="35"/>
+      <c r="EX2" s="35"/>
+      <c r="EY2" s="35"/>
+      <c r="EZ2" s="35"/>
+      <c r="FA2" s="35"/>
+      <c r="FB2" s="35"/>
+      <c r="FC2" s="35"/>
+      <c r="FD2" s="35"/>
+      <c r="FE2" s="35"/>
+      <c r="FF2" s="35"/>
+      <c r="FG2" s="35"/>
+      <c r="FH2" s="35"/>
+      <c r="FI2" s="35"/>
+      <c r="FJ2" s="35"/>
+      <c r="FK2" s="35"/>
+      <c r="FL2" s="35"/>
+      <c r="FM2" s="35"/>
+      <c r="FN2" s="35"/>
+      <c r="FO2" s="35"/>
+      <c r="FP2" s="35"/>
+      <c r="FQ2" s="35"/>
+      <c r="FR2" s="35"/>
+      <c r="FS2" s="35"/>
+      <c r="FT2" s="35"/>
+      <c r="FU2" s="35"/>
+      <c r="FV2" s="35"/>
+      <c r="FW2" s="35"/>
+      <c r="FX2" s="35"/>
+      <c r="FY2" s="35"/>
+      <c r="FZ2" s="35"/>
+      <c r="GA2" s="35"/>
+      <c r="GB2" s="35"/>
+      <c r="GC2" s="35"/>
+      <c r="GD2" s="35"/>
+      <c r="GE2" s="35"/>
+      <c r="GF2" s="35"/>
+      <c r="GG2" s="35"/>
+      <c r="GH2" s="35"/>
+      <c r="GI2" s="35"/>
+      <c r="GJ2" s="35"/>
+      <c r="GK2" s="35"/>
+      <c r="GL2" s="35"/>
+      <c r="GM2" s="35"/>
+      <c r="GN2" s="35"/>
+      <c r="GO2" s="35"/>
+      <c r="GP2" s="35"/>
+      <c r="GQ2" s="35"/>
+      <c r="GR2" s="35"/>
+      <c r="GS2" s="35"/>
+      <c r="GT2" s="35"/>
+      <c r="GU2" s="35"/>
+      <c r="GV2" s="35"/>
+      <c r="GW2" s="35"/>
+      <c r="GX2" s="35"/>
+      <c r="GY2" s="35"/>
+      <c r="GZ2" s="35"/>
+      <c r="HA2" s="35"/>
+      <c r="HB2" s="35"/>
+      <c r="HC2" s="35"/>
+      <c r="HD2" s="35"/>
+      <c r="HE2" s="35"/>
+      <c r="HF2" s="35"/>
+      <c r="HG2" s="35"/>
+      <c r="HH2" s="35"/>
+      <c r="HI2" s="35"/>
+      <c r="HJ2" s="35"/>
+      <c r="HK2" s="35"/>
+      <c r="HL2" s="35"/>
+      <c r="HM2" s="35"/>
+      <c r="HN2" s="35"/>
+      <c r="HO2" s="35"/>
+      <c r="HP2" s="35"/>
+      <c r="HQ2" s="35"/>
+      <c r="HR2" s="35"/>
+      <c r="HS2" s="35"/>
+      <c r="HT2" s="35"/>
+      <c r="HU2" s="35"/>
+      <c r="HV2" s="35"/>
+      <c r="HW2" s="35"/>
+      <c r="HX2" s="35"/>
+      <c r="HY2" s="35"/>
+      <c r="HZ2" s="35"/>
+      <c r="IA2" s="35"/>
+      <c r="IB2" s="35"/>
+      <c r="IC2" s="35"/>
+      <c r="ID2" s="35"/>
+      <c r="IE2" s="35"/>
+      <c r="IF2" s="35"/>
+      <c r="IG2" s="35"/>
+      <c r="IH2" s="35"/>
+      <c r="II2" s="35"/>
+      <c r="IJ2" s="35"/>
+      <c r="IK2" s="35"/>
+      <c r="IL2" s="35"/>
+      <c r="IM2" s="35"/>
+      <c r="IN2" s="35"/>
+      <c r="IO2" s="35"/>
+      <c r="IP2" s="35"/>
+      <c r="IQ2" s="35"/>
+      <c r="IR2" s="35"/>
+      <c r="IS2" s="35"/>
+      <c r="IT2" s="35"/>
+      <c r="IU2" s="35"/>
+      <c r="IV2" s="35"/>
+      <c r="IW2" s="35"/>
+      <c r="IX2" s="35"/>
+      <c r="IY2" s="35"/>
+      <c r="IZ2" s="35"/>
+      <c r="JA2" s="35"/>
+      <c r="JB2" s="35"/>
+      <c r="JC2" s="35"/>
+      <c r="JD2" s="35"/>
+      <c r="JE2" s="35"/>
+      <c r="JF2" s="35"/>
+      <c r="JG2" s="35"/>
+      <c r="JH2" s="35"/>
+      <c r="JI2" s="35"/>
+      <c r="JJ2" s="35"/>
+      <c r="JK2" s="35"/>
+      <c r="JL2" s="35"/>
+      <c r="JM2" s="35"/>
+      <c r="JN2" s="35"/>
+      <c r="JO2" s="35"/>
+      <c r="JP2" s="35"/>
+      <c r="JQ2" s="35"/>
+      <c r="JR2" s="35"/>
       <c r="JS2" s="10"/>
       <c r="JT2" s="10"/>
     </row>
     <row r="4" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="29">
+      <c r="B4" s="27">
         <v>2003</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27">
         <v>2004</v>
       </c>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29">
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27">
         <v>2005</v>
       </c>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29">
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27">
         <v>2006</v>
       </c>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="29"/>
-      <c r="AV4" s="29"/>
-      <c r="AW4" s="29"/>
-      <c r="AX4" s="29">
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="27"/>
+      <c r="AW4" s="27"/>
+      <c r="AX4" s="27">
         <v>2007</v>
       </c>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29">
+      <c r="AY4" s="27"/>
+      <c r="AZ4" s="27"/>
+      <c r="BA4" s="27"/>
+      <c r="BB4" s="27"/>
+      <c r="BC4" s="27"/>
+      <c r="BD4" s="27"/>
+      <c r="BE4" s="27"/>
+      <c r="BF4" s="27"/>
+      <c r="BG4" s="27"/>
+      <c r="BH4" s="27"/>
+      <c r="BI4" s="27"/>
+      <c r="BJ4" s="27">
         <v>2008</v>
       </c>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29">
+      <c r="BK4" s="27"/>
+      <c r="BL4" s="27"/>
+      <c r="BM4" s="27"/>
+      <c r="BN4" s="27"/>
+      <c r="BO4" s="27"/>
+      <c r="BP4" s="27"/>
+      <c r="BQ4" s="27"/>
+      <c r="BR4" s="27"/>
+      <c r="BS4" s="27"/>
+      <c r="BT4" s="27"/>
+      <c r="BU4" s="27"/>
+      <c r="BV4" s="27">
         <v>2009</v>
       </c>
-      <c r="BW4" s="29"/>
-      <c r="BX4" s="29"/>
-      <c r="BY4" s="29"/>
-      <c r="BZ4" s="29"/>
-      <c r="CA4" s="29"/>
-      <c r="CB4" s="29"/>
-      <c r="CC4" s="29"/>
-      <c r="CD4" s="29"/>
-      <c r="CE4" s="29"/>
-      <c r="CF4" s="29"/>
-      <c r="CG4" s="29"/>
-      <c r="CH4" s="29">
+      <c r="BW4" s="27"/>
+      <c r="BX4" s="27"/>
+      <c r="BY4" s="27"/>
+      <c r="BZ4" s="27"/>
+      <c r="CA4" s="27"/>
+      <c r="CB4" s="27"/>
+      <c r="CC4" s="27"/>
+      <c r="CD4" s="27"/>
+      <c r="CE4" s="27"/>
+      <c r="CF4" s="27"/>
+      <c r="CG4" s="27"/>
+      <c r="CH4" s="27">
         <v>2010</v>
       </c>
-      <c r="CI4" s="29"/>
-      <c r="CJ4" s="29"/>
-      <c r="CK4" s="29"/>
-      <c r="CL4" s="29"/>
-      <c r="CM4" s="29"/>
-      <c r="CN4" s="29"/>
-      <c r="CO4" s="29"/>
-      <c r="CP4" s="29"/>
-      <c r="CQ4" s="29"/>
-      <c r="CR4" s="29"/>
-      <c r="CS4" s="29"/>
-      <c r="CT4" s="29">
+      <c r="CI4" s="27"/>
+      <c r="CJ4" s="27"/>
+      <c r="CK4" s="27"/>
+      <c r="CL4" s="27"/>
+      <c r="CM4" s="27"/>
+      <c r="CN4" s="27"/>
+      <c r="CO4" s="27"/>
+      <c r="CP4" s="27"/>
+      <c r="CQ4" s="27"/>
+      <c r="CR4" s="27"/>
+      <c r="CS4" s="27"/>
+      <c r="CT4" s="27">
         <v>2011</v>
       </c>
-      <c r="CU4" s="29"/>
-      <c r="CV4" s="29"/>
-      <c r="CW4" s="29"/>
-      <c r="CX4" s="29"/>
-      <c r="CY4" s="29"/>
-      <c r="CZ4" s="29"/>
-      <c r="DA4" s="29"/>
-      <c r="DB4" s="29"/>
-      <c r="DC4" s="29"/>
-      <c r="DD4" s="29"/>
-      <c r="DE4" s="29"/>
-      <c r="DF4" s="29">
+      <c r="CU4" s="27"/>
+      <c r="CV4" s="27"/>
+      <c r="CW4" s="27"/>
+      <c r="CX4" s="27"/>
+      <c r="CY4" s="27"/>
+      <c r="CZ4" s="27"/>
+      <c r="DA4" s="27"/>
+      <c r="DB4" s="27"/>
+      <c r="DC4" s="27"/>
+      <c r="DD4" s="27"/>
+      <c r="DE4" s="27"/>
+      <c r="DF4" s="27">
         <v>2012</v>
       </c>
-      <c r="DG4" s="29"/>
-      <c r="DH4" s="29"/>
-      <c r="DI4" s="29"/>
-      <c r="DJ4" s="29"/>
-      <c r="DK4" s="29"/>
-      <c r="DL4" s="29"/>
-      <c r="DM4" s="29"/>
-      <c r="DN4" s="29"/>
-      <c r="DO4" s="29"/>
-      <c r="DP4" s="29"/>
-      <c r="DQ4" s="29"/>
-      <c r="DR4" s="29">
+      <c r="DG4" s="27"/>
+      <c r="DH4" s="27"/>
+      <c r="DI4" s="27"/>
+      <c r="DJ4" s="27"/>
+      <c r="DK4" s="27"/>
+      <c r="DL4" s="27"/>
+      <c r="DM4" s="27"/>
+      <c r="DN4" s="27"/>
+      <c r="DO4" s="27"/>
+      <c r="DP4" s="27"/>
+      <c r="DQ4" s="27"/>
+      <c r="DR4" s="27">
         <v>2013</v>
       </c>
-      <c r="DS4" s="29"/>
-      <c r="DT4" s="29"/>
-      <c r="DU4" s="29"/>
-      <c r="DV4" s="29"/>
-      <c r="DW4" s="29"/>
-      <c r="DX4" s="29"/>
-      <c r="DY4" s="29"/>
-      <c r="DZ4" s="29"/>
-      <c r="EA4" s="29"/>
-      <c r="EB4" s="29"/>
-      <c r="EC4" s="29"/>
-      <c r="ED4" s="29">
+      <c r="DS4" s="27"/>
+      <c r="DT4" s="27"/>
+      <c r="DU4" s="27"/>
+      <c r="DV4" s="27"/>
+      <c r="DW4" s="27"/>
+      <c r="DX4" s="27"/>
+      <c r="DY4" s="27"/>
+      <c r="DZ4" s="27"/>
+      <c r="EA4" s="27"/>
+      <c r="EB4" s="27"/>
+      <c r="EC4" s="27"/>
+      <c r="ED4" s="27">
         <v>2014</v>
       </c>
-      <c r="EE4" s="29"/>
-      <c r="EF4" s="29"/>
-      <c r="EG4" s="29"/>
-      <c r="EH4" s="29"/>
-      <c r="EI4" s="29"/>
-      <c r="EJ4" s="29"/>
-      <c r="EK4" s="29"/>
-      <c r="EL4" s="29"/>
-      <c r="EM4" s="29"/>
-      <c r="EN4" s="29"/>
-      <c r="EO4" s="29"/>
-      <c r="EP4" s="29">
+      <c r="EE4" s="27"/>
+      <c r="EF4" s="27"/>
+      <c r="EG4" s="27"/>
+      <c r="EH4" s="27"/>
+      <c r="EI4" s="27"/>
+      <c r="EJ4" s="27"/>
+      <c r="EK4" s="27"/>
+      <c r="EL4" s="27"/>
+      <c r="EM4" s="27"/>
+      <c r="EN4" s="27"/>
+      <c r="EO4" s="27"/>
+      <c r="EP4" s="27">
         <v>2015</v>
       </c>
-      <c r="EQ4" s="29"/>
-      <c r="ER4" s="29"/>
-      <c r="ES4" s="29"/>
-      <c r="ET4" s="29"/>
-      <c r="EU4" s="29"/>
-      <c r="EV4" s="29"/>
-      <c r="EW4" s="29"/>
-      <c r="EX4" s="29"/>
-      <c r="EY4" s="29"/>
-      <c r="EZ4" s="29"/>
-      <c r="FA4" s="29"/>
-      <c r="FB4" s="29">
+      <c r="EQ4" s="27"/>
+      <c r="ER4" s="27"/>
+      <c r="ES4" s="27"/>
+      <c r="ET4" s="27"/>
+      <c r="EU4" s="27"/>
+      <c r="EV4" s="27"/>
+      <c r="EW4" s="27"/>
+      <c r="EX4" s="27"/>
+      <c r="EY4" s="27"/>
+      <c r="EZ4" s="27"/>
+      <c r="FA4" s="27"/>
+      <c r="FB4" s="27">
         <v>2016</v>
       </c>
-      <c r="FC4" s="29"/>
-      <c r="FD4" s="29"/>
-      <c r="FE4" s="29"/>
-      <c r="FF4" s="29"/>
-      <c r="FG4" s="29"/>
-      <c r="FH4" s="29"/>
-      <c r="FI4" s="29"/>
-      <c r="FJ4" s="29"/>
-      <c r="FK4" s="29"/>
-      <c r="FL4" s="29"/>
-      <c r="FM4" s="29"/>
-      <c r="FN4" s="29">
+      <c r="FC4" s="27"/>
+      <c r="FD4" s="27"/>
+      <c r="FE4" s="27"/>
+      <c r="FF4" s="27"/>
+      <c r="FG4" s="27"/>
+      <c r="FH4" s="27"/>
+      <c r="FI4" s="27"/>
+      <c r="FJ4" s="27"/>
+      <c r="FK4" s="27"/>
+      <c r="FL4" s="27"/>
+      <c r="FM4" s="27"/>
+      <c r="FN4" s="27">
         <v>2017</v>
       </c>
-      <c r="FO4" s="29"/>
-      <c r="FP4" s="29"/>
-      <c r="FQ4" s="29"/>
-      <c r="FR4" s="29"/>
-      <c r="FS4" s="29"/>
-      <c r="FT4" s="29"/>
-      <c r="FU4" s="29"/>
-      <c r="FV4" s="29"/>
-      <c r="FW4" s="29"/>
-      <c r="FX4" s="29"/>
-      <c r="FY4" s="29"/>
-      <c r="FZ4" s="29">
+      <c r="FO4" s="27"/>
+      <c r="FP4" s="27"/>
+      <c r="FQ4" s="27"/>
+      <c r="FR4" s="27"/>
+      <c r="FS4" s="27"/>
+      <c r="FT4" s="27"/>
+      <c r="FU4" s="27"/>
+      <c r="FV4" s="27"/>
+      <c r="FW4" s="27"/>
+      <c r="FX4" s="27"/>
+      <c r="FY4" s="27"/>
+      <c r="FZ4" s="27">
         <v>2018</v>
       </c>
-      <c r="GA4" s="29"/>
-      <c r="GB4" s="29"/>
-      <c r="GC4" s="29"/>
-      <c r="GD4" s="29"/>
-      <c r="GE4" s="29"/>
-      <c r="GF4" s="29"/>
-      <c r="GG4" s="29"/>
-      <c r="GH4" s="29"/>
-      <c r="GI4" s="29"/>
-      <c r="GJ4" s="29"/>
-      <c r="GK4" s="29"/>
-      <c r="GL4" s="29">
+      <c r="GA4" s="27"/>
+      <c r="GB4" s="27"/>
+      <c r="GC4" s="27"/>
+      <c r="GD4" s="27"/>
+      <c r="GE4" s="27"/>
+      <c r="GF4" s="27"/>
+      <c r="GG4" s="27"/>
+      <c r="GH4" s="27"/>
+      <c r="GI4" s="27"/>
+      <c r="GJ4" s="27"/>
+      <c r="GK4" s="27"/>
+      <c r="GL4" s="27">
         <v>2019</v>
       </c>
-      <c r="GM4" s="29"/>
-      <c r="GN4" s="29"/>
-      <c r="GO4" s="29"/>
-      <c r="GP4" s="29"/>
-      <c r="GQ4" s="29"/>
-      <c r="GR4" s="29"/>
-      <c r="GS4" s="29"/>
-      <c r="GT4" s="29"/>
-      <c r="GU4" s="29"/>
-      <c r="GV4" s="29"/>
-      <c r="GW4" s="29"/>
-      <c r="GX4" s="29">
+      <c r="GM4" s="27"/>
+      <c r="GN4" s="27"/>
+      <c r="GO4" s="27"/>
+      <c r="GP4" s="27"/>
+      <c r="GQ4" s="27"/>
+      <c r="GR4" s="27"/>
+      <c r="GS4" s="27"/>
+      <c r="GT4" s="27"/>
+      <c r="GU4" s="27"/>
+      <c r="GV4" s="27"/>
+      <c r="GW4" s="27"/>
+      <c r="GX4" s="27">
         <v>2020</v>
       </c>
-      <c r="GY4" s="29"/>
-      <c r="GZ4" s="29"/>
-      <c r="HA4" s="29"/>
-      <c r="HB4" s="29"/>
-      <c r="HC4" s="29"/>
-      <c r="HD4" s="29"/>
-      <c r="HE4" s="29"/>
-      <c r="HF4" s="29"/>
-      <c r="HG4" s="29"/>
-      <c r="HH4" s="29"/>
-      <c r="HI4" s="29"/>
-      <c r="HJ4" s="29">
+      <c r="GY4" s="27"/>
+      <c r="GZ4" s="27"/>
+      <c r="HA4" s="27"/>
+      <c r="HB4" s="27"/>
+      <c r="HC4" s="27"/>
+      <c r="HD4" s="27"/>
+      <c r="HE4" s="27"/>
+      <c r="HF4" s="27"/>
+      <c r="HG4" s="27"/>
+      <c r="HH4" s="27"/>
+      <c r="HI4" s="27"/>
+      <c r="HJ4" s="27">
         <v>2021</v>
       </c>
-      <c r="HK4" s="29"/>
-      <c r="HL4" s="29"/>
-      <c r="HM4" s="29"/>
-      <c r="HN4" s="29"/>
-      <c r="HO4" s="29"/>
-      <c r="HP4" s="29"/>
-      <c r="HQ4" s="29"/>
-      <c r="HR4" s="29"/>
-      <c r="HS4" s="29"/>
-      <c r="HT4" s="29"/>
-      <c r="HU4" s="29"/>
-      <c r="HV4" s="29">
+      <c r="HK4" s="27"/>
+      <c r="HL4" s="27"/>
+      <c r="HM4" s="27"/>
+      <c r="HN4" s="27"/>
+      <c r="HO4" s="27"/>
+      <c r="HP4" s="27"/>
+      <c r="HQ4" s="27"/>
+      <c r="HR4" s="27"/>
+      <c r="HS4" s="27"/>
+      <c r="HT4" s="27"/>
+      <c r="HU4" s="27"/>
+      <c r="HV4" s="27">
         <v>2022</v>
       </c>
-      <c r="HW4" s="29"/>
-      <c r="HX4" s="29"/>
-      <c r="HY4" s="29"/>
-      <c r="HZ4" s="29"/>
-      <c r="IA4" s="29"/>
-      <c r="IB4" s="29"/>
-      <c r="IC4" s="29"/>
-      <c r="ID4" s="29"/>
-      <c r="IE4" s="29"/>
-      <c r="IF4" s="29"/>
-      <c r="IG4" s="29"/>
-      <c r="IH4" s="29">
+      <c r="HW4" s="27"/>
+      <c r="HX4" s="27"/>
+      <c r="HY4" s="27"/>
+      <c r="HZ4" s="27"/>
+      <c r="IA4" s="27"/>
+      <c r="IB4" s="27"/>
+      <c r="IC4" s="27"/>
+      <c r="ID4" s="27"/>
+      <c r="IE4" s="27"/>
+      <c r="IF4" s="27"/>
+      <c r="IG4" s="27"/>
+      <c r="IH4" s="27">
         <v>2023</v>
       </c>
-      <c r="II4" s="29"/>
-      <c r="IJ4" s="29"/>
-      <c r="IK4" s="29"/>
-      <c r="IL4" s="29"/>
-      <c r="IM4" s="29"/>
-      <c r="IN4" s="29"/>
-      <c r="IO4" s="29"/>
-      <c r="IP4" s="29"/>
-      <c r="IQ4" s="29"/>
-      <c r="IR4" s="29"/>
-      <c r="IS4" s="29"/>
-      <c r="IT4" s="29">
+      <c r="II4" s="27"/>
+      <c r="IJ4" s="27"/>
+      <c r="IK4" s="27"/>
+      <c r="IL4" s="27"/>
+      <c r="IM4" s="27"/>
+      <c r="IN4" s="27"/>
+      <c r="IO4" s="27"/>
+      <c r="IP4" s="27"/>
+      <c r="IQ4" s="27"/>
+      <c r="IR4" s="27"/>
+      <c r="IS4" s="27"/>
+      <c r="IT4" s="27">
         <v>2024</v>
       </c>
-      <c r="IU4" s="29"/>
-      <c r="IV4" s="29"/>
-      <c r="IW4" s="29"/>
-      <c r="IX4" s="29"/>
-      <c r="IY4" s="29"/>
-      <c r="IZ4" s="29"/>
-      <c r="JA4" s="29"/>
-      <c r="JB4" s="29"/>
-      <c r="JC4" s="29"/>
-      <c r="JD4" s="29"/>
-      <c r="JE4" s="29"/>
-      <c r="JF4" s="29">
+      <c r="IU4" s="27"/>
+      <c r="IV4" s="27"/>
+      <c r="IW4" s="27"/>
+      <c r="IX4" s="27"/>
+      <c r="IY4" s="27"/>
+      <c r="IZ4" s="27"/>
+      <c r="JA4" s="27"/>
+      <c r="JB4" s="27"/>
+      <c r="JC4" s="27"/>
+      <c r="JD4" s="27"/>
+      <c r="JE4" s="27"/>
+      <c r="JF4" s="27">
         <v>2025</v>
       </c>
-      <c r="JG4" s="29"/>
-      <c r="JH4" s="29"/>
-      <c r="JI4" s="29"/>
-      <c r="JJ4" s="29"/>
-      <c r="JK4" s="29"/>
-      <c r="JL4" s="29"/>
-      <c r="JM4" s="29"/>
-      <c r="JN4" s="29"/>
-      <c r="JO4" s="29"/>
-      <c r="JP4" s="29"/>
-      <c r="JQ4" s="31"/>
-      <c r="JR4" s="34">
+      <c r="JG4" s="27"/>
+      <c r="JH4" s="27"/>
+      <c r="JI4" s="27"/>
+      <c r="JJ4" s="27"/>
+      <c r="JK4" s="27"/>
+      <c r="JL4" s="27"/>
+      <c r="JM4" s="27"/>
+      <c r="JN4" s="27"/>
+      <c r="JO4" s="27"/>
+      <c r="JP4" s="27"/>
+      <c r="JQ4" s="28"/>
+      <c r="JR4" s="31">
         <v>2026</v>
       </c>
-      <c r="JS4" s="35"/>
-      <c r="JT4" s="36"/>
+      <c r="JS4" s="32"/>
+      <c r="JT4" s="33"/>
     </row>
     <row r="5" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -3405,13 +3405,13 @@
         <v>3974.17366249928</v>
       </c>
       <c r="JR6" s="5">
-        <v>1037.1023270143301</v>
+        <v>2138.82960815872</v>
       </c>
       <c r="JS6" s="13">
-        <v>-457.65576820684998</v>
+        <v>-518.41899183017995</v>
       </c>
       <c r="JT6" s="13">
-        <v>-1791.9971723619001</v>
+        <v>-1460.1505925306999</v>
       </c>
     </row>
     <row r="7" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -4247,13 +4247,13 @@
         <v>2545.5674864677098</v>
       </c>
       <c r="JR7" s="5">
-        <v>5643.3152426397301</v>
+        <v>6127.6722382961698</v>
       </c>
       <c r="JS7" s="13">
-        <v>-144.26505840165001</v>
+        <v>-369.58207491623</v>
       </c>
       <c r="JT7" s="13">
-        <v>-630.65916268001001</v>
+        <v>-277.06233034326999</v>
       </c>
     </row>
     <row r="8" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5089,13 +5089,13 @@
         <v>-1428.6061760315999</v>
       </c>
       <c r="JR8" s="5">
-        <v>4606.2129156253995</v>
+        <v>3988.8426301374402</v>
       </c>
       <c r="JS8" s="13">
-        <v>313.39070980519801</v>
+        <v>148.836916913956</v>
       </c>
       <c r="JT8" s="13">
-        <v>1161.3380096818801</v>
+        <v>1183.08826218742</v>
       </c>
     </row>
     <row r="9" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5931,13 +5931,13 @@
         <v>1233.07357156632</v>
       </c>
       <c r="JR9" s="5">
-        <v>-814.63135498387999</v>
+        <v>-971.24616424773001</v>
       </c>
       <c r="JS9" s="13">
-        <v>-1715.9752870149</v>
+        <v>-1285.6921412924</v>
       </c>
       <c r="JT9" s="13">
-        <v>-123.21843762915</v>
+        <v>-97.568136275667001</v>
       </c>
     </row>
     <row r="10" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -6773,13 +6773,13 @@
         <v>662.62178358904805</v>
       </c>
       <c r="JR10" s="7">
-        <v>988.75207400264503</v>
+        <v>1009.45025458903</v>
       </c>
       <c r="JS10" s="14">
-        <v>850.35542422505398</v>
+        <v>1045.9037535638399</v>
       </c>
       <c r="JT10" s="14">
-        <v>993.340014061283</v>
+        <v>1041.11875823281</v>
       </c>
     </row>
     <row r="11" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7615,13 +7615,13 @@
         <v>297.85444083016603</v>
       </c>
       <c r="JR11" s="7">
-        <v>303.45890342688199</v>
+        <v>311.37105533178999</v>
       </c>
       <c r="JS11" s="14">
-        <v>172.615561669253</v>
+        <v>174.448572229056</v>
       </c>
       <c r="JT11" s="14">
-        <v>246.56366097202499</v>
+        <v>189.36118779202499</v>
       </c>
     </row>
     <row r="12" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8457,13 +8457,13 @@
         <v>-108.24556839164001</v>
       </c>
       <c r="JR12" s="7">
-        <v>51.044465554100597</v>
+        <v>111.800251020009</v>
       </c>
       <c r="JS12" s="14">
-        <v>153.39134869341899</v>
+        <v>398.29988587829598</v>
       </c>
       <c r="JT12" s="14">
-        <v>592.13699388596501</v>
+        <v>656.91137890075902</v>
       </c>
     </row>
     <row r="13" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -9299,13 +9299,13 @@
         <v>473.012911150523</v>
       </c>
       <c r="JR13" s="7">
-        <v>634.248705021663</v>
+        <v>586.27894823723</v>
       </c>
       <c r="JS13" s="14">
-        <v>524.34851386238199</v>
+        <v>473.15529545648297</v>
       </c>
       <c r="JT13" s="14">
-        <v>154.639359203293</v>
+        <v>194.84619154002601</v>
       </c>
     </row>
     <row r="14" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10141,13 +10141,13 @@
         <v>-570.45178797726999</v>
       </c>
       <c r="JR14" s="7">
-        <v>1803.3834289865299</v>
+        <v>1980.6964188367599</v>
       </c>
       <c r="JS14" s="14">
-        <v>2566.3307112399598</v>
+        <v>2331.5958948562802</v>
       </c>
       <c r="JT14" s="14">
-        <v>1116.5584516904401</v>
+        <v>1138.68689450848</v>
       </c>
     </row>
     <row r="15" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10986,7 +10986,7 @@
         <v>272.365870470939</v>
       </c>
       <c r="JS15" s="14">
-        <v>175.55531654080701</v>
+        <v>176.555316063584</v>
       </c>
       <c r="JT15" s="14">
         <v>215.926776724597</v>
@@ -11825,13 +11825,13 @@
         <v>-338.88658230031001</v>
       </c>
       <c r="JR16" s="7">
-        <v>53.8616785100442</v>
+        <v>152.279183597117</v>
       </c>
       <c r="JS16" s="14">
-        <v>559.13327007328905</v>
+        <v>280.189612980986</v>
       </c>
       <c r="JT16" s="14">
-        <v>0.22057358829779999</v>
+        <v>41.645399171630999</v>
       </c>
     </row>
     <row r="17" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -12667,13 +12667,13 @@
         <v>-777.66056092955</v>
       </c>
       <c r="JR17" s="7">
-        <v>1477.15588000554</v>
+        <v>1556.0513647687101</v>
       </c>
       <c r="JS17" s="14">
-        <v>1831.6421246258601</v>
+        <v>1874.85096581172</v>
       </c>
       <c r="JT17" s="14">
-        <v>900.41110137754299</v>
+        <v>881.11471861224902</v>
       </c>
     </row>
     <row r="18" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -13509,13 +13509,13 @@
         <v>814.24194154188399</v>
       </c>
       <c r="JR18" s="5">
-        <v>-3354.4657471342998</v>
+        <v>-3198.4949310827001</v>
       </c>
       <c r="JS18" s="13">
-        <v>1936.88908388811</v>
+        <v>2204.6550268201299</v>
       </c>
       <c r="JT18" s="13">
-        <v>-869.06357683322005</v>
+        <v>-601.01338652072002</v>
       </c>
     </row>
     <row r="19" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14351,13 +14351,13 @@
         <v>1433.2682599829</v>
       </c>
       <c r="JR19" s="7">
-        <v>1219.2364803358</v>
+        <v>1340.28084183186</v>
       </c>
       <c r="JS19" s="14">
-        <v>2493.6477855128901</v>
+        <v>2609.7229876311599</v>
       </c>
       <c r="JT19" s="14">
-        <v>235.45631309248199</v>
+        <v>503.12831309248202</v>
       </c>
     </row>
     <row r="20" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15193,10 +15193,10 @@
         <v>1513.49289597231</v>
       </c>
       <c r="JR20" s="7">
-        <v>1295.16391503002</v>
+        <v>1417.3254955534101</v>
       </c>
       <c r="JS20" s="14">
-        <v>2303.8337792542002</v>
+        <v>2421.38375465013</v>
       </c>
       <c r="JT20" s="14">
         <v>369.39918577771198</v>
@@ -16035,13 +16035,13 @@
         <v>-80.224635989416996</v>
       </c>
       <c r="JR21" s="7">
-        <v>-75.927434694229007</v>
+        <v>-77.044653721553004</v>
       </c>
       <c r="JS21" s="14">
-        <v>189.81400625869199</v>
+        <v>188.33923298103301</v>
       </c>
       <c r="JT21" s="14">
-        <v>-133.94287268522999</v>
+        <v>133.72912731477001</v>
       </c>
     </row>
     <row r="22" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16877,13 +16877,13 @@
         <v>-88.998454208734003</v>
       </c>
       <c r="JR22" s="7">
-        <v>185.25839893528101</v>
+        <v>199.699581072477</v>
       </c>
       <c r="JS22" s="14">
-        <v>225.029749125206</v>
+        <v>187.771822123108</v>
       </c>
       <c r="JT22" s="14">
-        <v>301.71439026306598</v>
+        <v>321.09039026306601</v>
       </c>
     </row>
     <row r="23" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17719,13 +17719,13 @@
         <v>8.7738182193175902</v>
       </c>
       <c r="JR23" s="7">
-        <v>-261.18583362951</v>
+        <v>-276.74423479402998</v>
       </c>
       <c r="JS23" s="14">
-        <v>-35.215742866513999</v>
+        <v>0.56741085792533996</v>
       </c>
       <c r="JT23" s="14">
-        <v>-435.6572629483</v>
+        <v>-187.36126294830001</v>
       </c>
     </row>
     <row r="24" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18561,13 +18561,13 @@
         <v>619.02631844101199</v>
       </c>
       <c r="JR24" s="7">
-        <v>4573.7022274701303</v>
+        <v>4538.7757729145897</v>
       </c>
       <c r="JS24" s="14">
-        <v>556.75870162478202</v>
+        <v>405.06796081102402</v>
       </c>
       <c r="JT24" s="14">
-        <v>1104.5198899257</v>
+        <v>1104.1416996132</v>
       </c>
     </row>
     <row r="25" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20245,13 +20245,13 @@
         <v>761.33563826064403</v>
       </c>
       <c r="JR26" s="7">
-        <v>4442.8478312029101</v>
+        <v>4407.9213766473704</v>
       </c>
       <c r="JS26" s="14">
-        <v>992.63727698604498</v>
+        <v>840.94653617228801</v>
       </c>
       <c r="JT26" s="14">
-        <v>1259.19176117249</v>
+        <v>1258.81357085999</v>
       </c>
     </row>
     <row r="27" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -21087,10 +21087,10 @@
         <v>769.70208234903896</v>
       </c>
       <c r="JR27" s="7">
-        <v>4782.7133550756398</v>
+        <v>4748.1650910410899</v>
       </c>
       <c r="JS27" s="14">
-        <v>775.04262379891895</v>
+        <v>792.71235928617295</v>
       </c>
       <c r="JT27" s="14">
         <v>637.39290799523303</v>
@@ -21929,13 +21929,13 @@
         <v>-8.3664440883954008</v>
       </c>
       <c r="JR28" s="7">
-        <v>-339.86552387273002</v>
+        <v>-340.24371439371998</v>
       </c>
       <c r="JS28" s="14">
-        <v>217.594653187126</v>
+        <v>48.234176886114199</v>
       </c>
       <c r="JT28" s="14">
-        <v>621.79885317725302</v>
+        <v>621.42066286475301</v>
       </c>
     </row>
     <row r="29" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22771,10 +22771,10 @@
         <v>-124.71365373330001</v>
       </c>
       <c r="JR29" s="5">
-        <v>-248.61479256209</v>
+        <v>-250.08402148358999</v>
       </c>
       <c r="JS29" s="13">
-        <v>-203.30924334349999</v>
+        <v>-204.70273778306</v>
       </c>
       <c r="JT29" s="13">
         <v>-533.71735119058997</v>
@@ -23613,13 +23613,13 @@
         <v>1478.0955996103</v>
       </c>
       <c r="JR30" s="5">
-        <v>5447.00740252985</v>
+        <v>6550.8479058079902</v>
       </c>
       <c r="JS30" s="13">
-        <v>-1454.1110346932001</v>
+        <v>-2211.5298525314001</v>
       </c>
       <c r="JT30" s="13">
-        <v>-736.14305708759002</v>
+        <v>-697.99696892238001</v>
       </c>
     </row>
     <row r="31" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24455,13 +24455,13 @@
         <v>1906.09976452413</v>
       </c>
       <c r="JR31" s="7">
-        <v>5837.6537113240502</v>
+        <v>6182.53790799136</v>
       </c>
       <c r="JS31" s="14">
-        <v>-1815.2766953419</v>
+        <v>-2350.8237488740001</v>
       </c>
       <c r="JT31" s="14">
-        <v>423.552901234243</v>
+        <v>461.69898939944699</v>
       </c>
     </row>
     <row r="32" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26139,13 +26139,13 @@
         <v>2182.8766399727601</v>
       </c>
       <c r="JR33" s="7">
-        <v>539.19432200889605</v>
+        <v>811.93991484411197</v>
       </c>
       <c r="JS33" s="14">
-        <v>-1366.8626790773999</v>
+        <v>-1651.3142609091999</v>
       </c>
       <c r="JT33" s="14">
-        <v>597.18702029778694</v>
+        <v>647.18702029778694</v>
       </c>
     </row>
     <row r="34" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26981,13 +26981,13 @@
         <v>-121.09530640545</v>
       </c>
       <c r="JR34" s="7">
-        <v>-298.45582954593999</v>
+        <v>-296.35824386047</v>
       </c>
       <c r="JS34" s="14">
-        <v>147.80157153360599</v>
+        <v>146.64757159247901</v>
       </c>
       <c r="JT34" s="14">
-        <v>582.63625970682403</v>
+        <v>578.90425970682395</v>
       </c>
     </row>
     <row r="35" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -27823,13 +27823,13 @@
         <v>-152.70326051343</v>
       </c>
       <c r="JR35" s="7">
-        <v>5599.7042915846096</v>
+        <v>5648.07200033962</v>
       </c>
       <c r="JS35" s="14">
-        <v>-593.21475514147005</v>
+        <v>-843.15622690057</v>
       </c>
       <c r="JT35" s="14">
-        <v>-753.29851554178003</v>
+        <v>-760.87042737657998</v>
       </c>
     </row>
     <row r="36" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28665,13 +28665,13 @@
         <v>-2.9783085297472001</v>
       </c>
       <c r="JR36" s="7">
-        <v>-2.7890727235087001</v>
+        <v>18.884236668101298</v>
       </c>
       <c r="JS36" s="14">
         <v>-3.0008326566563999</v>
       </c>
       <c r="JT36" s="14">
-        <v>-2.9718632285884001</v>
+        <v>-3.5218632285884</v>
       </c>
     </row>
     <row r="37" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -29507,10 +29507,10 @@
         <v>428.00416491383299</v>
       </c>
       <c r="JR37" s="7">
-        <v>390.64630879420599</v>
+        <v>-368.30999781663002</v>
       </c>
       <c r="JS37" s="14">
-        <v>-361.16566064873001</v>
+        <v>-139.29389634253999</v>
       </c>
       <c r="JT37" s="14">
         <v>1159.6959583218299</v>
@@ -30349,10 +30349,10 @@
         <v>170.21198175084101</v>
       </c>
       <c r="JR38" s="7">
-        <v>-435.16125301766999</v>
+        <v>-408.03518850504997</v>
       </c>
       <c r="JS38" s="14">
-        <v>-392.70565980050998</v>
+        <v>-387.07682058658997</v>
       </c>
       <c r="JT38" s="14">
         <v>190.207973260139</v>
@@ -31191,10 +31191,10 @@
         <v>966.22699604498496</v>
       </c>
       <c r="JR39" s="7">
-        <v>589.98780122916503</v>
+        <v>135.91643010570399</v>
       </c>
       <c r="JS39" s="14">
-        <v>17.7723565924429</v>
+        <v>234.015281684717</v>
       </c>
       <c r="JT39" s="14">
         <v>928.83028183550596</v>
@@ -32033,7 +32033,7 @@
         <v>-716.22638999071</v>
       </c>
       <c r="JR40" s="7">
-        <v>228.09179297682101</v>
+        <v>-103.91920702317999</v>
       </c>
       <c r="JS40" s="14">
         <v>30.095974693617102</v>
@@ -34559,7 +34559,7 @@
         <v>573.47620351407295</v>
       </c>
       <c r="JR43" s="20">
-        <v>7.8068191647895997</v>
+        <v>7.8068191647895899</v>
       </c>
       <c r="JS43" s="15">
         <v>978.85071295660396</v>
@@ -34569,287 +34569,287 @@
       </c>
     </row>
     <row r="44" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="33"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="33"/>
-      <c r="V44" s="33"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="33"/>
-      <c r="Y44" s="33"/>
-      <c r="Z44" s="33"/>
-      <c r="AA44" s="33"/>
-      <c r="AB44" s="33"/>
-      <c r="AC44" s="33"/>
-      <c r="AD44" s="33"/>
-      <c r="AE44" s="33"/>
-      <c r="AF44" s="33"/>
-      <c r="AG44" s="33"/>
-      <c r="AH44" s="33"/>
-      <c r="AI44" s="33"/>
-      <c r="AJ44" s="33"/>
-      <c r="AK44" s="33"/>
-      <c r="AL44" s="33"/>
-      <c r="AM44" s="33"/>
-      <c r="AN44" s="33"/>
-      <c r="AO44" s="33"/>
-      <c r="AP44" s="33"/>
-      <c r="AQ44" s="33"/>
-      <c r="AR44" s="33"/>
-      <c r="AS44" s="33"/>
-      <c r="AT44" s="33"/>
-      <c r="AU44" s="33"/>
-      <c r="AV44" s="33"/>
-      <c r="AW44" s="33"/>
-      <c r="AX44" s="33"/>
-      <c r="AY44" s="33"/>
-      <c r="AZ44" s="33"/>
-      <c r="BA44" s="33"/>
-      <c r="BB44" s="33"/>
-      <c r="BC44" s="33"/>
-      <c r="BD44" s="33"/>
-      <c r="BE44" s="33"/>
-      <c r="BF44" s="33"/>
-      <c r="BG44" s="33"/>
-      <c r="BH44" s="33"/>
-      <c r="BI44" s="33"/>
-      <c r="BJ44" s="33"/>
-      <c r="BK44" s="33"/>
-      <c r="BL44" s="33"/>
-      <c r="BM44" s="33"/>
-      <c r="BN44" s="33"/>
-      <c r="BO44" s="33"/>
-      <c r="BP44" s="33"/>
-      <c r="BQ44" s="33"/>
-      <c r="BR44" s="33"/>
-      <c r="BS44" s="33"/>
-      <c r="BT44" s="33"/>
-      <c r="BU44" s="33"/>
-      <c r="BV44" s="33"/>
-      <c r="BW44" s="33"/>
-      <c r="BX44" s="33"/>
-      <c r="BY44" s="33"/>
-      <c r="BZ44" s="33"/>
-      <c r="CA44" s="33"/>
-      <c r="CB44" s="33"/>
-      <c r="CC44" s="33"/>
-      <c r="CD44" s="33"/>
-      <c r="CE44" s="33"/>
-      <c r="CF44" s="33"/>
-      <c r="CG44" s="33"/>
-      <c r="CH44" s="33"/>
-      <c r="CI44" s="33"/>
-      <c r="CJ44" s="33"/>
-      <c r="CK44" s="33"/>
-      <c r="CL44" s="33"/>
-      <c r="CM44" s="33"/>
-      <c r="CN44" s="33"/>
-      <c r="CO44" s="33"/>
-      <c r="CP44" s="33"/>
-      <c r="CQ44" s="33"/>
-      <c r="CR44" s="33"/>
-      <c r="CS44" s="33"/>
-      <c r="CT44" s="33"/>
-      <c r="CU44" s="33"/>
-      <c r="CV44" s="33"/>
-      <c r="CW44" s="33"/>
-      <c r="CX44" s="33"/>
-      <c r="CY44" s="33"/>
-      <c r="CZ44" s="33"/>
-      <c r="DA44" s="33"/>
-      <c r="DB44" s="33"/>
-      <c r="DC44" s="33"/>
-      <c r="DD44" s="33"/>
-      <c r="DE44" s="33"/>
-      <c r="DF44" s="33"/>
-      <c r="DG44" s="33"/>
-      <c r="DH44" s="33"/>
-      <c r="DI44" s="33"/>
-      <c r="DJ44" s="33"/>
-      <c r="DK44" s="33"/>
-      <c r="DL44" s="33"/>
-      <c r="DM44" s="33"/>
-      <c r="DN44" s="33"/>
-      <c r="DO44" s="33"/>
-      <c r="DP44" s="33"/>
-      <c r="DQ44" s="33"/>
-      <c r="DR44" s="33"/>
-      <c r="DS44" s="33"/>
-      <c r="DT44" s="33"/>
-      <c r="DU44" s="33"/>
-      <c r="DV44" s="33"/>
-      <c r="DW44" s="33"/>
-      <c r="DX44" s="33"/>
-      <c r="DY44" s="33"/>
-      <c r="DZ44" s="33"/>
-      <c r="EA44" s="33"/>
-      <c r="EB44" s="33"/>
-      <c r="EC44" s="33"/>
-      <c r="ED44" s="33"/>
-      <c r="EE44" s="33"/>
-      <c r="EF44" s="33"/>
-      <c r="EG44" s="33"/>
-      <c r="EH44" s="33"/>
-      <c r="EI44" s="33"/>
-      <c r="EJ44" s="33"/>
-      <c r="EK44" s="33"/>
-      <c r="EL44" s="33"/>
-      <c r="EM44" s="33"/>
-      <c r="EN44" s="33"/>
-      <c r="EO44" s="33"/>
-      <c r="EP44" s="33"/>
-      <c r="EQ44" s="33"/>
-      <c r="ER44" s="33"/>
-      <c r="ES44" s="33"/>
-      <c r="ET44" s="33"/>
-      <c r="EU44" s="33"/>
-      <c r="EV44" s="33"/>
-      <c r="EW44" s="33"/>
-      <c r="EX44" s="33"/>
-      <c r="EY44" s="33"/>
-      <c r="EZ44" s="33"/>
-      <c r="FA44" s="33"/>
-      <c r="FB44" s="33"/>
-      <c r="FC44" s="33"/>
-      <c r="FD44" s="33"/>
-      <c r="FE44" s="33"/>
-      <c r="FF44" s="33"/>
-      <c r="FG44" s="33"/>
-      <c r="FH44" s="33"/>
-      <c r="FI44" s="33"/>
-      <c r="FJ44" s="33"/>
-      <c r="FK44" s="33"/>
-      <c r="FL44" s="33"/>
-      <c r="FM44" s="33"/>
-      <c r="FN44" s="33"/>
-      <c r="FO44" s="33"/>
-      <c r="FP44" s="33"/>
-      <c r="FQ44" s="33"/>
-      <c r="FR44" s="33"/>
-      <c r="FS44" s="33"/>
-      <c r="FT44" s="33"/>
-      <c r="FU44" s="33"/>
-      <c r="FV44" s="33"/>
-      <c r="FW44" s="33"/>
-      <c r="FX44" s="33"/>
-      <c r="FY44" s="33"/>
-      <c r="FZ44" s="33"/>
-      <c r="GA44" s="33"/>
-      <c r="GB44" s="33"/>
-      <c r="GC44" s="33"/>
-      <c r="GD44" s="33"/>
-      <c r="GE44" s="33"/>
-      <c r="GF44" s="33"/>
-      <c r="GG44" s="33"/>
-      <c r="GH44" s="33"/>
-      <c r="GI44" s="33"/>
-      <c r="GJ44" s="33"/>
-      <c r="GK44" s="33"/>
-      <c r="GL44" s="33"/>
-      <c r="GM44" s="33"/>
-      <c r="GN44" s="33"/>
-      <c r="GO44" s="33"/>
-      <c r="GP44" s="33"/>
-      <c r="GQ44" s="33"/>
-      <c r="GR44" s="33"/>
-      <c r="GS44" s="33"/>
-      <c r="GT44" s="33"/>
-      <c r="GU44" s="33"/>
-      <c r="GV44" s="33"/>
-      <c r="GW44" s="33"/>
-      <c r="GX44" s="33"/>
-      <c r="GY44" s="33"/>
-      <c r="GZ44" s="33"/>
-      <c r="HA44" s="33"/>
-      <c r="HB44" s="33"/>
-      <c r="HC44" s="33"/>
-      <c r="HD44" s="33"/>
-      <c r="HE44" s="33"/>
-      <c r="HF44" s="33"/>
-      <c r="HG44" s="33"/>
-      <c r="HH44" s="33"/>
-      <c r="HI44" s="33"/>
-      <c r="HJ44" s="33"/>
-      <c r="HK44" s="33"/>
-      <c r="HL44" s="33"/>
-      <c r="HM44" s="33"/>
-      <c r="HN44" s="33"/>
-      <c r="HO44" s="33"/>
-      <c r="HP44" s="33"/>
-      <c r="HQ44" s="33"/>
-      <c r="HR44" s="33"/>
-      <c r="HS44" s="33"/>
-      <c r="HT44" s="33"/>
-      <c r="HU44" s="33"/>
-      <c r="HV44" s="33"/>
-      <c r="HW44" s="33"/>
-      <c r="HX44" s="33"/>
-      <c r="HY44" s="33"/>
-      <c r="HZ44" s="33"/>
-      <c r="IA44" s="33"/>
-      <c r="IB44" s="33"/>
-      <c r="IC44" s="33"/>
-      <c r="ID44" s="33"/>
-      <c r="IE44" s="33"/>
-      <c r="IF44" s="33"/>
-      <c r="IG44" s="33"/>
-      <c r="IH44" s="33"/>
-      <c r="II44" s="33"/>
-      <c r="IJ44" s="33"/>
-      <c r="IK44" s="33"/>
-      <c r="IL44" s="33"/>
-      <c r="IM44" s="33"/>
-      <c r="IN44" s="33"/>
-      <c r="IO44" s="33"/>
-      <c r="IP44" s="33"/>
-      <c r="IQ44" s="33"/>
-      <c r="IR44" s="33"/>
-      <c r="IS44" s="33"/>
-      <c r="IT44" s="33"/>
-      <c r="IU44" s="33"/>
-      <c r="IV44" s="33"/>
-      <c r="IW44" s="33"/>
-      <c r="IX44" s="33"/>
-      <c r="IY44" s="33"/>
-      <c r="IZ44" s="33"/>
-      <c r="JA44" s="33"/>
-      <c r="JB44" s="33"/>
-      <c r="JC44" s="33"/>
-      <c r="JD44" s="33"/>
-      <c r="JE44" s="33"/>
-      <c r="JF44" s="33"/>
-      <c r="JG44" s="33"/>
-      <c r="JH44" s="33"/>
-      <c r="JI44" s="33"/>
-      <c r="JJ44" s="33"/>
-      <c r="JK44" s="33"/>
-      <c r="JL44" s="33"/>
-      <c r="JM44" s="33"/>
-      <c r="JN44" s="33"/>
-      <c r="JO44" s="33"/>
-      <c r="JP44" s="33"/>
-      <c r="JQ44" s="33"/>
-      <c r="JR44" s="33"/>
-      <c r="JS44" s="33"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="30"/>
+      <c r="S44" s="30"/>
+      <c r="T44" s="30"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="30"/>
+      <c r="W44" s="30"/>
+      <c r="X44" s="30"/>
+      <c r="Y44" s="30"/>
+      <c r="Z44" s="30"/>
+      <c r="AA44" s="30"/>
+      <c r="AB44" s="30"/>
+      <c r="AC44" s="30"/>
+      <c r="AD44" s="30"/>
+      <c r="AE44" s="30"/>
+      <c r="AF44" s="30"/>
+      <c r="AG44" s="30"/>
+      <c r="AH44" s="30"/>
+      <c r="AI44" s="30"/>
+      <c r="AJ44" s="30"/>
+      <c r="AK44" s="30"/>
+      <c r="AL44" s="30"/>
+      <c r="AM44" s="30"/>
+      <c r="AN44" s="30"/>
+      <c r="AO44" s="30"/>
+      <c r="AP44" s="30"/>
+      <c r="AQ44" s="30"/>
+      <c r="AR44" s="30"/>
+      <c r="AS44" s="30"/>
+      <c r="AT44" s="30"/>
+      <c r="AU44" s="30"/>
+      <c r="AV44" s="30"/>
+      <c r="AW44" s="30"/>
+      <c r="AX44" s="30"/>
+      <c r="AY44" s="30"/>
+      <c r="AZ44" s="30"/>
+      <c r="BA44" s="30"/>
+      <c r="BB44" s="30"/>
+      <c r="BC44" s="30"/>
+      <c r="BD44" s="30"/>
+      <c r="BE44" s="30"/>
+      <c r="BF44" s="30"/>
+      <c r="BG44" s="30"/>
+      <c r="BH44" s="30"/>
+      <c r="BI44" s="30"/>
+      <c r="BJ44" s="30"/>
+      <c r="BK44" s="30"/>
+      <c r="BL44" s="30"/>
+      <c r="BM44" s="30"/>
+      <c r="BN44" s="30"/>
+      <c r="BO44" s="30"/>
+      <c r="BP44" s="30"/>
+      <c r="BQ44" s="30"/>
+      <c r="BR44" s="30"/>
+      <c r="BS44" s="30"/>
+      <c r="BT44" s="30"/>
+      <c r="BU44" s="30"/>
+      <c r="BV44" s="30"/>
+      <c r="BW44" s="30"/>
+      <c r="BX44" s="30"/>
+      <c r="BY44" s="30"/>
+      <c r="BZ44" s="30"/>
+      <c r="CA44" s="30"/>
+      <c r="CB44" s="30"/>
+      <c r="CC44" s="30"/>
+      <c r="CD44" s="30"/>
+      <c r="CE44" s="30"/>
+      <c r="CF44" s="30"/>
+      <c r="CG44" s="30"/>
+      <c r="CH44" s="30"/>
+      <c r="CI44" s="30"/>
+      <c r="CJ44" s="30"/>
+      <c r="CK44" s="30"/>
+      <c r="CL44" s="30"/>
+      <c r="CM44" s="30"/>
+      <c r="CN44" s="30"/>
+      <c r="CO44" s="30"/>
+      <c r="CP44" s="30"/>
+      <c r="CQ44" s="30"/>
+      <c r="CR44" s="30"/>
+      <c r="CS44" s="30"/>
+      <c r="CT44" s="30"/>
+      <c r="CU44" s="30"/>
+      <c r="CV44" s="30"/>
+      <c r="CW44" s="30"/>
+      <c r="CX44" s="30"/>
+      <c r="CY44" s="30"/>
+      <c r="CZ44" s="30"/>
+      <c r="DA44" s="30"/>
+      <c r="DB44" s="30"/>
+      <c r="DC44" s="30"/>
+      <c r="DD44" s="30"/>
+      <c r="DE44" s="30"/>
+      <c r="DF44" s="30"/>
+      <c r="DG44" s="30"/>
+      <c r="DH44" s="30"/>
+      <c r="DI44" s="30"/>
+      <c r="DJ44" s="30"/>
+      <c r="DK44" s="30"/>
+      <c r="DL44" s="30"/>
+      <c r="DM44" s="30"/>
+      <c r="DN44" s="30"/>
+      <c r="DO44" s="30"/>
+      <c r="DP44" s="30"/>
+      <c r="DQ44" s="30"/>
+      <c r="DR44" s="30"/>
+      <c r="DS44" s="30"/>
+      <c r="DT44" s="30"/>
+      <c r="DU44" s="30"/>
+      <c r="DV44" s="30"/>
+      <c r="DW44" s="30"/>
+      <c r="DX44" s="30"/>
+      <c r="DY44" s="30"/>
+      <c r="DZ44" s="30"/>
+      <c r="EA44" s="30"/>
+      <c r="EB44" s="30"/>
+      <c r="EC44" s="30"/>
+      <c r="ED44" s="30"/>
+      <c r="EE44" s="30"/>
+      <c r="EF44" s="30"/>
+      <c r="EG44" s="30"/>
+      <c r="EH44" s="30"/>
+      <c r="EI44" s="30"/>
+      <c r="EJ44" s="30"/>
+      <c r="EK44" s="30"/>
+      <c r="EL44" s="30"/>
+      <c r="EM44" s="30"/>
+      <c r="EN44" s="30"/>
+      <c r="EO44" s="30"/>
+      <c r="EP44" s="30"/>
+      <c r="EQ44" s="30"/>
+      <c r="ER44" s="30"/>
+      <c r="ES44" s="30"/>
+      <c r="ET44" s="30"/>
+      <c r="EU44" s="30"/>
+      <c r="EV44" s="30"/>
+      <c r="EW44" s="30"/>
+      <c r="EX44" s="30"/>
+      <c r="EY44" s="30"/>
+      <c r="EZ44" s="30"/>
+      <c r="FA44" s="30"/>
+      <c r="FB44" s="30"/>
+      <c r="FC44" s="30"/>
+      <c r="FD44" s="30"/>
+      <c r="FE44" s="30"/>
+      <c r="FF44" s="30"/>
+      <c r="FG44" s="30"/>
+      <c r="FH44" s="30"/>
+      <c r="FI44" s="30"/>
+      <c r="FJ44" s="30"/>
+      <c r="FK44" s="30"/>
+      <c r="FL44" s="30"/>
+      <c r="FM44" s="30"/>
+      <c r="FN44" s="30"/>
+      <c r="FO44" s="30"/>
+      <c r="FP44" s="30"/>
+      <c r="FQ44" s="30"/>
+      <c r="FR44" s="30"/>
+      <c r="FS44" s="30"/>
+      <c r="FT44" s="30"/>
+      <c r="FU44" s="30"/>
+      <c r="FV44" s="30"/>
+      <c r="FW44" s="30"/>
+      <c r="FX44" s="30"/>
+      <c r="FY44" s="30"/>
+      <c r="FZ44" s="30"/>
+      <c r="GA44" s="30"/>
+      <c r="GB44" s="30"/>
+      <c r="GC44" s="30"/>
+      <c r="GD44" s="30"/>
+      <c r="GE44" s="30"/>
+      <c r="GF44" s="30"/>
+      <c r="GG44" s="30"/>
+      <c r="GH44" s="30"/>
+      <c r="GI44" s="30"/>
+      <c r="GJ44" s="30"/>
+      <c r="GK44" s="30"/>
+      <c r="GL44" s="30"/>
+      <c r="GM44" s="30"/>
+      <c r="GN44" s="30"/>
+      <c r="GO44" s="30"/>
+      <c r="GP44" s="30"/>
+      <c r="GQ44" s="30"/>
+      <c r="GR44" s="30"/>
+      <c r="GS44" s="30"/>
+      <c r="GT44" s="30"/>
+      <c r="GU44" s="30"/>
+      <c r="GV44" s="30"/>
+      <c r="GW44" s="30"/>
+      <c r="GX44" s="30"/>
+      <c r="GY44" s="30"/>
+      <c r="GZ44" s="30"/>
+      <c r="HA44" s="30"/>
+      <c r="HB44" s="30"/>
+      <c r="HC44" s="30"/>
+      <c r="HD44" s="30"/>
+      <c r="HE44" s="30"/>
+      <c r="HF44" s="30"/>
+      <c r="HG44" s="30"/>
+      <c r="HH44" s="30"/>
+      <c r="HI44" s="30"/>
+      <c r="HJ44" s="30"/>
+      <c r="HK44" s="30"/>
+      <c r="HL44" s="30"/>
+      <c r="HM44" s="30"/>
+      <c r="HN44" s="30"/>
+      <c r="HO44" s="30"/>
+      <c r="HP44" s="30"/>
+      <c r="HQ44" s="30"/>
+      <c r="HR44" s="30"/>
+      <c r="HS44" s="30"/>
+      <c r="HT44" s="30"/>
+      <c r="HU44" s="30"/>
+      <c r="HV44" s="30"/>
+      <c r="HW44" s="30"/>
+      <c r="HX44" s="30"/>
+      <c r="HY44" s="30"/>
+      <c r="HZ44" s="30"/>
+      <c r="IA44" s="30"/>
+      <c r="IB44" s="30"/>
+      <c r="IC44" s="30"/>
+      <c r="ID44" s="30"/>
+      <c r="IE44" s="30"/>
+      <c r="IF44" s="30"/>
+      <c r="IG44" s="30"/>
+      <c r="IH44" s="30"/>
+      <c r="II44" s="30"/>
+      <c r="IJ44" s="30"/>
+      <c r="IK44" s="30"/>
+      <c r="IL44" s="30"/>
+      <c r="IM44" s="30"/>
+      <c r="IN44" s="30"/>
+      <c r="IO44" s="30"/>
+      <c r="IP44" s="30"/>
+      <c r="IQ44" s="30"/>
+      <c r="IR44" s="30"/>
+      <c r="IS44" s="30"/>
+      <c r="IT44" s="30"/>
+      <c r="IU44" s="30"/>
+      <c r="IV44" s="30"/>
+      <c r="IW44" s="30"/>
+      <c r="IX44" s="30"/>
+      <c r="IY44" s="30"/>
+      <c r="IZ44" s="30"/>
+      <c r="JA44" s="30"/>
+      <c r="JB44" s="30"/>
+      <c r="JC44" s="30"/>
+      <c r="JD44" s="30"/>
+      <c r="JE44" s="30"/>
+      <c r="JF44" s="30"/>
+      <c r="JG44" s="30"/>
+      <c r="JH44" s="30"/>
+      <c r="JI44" s="30"/>
+      <c r="JJ44" s="30"/>
+      <c r="JK44" s="30"/>
+      <c r="JL44" s="30"/>
+      <c r="JM44" s="30"/>
+      <c r="JN44" s="30"/>
+      <c r="JO44" s="30"/>
+      <c r="JP44" s="30"/>
+      <c r="JQ44" s="30"/>
+      <c r="JR44" s="30"/>
+      <c r="JS44" s="30"/>
       <c r="JT44" s="1"/>
     </row>
     <row r="45" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -35685,13 +35685,13 @@
         <v>3400.6974589851998</v>
       </c>
       <c r="JR45" s="22">
-        <v>1029.2955078495399</v>
+        <v>2131.0227889939301</v>
       </c>
       <c r="JS45" s="16">
-        <v>-1436.5064811633999</v>
+        <v>-1497.2697047868</v>
       </c>
       <c r="JT45" s="16">
-        <v>-2262.1424227406001</v>
+        <v>-1930.2958429094001</v>
       </c>
     </row>
     <row r="46" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -36527,13 +36527,13 @@
         <v>619.02631844101199</v>
       </c>
       <c r="JR46" s="7">
-        <v>4573.7022274701303</v>
+        <v>4538.7757729145897</v>
       </c>
       <c r="JS46" s="17">
-        <v>556.75870162478202</v>
+        <v>405.06796081102402</v>
       </c>
       <c r="JT46" s="17">
-        <v>1104.5198899257</v>
+        <v>1104.1416996132</v>
       </c>
     </row>
     <row r="47" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -37369,13 +37369,13 @@
         <v>761.33563826064403</v>
       </c>
       <c r="JR47" s="7">
-        <v>4442.8478312029101</v>
+        <v>4407.9213766473704</v>
       </c>
       <c r="JS47" s="17">
-        <v>992.63727698604498</v>
+        <v>840.94653617228801</v>
       </c>
       <c r="JT47" s="17">
-        <v>1259.19176117249</v>
+        <v>1258.81357085999</v>
       </c>
     </row>
     <row r="48" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -38211,13 +38211,13 @@
         <v>274.83499199059901</v>
       </c>
       <c r="JR48" s="7">
-        <v>3666.0922732930499</v>
+        <v>3631.4930076378901</v>
       </c>
       <c r="JS48" s="17">
-        <v>292.96925248142003</v>
+        <v>141.41106045551399</v>
       </c>
       <c r="JT48" s="17">
-        <v>604.75921625866795</v>
+        <v>604.38102594616805</v>
       </c>
     </row>
     <row r="49" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -39053,10 +39053,10 @@
         <v>486.50064627004502</v>
       </c>
       <c r="JR49" s="7">
-        <v>776.755557909863</v>
+        <v>776.42836900947395</v>
       </c>
       <c r="JS49" s="17">
-        <v>699.66802450462501</v>
+        <v>699.53547571677302</v>
       </c>
       <c r="JT49" s="17">
         <v>654.43254491381799</v>
@@ -41589,303 +41589,291 @@
       </c>
     </row>
     <row r="54" spans="1:280" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="30" t="s">
+      <c r="A54" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
-      <c r="O54" s="30"/>
-      <c r="P54" s="30"/>
-      <c r="Q54" s="30"/>
-      <c r="R54" s="30"/>
-      <c r="S54" s="30"/>
-      <c r="T54" s="30"/>
-      <c r="U54" s="30"/>
-      <c r="V54" s="30"/>
-      <c r="W54" s="30"/>
-      <c r="X54" s="30"/>
-      <c r="Y54" s="30"/>
-      <c r="Z54" s="30"/>
-      <c r="AA54" s="30"/>
-      <c r="AB54" s="30"/>
-      <c r="AC54" s="30"/>
-      <c r="AD54" s="30"/>
-      <c r="AE54" s="30"/>
-      <c r="AF54" s="30"/>
-      <c r="AG54" s="30"/>
-      <c r="AH54" s="30"/>
-      <c r="AI54" s="30"/>
-      <c r="AJ54" s="30"/>
-      <c r="AK54" s="30"/>
-      <c r="AL54" s="30"/>
-      <c r="AM54" s="30"/>
-      <c r="AN54" s="30"/>
-      <c r="AO54" s="30"/>
-      <c r="AP54" s="30"/>
-      <c r="AQ54" s="30"/>
-      <c r="AR54" s="30"/>
-      <c r="AS54" s="30"/>
-      <c r="AT54" s="30"/>
-      <c r="AU54" s="30"/>
-      <c r="AV54" s="30"/>
-      <c r="AW54" s="30"/>
-      <c r="AX54" s="30"/>
-      <c r="AY54" s="30"/>
-      <c r="AZ54" s="30"/>
-      <c r="BA54" s="30"/>
-      <c r="BB54" s="30"/>
-      <c r="BC54" s="30"/>
-      <c r="BD54" s="30"/>
-      <c r="BE54" s="30"/>
-      <c r="BF54" s="30"/>
-      <c r="BG54" s="30"/>
-      <c r="BH54" s="30"/>
-      <c r="BI54" s="30"/>
-      <c r="BJ54" s="30"/>
-      <c r="BK54" s="30"/>
-      <c r="BL54" s="30"/>
-      <c r="BM54" s="30"/>
-      <c r="BN54" s="30"/>
-      <c r="BO54" s="30"/>
-      <c r="BP54" s="30"/>
-      <c r="BQ54" s="30"/>
-      <c r="BR54" s="30"/>
-      <c r="BS54" s="30"/>
-      <c r="BT54" s="30"/>
-      <c r="BU54" s="30"/>
-      <c r="BV54" s="30"/>
-      <c r="BW54" s="30"/>
-      <c r="BX54" s="30"/>
-      <c r="BY54" s="30"/>
-      <c r="BZ54" s="30"/>
-      <c r="CA54" s="30"/>
-      <c r="CB54" s="30"/>
-      <c r="CC54" s="30"/>
-      <c r="CD54" s="30"/>
-      <c r="CE54" s="30"/>
-      <c r="CF54" s="30"/>
-      <c r="CG54" s="30"/>
-      <c r="CH54" s="30"/>
-      <c r="CI54" s="30"/>
-      <c r="CJ54" s="30"/>
-      <c r="CK54" s="30"/>
-      <c r="CL54" s="30"/>
-      <c r="CM54" s="30"/>
-      <c r="CN54" s="30"/>
-      <c r="CO54" s="30"/>
-      <c r="CP54" s="30"/>
-      <c r="CQ54" s="30"/>
-      <c r="CR54" s="30"/>
-      <c r="CS54" s="30"/>
-      <c r="CT54" s="30"/>
-      <c r="CU54" s="30"/>
-      <c r="CV54" s="30"/>
-      <c r="CW54" s="30"/>
-      <c r="CX54" s="30"/>
-      <c r="CY54" s="30"/>
-      <c r="CZ54" s="30"/>
-      <c r="DA54" s="30"/>
-      <c r="DB54" s="30"/>
-      <c r="DC54" s="30"/>
-      <c r="DD54" s="30"/>
-      <c r="DE54" s="30"/>
-      <c r="DF54" s="30"/>
-      <c r="DG54" s="30"/>
-      <c r="DH54" s="30"/>
-      <c r="DI54" s="30"/>
-      <c r="DJ54" s="30"/>
-      <c r="DK54" s="30"/>
-      <c r="DL54" s="30"/>
-      <c r="DM54" s="30"/>
-      <c r="DN54" s="30"/>
-      <c r="DO54" s="30"/>
-      <c r="DP54" s="30"/>
-      <c r="DQ54" s="30"/>
-      <c r="DR54" s="30"/>
-      <c r="DS54" s="30"/>
-      <c r="DT54" s="30"/>
-      <c r="DU54" s="30"/>
-      <c r="DV54" s="30"/>
-      <c r="DW54" s="30"/>
-      <c r="DX54" s="30"/>
-      <c r="DY54" s="30"/>
-      <c r="DZ54" s="30"/>
-      <c r="EA54" s="30"/>
-      <c r="EB54" s="30"/>
-      <c r="EC54" s="30"/>
-      <c r="ED54" s="30"/>
-      <c r="EE54" s="30"/>
-      <c r="EF54" s="30"/>
-      <c r="EG54" s="30"/>
-      <c r="EH54" s="30"/>
-      <c r="EI54" s="30"/>
-      <c r="EJ54" s="30"/>
-      <c r="EK54" s="30"/>
-      <c r="EL54" s="30"/>
-      <c r="EM54" s="30"/>
-      <c r="EN54" s="30"/>
-      <c r="EO54" s="30"/>
-      <c r="EP54" s="30"/>
-      <c r="EQ54" s="30"/>
-      <c r="ER54" s="30"/>
-      <c r="ES54" s="30"/>
-      <c r="ET54" s="30"/>
-      <c r="EU54" s="30"/>
-      <c r="EV54" s="30"/>
-      <c r="EW54" s="30"/>
-      <c r="EX54" s="30"/>
-      <c r="EY54" s="30"/>
-      <c r="EZ54" s="30"/>
-      <c r="FA54" s="30"/>
-      <c r="FB54" s="30"/>
-      <c r="FC54" s="30"/>
-      <c r="FD54" s="30"/>
-      <c r="FE54" s="30"/>
-      <c r="FF54" s="30"/>
-      <c r="FG54" s="30"/>
-      <c r="FH54" s="30"/>
-      <c r="FI54" s="30"/>
-      <c r="FJ54" s="30"/>
-      <c r="FK54" s="30"/>
-      <c r="FL54" s="30"/>
-      <c r="FM54" s="30"/>
-      <c r="FN54" s="30"/>
-      <c r="FO54" s="30"/>
-      <c r="FP54" s="30"/>
-      <c r="FQ54" s="30"/>
-      <c r="FR54" s="30"/>
-      <c r="FS54" s="30"/>
-      <c r="FT54" s="30"/>
-      <c r="FU54" s="30"/>
-      <c r="FV54" s="30"/>
-      <c r="FW54" s="30"/>
-      <c r="FX54" s="30"/>
-      <c r="FY54" s="30"/>
-      <c r="FZ54" s="30"/>
-      <c r="GA54" s="30"/>
-      <c r="GB54" s="30"/>
-      <c r="GC54" s="30"/>
-      <c r="GD54" s="30"/>
-      <c r="GE54" s="30"/>
-      <c r="GF54" s="30"/>
-      <c r="GG54" s="30"/>
-      <c r="GH54" s="30"/>
-      <c r="GI54" s="30"/>
-      <c r="GJ54" s="30"/>
-      <c r="GK54" s="30"/>
-      <c r="GL54" s="30"/>
-      <c r="GM54" s="30"/>
-      <c r="GN54" s="30"/>
-      <c r="GO54" s="30"/>
-      <c r="GP54" s="30"/>
-      <c r="GQ54" s="30"/>
-      <c r="GR54" s="30"/>
-      <c r="GS54" s="30"/>
-      <c r="GT54" s="30"/>
-      <c r="GU54" s="30"/>
-      <c r="GV54" s="30"/>
-      <c r="GW54" s="30"/>
-      <c r="GX54" s="30"/>
-      <c r="GY54" s="30"/>
-      <c r="GZ54" s="30"/>
-      <c r="HA54" s="30"/>
-      <c r="HB54" s="30"/>
-      <c r="HC54" s="30"/>
-      <c r="HD54" s="30"/>
-      <c r="HE54" s="30"/>
-      <c r="HF54" s="30"/>
-      <c r="HG54" s="30"/>
-      <c r="HH54" s="30"/>
-      <c r="HI54" s="30"/>
-      <c r="HJ54" s="30"/>
-      <c r="HK54" s="30"/>
-      <c r="HL54" s="30"/>
-      <c r="HM54" s="30"/>
-      <c r="HN54" s="30"/>
-      <c r="HO54" s="30"/>
-      <c r="HP54" s="30"/>
-      <c r="HQ54" s="30"/>
-      <c r="HR54" s="30"/>
-      <c r="HS54" s="30"/>
-      <c r="HT54" s="30"/>
-      <c r="HU54" s="30"/>
-      <c r="HV54" s="30"/>
-      <c r="HW54" s="30"/>
-      <c r="HX54" s="30"/>
-      <c r="HY54" s="30"/>
-      <c r="HZ54" s="30"/>
-      <c r="IA54" s="30"/>
-      <c r="IB54" s="30"/>
-      <c r="IC54" s="30"/>
-      <c r="ID54" s="30"/>
-      <c r="IE54" s="30"/>
-      <c r="IF54" s="30"/>
-      <c r="IG54" s="30"/>
-      <c r="IH54" s="30"/>
-      <c r="II54" s="30"/>
-      <c r="IJ54" s="30"/>
-      <c r="IK54" s="30"/>
-      <c r="IL54" s="30"/>
-      <c r="IM54" s="30"/>
-      <c r="IN54" s="30"/>
-      <c r="IO54" s="30"/>
-      <c r="IP54" s="30"/>
-      <c r="IQ54" s="30"/>
-      <c r="IR54" s="30"/>
-      <c r="IS54" s="30"/>
-      <c r="IT54" s="30"/>
-      <c r="IU54" s="30"/>
-      <c r="IV54" s="30"/>
-      <c r="IW54" s="30"/>
-      <c r="IX54" s="30"/>
-      <c r="IY54" s="30"/>
-      <c r="IZ54" s="30"/>
-      <c r="JA54" s="30"/>
-      <c r="JB54" s="30"/>
-      <c r="JC54" s="30"/>
-      <c r="JD54" s="30"/>
-      <c r="JE54" s="30"/>
-      <c r="JF54" s="30"/>
-      <c r="JG54" s="30"/>
-      <c r="JH54" s="30"/>
-      <c r="JI54" s="30"/>
-      <c r="JJ54" s="30"/>
-      <c r="JK54" s="30"/>
-      <c r="JL54" s="30"/>
-      <c r="JM54" s="30"/>
-      <c r="JN54" s="30"/>
-      <c r="JO54" s="30"/>
-      <c r="JP54" s="30"/>
-      <c r="JQ54" s="30"/>
-      <c r="JR54" s="30"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="26"/>
+      <c r="O54" s="26"/>
+      <c r="P54" s="26"/>
+      <c r="Q54" s="26"/>
+      <c r="R54" s="26"/>
+      <c r="S54" s="26"/>
+      <c r="T54" s="26"/>
+      <c r="U54" s="26"/>
+      <c r="V54" s="26"/>
+      <c r="W54" s="26"/>
+      <c r="X54" s="26"/>
+      <c r="Y54" s="26"/>
+      <c r="Z54" s="26"/>
+      <c r="AA54" s="26"/>
+      <c r="AB54" s="26"/>
+      <c r="AC54" s="26"/>
+      <c r="AD54" s="26"/>
+      <c r="AE54" s="26"/>
+      <c r="AF54" s="26"/>
+      <c r="AG54" s="26"/>
+      <c r="AH54" s="26"/>
+      <c r="AI54" s="26"/>
+      <c r="AJ54" s="26"/>
+      <c r="AK54" s="26"/>
+      <c r="AL54" s="26"/>
+      <c r="AM54" s="26"/>
+      <c r="AN54" s="26"/>
+      <c r="AO54" s="26"/>
+      <c r="AP54" s="26"/>
+      <c r="AQ54" s="26"/>
+      <c r="AR54" s="26"/>
+      <c r="AS54" s="26"/>
+      <c r="AT54" s="26"/>
+      <c r="AU54" s="26"/>
+      <c r="AV54" s="26"/>
+      <c r="AW54" s="26"/>
+      <c r="AX54" s="26"/>
+      <c r="AY54" s="26"/>
+      <c r="AZ54" s="26"/>
+      <c r="BA54" s="26"/>
+      <c r="BB54" s="26"/>
+      <c r="BC54" s="26"/>
+      <c r="BD54" s="26"/>
+      <c r="BE54" s="26"/>
+      <c r="BF54" s="26"/>
+      <c r="BG54" s="26"/>
+      <c r="BH54" s="26"/>
+      <c r="BI54" s="26"/>
+      <c r="BJ54" s="26"/>
+      <c r="BK54" s="26"/>
+      <c r="BL54" s="26"/>
+      <c r="BM54" s="26"/>
+      <c r="BN54" s="26"/>
+      <c r="BO54" s="26"/>
+      <c r="BP54" s="26"/>
+      <c r="BQ54" s="26"/>
+      <c r="BR54" s="26"/>
+      <c r="BS54" s="26"/>
+      <c r="BT54" s="26"/>
+      <c r="BU54" s="26"/>
+      <c r="BV54" s="26"/>
+      <c r="BW54" s="26"/>
+      <c r="BX54" s="26"/>
+      <c r="BY54" s="26"/>
+      <c r="BZ54" s="26"/>
+      <c r="CA54" s="26"/>
+      <c r="CB54" s="26"/>
+      <c r="CC54" s="26"/>
+      <c r="CD54" s="26"/>
+      <c r="CE54" s="26"/>
+      <c r="CF54" s="26"/>
+      <c r="CG54" s="26"/>
+      <c r="CH54" s="26"/>
+      <c r="CI54" s="26"/>
+      <c r="CJ54" s="26"/>
+      <c r="CK54" s="26"/>
+      <c r="CL54" s="26"/>
+      <c r="CM54" s="26"/>
+      <c r="CN54" s="26"/>
+      <c r="CO54" s="26"/>
+      <c r="CP54" s="26"/>
+      <c r="CQ54" s="26"/>
+      <c r="CR54" s="26"/>
+      <c r="CS54" s="26"/>
+      <c r="CT54" s="26"/>
+      <c r="CU54" s="26"/>
+      <c r="CV54" s="26"/>
+      <c r="CW54" s="26"/>
+      <c r="CX54" s="26"/>
+      <c r="CY54" s="26"/>
+      <c r="CZ54" s="26"/>
+      <c r="DA54" s="26"/>
+      <c r="DB54" s="26"/>
+      <c r="DC54" s="26"/>
+      <c r="DD54" s="26"/>
+      <c r="DE54" s="26"/>
+      <c r="DF54" s="26"/>
+      <c r="DG54" s="26"/>
+      <c r="DH54" s="26"/>
+      <c r="DI54" s="26"/>
+      <c r="DJ54" s="26"/>
+      <c r="DK54" s="26"/>
+      <c r="DL54" s="26"/>
+      <c r="DM54" s="26"/>
+      <c r="DN54" s="26"/>
+      <c r="DO54" s="26"/>
+      <c r="DP54" s="26"/>
+      <c r="DQ54" s="26"/>
+      <c r="DR54" s="26"/>
+      <c r="DS54" s="26"/>
+      <c r="DT54" s="26"/>
+      <c r="DU54" s="26"/>
+      <c r="DV54" s="26"/>
+      <c r="DW54" s="26"/>
+      <c r="DX54" s="26"/>
+      <c r="DY54" s="26"/>
+      <c r="DZ54" s="26"/>
+      <c r="EA54" s="26"/>
+      <c r="EB54" s="26"/>
+      <c r="EC54" s="26"/>
+      <c r="ED54" s="26"/>
+      <c r="EE54" s="26"/>
+      <c r="EF54" s="26"/>
+      <c r="EG54" s="26"/>
+      <c r="EH54" s="26"/>
+      <c r="EI54" s="26"/>
+      <c r="EJ54" s="26"/>
+      <c r="EK54" s="26"/>
+      <c r="EL54" s="26"/>
+      <c r="EM54" s="26"/>
+      <c r="EN54" s="26"/>
+      <c r="EO54" s="26"/>
+      <c r="EP54" s="26"/>
+      <c r="EQ54" s="26"/>
+      <c r="ER54" s="26"/>
+      <c r="ES54" s="26"/>
+      <c r="ET54" s="26"/>
+      <c r="EU54" s="26"/>
+      <c r="EV54" s="26"/>
+      <c r="EW54" s="26"/>
+      <c r="EX54" s="26"/>
+      <c r="EY54" s="26"/>
+      <c r="EZ54" s="26"/>
+      <c r="FA54" s="26"/>
+      <c r="FB54" s="26"/>
+      <c r="FC54" s="26"/>
+      <c r="FD54" s="26"/>
+      <c r="FE54" s="26"/>
+      <c r="FF54" s="26"/>
+      <c r="FG54" s="26"/>
+      <c r="FH54" s="26"/>
+      <c r="FI54" s="26"/>
+      <c r="FJ54" s="26"/>
+      <c r="FK54" s="26"/>
+      <c r="FL54" s="26"/>
+      <c r="FM54" s="26"/>
+      <c r="FN54" s="26"/>
+      <c r="FO54" s="26"/>
+      <c r="FP54" s="26"/>
+      <c r="FQ54" s="26"/>
+      <c r="FR54" s="26"/>
+      <c r="FS54" s="26"/>
+      <c r="FT54" s="26"/>
+      <c r="FU54" s="26"/>
+      <c r="FV54" s="26"/>
+      <c r="FW54" s="26"/>
+      <c r="FX54" s="26"/>
+      <c r="FY54" s="26"/>
+      <c r="FZ54" s="26"/>
+      <c r="GA54" s="26"/>
+      <c r="GB54" s="26"/>
+      <c r="GC54" s="26"/>
+      <c r="GD54" s="26"/>
+      <c r="GE54" s="26"/>
+      <c r="GF54" s="26"/>
+      <c r="GG54" s="26"/>
+      <c r="GH54" s="26"/>
+      <c r="GI54" s="26"/>
+      <c r="GJ54" s="26"/>
+      <c r="GK54" s="26"/>
+      <c r="GL54" s="26"/>
+      <c r="GM54" s="26"/>
+      <c r="GN54" s="26"/>
+      <c r="GO54" s="26"/>
+      <c r="GP54" s="26"/>
+      <c r="GQ54" s="26"/>
+      <c r="GR54" s="26"/>
+      <c r="GS54" s="26"/>
+      <c r="GT54" s="26"/>
+      <c r="GU54" s="26"/>
+      <c r="GV54" s="26"/>
+      <c r="GW54" s="26"/>
+      <c r="GX54" s="26"/>
+      <c r="GY54" s="26"/>
+      <c r="GZ54" s="26"/>
+      <c r="HA54" s="26"/>
+      <c r="HB54" s="26"/>
+      <c r="HC54" s="26"/>
+      <c r="HD54" s="26"/>
+      <c r="HE54" s="26"/>
+      <c r="HF54" s="26"/>
+      <c r="HG54" s="26"/>
+      <c r="HH54" s="26"/>
+      <c r="HI54" s="26"/>
+      <c r="HJ54" s="26"/>
+      <c r="HK54" s="26"/>
+      <c r="HL54" s="26"/>
+      <c r="HM54" s="26"/>
+      <c r="HN54" s="26"/>
+      <c r="HO54" s="26"/>
+      <c r="HP54" s="26"/>
+      <c r="HQ54" s="26"/>
+      <c r="HR54" s="26"/>
+      <c r="HS54" s="26"/>
+      <c r="HT54" s="26"/>
+      <c r="HU54" s="26"/>
+      <c r="HV54" s="26"/>
+      <c r="HW54" s="26"/>
+      <c r="HX54" s="26"/>
+      <c r="HY54" s="26"/>
+      <c r="HZ54" s="26"/>
+      <c r="IA54" s="26"/>
+      <c r="IB54" s="26"/>
+      <c r="IC54" s="26"/>
+      <c r="ID54" s="26"/>
+      <c r="IE54" s="26"/>
+      <c r="IF54" s="26"/>
+      <c r="IG54" s="26"/>
+      <c r="IH54" s="26"/>
+      <c r="II54" s="26"/>
+      <c r="IJ54" s="26"/>
+      <c r="IK54" s="26"/>
+      <c r="IL54" s="26"/>
+      <c r="IM54" s="26"/>
+      <c r="IN54" s="26"/>
+      <c r="IO54" s="26"/>
+      <c r="IP54" s="26"/>
+      <c r="IQ54" s="26"/>
+      <c r="IR54" s="26"/>
+      <c r="IS54" s="26"/>
+      <c r="IT54" s="26"/>
+      <c r="IU54" s="26"/>
+      <c r="IV54" s="26"/>
+      <c r="IW54" s="26"/>
+      <c r="IX54" s="26"/>
+      <c r="IY54" s="26"/>
+      <c r="IZ54" s="26"/>
+      <c r="JA54" s="26"/>
+      <c r="JB54" s="26"/>
+      <c r="JC54" s="26"/>
+      <c r="JD54" s="26"/>
+      <c r="JE54" s="26"/>
+      <c r="JF54" s="26"/>
+      <c r="JG54" s="26"/>
+      <c r="JH54" s="26"/>
+      <c r="JI54" s="26"/>
+      <c r="JJ54" s="26"/>
+      <c r="JK54" s="26"/>
+      <c r="JL54" s="26"/>
+      <c r="JM54" s="26"/>
+      <c r="JN54" s="26"/>
+      <c r="JO54" s="26"/>
+      <c r="JP54" s="26"/>
+      <c r="JQ54" s="26"/>
+      <c r="JR54" s="26"/>
       <c r="JS54" s="10"/>
       <c r="JT54" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A54:JR54"/>
-    <mergeCell ref="IH4:IS4"/>
-    <mergeCell ref="IT4:JE4"/>
-    <mergeCell ref="JF4:JQ4"/>
-    <mergeCell ref="DF4:DQ4"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="Z4:AK4"/>
-    <mergeCell ref="AL4:AW4"/>
-    <mergeCell ref="AX4:BI4"/>
-    <mergeCell ref="A44:JS44"/>
-    <mergeCell ref="JR4:JT4"/>
     <mergeCell ref="A1:JR1"/>
     <mergeCell ref="A2:JR2"/>
     <mergeCell ref="FZ4:GK4"/>
@@ -41902,6 +41890,18 @@
     <mergeCell ref="BV4:CG4"/>
     <mergeCell ref="CH4:CS4"/>
     <mergeCell ref="CT4:DE4"/>
+    <mergeCell ref="A54:JR54"/>
+    <mergeCell ref="IH4:IS4"/>
+    <mergeCell ref="IT4:JE4"/>
+    <mergeCell ref="JF4:JQ4"/>
+    <mergeCell ref="DF4:DQ4"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="Z4:AK4"/>
+    <mergeCell ref="AL4:AW4"/>
+    <mergeCell ref="AX4:BI4"/>
+    <mergeCell ref="A44:JS44"/>
+    <mergeCell ref="JR4:JT4"/>
   </mergeCells>
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -41925,60 +41925,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
     </row>
     <row r="2" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
     </row>
     <row r="4" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -45487,32 +45487,32 @@
       </c>
     </row>
     <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="30"/>
-      <c r="J53" s="30"/>
-      <c r="K53" s="30"/>
-      <c r="L53" s="30"/>
-      <c r="M53" s="30"/>
-      <c r="N53" s="30"/>
-      <c r="O53" s="30"/>
-      <c r="P53" s="30"/>
-      <c r="Q53" s="30"/>
-      <c r="R53" s="30"/>
-      <c r="S53" s="30"/>
-      <c r="T53" s="30"/>
-      <c r="U53" s="30"/>
-      <c r="V53" s="30"/>
-      <c r="W53" s="30"/>
-      <c r="X53" s="30"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="26"/>
+      <c r="Q53" s="26"/>
+      <c r="R53" s="26"/>
+      <c r="S53" s="26"/>
+      <c r="T53" s="26"/>
+      <c r="U53" s="26"/>
+      <c r="V53" s="26"/>
+      <c r="W53" s="26"/>
+      <c r="X53" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
+++ b/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.18.05.2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.06.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E731768-D490-44C0-B2B9-B3BCD172355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E7EE21-4375-449D-8064-E10F5AF5CEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mensual" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="49">
   <si>
     <t>FLUJOS DE LA CUENTA FINANCIERA DE BALANZA DE PAGOS</t>
   </si>
@@ -519,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -598,11 +598,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -621,15 +633,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -767,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:JT54"/>
+  <dimension ref="A1:JU54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -828,909 +831,912 @@
     <col min="191" max="265" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="266" max="266" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="267" max="278" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="279" max="280" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="281" max="16384" width="11.42578125" style="1"/>
+    <col min="279" max="281" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="282" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="35"/>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="35"/>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
-      <c r="AP1" s="35"/>
-      <c r="AQ1" s="35"/>
-      <c r="AR1" s="35"/>
-      <c r="AS1" s="35"/>
-      <c r="AT1" s="35"/>
-      <c r="AU1" s="35"/>
-      <c r="AV1" s="35"/>
-      <c r="AW1" s="35"/>
-      <c r="AX1" s="35"/>
-      <c r="AY1" s="35"/>
-      <c r="AZ1" s="35"/>
-      <c r="BA1" s="35"/>
-      <c r="BB1" s="35"/>
-      <c r="BC1" s="35"/>
-      <c r="BD1" s="35"/>
-      <c r="BE1" s="35"/>
-      <c r="BF1" s="35"/>
-      <c r="BG1" s="35"/>
-      <c r="BH1" s="35"/>
-      <c r="BI1" s="35"/>
-      <c r="BJ1" s="35"/>
-      <c r="BK1" s="35"/>
-      <c r="BL1" s="35"/>
-      <c r="BM1" s="35"/>
-      <c r="BN1" s="35"/>
-      <c r="BO1" s="35"/>
-      <c r="BP1" s="35"/>
-      <c r="BQ1" s="35"/>
-      <c r="BR1" s="35"/>
-      <c r="BS1" s="35"/>
-      <c r="BT1" s="35"/>
-      <c r="BU1" s="35"/>
-      <c r="BV1" s="35"/>
-      <c r="BW1" s="35"/>
-      <c r="BX1" s="35"/>
-      <c r="BY1" s="35"/>
-      <c r="BZ1" s="35"/>
-      <c r="CA1" s="35"/>
-      <c r="CB1" s="35"/>
-      <c r="CC1" s="35"/>
-      <c r="CD1" s="35"/>
-      <c r="CE1" s="35"/>
-      <c r="CF1" s="35"/>
-      <c r="CG1" s="35"/>
-      <c r="CH1" s="35"/>
-      <c r="CI1" s="35"/>
-      <c r="CJ1" s="35"/>
-      <c r="CK1" s="35"/>
-      <c r="CL1" s="35"/>
-      <c r="CM1" s="35"/>
-      <c r="CN1" s="35"/>
-      <c r="CO1" s="35"/>
-      <c r="CP1" s="35"/>
-      <c r="CQ1" s="35"/>
-      <c r="CR1" s="35"/>
-      <c r="CS1" s="35"/>
-      <c r="CT1" s="35"/>
-      <c r="CU1" s="35"/>
-      <c r="CV1" s="35"/>
-      <c r="CW1" s="35"/>
-      <c r="CX1" s="35"/>
-      <c r="CY1" s="35"/>
-      <c r="CZ1" s="35"/>
-      <c r="DA1" s="35"/>
-      <c r="DB1" s="35"/>
-      <c r="DC1" s="35"/>
-      <c r="DD1" s="35"/>
-      <c r="DE1" s="35"/>
-      <c r="DF1" s="35"/>
-      <c r="DG1" s="35"/>
-      <c r="DH1" s="35"/>
-      <c r="DI1" s="35"/>
-      <c r="DJ1" s="35"/>
-      <c r="DK1" s="35"/>
-      <c r="DL1" s="35"/>
-      <c r="DM1" s="35"/>
-      <c r="DN1" s="35"/>
-      <c r="DO1" s="35"/>
-      <c r="DP1" s="35"/>
-      <c r="DQ1" s="35"/>
-      <c r="DR1" s="35"/>
-      <c r="DS1" s="35"/>
-      <c r="DT1" s="35"/>
-      <c r="DU1" s="35"/>
-      <c r="DV1" s="35"/>
-      <c r="DW1" s="35"/>
-      <c r="DX1" s="35"/>
-      <c r="DY1" s="35"/>
-      <c r="DZ1" s="35"/>
-      <c r="EA1" s="35"/>
-      <c r="EB1" s="35"/>
-      <c r="EC1" s="35"/>
-      <c r="ED1" s="35"/>
-      <c r="EE1" s="35"/>
-      <c r="EF1" s="35"/>
-      <c r="EG1" s="35"/>
-      <c r="EH1" s="35"/>
-      <c r="EI1" s="35"/>
-      <c r="EJ1" s="35"/>
-      <c r="EK1" s="35"/>
-      <c r="EL1" s="35"/>
-      <c r="EM1" s="35"/>
-      <c r="EN1" s="35"/>
-      <c r="EO1" s="35"/>
-      <c r="EP1" s="35"/>
-      <c r="EQ1" s="35"/>
-      <c r="ER1" s="35"/>
-      <c r="ES1" s="35"/>
-      <c r="ET1" s="35"/>
-      <c r="EU1" s="35"/>
-      <c r="EV1" s="35"/>
-      <c r="EW1" s="35"/>
-      <c r="EX1" s="35"/>
-      <c r="EY1" s="35"/>
-      <c r="EZ1" s="35"/>
-      <c r="FA1" s="35"/>
-      <c r="FB1" s="35"/>
-      <c r="FC1" s="35"/>
-      <c r="FD1" s="35"/>
-      <c r="FE1" s="35"/>
-      <c r="FF1" s="35"/>
-      <c r="FG1" s="35"/>
-      <c r="FH1" s="35"/>
-      <c r="FI1" s="35"/>
-      <c r="FJ1" s="35"/>
-      <c r="FK1" s="35"/>
-      <c r="FL1" s="35"/>
-      <c r="FM1" s="35"/>
-      <c r="FN1" s="35"/>
-      <c r="FO1" s="35"/>
-      <c r="FP1" s="35"/>
-      <c r="FQ1" s="35"/>
-      <c r="FR1" s="35"/>
-      <c r="FS1" s="35"/>
-      <c r="FT1" s="35"/>
-      <c r="FU1" s="35"/>
-      <c r="FV1" s="35"/>
-      <c r="FW1" s="35"/>
-      <c r="FX1" s="35"/>
-      <c r="FY1" s="35"/>
-      <c r="FZ1" s="35"/>
-      <c r="GA1" s="35"/>
-      <c r="GB1" s="35"/>
-      <c r="GC1" s="35"/>
-      <c r="GD1" s="35"/>
-      <c r="GE1" s="35"/>
-      <c r="GF1" s="35"/>
-      <c r="GG1" s="35"/>
-      <c r="GH1" s="35"/>
-      <c r="GI1" s="35"/>
-      <c r="GJ1" s="35"/>
-      <c r="GK1" s="35"/>
-      <c r="GL1" s="35"/>
-      <c r="GM1" s="35"/>
-      <c r="GN1" s="35"/>
-      <c r="GO1" s="35"/>
-      <c r="GP1" s="35"/>
-      <c r="GQ1" s="35"/>
-      <c r="GR1" s="35"/>
-      <c r="GS1" s="35"/>
-      <c r="GT1" s="35"/>
-      <c r="GU1" s="35"/>
-      <c r="GV1" s="35"/>
-      <c r="GW1" s="35"/>
-      <c r="GX1" s="35"/>
-      <c r="GY1" s="35"/>
-      <c r="GZ1" s="35"/>
-      <c r="HA1" s="35"/>
-      <c r="HB1" s="35"/>
-      <c r="HC1" s="35"/>
-      <c r="HD1" s="35"/>
-      <c r="HE1" s="35"/>
-      <c r="HF1" s="35"/>
-      <c r="HG1" s="35"/>
-      <c r="HH1" s="35"/>
-      <c r="HI1" s="35"/>
-      <c r="HJ1" s="35"/>
-      <c r="HK1" s="35"/>
-      <c r="HL1" s="35"/>
-      <c r="HM1" s="35"/>
-      <c r="HN1" s="35"/>
-      <c r="HO1" s="35"/>
-      <c r="HP1" s="35"/>
-      <c r="HQ1" s="35"/>
-      <c r="HR1" s="35"/>
-      <c r="HS1" s="35"/>
-      <c r="HT1" s="35"/>
-      <c r="HU1" s="35"/>
-      <c r="HV1" s="35"/>
-      <c r="HW1" s="35"/>
-      <c r="HX1" s="35"/>
-      <c r="HY1" s="35"/>
-      <c r="HZ1" s="35"/>
-      <c r="IA1" s="35"/>
-      <c r="IB1" s="35"/>
-      <c r="IC1" s="35"/>
-      <c r="ID1" s="35"/>
-      <c r="IE1" s="35"/>
-      <c r="IF1" s="35"/>
-      <c r="IG1" s="35"/>
-      <c r="IH1" s="35"/>
-      <c r="II1" s="35"/>
-      <c r="IJ1" s="35"/>
-      <c r="IK1" s="35"/>
-      <c r="IL1" s="35"/>
-      <c r="IM1" s="35"/>
-      <c r="IN1" s="35"/>
-      <c r="IO1" s="35"/>
-      <c r="IP1" s="35"/>
-      <c r="IQ1" s="35"/>
-      <c r="IR1" s="35"/>
-      <c r="IS1" s="35"/>
-      <c r="IT1" s="35"/>
-      <c r="IU1" s="35"/>
-      <c r="IV1" s="35"/>
-      <c r="IW1" s="35"/>
-      <c r="IX1" s="35"/>
-      <c r="IY1" s="35"/>
-      <c r="IZ1" s="35"/>
-      <c r="JA1" s="35"/>
-      <c r="JB1" s="35"/>
-      <c r="JC1" s="35"/>
-      <c r="JD1" s="35"/>
-      <c r="JE1" s="35"/>
-      <c r="JF1" s="35"/>
-      <c r="JG1" s="35"/>
-      <c r="JH1" s="35"/>
-      <c r="JI1" s="35"/>
-      <c r="JJ1" s="35"/>
-      <c r="JK1" s="35"/>
-      <c r="JL1" s="35"/>
-      <c r="JM1" s="35"/>
-      <c r="JN1" s="35"/>
-      <c r="JO1" s="35"/>
-      <c r="JP1" s="35"/>
-      <c r="JQ1" s="35"/>
-      <c r="JR1" s="35"/>
+    <row r="1" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="28"/>
+      <c r="AP1" s="28"/>
+      <c r="AQ1" s="28"/>
+      <c r="AR1" s="28"/>
+      <c r="AS1" s="28"/>
+      <c r="AT1" s="28"/>
+      <c r="AU1" s="28"/>
+      <c r="AV1" s="28"/>
+      <c r="AW1" s="28"/>
+      <c r="AX1" s="28"/>
+      <c r="AY1" s="28"/>
+      <c r="AZ1" s="28"/>
+      <c r="BA1" s="28"/>
+      <c r="BB1" s="28"/>
+      <c r="BC1" s="28"/>
+      <c r="BD1" s="28"/>
+      <c r="BE1" s="28"/>
+      <c r="BF1" s="28"/>
+      <c r="BG1" s="28"/>
+      <c r="BH1" s="28"/>
+      <c r="BI1" s="28"/>
+      <c r="BJ1" s="28"/>
+      <c r="BK1" s="28"/>
+      <c r="BL1" s="28"/>
+      <c r="BM1" s="28"/>
+      <c r="BN1" s="28"/>
+      <c r="BO1" s="28"/>
+      <c r="BP1" s="28"/>
+      <c r="BQ1" s="28"/>
+      <c r="BR1" s="28"/>
+      <c r="BS1" s="28"/>
+      <c r="BT1" s="28"/>
+      <c r="BU1" s="28"/>
+      <c r="BV1" s="28"/>
+      <c r="BW1" s="28"/>
+      <c r="BX1" s="28"/>
+      <c r="BY1" s="28"/>
+      <c r="BZ1" s="28"/>
+      <c r="CA1" s="28"/>
+      <c r="CB1" s="28"/>
+      <c r="CC1" s="28"/>
+      <c r="CD1" s="28"/>
+      <c r="CE1" s="28"/>
+      <c r="CF1" s="28"/>
+      <c r="CG1" s="28"/>
+      <c r="CH1" s="28"/>
+      <c r="CI1" s="28"/>
+      <c r="CJ1" s="28"/>
+      <c r="CK1" s="28"/>
+      <c r="CL1" s="28"/>
+      <c r="CM1" s="28"/>
+      <c r="CN1" s="28"/>
+      <c r="CO1" s="28"/>
+      <c r="CP1" s="28"/>
+      <c r="CQ1" s="28"/>
+      <c r="CR1" s="28"/>
+      <c r="CS1" s="28"/>
+      <c r="CT1" s="28"/>
+      <c r="CU1" s="28"/>
+      <c r="CV1" s="28"/>
+      <c r="CW1" s="28"/>
+      <c r="CX1" s="28"/>
+      <c r="CY1" s="28"/>
+      <c r="CZ1" s="28"/>
+      <c r="DA1" s="28"/>
+      <c r="DB1" s="28"/>
+      <c r="DC1" s="28"/>
+      <c r="DD1" s="28"/>
+      <c r="DE1" s="28"/>
+      <c r="DF1" s="28"/>
+      <c r="DG1" s="28"/>
+      <c r="DH1" s="28"/>
+      <c r="DI1" s="28"/>
+      <c r="DJ1" s="28"/>
+      <c r="DK1" s="28"/>
+      <c r="DL1" s="28"/>
+      <c r="DM1" s="28"/>
+      <c r="DN1" s="28"/>
+      <c r="DO1" s="28"/>
+      <c r="DP1" s="28"/>
+      <c r="DQ1" s="28"/>
+      <c r="DR1" s="28"/>
+      <c r="DS1" s="28"/>
+      <c r="DT1" s="28"/>
+      <c r="DU1" s="28"/>
+      <c r="DV1" s="28"/>
+      <c r="DW1" s="28"/>
+      <c r="DX1" s="28"/>
+      <c r="DY1" s="28"/>
+      <c r="DZ1" s="28"/>
+      <c r="EA1" s="28"/>
+      <c r="EB1" s="28"/>
+      <c r="EC1" s="28"/>
+      <c r="ED1" s="28"/>
+      <c r="EE1" s="28"/>
+      <c r="EF1" s="28"/>
+      <c r="EG1" s="28"/>
+      <c r="EH1" s="28"/>
+      <c r="EI1" s="28"/>
+      <c r="EJ1" s="28"/>
+      <c r="EK1" s="28"/>
+      <c r="EL1" s="28"/>
+      <c r="EM1" s="28"/>
+      <c r="EN1" s="28"/>
+      <c r="EO1" s="28"/>
+      <c r="EP1" s="28"/>
+      <c r="EQ1" s="28"/>
+      <c r="ER1" s="28"/>
+      <c r="ES1" s="28"/>
+      <c r="ET1" s="28"/>
+      <c r="EU1" s="28"/>
+      <c r="EV1" s="28"/>
+      <c r="EW1" s="28"/>
+      <c r="EX1" s="28"/>
+      <c r="EY1" s="28"/>
+      <c r="EZ1" s="28"/>
+      <c r="FA1" s="28"/>
+      <c r="FB1" s="28"/>
+      <c r="FC1" s="28"/>
+      <c r="FD1" s="28"/>
+      <c r="FE1" s="28"/>
+      <c r="FF1" s="28"/>
+      <c r="FG1" s="28"/>
+      <c r="FH1" s="28"/>
+      <c r="FI1" s="28"/>
+      <c r="FJ1" s="28"/>
+      <c r="FK1" s="28"/>
+      <c r="FL1" s="28"/>
+      <c r="FM1" s="28"/>
+      <c r="FN1" s="28"/>
+      <c r="FO1" s="28"/>
+      <c r="FP1" s="28"/>
+      <c r="FQ1" s="28"/>
+      <c r="FR1" s="28"/>
+      <c r="FS1" s="28"/>
+      <c r="FT1" s="28"/>
+      <c r="FU1" s="28"/>
+      <c r="FV1" s="28"/>
+      <c r="FW1" s="28"/>
+      <c r="FX1" s="28"/>
+      <c r="FY1" s="28"/>
+      <c r="FZ1" s="28"/>
+      <c r="GA1" s="28"/>
+      <c r="GB1" s="28"/>
+      <c r="GC1" s="28"/>
+      <c r="GD1" s="28"/>
+      <c r="GE1" s="28"/>
+      <c r="GF1" s="28"/>
+      <c r="GG1" s="28"/>
+      <c r="GH1" s="28"/>
+      <c r="GI1" s="28"/>
+      <c r="GJ1" s="28"/>
+      <c r="GK1" s="28"/>
+      <c r="GL1" s="28"/>
+      <c r="GM1" s="28"/>
+      <c r="GN1" s="28"/>
+      <c r="GO1" s="28"/>
+      <c r="GP1" s="28"/>
+      <c r="GQ1" s="28"/>
+      <c r="GR1" s="28"/>
+      <c r="GS1" s="28"/>
+      <c r="GT1" s="28"/>
+      <c r="GU1" s="28"/>
+      <c r="GV1" s="28"/>
+      <c r="GW1" s="28"/>
+      <c r="GX1" s="28"/>
+      <c r="GY1" s="28"/>
+      <c r="GZ1" s="28"/>
+      <c r="HA1" s="28"/>
+      <c r="HB1" s="28"/>
+      <c r="HC1" s="28"/>
+      <c r="HD1" s="28"/>
+      <c r="HE1" s="28"/>
+      <c r="HF1" s="28"/>
+      <c r="HG1" s="28"/>
+      <c r="HH1" s="28"/>
+      <c r="HI1" s="28"/>
+      <c r="HJ1" s="28"/>
+      <c r="HK1" s="28"/>
+      <c r="HL1" s="28"/>
+      <c r="HM1" s="28"/>
+      <c r="HN1" s="28"/>
+      <c r="HO1" s="28"/>
+      <c r="HP1" s="28"/>
+      <c r="HQ1" s="28"/>
+      <c r="HR1" s="28"/>
+      <c r="HS1" s="28"/>
+      <c r="HT1" s="28"/>
+      <c r="HU1" s="28"/>
+      <c r="HV1" s="28"/>
+      <c r="HW1" s="28"/>
+      <c r="HX1" s="28"/>
+      <c r="HY1" s="28"/>
+      <c r="HZ1" s="28"/>
+      <c r="IA1" s="28"/>
+      <c r="IB1" s="28"/>
+      <c r="IC1" s="28"/>
+      <c r="ID1" s="28"/>
+      <c r="IE1" s="28"/>
+      <c r="IF1" s="28"/>
+      <c r="IG1" s="28"/>
+      <c r="IH1" s="28"/>
+      <c r="II1" s="28"/>
+      <c r="IJ1" s="28"/>
+      <c r="IK1" s="28"/>
+      <c r="IL1" s="28"/>
+      <c r="IM1" s="28"/>
+      <c r="IN1" s="28"/>
+      <c r="IO1" s="28"/>
+      <c r="IP1" s="28"/>
+      <c r="IQ1" s="28"/>
+      <c r="IR1" s="28"/>
+      <c r="IS1" s="28"/>
+      <c r="IT1" s="28"/>
+      <c r="IU1" s="28"/>
+      <c r="IV1" s="28"/>
+      <c r="IW1" s="28"/>
+      <c r="IX1" s="28"/>
+      <c r="IY1" s="28"/>
+      <c r="IZ1" s="28"/>
+      <c r="JA1" s="28"/>
+      <c r="JB1" s="28"/>
+      <c r="JC1" s="28"/>
+      <c r="JD1" s="28"/>
+      <c r="JE1" s="28"/>
+      <c r="JF1" s="28"/>
+      <c r="JG1" s="28"/>
+      <c r="JH1" s="28"/>
+      <c r="JI1" s="28"/>
+      <c r="JJ1" s="28"/>
+      <c r="JK1" s="28"/>
+      <c r="JL1" s="28"/>
+      <c r="JM1" s="28"/>
+      <c r="JN1" s="28"/>
+      <c r="JO1" s="28"/>
+      <c r="JP1" s="28"/>
+      <c r="JQ1" s="28"/>
+      <c r="JR1" s="28"/>
       <c r="JS1" s="10"/>
       <c r="JT1" s="10"/>
+      <c r="JU1" s="10"/>
     </row>
-    <row r="2" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="35"/>
-      <c r="CF2" s="35"/>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
-      <c r="CI2" s="35"/>
-      <c r="CJ2" s="35"/>
-      <c r="CK2" s="35"/>
-      <c r="CL2" s="35"/>
-      <c r="CM2" s="35"/>
-      <c r="CN2" s="35"/>
-      <c r="CO2" s="35"/>
-      <c r="CP2" s="35"/>
-      <c r="CQ2" s="35"/>
-      <c r="CR2" s="35"/>
-      <c r="CS2" s="35"/>
-      <c r="CT2" s="35"/>
-      <c r="CU2" s="35"/>
-      <c r="CV2" s="35"/>
-      <c r="CW2" s="35"/>
-      <c r="CX2" s="35"/>
-      <c r="CY2" s="35"/>
-      <c r="CZ2" s="35"/>
-      <c r="DA2" s="35"/>
-      <c r="DB2" s="35"/>
-      <c r="DC2" s="35"/>
-      <c r="DD2" s="35"/>
-      <c r="DE2" s="35"/>
-      <c r="DF2" s="35"/>
-      <c r="DG2" s="35"/>
-      <c r="DH2" s="35"/>
-      <c r="DI2" s="35"/>
-      <c r="DJ2" s="35"/>
-      <c r="DK2" s="35"/>
-      <c r="DL2" s="35"/>
-      <c r="DM2" s="35"/>
-      <c r="DN2" s="35"/>
-      <c r="DO2" s="35"/>
-      <c r="DP2" s="35"/>
-      <c r="DQ2" s="35"/>
-      <c r="DR2" s="35"/>
-      <c r="DS2" s="35"/>
-      <c r="DT2" s="35"/>
-      <c r="DU2" s="35"/>
-      <c r="DV2" s="35"/>
-      <c r="DW2" s="35"/>
-      <c r="DX2" s="35"/>
-      <c r="DY2" s="35"/>
-      <c r="DZ2" s="35"/>
-      <c r="EA2" s="35"/>
-      <c r="EB2" s="35"/>
-      <c r="EC2" s="35"/>
-      <c r="ED2" s="35"/>
-      <c r="EE2" s="35"/>
-      <c r="EF2" s="35"/>
-      <c r="EG2" s="35"/>
-      <c r="EH2" s="35"/>
-      <c r="EI2" s="35"/>
-      <c r="EJ2" s="35"/>
-      <c r="EK2" s="35"/>
-      <c r="EL2" s="35"/>
-      <c r="EM2" s="35"/>
-      <c r="EN2" s="35"/>
-      <c r="EO2" s="35"/>
-      <c r="EP2" s="35"/>
-      <c r="EQ2" s="35"/>
-      <c r="ER2" s="35"/>
-      <c r="ES2" s="35"/>
-      <c r="ET2" s="35"/>
-      <c r="EU2" s="35"/>
-      <c r="EV2" s="35"/>
-      <c r="EW2" s="35"/>
-      <c r="EX2" s="35"/>
-      <c r="EY2" s="35"/>
-      <c r="EZ2" s="35"/>
-      <c r="FA2" s="35"/>
-      <c r="FB2" s="35"/>
-      <c r="FC2" s="35"/>
-      <c r="FD2" s="35"/>
-      <c r="FE2" s="35"/>
-      <c r="FF2" s="35"/>
-      <c r="FG2" s="35"/>
-      <c r="FH2" s="35"/>
-      <c r="FI2" s="35"/>
-      <c r="FJ2" s="35"/>
-      <c r="FK2" s="35"/>
-      <c r="FL2" s="35"/>
-      <c r="FM2" s="35"/>
-      <c r="FN2" s="35"/>
-      <c r="FO2" s="35"/>
-      <c r="FP2" s="35"/>
-      <c r="FQ2" s="35"/>
-      <c r="FR2" s="35"/>
-      <c r="FS2" s="35"/>
-      <c r="FT2" s="35"/>
-      <c r="FU2" s="35"/>
-      <c r="FV2" s="35"/>
-      <c r="FW2" s="35"/>
-      <c r="FX2" s="35"/>
-      <c r="FY2" s="35"/>
-      <c r="FZ2" s="35"/>
-      <c r="GA2" s="35"/>
-      <c r="GB2" s="35"/>
-      <c r="GC2" s="35"/>
-      <c r="GD2" s="35"/>
-      <c r="GE2" s="35"/>
-      <c r="GF2" s="35"/>
-      <c r="GG2" s="35"/>
-      <c r="GH2" s="35"/>
-      <c r="GI2" s="35"/>
-      <c r="GJ2" s="35"/>
-      <c r="GK2" s="35"/>
-      <c r="GL2" s="35"/>
-      <c r="GM2" s="35"/>
-      <c r="GN2" s="35"/>
-      <c r="GO2" s="35"/>
-      <c r="GP2" s="35"/>
-      <c r="GQ2" s="35"/>
-      <c r="GR2" s="35"/>
-      <c r="GS2" s="35"/>
-      <c r="GT2" s="35"/>
-      <c r="GU2" s="35"/>
-      <c r="GV2" s="35"/>
-      <c r="GW2" s="35"/>
-      <c r="GX2" s="35"/>
-      <c r="GY2" s="35"/>
-      <c r="GZ2" s="35"/>
-      <c r="HA2" s="35"/>
-      <c r="HB2" s="35"/>
-      <c r="HC2" s="35"/>
-      <c r="HD2" s="35"/>
-      <c r="HE2" s="35"/>
-      <c r="HF2" s="35"/>
-      <c r="HG2" s="35"/>
-      <c r="HH2" s="35"/>
-      <c r="HI2" s="35"/>
-      <c r="HJ2" s="35"/>
-      <c r="HK2" s="35"/>
-      <c r="HL2" s="35"/>
-      <c r="HM2" s="35"/>
-      <c r="HN2" s="35"/>
-      <c r="HO2" s="35"/>
-      <c r="HP2" s="35"/>
-      <c r="HQ2" s="35"/>
-      <c r="HR2" s="35"/>
-      <c r="HS2" s="35"/>
-      <c r="HT2" s="35"/>
-      <c r="HU2" s="35"/>
-      <c r="HV2" s="35"/>
-      <c r="HW2" s="35"/>
-      <c r="HX2" s="35"/>
-      <c r="HY2" s="35"/>
-      <c r="HZ2" s="35"/>
-      <c r="IA2" s="35"/>
-      <c r="IB2" s="35"/>
-      <c r="IC2" s="35"/>
-      <c r="ID2" s="35"/>
-      <c r="IE2" s="35"/>
-      <c r="IF2" s="35"/>
-      <c r="IG2" s="35"/>
-      <c r="IH2" s="35"/>
-      <c r="II2" s="35"/>
-      <c r="IJ2" s="35"/>
-      <c r="IK2" s="35"/>
-      <c r="IL2" s="35"/>
-      <c r="IM2" s="35"/>
-      <c r="IN2" s="35"/>
-      <c r="IO2" s="35"/>
-      <c r="IP2" s="35"/>
-      <c r="IQ2" s="35"/>
-      <c r="IR2" s="35"/>
-      <c r="IS2" s="35"/>
-      <c r="IT2" s="35"/>
-      <c r="IU2" s="35"/>
-      <c r="IV2" s="35"/>
-      <c r="IW2" s="35"/>
-      <c r="IX2" s="35"/>
-      <c r="IY2" s="35"/>
-      <c r="IZ2" s="35"/>
-      <c r="JA2" s="35"/>
-      <c r="JB2" s="35"/>
-      <c r="JC2" s="35"/>
-      <c r="JD2" s="35"/>
-      <c r="JE2" s="35"/>
-      <c r="JF2" s="35"/>
-      <c r="JG2" s="35"/>
-      <c r="JH2" s="35"/>
-      <c r="JI2" s="35"/>
-      <c r="JJ2" s="35"/>
-      <c r="JK2" s="35"/>
-      <c r="JL2" s="35"/>
-      <c r="JM2" s="35"/>
-      <c r="JN2" s="35"/>
-      <c r="JO2" s="35"/>
-      <c r="JP2" s="35"/>
-      <c r="JQ2" s="35"/>
-      <c r="JR2" s="35"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
+      <c r="CI2" s="28"/>
+      <c r="CJ2" s="28"/>
+      <c r="CK2" s="28"/>
+      <c r="CL2" s="28"/>
+      <c r="CM2" s="28"/>
+      <c r="CN2" s="28"/>
+      <c r="CO2" s="28"/>
+      <c r="CP2" s="28"/>
+      <c r="CQ2" s="28"/>
+      <c r="CR2" s="28"/>
+      <c r="CS2" s="28"/>
+      <c r="CT2" s="28"/>
+      <c r="CU2" s="28"/>
+      <c r="CV2" s="28"/>
+      <c r="CW2" s="28"/>
+      <c r="CX2" s="28"/>
+      <c r="CY2" s="28"/>
+      <c r="CZ2" s="28"/>
+      <c r="DA2" s="28"/>
+      <c r="DB2" s="28"/>
+      <c r="DC2" s="28"/>
+      <c r="DD2" s="28"/>
+      <c r="DE2" s="28"/>
+      <c r="DF2" s="28"/>
+      <c r="DG2" s="28"/>
+      <c r="DH2" s="28"/>
+      <c r="DI2" s="28"/>
+      <c r="DJ2" s="28"/>
+      <c r="DK2" s="28"/>
+      <c r="DL2" s="28"/>
+      <c r="DM2" s="28"/>
+      <c r="DN2" s="28"/>
+      <c r="DO2" s="28"/>
+      <c r="DP2" s="28"/>
+      <c r="DQ2" s="28"/>
+      <c r="DR2" s="28"/>
+      <c r="DS2" s="28"/>
+      <c r="DT2" s="28"/>
+      <c r="DU2" s="28"/>
+      <c r="DV2" s="28"/>
+      <c r="DW2" s="28"/>
+      <c r="DX2" s="28"/>
+      <c r="DY2" s="28"/>
+      <c r="DZ2" s="28"/>
+      <c r="EA2" s="28"/>
+      <c r="EB2" s="28"/>
+      <c r="EC2" s="28"/>
+      <c r="ED2" s="28"/>
+      <c r="EE2" s="28"/>
+      <c r="EF2" s="28"/>
+      <c r="EG2" s="28"/>
+      <c r="EH2" s="28"/>
+      <c r="EI2" s="28"/>
+      <c r="EJ2" s="28"/>
+      <c r="EK2" s="28"/>
+      <c r="EL2" s="28"/>
+      <c r="EM2" s="28"/>
+      <c r="EN2" s="28"/>
+      <c r="EO2" s="28"/>
+      <c r="EP2" s="28"/>
+      <c r="EQ2" s="28"/>
+      <c r="ER2" s="28"/>
+      <c r="ES2" s="28"/>
+      <c r="ET2" s="28"/>
+      <c r="EU2" s="28"/>
+      <c r="EV2" s="28"/>
+      <c r="EW2" s="28"/>
+      <c r="EX2" s="28"/>
+      <c r="EY2" s="28"/>
+      <c r="EZ2" s="28"/>
+      <c r="FA2" s="28"/>
+      <c r="FB2" s="28"/>
+      <c r="FC2" s="28"/>
+      <c r="FD2" s="28"/>
+      <c r="FE2" s="28"/>
+      <c r="FF2" s="28"/>
+      <c r="FG2" s="28"/>
+      <c r="FH2" s="28"/>
+      <c r="FI2" s="28"/>
+      <c r="FJ2" s="28"/>
+      <c r="FK2" s="28"/>
+      <c r="FL2" s="28"/>
+      <c r="FM2" s="28"/>
+      <c r="FN2" s="28"/>
+      <c r="FO2" s="28"/>
+      <c r="FP2" s="28"/>
+      <c r="FQ2" s="28"/>
+      <c r="FR2" s="28"/>
+      <c r="FS2" s="28"/>
+      <c r="FT2" s="28"/>
+      <c r="FU2" s="28"/>
+      <c r="FV2" s="28"/>
+      <c r="FW2" s="28"/>
+      <c r="FX2" s="28"/>
+      <c r="FY2" s="28"/>
+      <c r="FZ2" s="28"/>
+      <c r="GA2" s="28"/>
+      <c r="GB2" s="28"/>
+      <c r="GC2" s="28"/>
+      <c r="GD2" s="28"/>
+      <c r="GE2" s="28"/>
+      <c r="GF2" s="28"/>
+      <c r="GG2" s="28"/>
+      <c r="GH2" s="28"/>
+      <c r="GI2" s="28"/>
+      <c r="GJ2" s="28"/>
+      <c r="GK2" s="28"/>
+      <c r="GL2" s="28"/>
+      <c r="GM2" s="28"/>
+      <c r="GN2" s="28"/>
+      <c r="GO2" s="28"/>
+      <c r="GP2" s="28"/>
+      <c r="GQ2" s="28"/>
+      <c r="GR2" s="28"/>
+      <c r="GS2" s="28"/>
+      <c r="GT2" s="28"/>
+      <c r="GU2" s="28"/>
+      <c r="GV2" s="28"/>
+      <c r="GW2" s="28"/>
+      <c r="GX2" s="28"/>
+      <c r="GY2" s="28"/>
+      <c r="GZ2" s="28"/>
+      <c r="HA2" s="28"/>
+      <c r="HB2" s="28"/>
+      <c r="HC2" s="28"/>
+      <c r="HD2" s="28"/>
+      <c r="HE2" s="28"/>
+      <c r="HF2" s="28"/>
+      <c r="HG2" s="28"/>
+      <c r="HH2" s="28"/>
+      <c r="HI2" s="28"/>
+      <c r="HJ2" s="28"/>
+      <c r="HK2" s="28"/>
+      <c r="HL2" s="28"/>
+      <c r="HM2" s="28"/>
+      <c r="HN2" s="28"/>
+      <c r="HO2" s="28"/>
+      <c r="HP2" s="28"/>
+      <c r="HQ2" s="28"/>
+      <c r="HR2" s="28"/>
+      <c r="HS2" s="28"/>
+      <c r="HT2" s="28"/>
+      <c r="HU2" s="28"/>
+      <c r="HV2" s="28"/>
+      <c r="HW2" s="28"/>
+      <c r="HX2" s="28"/>
+      <c r="HY2" s="28"/>
+      <c r="HZ2" s="28"/>
+      <c r="IA2" s="28"/>
+      <c r="IB2" s="28"/>
+      <c r="IC2" s="28"/>
+      <c r="ID2" s="28"/>
+      <c r="IE2" s="28"/>
+      <c r="IF2" s="28"/>
+      <c r="IG2" s="28"/>
+      <c r="IH2" s="28"/>
+      <c r="II2" s="28"/>
+      <c r="IJ2" s="28"/>
+      <c r="IK2" s="28"/>
+      <c r="IL2" s="28"/>
+      <c r="IM2" s="28"/>
+      <c r="IN2" s="28"/>
+      <c r="IO2" s="28"/>
+      <c r="IP2" s="28"/>
+      <c r="IQ2" s="28"/>
+      <c r="IR2" s="28"/>
+      <c r="IS2" s="28"/>
+      <c r="IT2" s="28"/>
+      <c r="IU2" s="28"/>
+      <c r="IV2" s="28"/>
+      <c r="IW2" s="28"/>
+      <c r="IX2" s="28"/>
+      <c r="IY2" s="28"/>
+      <c r="IZ2" s="28"/>
+      <c r="JA2" s="28"/>
+      <c r="JB2" s="28"/>
+      <c r="JC2" s="28"/>
+      <c r="JD2" s="28"/>
+      <c r="JE2" s="28"/>
+      <c r="JF2" s="28"/>
+      <c r="JG2" s="28"/>
+      <c r="JH2" s="28"/>
+      <c r="JI2" s="28"/>
+      <c r="JJ2" s="28"/>
+      <c r="JK2" s="28"/>
+      <c r="JL2" s="28"/>
+      <c r="JM2" s="28"/>
+      <c r="JN2" s="28"/>
+      <c r="JO2" s="28"/>
+      <c r="JP2" s="28"/>
+      <c r="JQ2" s="28"/>
+      <c r="JR2" s="28"/>
       <c r="JS2" s="10"/>
       <c r="JT2" s="10"/>
+      <c r="JU2" s="10"/>
     </row>
-    <row r="4" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="27">
+      <c r="B4" s="30">
         <v>2003</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27">
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30">
         <v>2004</v>
       </c>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27">
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30">
         <v>2005</v>
       </c>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="27"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="27"/>
-      <c r="AL4" s="27">
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="30"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="30">
         <v>2006</v>
       </c>
-      <c r="AM4" s="27"/>
-      <c r="AN4" s="27"/>
-      <c r="AO4" s="27"/>
-      <c r="AP4" s="27"/>
-      <c r="AQ4" s="27"/>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27"/>
-      <c r="AU4" s="27"/>
-      <c r="AV4" s="27"/>
-      <c r="AW4" s="27"/>
-      <c r="AX4" s="27">
+      <c r="AM4" s="30"/>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="30"/>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="30"/>
+      <c r="AS4" s="30"/>
+      <c r="AT4" s="30"/>
+      <c r="AU4" s="30"/>
+      <c r="AV4" s="30"/>
+      <c r="AW4" s="30"/>
+      <c r="AX4" s="30">
         <v>2007</v>
       </c>
-      <c r="AY4" s="27"/>
-      <c r="AZ4" s="27"/>
-      <c r="BA4" s="27"/>
-      <c r="BB4" s="27"/>
-      <c r="BC4" s="27"/>
-      <c r="BD4" s="27"/>
-      <c r="BE4" s="27"/>
-      <c r="BF4" s="27"/>
-      <c r="BG4" s="27"/>
-      <c r="BH4" s="27"/>
-      <c r="BI4" s="27"/>
-      <c r="BJ4" s="27">
+      <c r="AY4" s="30"/>
+      <c r="AZ4" s="30"/>
+      <c r="BA4" s="30"/>
+      <c r="BB4" s="30"/>
+      <c r="BC4" s="30"/>
+      <c r="BD4" s="30"/>
+      <c r="BE4" s="30"/>
+      <c r="BF4" s="30"/>
+      <c r="BG4" s="30"/>
+      <c r="BH4" s="30"/>
+      <c r="BI4" s="30"/>
+      <c r="BJ4" s="30">
         <v>2008</v>
       </c>
-      <c r="BK4" s="27"/>
-      <c r="BL4" s="27"/>
-      <c r="BM4" s="27"/>
-      <c r="BN4" s="27"/>
-      <c r="BO4" s="27"/>
-      <c r="BP4" s="27"/>
-      <c r="BQ4" s="27"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="27"/>
-      <c r="BV4" s="27">
+      <c r="BK4" s="30"/>
+      <c r="BL4" s="30"/>
+      <c r="BM4" s="30"/>
+      <c r="BN4" s="30"/>
+      <c r="BO4" s="30"/>
+      <c r="BP4" s="30"/>
+      <c r="BQ4" s="30"/>
+      <c r="BR4" s="30"/>
+      <c r="BS4" s="30"/>
+      <c r="BT4" s="30"/>
+      <c r="BU4" s="30"/>
+      <c r="BV4" s="30">
         <v>2009</v>
       </c>
-      <c r="BW4" s="27"/>
-      <c r="BX4" s="27"/>
-      <c r="BY4" s="27"/>
-      <c r="BZ4" s="27"/>
-      <c r="CA4" s="27"/>
-      <c r="CB4" s="27"/>
-      <c r="CC4" s="27"/>
-      <c r="CD4" s="27"/>
-      <c r="CE4" s="27"/>
-      <c r="CF4" s="27"/>
-      <c r="CG4" s="27"/>
-      <c r="CH4" s="27">
+      <c r="BW4" s="30"/>
+      <c r="BX4" s="30"/>
+      <c r="BY4" s="30"/>
+      <c r="BZ4" s="30"/>
+      <c r="CA4" s="30"/>
+      <c r="CB4" s="30"/>
+      <c r="CC4" s="30"/>
+      <c r="CD4" s="30"/>
+      <c r="CE4" s="30"/>
+      <c r="CF4" s="30"/>
+      <c r="CG4" s="30"/>
+      <c r="CH4" s="30">
         <v>2010</v>
       </c>
-      <c r="CI4" s="27"/>
-      <c r="CJ4" s="27"/>
-      <c r="CK4" s="27"/>
-      <c r="CL4" s="27"/>
-      <c r="CM4" s="27"/>
-      <c r="CN4" s="27"/>
-      <c r="CO4" s="27"/>
-      <c r="CP4" s="27"/>
-      <c r="CQ4" s="27"/>
-      <c r="CR4" s="27"/>
-      <c r="CS4" s="27"/>
-      <c r="CT4" s="27">
+      <c r="CI4" s="30"/>
+      <c r="CJ4" s="30"/>
+      <c r="CK4" s="30"/>
+      <c r="CL4" s="30"/>
+      <c r="CM4" s="30"/>
+      <c r="CN4" s="30"/>
+      <c r="CO4" s="30"/>
+      <c r="CP4" s="30"/>
+      <c r="CQ4" s="30"/>
+      <c r="CR4" s="30"/>
+      <c r="CS4" s="30"/>
+      <c r="CT4" s="30">
         <v>2011</v>
       </c>
-      <c r="CU4" s="27"/>
-      <c r="CV4" s="27"/>
-      <c r="CW4" s="27"/>
-      <c r="CX4" s="27"/>
-      <c r="CY4" s="27"/>
-      <c r="CZ4" s="27"/>
-      <c r="DA4" s="27"/>
-      <c r="DB4" s="27"/>
-      <c r="DC4" s="27"/>
-      <c r="DD4" s="27"/>
-      <c r="DE4" s="27"/>
-      <c r="DF4" s="27">
+      <c r="CU4" s="30"/>
+      <c r="CV4" s="30"/>
+      <c r="CW4" s="30"/>
+      <c r="CX4" s="30"/>
+      <c r="CY4" s="30"/>
+      <c r="CZ4" s="30"/>
+      <c r="DA4" s="30"/>
+      <c r="DB4" s="30"/>
+      <c r="DC4" s="30"/>
+      <c r="DD4" s="30"/>
+      <c r="DE4" s="30"/>
+      <c r="DF4" s="30">
         <v>2012</v>
       </c>
-      <c r="DG4" s="27"/>
-      <c r="DH4" s="27"/>
-      <c r="DI4" s="27"/>
-      <c r="DJ4" s="27"/>
-      <c r="DK4" s="27"/>
-      <c r="DL4" s="27"/>
-      <c r="DM4" s="27"/>
-      <c r="DN4" s="27"/>
-      <c r="DO4" s="27"/>
-      <c r="DP4" s="27"/>
-      <c r="DQ4" s="27"/>
-      <c r="DR4" s="27">
+      <c r="DG4" s="30"/>
+      <c r="DH4" s="30"/>
+      <c r="DI4" s="30"/>
+      <c r="DJ4" s="30"/>
+      <c r="DK4" s="30"/>
+      <c r="DL4" s="30"/>
+      <c r="DM4" s="30"/>
+      <c r="DN4" s="30"/>
+      <c r="DO4" s="30"/>
+      <c r="DP4" s="30"/>
+      <c r="DQ4" s="30"/>
+      <c r="DR4" s="30">
         <v>2013</v>
       </c>
-      <c r="DS4" s="27"/>
-      <c r="DT4" s="27"/>
-      <c r="DU4" s="27"/>
-      <c r="DV4" s="27"/>
-      <c r="DW4" s="27"/>
-      <c r="DX4" s="27"/>
-      <c r="DY4" s="27"/>
-      <c r="DZ4" s="27"/>
-      <c r="EA4" s="27"/>
-      <c r="EB4" s="27"/>
-      <c r="EC4" s="27"/>
-      <c r="ED4" s="27">
+      <c r="DS4" s="30"/>
+      <c r="DT4" s="30"/>
+      <c r="DU4" s="30"/>
+      <c r="DV4" s="30"/>
+      <c r="DW4" s="30"/>
+      <c r="DX4" s="30"/>
+      <c r="DY4" s="30"/>
+      <c r="DZ4" s="30"/>
+      <c r="EA4" s="30"/>
+      <c r="EB4" s="30"/>
+      <c r="EC4" s="30"/>
+      <c r="ED4" s="30">
         <v>2014</v>
       </c>
-      <c r="EE4" s="27"/>
-      <c r="EF4" s="27"/>
-      <c r="EG4" s="27"/>
-      <c r="EH4" s="27"/>
-      <c r="EI4" s="27"/>
-      <c r="EJ4" s="27"/>
-      <c r="EK4" s="27"/>
-      <c r="EL4" s="27"/>
-      <c r="EM4" s="27"/>
-      <c r="EN4" s="27"/>
-      <c r="EO4" s="27"/>
-      <c r="EP4" s="27">
+      <c r="EE4" s="30"/>
+      <c r="EF4" s="30"/>
+      <c r="EG4" s="30"/>
+      <c r="EH4" s="30"/>
+      <c r="EI4" s="30"/>
+      <c r="EJ4" s="30"/>
+      <c r="EK4" s="30"/>
+      <c r="EL4" s="30"/>
+      <c r="EM4" s="30"/>
+      <c r="EN4" s="30"/>
+      <c r="EO4" s="30"/>
+      <c r="EP4" s="30">
         <v>2015</v>
       </c>
-      <c r="EQ4" s="27"/>
-      <c r="ER4" s="27"/>
-      <c r="ES4" s="27"/>
-      <c r="ET4" s="27"/>
-      <c r="EU4" s="27"/>
-      <c r="EV4" s="27"/>
-      <c r="EW4" s="27"/>
-      <c r="EX4" s="27"/>
-      <c r="EY4" s="27"/>
-      <c r="EZ4" s="27"/>
-      <c r="FA4" s="27"/>
-      <c r="FB4" s="27">
+      <c r="EQ4" s="30"/>
+      <c r="ER4" s="30"/>
+      <c r="ES4" s="30"/>
+      <c r="ET4" s="30"/>
+      <c r="EU4" s="30"/>
+      <c r="EV4" s="30"/>
+      <c r="EW4" s="30"/>
+      <c r="EX4" s="30"/>
+      <c r="EY4" s="30"/>
+      <c r="EZ4" s="30"/>
+      <c r="FA4" s="30"/>
+      <c r="FB4" s="30">
         <v>2016</v>
       </c>
-      <c r="FC4" s="27"/>
-      <c r="FD4" s="27"/>
-      <c r="FE4" s="27"/>
-      <c r="FF4" s="27"/>
-      <c r="FG4" s="27"/>
-      <c r="FH4" s="27"/>
-      <c r="FI4" s="27"/>
-      <c r="FJ4" s="27"/>
-      <c r="FK4" s="27"/>
-      <c r="FL4" s="27"/>
-      <c r="FM4" s="27"/>
-      <c r="FN4" s="27">
+      <c r="FC4" s="30"/>
+      <c r="FD4" s="30"/>
+      <c r="FE4" s="30"/>
+      <c r="FF4" s="30"/>
+      <c r="FG4" s="30"/>
+      <c r="FH4" s="30"/>
+      <c r="FI4" s="30"/>
+      <c r="FJ4" s="30"/>
+      <c r="FK4" s="30"/>
+      <c r="FL4" s="30"/>
+      <c r="FM4" s="30"/>
+      <c r="FN4" s="30">
         <v>2017</v>
       </c>
-      <c r="FO4" s="27"/>
-      <c r="FP4" s="27"/>
-      <c r="FQ4" s="27"/>
-      <c r="FR4" s="27"/>
-      <c r="FS4" s="27"/>
-      <c r="FT4" s="27"/>
-      <c r="FU4" s="27"/>
-      <c r="FV4" s="27"/>
-      <c r="FW4" s="27"/>
-      <c r="FX4" s="27"/>
-      <c r="FY4" s="27"/>
-      <c r="FZ4" s="27">
+      <c r="FO4" s="30"/>
+      <c r="FP4" s="30"/>
+      <c r="FQ4" s="30"/>
+      <c r="FR4" s="30"/>
+      <c r="FS4" s="30"/>
+      <c r="FT4" s="30"/>
+      <c r="FU4" s="30"/>
+      <c r="FV4" s="30"/>
+      <c r="FW4" s="30"/>
+      <c r="FX4" s="30"/>
+      <c r="FY4" s="30"/>
+      <c r="FZ4" s="30">
         <v>2018</v>
       </c>
-      <c r="GA4" s="27"/>
-      <c r="GB4" s="27"/>
-      <c r="GC4" s="27"/>
-      <c r="GD4" s="27"/>
-      <c r="GE4" s="27"/>
-      <c r="GF4" s="27"/>
-      <c r="GG4" s="27"/>
-      <c r="GH4" s="27"/>
-      <c r="GI4" s="27"/>
-      <c r="GJ4" s="27"/>
-      <c r="GK4" s="27"/>
-      <c r="GL4" s="27">
+      <c r="GA4" s="30"/>
+      <c r="GB4" s="30"/>
+      <c r="GC4" s="30"/>
+      <c r="GD4" s="30"/>
+      <c r="GE4" s="30"/>
+      <c r="GF4" s="30"/>
+      <c r="GG4" s="30"/>
+      <c r="GH4" s="30"/>
+      <c r="GI4" s="30"/>
+      <c r="GJ4" s="30"/>
+      <c r="GK4" s="30"/>
+      <c r="GL4" s="30">
         <v>2019</v>
       </c>
-      <c r="GM4" s="27"/>
-      <c r="GN4" s="27"/>
-      <c r="GO4" s="27"/>
-      <c r="GP4" s="27"/>
-      <c r="GQ4" s="27"/>
-      <c r="GR4" s="27"/>
-      <c r="GS4" s="27"/>
-      <c r="GT4" s="27"/>
-      <c r="GU4" s="27"/>
-      <c r="GV4" s="27"/>
-      <c r="GW4" s="27"/>
-      <c r="GX4" s="27">
+      <c r="GM4" s="30"/>
+      <c r="GN4" s="30"/>
+      <c r="GO4" s="30"/>
+      <c r="GP4" s="30"/>
+      <c r="GQ4" s="30"/>
+      <c r="GR4" s="30"/>
+      <c r="GS4" s="30"/>
+      <c r="GT4" s="30"/>
+      <c r="GU4" s="30"/>
+      <c r="GV4" s="30"/>
+      <c r="GW4" s="30"/>
+      <c r="GX4" s="30">
         <v>2020</v>
       </c>
-      <c r="GY4" s="27"/>
-      <c r="GZ4" s="27"/>
-      <c r="HA4" s="27"/>
-      <c r="HB4" s="27"/>
-      <c r="HC4" s="27"/>
-      <c r="HD4" s="27"/>
-      <c r="HE4" s="27"/>
-      <c r="HF4" s="27"/>
-      <c r="HG4" s="27"/>
-      <c r="HH4" s="27"/>
-      <c r="HI4" s="27"/>
-      <c r="HJ4" s="27">
+      <c r="GY4" s="30"/>
+      <c r="GZ4" s="30"/>
+      <c r="HA4" s="30"/>
+      <c r="HB4" s="30"/>
+      <c r="HC4" s="30"/>
+      <c r="HD4" s="30"/>
+      <c r="HE4" s="30"/>
+      <c r="HF4" s="30"/>
+      <c r="HG4" s="30"/>
+      <c r="HH4" s="30"/>
+      <c r="HI4" s="30"/>
+      <c r="HJ4" s="30">
         <v>2021</v>
       </c>
-      <c r="HK4" s="27"/>
-      <c r="HL4" s="27"/>
-      <c r="HM4" s="27"/>
-      <c r="HN4" s="27"/>
-      <c r="HO4" s="27"/>
-      <c r="HP4" s="27"/>
-      <c r="HQ4" s="27"/>
-      <c r="HR4" s="27"/>
-      <c r="HS4" s="27"/>
-      <c r="HT4" s="27"/>
-      <c r="HU4" s="27"/>
-      <c r="HV4" s="27">
+      <c r="HK4" s="30"/>
+      <c r="HL4" s="30"/>
+      <c r="HM4" s="30"/>
+      <c r="HN4" s="30"/>
+      <c r="HO4" s="30"/>
+      <c r="HP4" s="30"/>
+      <c r="HQ4" s="30"/>
+      <c r="HR4" s="30"/>
+      <c r="HS4" s="30"/>
+      <c r="HT4" s="30"/>
+      <c r="HU4" s="30"/>
+      <c r="HV4" s="30">
         <v>2022</v>
       </c>
-      <c r="HW4" s="27"/>
-      <c r="HX4" s="27"/>
-      <c r="HY4" s="27"/>
-      <c r="HZ4" s="27"/>
-      <c r="IA4" s="27"/>
-      <c r="IB4" s="27"/>
-      <c r="IC4" s="27"/>
-      <c r="ID4" s="27"/>
-      <c r="IE4" s="27"/>
-      <c r="IF4" s="27"/>
-      <c r="IG4" s="27"/>
-      <c r="IH4" s="27">
+      <c r="HW4" s="30"/>
+      <c r="HX4" s="30"/>
+      <c r="HY4" s="30"/>
+      <c r="HZ4" s="30"/>
+      <c r="IA4" s="30"/>
+      <c r="IB4" s="30"/>
+      <c r="IC4" s="30"/>
+      <c r="ID4" s="30"/>
+      <c r="IE4" s="30"/>
+      <c r="IF4" s="30"/>
+      <c r="IG4" s="30"/>
+      <c r="IH4" s="30">
         <v>2023</v>
       </c>
-      <c r="II4" s="27"/>
-      <c r="IJ4" s="27"/>
-      <c r="IK4" s="27"/>
-      <c r="IL4" s="27"/>
-      <c r="IM4" s="27"/>
-      <c r="IN4" s="27"/>
-      <c r="IO4" s="27"/>
-      <c r="IP4" s="27"/>
-      <c r="IQ4" s="27"/>
-      <c r="IR4" s="27"/>
-      <c r="IS4" s="27"/>
-      <c r="IT4" s="27">
+      <c r="II4" s="30"/>
+      <c r="IJ4" s="30"/>
+      <c r="IK4" s="30"/>
+      <c r="IL4" s="30"/>
+      <c r="IM4" s="30"/>
+      <c r="IN4" s="30"/>
+      <c r="IO4" s="30"/>
+      <c r="IP4" s="30"/>
+      <c r="IQ4" s="30"/>
+      <c r="IR4" s="30"/>
+      <c r="IS4" s="30"/>
+      <c r="IT4" s="30">
         <v>2024</v>
       </c>
-      <c r="IU4" s="27"/>
-      <c r="IV4" s="27"/>
-      <c r="IW4" s="27"/>
-      <c r="IX4" s="27"/>
-      <c r="IY4" s="27"/>
-      <c r="IZ4" s="27"/>
-      <c r="JA4" s="27"/>
-      <c r="JB4" s="27"/>
-      <c r="JC4" s="27"/>
-      <c r="JD4" s="27"/>
-      <c r="JE4" s="27"/>
-      <c r="JF4" s="27">
+      <c r="IU4" s="30"/>
+      <c r="IV4" s="30"/>
+      <c r="IW4" s="30"/>
+      <c r="IX4" s="30"/>
+      <c r="IY4" s="30"/>
+      <c r="IZ4" s="30"/>
+      <c r="JA4" s="30"/>
+      <c r="JB4" s="30"/>
+      <c r="JC4" s="30"/>
+      <c r="JD4" s="30"/>
+      <c r="JE4" s="30"/>
+      <c r="JF4" s="30">
         <v>2025</v>
       </c>
-      <c r="JG4" s="27"/>
-      <c r="JH4" s="27"/>
-      <c r="JI4" s="27"/>
-      <c r="JJ4" s="27"/>
-      <c r="JK4" s="27"/>
-      <c r="JL4" s="27"/>
-      <c r="JM4" s="27"/>
-      <c r="JN4" s="27"/>
-      <c r="JO4" s="27"/>
-      <c r="JP4" s="27"/>
-      <c r="JQ4" s="28"/>
-      <c r="JR4" s="31">
+      <c r="JG4" s="30"/>
+      <c r="JH4" s="30"/>
+      <c r="JI4" s="30"/>
+      <c r="JJ4" s="30"/>
+      <c r="JK4" s="30"/>
+      <c r="JL4" s="30"/>
+      <c r="JM4" s="30"/>
+      <c r="JN4" s="30"/>
+      <c r="JO4" s="30"/>
+      <c r="JP4" s="30"/>
+      <c r="JQ4" s="32"/>
+      <c r="JR4" s="35">
         <v>2026</v>
       </c>
-      <c r="JS4" s="32"/>
-      <c r="JT4" s="33"/>
+      <c r="JS4" s="36"/>
+      <c r="JT4" s="36"/>
+      <c r="JU4" s="37"/>
     </row>
-    <row r="5" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2571,8 +2577,11 @@
       <c r="JT5" s="12" t="s">
         <v>5</v>
       </c>
+      <c r="JU5" s="12" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -3413,8 +3422,11 @@
       <c r="JT6" s="13">
         <v>-1460.1505925306999</v>
       </c>
+      <c r="JU6" s="13">
+        <v>-4410.93432889</v>
+      </c>
     </row>
-    <row r="7" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -4255,8 +4267,11 @@
       <c r="JT7" s="13">
         <v>-277.06233034326999</v>
       </c>
+      <c r="JU7" s="13">
+        <v>-1209.8447660776999</v>
+      </c>
     </row>
-    <row r="8" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -5097,8 +5112,11 @@
       <c r="JT8" s="13">
         <v>1183.08826218742</v>
       </c>
+      <c r="JU8" s="13">
+        <v>3201.0895628122898</v>
+      </c>
     </row>
-    <row r="9" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -5939,8 +5957,11 @@
       <c r="JT9" s="13">
         <v>-97.568136275667001</v>
       </c>
+      <c r="JU9" s="13">
+        <v>-1567.1094068355001</v>
+      </c>
     </row>
-    <row r="10" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
@@ -6781,8 +6802,11 @@
       <c r="JT10" s="14">
         <v>1041.11875823281</v>
       </c>
+      <c r="JU10" s="14">
+        <v>667.98608566245503</v>
+      </c>
     </row>
-    <row r="11" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
@@ -7623,8 +7647,11 @@
       <c r="JT11" s="14">
         <v>189.36118779202499</v>
       </c>
+      <c r="JU11" s="14">
+        <v>259.44713658627001</v>
+      </c>
     </row>
-    <row r="12" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
@@ -8465,8 +8492,11 @@
       <c r="JT12" s="14">
         <v>656.91137890075902</v>
       </c>
+      <c r="JU12" s="14">
+        <v>-87.706030654960003</v>
+      </c>
     </row>
-    <row r="13" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
@@ -9307,8 +9337,11 @@
       <c r="JT13" s="14">
         <v>194.84619154002601</v>
       </c>
+      <c r="JU13" s="14">
+        <v>496.24497973114501</v>
+      </c>
     </row>
-    <row r="14" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -10149,8 +10182,11 @@
       <c r="JT14" s="14">
         <v>1138.68689450848</v>
       </c>
+      <c r="JU14" s="14">
+        <v>2235.0954924979101</v>
+      </c>
     </row>
-    <row r="15" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -10991,8 +11027,11 @@
       <c r="JT15" s="14">
         <v>215.926776724597</v>
       </c>
+      <c r="JU15" s="14">
+        <v>223.850637124803</v>
+      </c>
     </row>
-    <row r="16" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
@@ -11833,8 +11872,11 @@
       <c r="JT16" s="14">
         <v>41.645399171630999</v>
       </c>
+      <c r="JU16" s="14">
+        <v>428.33030543049301</v>
+      </c>
     </row>
-    <row r="17" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
@@ -12675,8 +12717,11 @@
       <c r="JT17" s="14">
         <v>881.11471861224902</v>
       </c>
+      <c r="JU17" s="14">
+        <v>1582.9145499426099</v>
+      </c>
     </row>
-    <row r="18" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -13517,8 +13562,11 @@
       <c r="JT18" s="13">
         <v>-601.01338652072002</v>
       </c>
+      <c r="JU18" s="13">
+        <v>-1207.6794680788</v>
+      </c>
     </row>
-    <row r="19" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
@@ -14359,8 +14407,11 @@
       <c r="JT19" s="14">
         <v>503.12831309248202</v>
       </c>
+      <c r="JU19" s="14">
+        <v>960.678971485484</v>
+      </c>
     </row>
-    <row r="20" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>25</v>
       </c>
@@ -15201,8 +15252,11 @@
       <c r="JT20" s="14">
         <v>369.39918577771198</v>
       </c>
+      <c r="JU20" s="14">
+        <v>417.09790611430401</v>
+      </c>
     </row>
-    <row r="21" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>26</v>
       </c>
@@ -16043,8 +16097,11 @@
       <c r="JT21" s="14">
         <v>133.72912731477001</v>
       </c>
+      <c r="JU21" s="14">
+        <v>543.58106537117999</v>
+      </c>
     </row>
-    <row r="22" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>27</v>
       </c>
@@ -16885,8 +16942,11 @@
       <c r="JT22" s="14">
         <v>321.09039026306601</v>
       </c>
+      <c r="JU22" s="14">
+        <v>189.24332829689101</v>
+      </c>
     </row>
-    <row r="23" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
@@ -17727,8 +17787,11 @@
       <c r="JT23" s="14">
         <v>-187.36126294830001</v>
       </c>
+      <c r="JU23" s="14">
+        <v>354.33773707428901</v>
+      </c>
     </row>
-    <row r="24" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
@@ -18569,8 +18632,11 @@
       <c r="JT24" s="14">
         <v>1104.1416996132</v>
       </c>
+      <c r="JU24" s="14">
+        <v>2168.3584395643102</v>
+      </c>
     </row>
-    <row r="25" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
@@ -19411,8 +19477,11 @@
       <c r="JT25" s="14">
         <v>-154.67187124678</v>
       </c>
+      <c r="JU25" s="14">
+        <v>127.803024629465</v>
+      </c>
     </row>
-    <row r="26" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -20253,8 +20322,11 @@
       <c r="JT26" s="14">
         <v>1258.81357085999</v>
       </c>
+      <c r="JU26" s="14">
+        <v>2040.55541493484</v>
+      </c>
     </row>
-    <row r="27" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
@@ -21095,8 +21167,11 @@
       <c r="JT27" s="14">
         <v>637.39290799523303</v>
       </c>
+      <c r="JU27" s="14">
+        <v>2105.5442797692999</v>
+      </c>
     </row>
-    <row r="28" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -21937,8 +22012,11 @@
       <c r="JT28" s="14">
         <v>621.42066286475301</v>
       </c>
+      <c r="JU28" s="14">
+        <v>-64.988864834460998</v>
+      </c>
     </row>
-    <row r="29" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>30</v>
       </c>
@@ -22779,8 +22857,11 @@
       <c r="JT29" s="13">
         <v>-533.71735119058997</v>
       </c>
+      <c r="JU29" s="13">
+        <v>-148.15686460025</v>
+      </c>
     </row>
-    <row r="30" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -23621,8 +23702,11 @@
       <c r="JT30" s="13">
         <v>-697.99696892238001</v>
       </c>
+      <c r="JU30" s="13">
+        <v>-1756.5338596747999</v>
+      </c>
     </row>
-    <row r="31" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>19</v>
       </c>
@@ -24463,8 +24547,11 @@
       <c r="JT31" s="14">
         <v>461.69898939944699</v>
       </c>
+      <c r="JU31" s="14">
+        <v>-971.18770325715002</v>
+      </c>
     </row>
-    <row r="32" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>32</v>
       </c>
@@ -25305,8 +25392,11 @@
       <c r="JT32" s="14">
         <v>0</v>
       </c>
+      <c r="JU32" s="14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>33</v>
       </c>
@@ -26147,8 +26237,11 @@
       <c r="JT33" s="14">
         <v>647.18702029778694</v>
       </c>
+      <c r="JU33" s="14">
+        <v>-671.56428628590004</v>
+      </c>
     </row>
-    <row r="34" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
@@ -26989,8 +27082,11 @@
       <c r="JT34" s="14">
         <v>578.90425970682395</v>
       </c>
+      <c r="JU34" s="14">
+        <v>139.919355204916</v>
+      </c>
     </row>
-    <row r="35" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>35</v>
       </c>
@@ -27831,8 +27927,11 @@
       <c r="JT35" s="14">
         <v>-760.87042737657998</v>
       </c>
+      <c r="JU35" s="14">
+        <v>-436.55846836137999</v>
+      </c>
     </row>
-    <row r="36" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>36</v>
       </c>
@@ -28673,8 +28772,11 @@
       <c r="JT36" s="14">
         <v>-3.5218632285884</v>
       </c>
+      <c r="JU36" s="14">
+        <v>-2.9843038147938001</v>
+      </c>
     </row>
-    <row r="37" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>23</v>
       </c>
@@ -29515,8 +29617,11 @@
       <c r="JT37" s="14">
         <v>1159.6959583218299</v>
       </c>
+      <c r="JU37" s="14">
+        <v>785.346156417673</v>
+      </c>
     </row>
-    <row r="38" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>33</v>
       </c>
@@ -30357,8 +30462,11 @@
       <c r="JT38" s="14">
         <v>190.207973260139</v>
       </c>
+      <c r="JU38" s="14">
+        <v>432.722011012834</v>
+      </c>
     </row>
-    <row r="39" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>34</v>
       </c>
@@ -31199,8 +31307,11 @@
       <c r="JT39" s="14">
         <v>928.83028183550596</v>
       </c>
+      <c r="JU39" s="14">
+        <v>253.444768609097</v>
+      </c>
     </row>
-    <row r="40" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>35</v>
       </c>
@@ -32041,8 +32152,11 @@
       <c r="JT40" s="14">
         <v>32.827728776506</v>
       </c>
+      <c r="JU40" s="14">
+        <v>91.483759025203298</v>
+      </c>
     </row>
-    <row r="41" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>37</v>
       </c>
@@ -32883,8 +32997,11 @@
       <c r="JT41" s="14">
         <v>3.5743999999999999E-4</v>
       </c>
+      <c r="JU41" s="14">
+        <v>4.5069000000000001E-4</v>
+      </c>
     </row>
-    <row r="42" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>38</v>
       </c>
@@ -33725,8 +33842,11 @@
       <c r="JT42" s="14">
         <v>7.8296170096769799</v>
       </c>
+      <c r="JU42" s="14">
+        <v>7.6951670805388801</v>
+      </c>
     </row>
-    <row r="43" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>39</v>
       </c>
@@ -34567,292 +34687,296 @@
       <c r="JT43" s="15">
         <v>470.14525037866002</v>
       </c>
+      <c r="JU43" s="15">
+        <v>268.54527029939601</v>
+      </c>
     </row>
-    <row r="44" spans="1:280" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29" t="s">
+    <row r="44" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="30"/>
-      <c r="S44" s="30"/>
-      <c r="T44" s="30"/>
-      <c r="U44" s="30"/>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
-      <c r="X44" s="30"/>
-      <c r="Y44" s="30"/>
-      <c r="Z44" s="30"/>
-      <c r="AA44" s="30"/>
-      <c r="AB44" s="30"/>
-      <c r="AC44" s="30"/>
-      <c r="AD44" s="30"/>
-      <c r="AE44" s="30"/>
-      <c r="AF44" s="30"/>
-      <c r="AG44" s="30"/>
-      <c r="AH44" s="30"/>
-      <c r="AI44" s="30"/>
-      <c r="AJ44" s="30"/>
-      <c r="AK44" s="30"/>
-      <c r="AL44" s="30"/>
-      <c r="AM44" s="30"/>
-      <c r="AN44" s="30"/>
-      <c r="AO44" s="30"/>
-      <c r="AP44" s="30"/>
-      <c r="AQ44" s="30"/>
-      <c r="AR44" s="30"/>
-      <c r="AS44" s="30"/>
-      <c r="AT44" s="30"/>
-      <c r="AU44" s="30"/>
-      <c r="AV44" s="30"/>
-      <c r="AW44" s="30"/>
-      <c r="AX44" s="30"/>
-      <c r="AY44" s="30"/>
-      <c r="AZ44" s="30"/>
-      <c r="BA44" s="30"/>
-      <c r="BB44" s="30"/>
-      <c r="BC44" s="30"/>
-      <c r="BD44" s="30"/>
-      <c r="BE44" s="30"/>
-      <c r="BF44" s="30"/>
-      <c r="BG44" s="30"/>
-      <c r="BH44" s="30"/>
-      <c r="BI44" s="30"/>
-      <c r="BJ44" s="30"/>
-      <c r="BK44" s="30"/>
-      <c r="BL44" s="30"/>
-      <c r="BM44" s="30"/>
-      <c r="BN44" s="30"/>
-      <c r="BO44" s="30"/>
-      <c r="BP44" s="30"/>
-      <c r="BQ44" s="30"/>
-      <c r="BR44" s="30"/>
-      <c r="BS44" s="30"/>
-      <c r="BT44" s="30"/>
-      <c r="BU44" s="30"/>
-      <c r="BV44" s="30"/>
-      <c r="BW44" s="30"/>
-      <c r="BX44" s="30"/>
-      <c r="BY44" s="30"/>
-      <c r="BZ44" s="30"/>
-      <c r="CA44" s="30"/>
-      <c r="CB44" s="30"/>
-      <c r="CC44" s="30"/>
-      <c r="CD44" s="30"/>
-      <c r="CE44" s="30"/>
-      <c r="CF44" s="30"/>
-      <c r="CG44" s="30"/>
-      <c r="CH44" s="30"/>
-      <c r="CI44" s="30"/>
-      <c r="CJ44" s="30"/>
-      <c r="CK44" s="30"/>
-      <c r="CL44" s="30"/>
-      <c r="CM44" s="30"/>
-      <c r="CN44" s="30"/>
-      <c r="CO44" s="30"/>
-      <c r="CP44" s="30"/>
-      <c r="CQ44" s="30"/>
-      <c r="CR44" s="30"/>
-      <c r="CS44" s="30"/>
-      <c r="CT44" s="30"/>
-      <c r="CU44" s="30"/>
-      <c r="CV44" s="30"/>
-      <c r="CW44" s="30"/>
-      <c r="CX44" s="30"/>
-      <c r="CY44" s="30"/>
-      <c r="CZ44" s="30"/>
-      <c r="DA44" s="30"/>
-      <c r="DB44" s="30"/>
-      <c r="DC44" s="30"/>
-      <c r="DD44" s="30"/>
-      <c r="DE44" s="30"/>
-      <c r="DF44" s="30"/>
-      <c r="DG44" s="30"/>
-      <c r="DH44" s="30"/>
-      <c r="DI44" s="30"/>
-      <c r="DJ44" s="30"/>
-      <c r="DK44" s="30"/>
-      <c r="DL44" s="30"/>
-      <c r="DM44" s="30"/>
-      <c r="DN44" s="30"/>
-      <c r="DO44" s="30"/>
-      <c r="DP44" s="30"/>
-      <c r="DQ44" s="30"/>
-      <c r="DR44" s="30"/>
-      <c r="DS44" s="30"/>
-      <c r="DT44" s="30"/>
-      <c r="DU44" s="30"/>
-      <c r="DV44" s="30"/>
-      <c r="DW44" s="30"/>
-      <c r="DX44" s="30"/>
-      <c r="DY44" s="30"/>
-      <c r="DZ44" s="30"/>
-      <c r="EA44" s="30"/>
-      <c r="EB44" s="30"/>
-      <c r="EC44" s="30"/>
-      <c r="ED44" s="30"/>
-      <c r="EE44" s="30"/>
-      <c r="EF44" s="30"/>
-      <c r="EG44" s="30"/>
-      <c r="EH44" s="30"/>
-      <c r="EI44" s="30"/>
-      <c r="EJ44" s="30"/>
-      <c r="EK44" s="30"/>
-      <c r="EL44" s="30"/>
-      <c r="EM44" s="30"/>
-      <c r="EN44" s="30"/>
-      <c r="EO44" s="30"/>
-      <c r="EP44" s="30"/>
-      <c r="EQ44" s="30"/>
-      <c r="ER44" s="30"/>
-      <c r="ES44" s="30"/>
-      <c r="ET44" s="30"/>
-      <c r="EU44" s="30"/>
-      <c r="EV44" s="30"/>
-      <c r="EW44" s="30"/>
-      <c r="EX44" s="30"/>
-      <c r="EY44" s="30"/>
-      <c r="EZ44" s="30"/>
-      <c r="FA44" s="30"/>
-      <c r="FB44" s="30"/>
-      <c r="FC44" s="30"/>
-      <c r="FD44" s="30"/>
-      <c r="FE44" s="30"/>
-      <c r="FF44" s="30"/>
-      <c r="FG44" s="30"/>
-      <c r="FH44" s="30"/>
-      <c r="FI44" s="30"/>
-      <c r="FJ44" s="30"/>
-      <c r="FK44" s="30"/>
-      <c r="FL44" s="30"/>
-      <c r="FM44" s="30"/>
-      <c r="FN44" s="30"/>
-      <c r="FO44" s="30"/>
-      <c r="FP44" s="30"/>
-      <c r="FQ44" s="30"/>
-      <c r="FR44" s="30"/>
-      <c r="FS44" s="30"/>
-      <c r="FT44" s="30"/>
-      <c r="FU44" s="30"/>
-      <c r="FV44" s="30"/>
-      <c r="FW44" s="30"/>
-      <c r="FX44" s="30"/>
-      <c r="FY44" s="30"/>
-      <c r="FZ44" s="30"/>
-      <c r="GA44" s="30"/>
-      <c r="GB44" s="30"/>
-      <c r="GC44" s="30"/>
-      <c r="GD44" s="30"/>
-      <c r="GE44" s="30"/>
-      <c r="GF44" s="30"/>
-      <c r="GG44" s="30"/>
-      <c r="GH44" s="30"/>
-      <c r="GI44" s="30"/>
-      <c r="GJ44" s="30"/>
-      <c r="GK44" s="30"/>
-      <c r="GL44" s="30"/>
-      <c r="GM44" s="30"/>
-      <c r="GN44" s="30"/>
-      <c r="GO44" s="30"/>
-      <c r="GP44" s="30"/>
-      <c r="GQ44" s="30"/>
-      <c r="GR44" s="30"/>
-      <c r="GS44" s="30"/>
-      <c r="GT44" s="30"/>
-      <c r="GU44" s="30"/>
-      <c r="GV44" s="30"/>
-      <c r="GW44" s="30"/>
-      <c r="GX44" s="30"/>
-      <c r="GY44" s="30"/>
-      <c r="GZ44" s="30"/>
-      <c r="HA44" s="30"/>
-      <c r="HB44" s="30"/>
-      <c r="HC44" s="30"/>
-      <c r="HD44" s="30"/>
-      <c r="HE44" s="30"/>
-      <c r="HF44" s="30"/>
-      <c r="HG44" s="30"/>
-      <c r="HH44" s="30"/>
-      <c r="HI44" s="30"/>
-      <c r="HJ44" s="30"/>
-      <c r="HK44" s="30"/>
-      <c r="HL44" s="30"/>
-      <c r="HM44" s="30"/>
-      <c r="HN44" s="30"/>
-      <c r="HO44" s="30"/>
-      <c r="HP44" s="30"/>
-      <c r="HQ44" s="30"/>
-      <c r="HR44" s="30"/>
-      <c r="HS44" s="30"/>
-      <c r="HT44" s="30"/>
-      <c r="HU44" s="30"/>
-      <c r="HV44" s="30"/>
-      <c r="HW44" s="30"/>
-      <c r="HX44" s="30"/>
-      <c r="HY44" s="30"/>
-      <c r="HZ44" s="30"/>
-      <c r="IA44" s="30"/>
-      <c r="IB44" s="30"/>
-      <c r="IC44" s="30"/>
-      <c r="ID44" s="30"/>
-      <c r="IE44" s="30"/>
-      <c r="IF44" s="30"/>
-      <c r="IG44" s="30"/>
-      <c r="IH44" s="30"/>
-      <c r="II44" s="30"/>
-      <c r="IJ44" s="30"/>
-      <c r="IK44" s="30"/>
-      <c r="IL44" s="30"/>
-      <c r="IM44" s="30"/>
-      <c r="IN44" s="30"/>
-      <c r="IO44" s="30"/>
-      <c r="IP44" s="30"/>
-      <c r="IQ44" s="30"/>
-      <c r="IR44" s="30"/>
-      <c r="IS44" s="30"/>
-      <c r="IT44" s="30"/>
-      <c r="IU44" s="30"/>
-      <c r="IV44" s="30"/>
-      <c r="IW44" s="30"/>
-      <c r="IX44" s="30"/>
-      <c r="IY44" s="30"/>
-      <c r="IZ44" s="30"/>
-      <c r="JA44" s="30"/>
-      <c r="JB44" s="30"/>
-      <c r="JC44" s="30"/>
-      <c r="JD44" s="30"/>
-      <c r="JE44" s="30"/>
-      <c r="JF44" s="30"/>
-      <c r="JG44" s="30"/>
-      <c r="JH44" s="30"/>
-      <c r="JI44" s="30"/>
-      <c r="JJ44" s="30"/>
-      <c r="JK44" s="30"/>
-      <c r="JL44" s="30"/>
-      <c r="JM44" s="30"/>
-      <c r="JN44" s="30"/>
-      <c r="JO44" s="30"/>
-      <c r="JP44" s="30"/>
-      <c r="JQ44" s="30"/>
-      <c r="JR44" s="30"/>
-      <c r="JS44" s="30"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="34"/>
+      <c r="N44" s="34"/>
+      <c r="O44" s="34"/>
+      <c r="P44" s="34"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="34"/>
+      <c r="S44" s="34"/>
+      <c r="T44" s="34"/>
+      <c r="U44" s="34"/>
+      <c r="V44" s="34"/>
+      <c r="W44" s="34"/>
+      <c r="X44" s="34"/>
+      <c r="Y44" s="34"/>
+      <c r="Z44" s="34"/>
+      <c r="AA44" s="34"/>
+      <c r="AB44" s="34"/>
+      <c r="AC44" s="34"/>
+      <c r="AD44" s="34"/>
+      <c r="AE44" s="34"/>
+      <c r="AF44" s="34"/>
+      <c r="AG44" s="34"/>
+      <c r="AH44" s="34"/>
+      <c r="AI44" s="34"/>
+      <c r="AJ44" s="34"/>
+      <c r="AK44" s="34"/>
+      <c r="AL44" s="34"/>
+      <c r="AM44" s="34"/>
+      <c r="AN44" s="34"/>
+      <c r="AO44" s="34"/>
+      <c r="AP44" s="34"/>
+      <c r="AQ44" s="34"/>
+      <c r="AR44" s="34"/>
+      <c r="AS44" s="34"/>
+      <c r="AT44" s="34"/>
+      <c r="AU44" s="34"/>
+      <c r="AV44" s="34"/>
+      <c r="AW44" s="34"/>
+      <c r="AX44" s="34"/>
+      <c r="AY44" s="34"/>
+      <c r="AZ44" s="34"/>
+      <c r="BA44" s="34"/>
+      <c r="BB44" s="34"/>
+      <c r="BC44" s="34"/>
+      <c r="BD44" s="34"/>
+      <c r="BE44" s="34"/>
+      <c r="BF44" s="34"/>
+      <c r="BG44" s="34"/>
+      <c r="BH44" s="34"/>
+      <c r="BI44" s="34"/>
+      <c r="BJ44" s="34"/>
+      <c r="BK44" s="34"/>
+      <c r="BL44" s="34"/>
+      <c r="BM44" s="34"/>
+      <c r="BN44" s="34"/>
+      <c r="BO44" s="34"/>
+      <c r="BP44" s="34"/>
+      <c r="BQ44" s="34"/>
+      <c r="BR44" s="34"/>
+      <c r="BS44" s="34"/>
+      <c r="BT44" s="34"/>
+      <c r="BU44" s="34"/>
+      <c r="BV44" s="34"/>
+      <c r="BW44" s="34"/>
+      <c r="BX44" s="34"/>
+      <c r="BY44" s="34"/>
+      <c r="BZ44" s="34"/>
+      <c r="CA44" s="34"/>
+      <c r="CB44" s="34"/>
+      <c r="CC44" s="34"/>
+      <c r="CD44" s="34"/>
+      <c r="CE44" s="34"/>
+      <c r="CF44" s="34"/>
+      <c r="CG44" s="34"/>
+      <c r="CH44" s="34"/>
+      <c r="CI44" s="34"/>
+      <c r="CJ44" s="34"/>
+      <c r="CK44" s="34"/>
+      <c r="CL44" s="34"/>
+      <c r="CM44" s="34"/>
+      <c r="CN44" s="34"/>
+      <c r="CO44" s="34"/>
+      <c r="CP44" s="34"/>
+      <c r="CQ44" s="34"/>
+      <c r="CR44" s="34"/>
+      <c r="CS44" s="34"/>
+      <c r="CT44" s="34"/>
+      <c r="CU44" s="34"/>
+      <c r="CV44" s="34"/>
+      <c r="CW44" s="34"/>
+      <c r="CX44" s="34"/>
+      <c r="CY44" s="34"/>
+      <c r="CZ44" s="34"/>
+      <c r="DA44" s="34"/>
+      <c r="DB44" s="34"/>
+      <c r="DC44" s="34"/>
+      <c r="DD44" s="34"/>
+      <c r="DE44" s="34"/>
+      <c r="DF44" s="34"/>
+      <c r="DG44" s="34"/>
+      <c r="DH44" s="34"/>
+      <c r="DI44" s="34"/>
+      <c r="DJ44" s="34"/>
+      <c r="DK44" s="34"/>
+      <c r="DL44" s="34"/>
+      <c r="DM44" s="34"/>
+      <c r="DN44" s="34"/>
+      <c r="DO44" s="34"/>
+      <c r="DP44" s="34"/>
+      <c r="DQ44" s="34"/>
+      <c r="DR44" s="34"/>
+      <c r="DS44" s="34"/>
+      <c r="DT44" s="34"/>
+      <c r="DU44" s="34"/>
+      <c r="DV44" s="34"/>
+      <c r="DW44" s="34"/>
+      <c r="DX44" s="34"/>
+      <c r="DY44" s="34"/>
+      <c r="DZ44" s="34"/>
+      <c r="EA44" s="34"/>
+      <c r="EB44" s="34"/>
+      <c r="EC44" s="34"/>
+      <c r="ED44" s="34"/>
+      <c r="EE44" s="34"/>
+      <c r="EF44" s="34"/>
+      <c r="EG44" s="34"/>
+      <c r="EH44" s="34"/>
+      <c r="EI44" s="34"/>
+      <c r="EJ44" s="34"/>
+      <c r="EK44" s="34"/>
+      <c r="EL44" s="34"/>
+      <c r="EM44" s="34"/>
+      <c r="EN44" s="34"/>
+      <c r="EO44" s="34"/>
+      <c r="EP44" s="34"/>
+      <c r="EQ44" s="34"/>
+      <c r="ER44" s="34"/>
+      <c r="ES44" s="34"/>
+      <c r="ET44" s="34"/>
+      <c r="EU44" s="34"/>
+      <c r="EV44" s="34"/>
+      <c r="EW44" s="34"/>
+      <c r="EX44" s="34"/>
+      <c r="EY44" s="34"/>
+      <c r="EZ44" s="34"/>
+      <c r="FA44" s="34"/>
+      <c r="FB44" s="34"/>
+      <c r="FC44" s="34"/>
+      <c r="FD44" s="34"/>
+      <c r="FE44" s="34"/>
+      <c r="FF44" s="34"/>
+      <c r="FG44" s="34"/>
+      <c r="FH44" s="34"/>
+      <c r="FI44" s="34"/>
+      <c r="FJ44" s="34"/>
+      <c r="FK44" s="34"/>
+      <c r="FL44" s="34"/>
+      <c r="FM44" s="34"/>
+      <c r="FN44" s="34"/>
+      <c r="FO44" s="34"/>
+      <c r="FP44" s="34"/>
+      <c r="FQ44" s="34"/>
+      <c r="FR44" s="34"/>
+      <c r="FS44" s="34"/>
+      <c r="FT44" s="34"/>
+      <c r="FU44" s="34"/>
+      <c r="FV44" s="34"/>
+      <c r="FW44" s="34"/>
+      <c r="FX44" s="34"/>
+      <c r="FY44" s="34"/>
+      <c r="FZ44" s="34"/>
+      <c r="GA44" s="34"/>
+      <c r="GB44" s="34"/>
+      <c r="GC44" s="34"/>
+      <c r="GD44" s="34"/>
+      <c r="GE44" s="34"/>
+      <c r="GF44" s="34"/>
+      <c r="GG44" s="34"/>
+      <c r="GH44" s="34"/>
+      <c r="GI44" s="34"/>
+      <c r="GJ44" s="34"/>
+      <c r="GK44" s="34"/>
+      <c r="GL44" s="34"/>
+      <c r="GM44" s="34"/>
+      <c r="GN44" s="34"/>
+      <c r="GO44" s="34"/>
+      <c r="GP44" s="34"/>
+      <c r="GQ44" s="34"/>
+      <c r="GR44" s="34"/>
+      <c r="GS44" s="34"/>
+      <c r="GT44" s="34"/>
+      <c r="GU44" s="34"/>
+      <c r="GV44" s="34"/>
+      <c r="GW44" s="34"/>
+      <c r="GX44" s="34"/>
+      <c r="GY44" s="34"/>
+      <c r="GZ44" s="34"/>
+      <c r="HA44" s="34"/>
+      <c r="HB44" s="34"/>
+      <c r="HC44" s="34"/>
+      <c r="HD44" s="34"/>
+      <c r="HE44" s="34"/>
+      <c r="HF44" s="34"/>
+      <c r="HG44" s="34"/>
+      <c r="HH44" s="34"/>
+      <c r="HI44" s="34"/>
+      <c r="HJ44" s="34"/>
+      <c r="HK44" s="34"/>
+      <c r="HL44" s="34"/>
+      <c r="HM44" s="34"/>
+      <c r="HN44" s="34"/>
+      <c r="HO44" s="34"/>
+      <c r="HP44" s="34"/>
+      <c r="HQ44" s="34"/>
+      <c r="HR44" s="34"/>
+      <c r="HS44" s="34"/>
+      <c r="HT44" s="34"/>
+      <c r="HU44" s="34"/>
+      <c r="HV44" s="34"/>
+      <c r="HW44" s="34"/>
+      <c r="HX44" s="34"/>
+      <c r="HY44" s="34"/>
+      <c r="HZ44" s="34"/>
+      <c r="IA44" s="34"/>
+      <c r="IB44" s="34"/>
+      <c r="IC44" s="34"/>
+      <c r="ID44" s="34"/>
+      <c r="IE44" s="34"/>
+      <c r="IF44" s="34"/>
+      <c r="IG44" s="34"/>
+      <c r="IH44" s="34"/>
+      <c r="II44" s="34"/>
+      <c r="IJ44" s="34"/>
+      <c r="IK44" s="34"/>
+      <c r="IL44" s="34"/>
+      <c r="IM44" s="34"/>
+      <c r="IN44" s="34"/>
+      <c r="IO44" s="34"/>
+      <c r="IP44" s="34"/>
+      <c r="IQ44" s="34"/>
+      <c r="IR44" s="34"/>
+      <c r="IS44" s="34"/>
+      <c r="IT44" s="34"/>
+      <c r="IU44" s="34"/>
+      <c r="IV44" s="34"/>
+      <c r="IW44" s="34"/>
+      <c r="IX44" s="34"/>
+      <c r="IY44" s="34"/>
+      <c r="IZ44" s="34"/>
+      <c r="JA44" s="34"/>
+      <c r="JB44" s="34"/>
+      <c r="JC44" s="34"/>
+      <c r="JD44" s="34"/>
+      <c r="JE44" s="34"/>
+      <c r="JF44" s="34"/>
+      <c r="JG44" s="34"/>
+      <c r="JH44" s="34"/>
+      <c r="JI44" s="34"/>
+      <c r="JJ44" s="34"/>
+      <c r="JK44" s="34"/>
+      <c r="JL44" s="34"/>
+      <c r="JM44" s="34"/>
+      <c r="JN44" s="34"/>
+      <c r="JO44" s="34"/>
+      <c r="JP44" s="34"/>
+      <c r="JQ44" s="34"/>
+      <c r="JR44" s="34"/>
+      <c r="JS44" s="34"/>
       <c r="JT44" s="1"/>
+      <c r="JU44" s="26"/>
     </row>
-    <row r="45" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="21" t="s">
         <v>41</v>
       </c>
@@ -35693,8 +35817,11 @@
       <c r="JT45" s="16">
         <v>-1930.2958429094001</v>
       </c>
+      <c r="JU45" s="16">
+        <v>-4679.4795991893998</v>
+      </c>
     </row>
-    <row r="46" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="23" t="s">
         <v>42</v>
       </c>
@@ -36535,8 +36662,11 @@
       <c r="JT46" s="17">
         <v>1104.1416996132</v>
       </c>
+      <c r="JU46" s="17">
+        <v>2168.3584395643102</v>
+      </c>
     </row>
-    <row r="47" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="23" t="s">
         <v>26</v>
       </c>
@@ -37377,8 +37507,11 @@
       <c r="JT47" s="17">
         <v>1258.81357085999</v>
       </c>
+      <c r="JU47" s="17">
+        <v>2040.55541493484</v>
+      </c>
     </row>
-    <row r="48" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="23" t="s">
         <v>43</v>
       </c>
@@ -38219,8 +38352,11 @@
       <c r="JT48" s="17">
         <v>604.38102594616805</v>
       </c>
+      <c r="JU48" s="17">
+        <v>1529.6102030053501</v>
+      </c>
     </row>
-    <row r="49" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="23" t="s">
         <v>45</v>
       </c>
@@ -39061,8 +39197,11 @@
       <c r="JT49" s="17">
         <v>654.43254491381799</v>
       </c>
+      <c r="JU49" s="17">
+        <v>510.94521192949298</v>
+      </c>
     </row>
-    <row r="50" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="23" t="s">
         <v>25</v>
       </c>
@@ -39903,8 +40042,11 @@
       <c r="JT50" s="17">
         <v>-154.67187124678</v>
       </c>
+      <c r="JU50" s="17">
+        <v>127.803024629465</v>
+      </c>
     </row>
-    <row r="51" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="23" t="s">
         <v>46</v>
       </c>
@@ -40745,8 +40887,11 @@
       <c r="JT51" s="17">
         <v>-29.708108825277002</v>
       </c>
+      <c r="JU51" s="17">
+        <v>24.918333942348401</v>
+      </c>
     </row>
-    <row r="52" spans="1:280" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="24" t="s">
         <v>47</v>
       </c>
@@ -41587,293 +41732,309 @@
       <c r="JT52" s="18">
         <v>-124.96376242151</v>
       </c>
+      <c r="JU52" s="18">
+        <v>102.884690687117</v>
+      </c>
     </row>
-    <row r="54" spans="1:280" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="26" t="s">
+    <row r="54" spans="1:281" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
-      <c r="M54" s="26"/>
-      <c r="N54" s="26"/>
-      <c r="O54" s="26"/>
-      <c r="P54" s="26"/>
-      <c r="Q54" s="26"/>
-      <c r="R54" s="26"/>
-      <c r="S54" s="26"/>
-      <c r="T54" s="26"/>
-      <c r="U54" s="26"/>
-      <c r="V54" s="26"/>
-      <c r="W54" s="26"/>
-      <c r="X54" s="26"/>
-      <c r="Y54" s="26"/>
-      <c r="Z54" s="26"/>
-      <c r="AA54" s="26"/>
-      <c r="AB54" s="26"/>
-      <c r="AC54" s="26"/>
-      <c r="AD54" s="26"/>
-      <c r="AE54" s="26"/>
-      <c r="AF54" s="26"/>
-      <c r="AG54" s="26"/>
-      <c r="AH54" s="26"/>
-      <c r="AI54" s="26"/>
-      <c r="AJ54" s="26"/>
-      <c r="AK54" s="26"/>
-      <c r="AL54" s="26"/>
-      <c r="AM54" s="26"/>
-      <c r="AN54" s="26"/>
-      <c r="AO54" s="26"/>
-      <c r="AP54" s="26"/>
-      <c r="AQ54" s="26"/>
-      <c r="AR54" s="26"/>
-      <c r="AS54" s="26"/>
-      <c r="AT54" s="26"/>
-      <c r="AU54" s="26"/>
-      <c r="AV54" s="26"/>
-      <c r="AW54" s="26"/>
-      <c r="AX54" s="26"/>
-      <c r="AY54" s="26"/>
-      <c r="AZ54" s="26"/>
-      <c r="BA54" s="26"/>
-      <c r="BB54" s="26"/>
-      <c r="BC54" s="26"/>
-      <c r="BD54" s="26"/>
-      <c r="BE54" s="26"/>
-      <c r="BF54" s="26"/>
-      <c r="BG54" s="26"/>
-      <c r="BH54" s="26"/>
-      <c r="BI54" s="26"/>
-      <c r="BJ54" s="26"/>
-      <c r="BK54" s="26"/>
-      <c r="BL54" s="26"/>
-      <c r="BM54" s="26"/>
-      <c r="BN54" s="26"/>
-      <c r="BO54" s="26"/>
-      <c r="BP54" s="26"/>
-      <c r="BQ54" s="26"/>
-      <c r="BR54" s="26"/>
-      <c r="BS54" s="26"/>
-      <c r="BT54" s="26"/>
-      <c r="BU54" s="26"/>
-      <c r="BV54" s="26"/>
-      <c r="BW54" s="26"/>
-      <c r="BX54" s="26"/>
-      <c r="BY54" s="26"/>
-      <c r="BZ54" s="26"/>
-      <c r="CA54" s="26"/>
-      <c r="CB54" s="26"/>
-      <c r="CC54" s="26"/>
-      <c r="CD54" s="26"/>
-      <c r="CE54" s="26"/>
-      <c r="CF54" s="26"/>
-      <c r="CG54" s="26"/>
-      <c r="CH54" s="26"/>
-      <c r="CI54" s="26"/>
-      <c r="CJ54" s="26"/>
-      <c r="CK54" s="26"/>
-      <c r="CL54" s="26"/>
-      <c r="CM54" s="26"/>
-      <c r="CN54" s="26"/>
-      <c r="CO54" s="26"/>
-      <c r="CP54" s="26"/>
-      <c r="CQ54" s="26"/>
-      <c r="CR54" s="26"/>
-      <c r="CS54" s="26"/>
-      <c r="CT54" s="26"/>
-      <c r="CU54" s="26"/>
-      <c r="CV54" s="26"/>
-      <c r="CW54" s="26"/>
-      <c r="CX54" s="26"/>
-      <c r="CY54" s="26"/>
-      <c r="CZ54" s="26"/>
-      <c r="DA54" s="26"/>
-      <c r="DB54" s="26"/>
-      <c r="DC54" s="26"/>
-      <c r="DD54" s="26"/>
-      <c r="DE54" s="26"/>
-      <c r="DF54" s="26"/>
-      <c r="DG54" s="26"/>
-      <c r="DH54" s="26"/>
-      <c r="DI54" s="26"/>
-      <c r="DJ54" s="26"/>
-      <c r="DK54" s="26"/>
-      <c r="DL54" s="26"/>
-      <c r="DM54" s="26"/>
-      <c r="DN54" s="26"/>
-      <c r="DO54" s="26"/>
-      <c r="DP54" s="26"/>
-      <c r="DQ54" s="26"/>
-      <c r="DR54" s="26"/>
-      <c r="DS54" s="26"/>
-      <c r="DT54" s="26"/>
-      <c r="DU54" s="26"/>
-      <c r="DV54" s="26"/>
-      <c r="DW54" s="26"/>
-      <c r="DX54" s="26"/>
-      <c r="DY54" s="26"/>
-      <c r="DZ54" s="26"/>
-      <c r="EA54" s="26"/>
-      <c r="EB54" s="26"/>
-      <c r="EC54" s="26"/>
-      <c r="ED54" s="26"/>
-      <c r="EE54" s="26"/>
-      <c r="EF54" s="26"/>
-      <c r="EG54" s="26"/>
-      <c r="EH54" s="26"/>
-      <c r="EI54" s="26"/>
-      <c r="EJ54" s="26"/>
-      <c r="EK54" s="26"/>
-      <c r="EL54" s="26"/>
-      <c r="EM54" s="26"/>
-      <c r="EN54" s="26"/>
-      <c r="EO54" s="26"/>
-      <c r="EP54" s="26"/>
-      <c r="EQ54" s="26"/>
-      <c r="ER54" s="26"/>
-      <c r="ES54" s="26"/>
-      <c r="ET54" s="26"/>
-      <c r="EU54" s="26"/>
-      <c r="EV54" s="26"/>
-      <c r="EW54" s="26"/>
-      <c r="EX54" s="26"/>
-      <c r="EY54" s="26"/>
-      <c r="EZ54" s="26"/>
-      <c r="FA54" s="26"/>
-      <c r="FB54" s="26"/>
-      <c r="FC54" s="26"/>
-      <c r="FD54" s="26"/>
-      <c r="FE54" s="26"/>
-      <c r="FF54" s="26"/>
-      <c r="FG54" s="26"/>
-      <c r="FH54" s="26"/>
-      <c r="FI54" s="26"/>
-      <c r="FJ54" s="26"/>
-      <c r="FK54" s="26"/>
-      <c r="FL54" s="26"/>
-      <c r="FM54" s="26"/>
-      <c r="FN54" s="26"/>
-      <c r="FO54" s="26"/>
-      <c r="FP54" s="26"/>
-      <c r="FQ54" s="26"/>
-      <c r="FR54" s="26"/>
-      <c r="FS54" s="26"/>
-      <c r="FT54" s="26"/>
-      <c r="FU54" s="26"/>
-      <c r="FV54" s="26"/>
-      <c r="FW54" s="26"/>
-      <c r="FX54" s="26"/>
-      <c r="FY54" s="26"/>
-      <c r="FZ54" s="26"/>
-      <c r="GA54" s="26"/>
-      <c r="GB54" s="26"/>
-      <c r="GC54" s="26"/>
-      <c r="GD54" s="26"/>
-      <c r="GE54" s="26"/>
-      <c r="GF54" s="26"/>
-      <c r="GG54" s="26"/>
-      <c r="GH54" s="26"/>
-      <c r="GI54" s="26"/>
-      <c r="GJ54" s="26"/>
-      <c r="GK54" s="26"/>
-      <c r="GL54" s="26"/>
-      <c r="GM54" s="26"/>
-      <c r="GN54" s="26"/>
-      <c r="GO54" s="26"/>
-      <c r="GP54" s="26"/>
-      <c r="GQ54" s="26"/>
-      <c r="GR54" s="26"/>
-      <c r="GS54" s="26"/>
-      <c r="GT54" s="26"/>
-      <c r="GU54" s="26"/>
-      <c r="GV54" s="26"/>
-      <c r="GW54" s="26"/>
-      <c r="GX54" s="26"/>
-      <c r="GY54" s="26"/>
-      <c r="GZ54" s="26"/>
-      <c r="HA54" s="26"/>
-      <c r="HB54" s="26"/>
-      <c r="HC54" s="26"/>
-      <c r="HD54" s="26"/>
-      <c r="HE54" s="26"/>
-      <c r="HF54" s="26"/>
-      <c r="HG54" s="26"/>
-      <c r="HH54" s="26"/>
-      <c r="HI54" s="26"/>
-      <c r="HJ54" s="26"/>
-      <c r="HK54" s="26"/>
-      <c r="HL54" s="26"/>
-      <c r="HM54" s="26"/>
-      <c r="HN54" s="26"/>
-      <c r="HO54" s="26"/>
-      <c r="HP54" s="26"/>
-      <c r="HQ54" s="26"/>
-      <c r="HR54" s="26"/>
-      <c r="HS54" s="26"/>
-      <c r="HT54" s="26"/>
-      <c r="HU54" s="26"/>
-      <c r="HV54" s="26"/>
-      <c r="HW54" s="26"/>
-      <c r="HX54" s="26"/>
-      <c r="HY54" s="26"/>
-      <c r="HZ54" s="26"/>
-      <c r="IA54" s="26"/>
-      <c r="IB54" s="26"/>
-      <c r="IC54" s="26"/>
-      <c r="ID54" s="26"/>
-      <c r="IE54" s="26"/>
-      <c r="IF54" s="26"/>
-      <c r="IG54" s="26"/>
-      <c r="IH54" s="26"/>
-      <c r="II54" s="26"/>
-      <c r="IJ54" s="26"/>
-      <c r="IK54" s="26"/>
-      <c r="IL54" s="26"/>
-      <c r="IM54" s="26"/>
-      <c r="IN54" s="26"/>
-      <c r="IO54" s="26"/>
-      <c r="IP54" s="26"/>
-      <c r="IQ54" s="26"/>
-      <c r="IR54" s="26"/>
-      <c r="IS54" s="26"/>
-      <c r="IT54" s="26"/>
-      <c r="IU54" s="26"/>
-      <c r="IV54" s="26"/>
-      <c r="IW54" s="26"/>
-      <c r="IX54" s="26"/>
-      <c r="IY54" s="26"/>
-      <c r="IZ54" s="26"/>
-      <c r="JA54" s="26"/>
-      <c r="JB54" s="26"/>
-      <c r="JC54" s="26"/>
-      <c r="JD54" s="26"/>
-      <c r="JE54" s="26"/>
-      <c r="JF54" s="26"/>
-      <c r="JG54" s="26"/>
-      <c r="JH54" s="26"/>
-      <c r="JI54" s="26"/>
-      <c r="JJ54" s="26"/>
-      <c r="JK54" s="26"/>
-      <c r="JL54" s="26"/>
-      <c r="JM54" s="26"/>
-      <c r="JN54" s="26"/>
-      <c r="JO54" s="26"/>
-      <c r="JP54" s="26"/>
-      <c r="JQ54" s="26"/>
-      <c r="JR54" s="26"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="31"/>
+      <c r="R54" s="31"/>
+      <c r="S54" s="31"/>
+      <c r="T54" s="31"/>
+      <c r="U54" s="31"/>
+      <c r="V54" s="31"/>
+      <c r="W54" s="31"/>
+      <c r="X54" s="31"/>
+      <c r="Y54" s="31"/>
+      <c r="Z54" s="31"/>
+      <c r="AA54" s="31"/>
+      <c r="AB54" s="31"/>
+      <c r="AC54" s="31"/>
+      <c r="AD54" s="31"/>
+      <c r="AE54" s="31"/>
+      <c r="AF54" s="31"/>
+      <c r="AG54" s="31"/>
+      <c r="AH54" s="31"/>
+      <c r="AI54" s="31"/>
+      <c r="AJ54" s="31"/>
+      <c r="AK54" s="31"/>
+      <c r="AL54" s="31"/>
+      <c r="AM54" s="31"/>
+      <c r="AN54" s="31"/>
+      <c r="AO54" s="31"/>
+      <c r="AP54" s="31"/>
+      <c r="AQ54" s="31"/>
+      <c r="AR54" s="31"/>
+      <c r="AS54" s="31"/>
+      <c r="AT54" s="31"/>
+      <c r="AU54" s="31"/>
+      <c r="AV54" s="31"/>
+      <c r="AW54" s="31"/>
+      <c r="AX54" s="31"/>
+      <c r="AY54" s="31"/>
+      <c r="AZ54" s="31"/>
+      <c r="BA54" s="31"/>
+      <c r="BB54" s="31"/>
+      <c r="BC54" s="31"/>
+      <c r="BD54" s="31"/>
+      <c r="BE54" s="31"/>
+      <c r="BF54" s="31"/>
+      <c r="BG54" s="31"/>
+      <c r="BH54" s="31"/>
+      <c r="BI54" s="31"/>
+      <c r="BJ54" s="31"/>
+      <c r="BK54" s="31"/>
+      <c r="BL54" s="31"/>
+      <c r="BM54" s="31"/>
+      <c r="BN54" s="31"/>
+      <c r="BO54" s="31"/>
+      <c r="BP54" s="31"/>
+      <c r="BQ54" s="31"/>
+      <c r="BR54" s="31"/>
+      <c r="BS54" s="31"/>
+      <c r="BT54" s="31"/>
+      <c r="BU54" s="31"/>
+      <c r="BV54" s="31"/>
+      <c r="BW54" s="31"/>
+      <c r="BX54" s="31"/>
+      <c r="BY54" s="31"/>
+      <c r="BZ54" s="31"/>
+      <c r="CA54" s="31"/>
+      <c r="CB54" s="31"/>
+      <c r="CC54" s="31"/>
+      <c r="CD54" s="31"/>
+      <c r="CE54" s="31"/>
+      <c r="CF54" s="31"/>
+      <c r="CG54" s="31"/>
+      <c r="CH54" s="31"/>
+      <c r="CI54" s="31"/>
+      <c r="CJ54" s="31"/>
+      <c r="CK54" s="31"/>
+      <c r="CL54" s="31"/>
+      <c r="CM54" s="31"/>
+      <c r="CN54" s="31"/>
+      <c r="CO54" s="31"/>
+      <c r="CP54" s="31"/>
+      <c r="CQ54" s="31"/>
+      <c r="CR54" s="31"/>
+      <c r="CS54" s="31"/>
+      <c r="CT54" s="31"/>
+      <c r="CU54" s="31"/>
+      <c r="CV54" s="31"/>
+      <c r="CW54" s="31"/>
+      <c r="CX54" s="31"/>
+      <c r="CY54" s="31"/>
+      <c r="CZ54" s="31"/>
+      <c r="DA54" s="31"/>
+      <c r="DB54" s="31"/>
+      <c r="DC54" s="31"/>
+      <c r="DD54" s="31"/>
+      <c r="DE54" s="31"/>
+      <c r="DF54" s="31"/>
+      <c r="DG54" s="31"/>
+      <c r="DH54" s="31"/>
+      <c r="DI54" s="31"/>
+      <c r="DJ54" s="31"/>
+      <c r="DK54" s="31"/>
+      <c r="DL54" s="31"/>
+      <c r="DM54" s="31"/>
+      <c r="DN54" s="31"/>
+      <c r="DO54" s="31"/>
+      <c r="DP54" s="31"/>
+      <c r="DQ54" s="31"/>
+      <c r="DR54" s="31"/>
+      <c r="DS54" s="31"/>
+      <c r="DT54" s="31"/>
+      <c r="DU54" s="31"/>
+      <c r="DV54" s="31"/>
+      <c r="DW54" s="31"/>
+      <c r="DX54" s="31"/>
+      <c r="DY54" s="31"/>
+      <c r="DZ54" s="31"/>
+      <c r="EA54" s="31"/>
+      <c r="EB54" s="31"/>
+      <c r="EC54" s="31"/>
+      <c r="ED54" s="31"/>
+      <c r="EE54" s="31"/>
+      <c r="EF54" s="31"/>
+      <c r="EG54" s="31"/>
+      <c r="EH54" s="31"/>
+      <c r="EI54" s="31"/>
+      <c r="EJ54" s="31"/>
+      <c r="EK54" s="31"/>
+      <c r="EL54" s="31"/>
+      <c r="EM54" s="31"/>
+      <c r="EN54" s="31"/>
+      <c r="EO54" s="31"/>
+      <c r="EP54" s="31"/>
+      <c r="EQ54" s="31"/>
+      <c r="ER54" s="31"/>
+      <c r="ES54" s="31"/>
+      <c r="ET54" s="31"/>
+      <c r="EU54" s="31"/>
+      <c r="EV54" s="31"/>
+      <c r="EW54" s="31"/>
+      <c r="EX54" s="31"/>
+      <c r="EY54" s="31"/>
+      <c r="EZ54" s="31"/>
+      <c r="FA54" s="31"/>
+      <c r="FB54" s="31"/>
+      <c r="FC54" s="31"/>
+      <c r="FD54" s="31"/>
+      <c r="FE54" s="31"/>
+      <c r="FF54" s="31"/>
+      <c r="FG54" s="31"/>
+      <c r="FH54" s="31"/>
+      <c r="FI54" s="31"/>
+      <c r="FJ54" s="31"/>
+      <c r="FK54" s="31"/>
+      <c r="FL54" s="31"/>
+      <c r="FM54" s="31"/>
+      <c r="FN54" s="31"/>
+      <c r="FO54" s="31"/>
+      <c r="FP54" s="31"/>
+      <c r="FQ54" s="31"/>
+      <c r="FR54" s="31"/>
+      <c r="FS54" s="31"/>
+      <c r="FT54" s="31"/>
+      <c r="FU54" s="31"/>
+      <c r="FV54" s="31"/>
+      <c r="FW54" s="31"/>
+      <c r="FX54" s="31"/>
+      <c r="FY54" s="31"/>
+      <c r="FZ54" s="31"/>
+      <c r="GA54" s="31"/>
+      <c r="GB54" s="31"/>
+      <c r="GC54" s="31"/>
+      <c r="GD54" s="31"/>
+      <c r="GE54" s="31"/>
+      <c r="GF54" s="31"/>
+      <c r="GG54" s="31"/>
+      <c r="GH54" s="31"/>
+      <c r="GI54" s="31"/>
+      <c r="GJ54" s="31"/>
+      <c r="GK54" s="31"/>
+      <c r="GL54" s="31"/>
+      <c r="GM54" s="31"/>
+      <c r="GN54" s="31"/>
+      <c r="GO54" s="31"/>
+      <c r="GP54" s="31"/>
+      <c r="GQ54" s="31"/>
+      <c r="GR54" s="31"/>
+      <c r="GS54" s="31"/>
+      <c r="GT54" s="31"/>
+      <c r="GU54" s="31"/>
+      <c r="GV54" s="31"/>
+      <c r="GW54" s="31"/>
+      <c r="GX54" s="31"/>
+      <c r="GY54" s="31"/>
+      <c r="GZ54" s="31"/>
+      <c r="HA54" s="31"/>
+      <c r="HB54" s="31"/>
+      <c r="HC54" s="31"/>
+      <c r="HD54" s="31"/>
+      <c r="HE54" s="31"/>
+      <c r="HF54" s="31"/>
+      <c r="HG54" s="31"/>
+      <c r="HH54" s="31"/>
+      <c r="HI54" s="31"/>
+      <c r="HJ54" s="31"/>
+      <c r="HK54" s="31"/>
+      <c r="HL54" s="31"/>
+      <c r="HM54" s="31"/>
+      <c r="HN54" s="31"/>
+      <c r="HO54" s="31"/>
+      <c r="HP54" s="31"/>
+      <c r="HQ54" s="31"/>
+      <c r="HR54" s="31"/>
+      <c r="HS54" s="31"/>
+      <c r="HT54" s="31"/>
+      <c r="HU54" s="31"/>
+      <c r="HV54" s="31"/>
+      <c r="HW54" s="31"/>
+      <c r="HX54" s="31"/>
+      <c r="HY54" s="31"/>
+      <c r="HZ54" s="31"/>
+      <c r="IA54" s="31"/>
+      <c r="IB54" s="31"/>
+      <c r="IC54" s="31"/>
+      <c r="ID54" s="31"/>
+      <c r="IE54" s="31"/>
+      <c r="IF54" s="31"/>
+      <c r="IG54" s="31"/>
+      <c r="IH54" s="31"/>
+      <c r="II54" s="31"/>
+      <c r="IJ54" s="31"/>
+      <c r="IK54" s="31"/>
+      <c r="IL54" s="31"/>
+      <c r="IM54" s="31"/>
+      <c r="IN54" s="31"/>
+      <c r="IO54" s="31"/>
+      <c r="IP54" s="31"/>
+      <c r="IQ54" s="31"/>
+      <c r="IR54" s="31"/>
+      <c r="IS54" s="31"/>
+      <c r="IT54" s="31"/>
+      <c r="IU54" s="31"/>
+      <c r="IV54" s="31"/>
+      <c r="IW54" s="31"/>
+      <c r="IX54" s="31"/>
+      <c r="IY54" s="31"/>
+      <c r="IZ54" s="31"/>
+      <c r="JA54" s="31"/>
+      <c r="JB54" s="31"/>
+      <c r="JC54" s="31"/>
+      <c r="JD54" s="31"/>
+      <c r="JE54" s="31"/>
+      <c r="JF54" s="31"/>
+      <c r="JG54" s="31"/>
+      <c r="JH54" s="31"/>
+      <c r="JI54" s="31"/>
+      <c r="JJ54" s="31"/>
+      <c r="JK54" s="31"/>
+      <c r="JL54" s="31"/>
+      <c r="JM54" s="31"/>
+      <c r="JN54" s="31"/>
+      <c r="JO54" s="31"/>
+      <c r="JP54" s="31"/>
+      <c r="JQ54" s="31"/>
+      <c r="JR54" s="31"/>
       <c r="JS54" s="10"/>
       <c r="JT54" s="10"/>
+      <c r="JU54" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A54:JR54"/>
+    <mergeCell ref="IH4:IS4"/>
+    <mergeCell ref="IT4:JE4"/>
+    <mergeCell ref="JF4:JQ4"/>
+    <mergeCell ref="DF4:DQ4"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="Z4:AK4"/>
+    <mergeCell ref="AL4:AW4"/>
+    <mergeCell ref="AX4:BI4"/>
+    <mergeCell ref="A44:JS44"/>
+    <mergeCell ref="JR4:JU4"/>
     <mergeCell ref="A1:JR1"/>
     <mergeCell ref="A2:JR2"/>
     <mergeCell ref="FZ4:GK4"/>
@@ -41890,18 +42051,6 @@
     <mergeCell ref="BV4:CG4"/>
     <mergeCell ref="CH4:CS4"/>
     <mergeCell ref="CT4:DE4"/>
-    <mergeCell ref="A54:JR54"/>
-    <mergeCell ref="IH4:IS4"/>
-    <mergeCell ref="IT4:JE4"/>
-    <mergeCell ref="JF4:JQ4"/>
-    <mergeCell ref="DF4:DQ4"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="Z4:AK4"/>
-    <mergeCell ref="AL4:AW4"/>
-    <mergeCell ref="AX4:BI4"/>
-    <mergeCell ref="A44:JS44"/>
-    <mergeCell ref="JR4:JT4"/>
   </mergeCells>
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -41925,60 +42074,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
     </row>
     <row r="2" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
     </row>
     <row r="4" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -44867,32 +45016,32 @@
       </c>
     </row>
     <row r="43" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="37" t="s">
+      <c r="A43" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="37"/>
-      <c r="K43" s="37"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="37"/>
-      <c r="N43" s="37"/>
-      <c r="O43" s="37"/>
-      <c r="P43" s="37"/>
-      <c r="Q43" s="37"/>
-      <c r="R43" s="37"/>
-      <c r="S43" s="37"/>
-      <c r="T43" s="37"/>
-      <c r="U43" s="37"/>
-      <c r="V43" s="37"/>
-      <c r="W43" s="37"/>
-      <c r="X43" s="37"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="38"/>
+      <c r="W43" s="38"/>
+      <c r="X43" s="38"/>
     </row>
     <row r="44" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -45487,32 +45636,32 @@
       </c>
     </row>
     <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="26"/>
-      <c r="O53" s="26"/>
-      <c r="P53" s="26"/>
-      <c r="Q53" s="26"/>
-      <c r="R53" s="26"/>
-      <c r="S53" s="26"/>
-      <c r="T53" s="26"/>
-      <c r="U53" s="26"/>
-      <c r="V53" s="26"/>
-      <c r="W53" s="26"/>
-      <c r="X53" s="26"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
+      <c r="P53" s="31"/>
+      <c r="Q53" s="31"/>
+      <c r="R53" s="31"/>
+      <c r="S53" s="31"/>
+      <c r="T53" s="31"/>
+      <c r="U53" s="31"/>
+      <c r="V53" s="31"/>
+      <c r="W53" s="31"/>
+      <c r="X53" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
+++ b/fuentes/bc_inv_extranjera/Cuenta_Financiera_categoria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.06.2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srvbalpagos\01_DBDP\04_PRODUCTOS\02_CF\CF.07.07.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E7EE21-4375-449D-8064-E10F5AF5CEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644F67E1-5F28-44D3-8D94-6442693FFED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mensual" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="49">
   <si>
     <t>FLUJOS DE LA CUENTA FINANCIERA DE BALANZA DE PAGOS</t>
   </si>
@@ -229,7 +229,7 @@
       <name val="Helvetica"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,6 +251,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFBFE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -519,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -601,20 +607,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -634,7 +631,19 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -770,973 +779,977 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:JU54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:JV54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="19" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="40" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="53" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="57" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="61" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="64" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="78" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="79" max="80" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="81" max="83" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="84" max="85" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="86" max="88" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="89" max="90" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="91" max="93" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="97" max="100" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="101" max="102" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="103" max="125" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="127" max="136" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="138" max="141" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="143" max="148" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="150" max="154" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="156" max="159" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="160" max="161" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="162" max="170" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="172" max="185" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="186" max="186" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="187" max="189" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="191" max="265" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="266" max="266" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="267" max="278" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="279" max="281" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="282" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="19" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="40" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="53" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="57" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="78" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="79" max="80" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="81" max="83" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="84" max="85" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="86" max="88" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="89" max="90" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="91" max="93" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="97" max="100" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="101" max="102" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="103" max="125" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="127" max="136" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="138" max="141" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="143" max="148" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="150" max="154" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="156" max="159" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="160" max="161" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="162" max="170" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="172" max="185" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="186" max="186" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="187" max="189" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="190" max="190" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="191" max="265" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="266" max="266" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="267" max="278" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="279" max="281" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="282" max="282" width="7.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="283" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="28"/>
-      <c r="AM1" s="28"/>
-      <c r="AN1" s="28"/>
-      <c r="AO1" s="28"/>
-      <c r="AP1" s="28"/>
-      <c r="AQ1" s="28"/>
-      <c r="AR1" s="28"/>
-      <c r="AS1" s="28"/>
-      <c r="AT1" s="28"/>
-      <c r="AU1" s="28"/>
-      <c r="AV1" s="28"/>
-      <c r="AW1" s="28"/>
-      <c r="AX1" s="28"/>
-      <c r="AY1" s="28"/>
-      <c r="AZ1" s="28"/>
-      <c r="BA1" s="28"/>
-      <c r="BB1" s="28"/>
-      <c r="BC1" s="28"/>
-      <c r="BD1" s="28"/>
-      <c r="BE1" s="28"/>
-      <c r="BF1" s="28"/>
-      <c r="BG1" s="28"/>
-      <c r="BH1" s="28"/>
-      <c r="BI1" s="28"/>
-      <c r="BJ1" s="28"/>
-      <c r="BK1" s="28"/>
-      <c r="BL1" s="28"/>
-      <c r="BM1" s="28"/>
-      <c r="BN1" s="28"/>
-      <c r="BO1" s="28"/>
-      <c r="BP1" s="28"/>
-      <c r="BQ1" s="28"/>
-      <c r="BR1" s="28"/>
-      <c r="BS1" s="28"/>
-      <c r="BT1" s="28"/>
-      <c r="BU1" s="28"/>
-      <c r="BV1" s="28"/>
-      <c r="BW1" s="28"/>
-      <c r="BX1" s="28"/>
-      <c r="BY1" s="28"/>
-      <c r="BZ1" s="28"/>
-      <c r="CA1" s="28"/>
-      <c r="CB1" s="28"/>
-      <c r="CC1" s="28"/>
-      <c r="CD1" s="28"/>
-      <c r="CE1" s="28"/>
-      <c r="CF1" s="28"/>
-      <c r="CG1" s="28"/>
-      <c r="CH1" s="28"/>
-      <c r="CI1" s="28"/>
-      <c r="CJ1" s="28"/>
-      <c r="CK1" s="28"/>
-      <c r="CL1" s="28"/>
-      <c r="CM1" s="28"/>
-      <c r="CN1" s="28"/>
-      <c r="CO1" s="28"/>
-      <c r="CP1" s="28"/>
-      <c r="CQ1" s="28"/>
-      <c r="CR1" s="28"/>
-      <c r="CS1" s="28"/>
-      <c r="CT1" s="28"/>
-      <c r="CU1" s="28"/>
-      <c r="CV1" s="28"/>
-      <c r="CW1" s="28"/>
-      <c r="CX1" s="28"/>
-      <c r="CY1" s="28"/>
-      <c r="CZ1" s="28"/>
-      <c r="DA1" s="28"/>
-      <c r="DB1" s="28"/>
-      <c r="DC1" s="28"/>
-      <c r="DD1" s="28"/>
-      <c r="DE1" s="28"/>
-      <c r="DF1" s="28"/>
-      <c r="DG1" s="28"/>
-      <c r="DH1" s="28"/>
-      <c r="DI1" s="28"/>
-      <c r="DJ1" s="28"/>
-      <c r="DK1" s="28"/>
-      <c r="DL1" s="28"/>
-      <c r="DM1" s="28"/>
-      <c r="DN1" s="28"/>
-      <c r="DO1" s="28"/>
-      <c r="DP1" s="28"/>
-      <c r="DQ1" s="28"/>
-      <c r="DR1" s="28"/>
-      <c r="DS1" s="28"/>
-      <c r="DT1" s="28"/>
-      <c r="DU1" s="28"/>
-      <c r="DV1" s="28"/>
-      <c r="DW1" s="28"/>
-      <c r="DX1" s="28"/>
-      <c r="DY1" s="28"/>
-      <c r="DZ1" s="28"/>
-      <c r="EA1" s="28"/>
-      <c r="EB1" s="28"/>
-      <c r="EC1" s="28"/>
-      <c r="ED1" s="28"/>
-      <c r="EE1" s="28"/>
-      <c r="EF1" s="28"/>
-      <c r="EG1" s="28"/>
-      <c r="EH1" s="28"/>
-      <c r="EI1" s="28"/>
-      <c r="EJ1" s="28"/>
-      <c r="EK1" s="28"/>
-      <c r="EL1" s="28"/>
-      <c r="EM1" s="28"/>
-      <c r="EN1" s="28"/>
-      <c r="EO1" s="28"/>
-      <c r="EP1" s="28"/>
-      <c r="EQ1" s="28"/>
-      <c r="ER1" s="28"/>
-      <c r="ES1" s="28"/>
-      <c r="ET1" s="28"/>
-      <c r="EU1" s="28"/>
-      <c r="EV1" s="28"/>
-      <c r="EW1" s="28"/>
-      <c r="EX1" s="28"/>
-      <c r="EY1" s="28"/>
-      <c r="EZ1" s="28"/>
-      <c r="FA1" s="28"/>
-      <c r="FB1" s="28"/>
-      <c r="FC1" s="28"/>
-      <c r="FD1" s="28"/>
-      <c r="FE1" s="28"/>
-      <c r="FF1" s="28"/>
-      <c r="FG1" s="28"/>
-      <c r="FH1" s="28"/>
-      <c r="FI1" s="28"/>
-      <c r="FJ1" s="28"/>
-      <c r="FK1" s="28"/>
-      <c r="FL1" s="28"/>
-      <c r="FM1" s="28"/>
-      <c r="FN1" s="28"/>
-      <c r="FO1" s="28"/>
-      <c r="FP1" s="28"/>
-      <c r="FQ1" s="28"/>
-      <c r="FR1" s="28"/>
-      <c r="FS1" s="28"/>
-      <c r="FT1" s="28"/>
-      <c r="FU1" s="28"/>
-      <c r="FV1" s="28"/>
-      <c r="FW1" s="28"/>
-      <c r="FX1" s="28"/>
-      <c r="FY1" s="28"/>
-      <c r="FZ1" s="28"/>
-      <c r="GA1" s="28"/>
-      <c r="GB1" s="28"/>
-      <c r="GC1" s="28"/>
-      <c r="GD1" s="28"/>
-      <c r="GE1" s="28"/>
-      <c r="GF1" s="28"/>
-      <c r="GG1" s="28"/>
-      <c r="GH1" s="28"/>
-      <c r="GI1" s="28"/>
-      <c r="GJ1" s="28"/>
-      <c r="GK1" s="28"/>
-      <c r="GL1" s="28"/>
-      <c r="GM1" s="28"/>
-      <c r="GN1" s="28"/>
-      <c r="GO1" s="28"/>
-      <c r="GP1" s="28"/>
-      <c r="GQ1" s="28"/>
-      <c r="GR1" s="28"/>
-      <c r="GS1" s="28"/>
-      <c r="GT1" s="28"/>
-      <c r="GU1" s="28"/>
-      <c r="GV1" s="28"/>
-      <c r="GW1" s="28"/>
-      <c r="GX1" s="28"/>
-      <c r="GY1" s="28"/>
-      <c r="GZ1" s="28"/>
-      <c r="HA1" s="28"/>
-      <c r="HB1" s="28"/>
-      <c r="HC1" s="28"/>
-      <c r="HD1" s="28"/>
-      <c r="HE1" s="28"/>
-      <c r="HF1" s="28"/>
-      <c r="HG1" s="28"/>
-      <c r="HH1" s="28"/>
-      <c r="HI1" s="28"/>
-      <c r="HJ1" s="28"/>
-      <c r="HK1" s="28"/>
-      <c r="HL1" s="28"/>
-      <c r="HM1" s="28"/>
-      <c r="HN1" s="28"/>
-      <c r="HO1" s="28"/>
-      <c r="HP1" s="28"/>
-      <c r="HQ1" s="28"/>
-      <c r="HR1" s="28"/>
-      <c r="HS1" s="28"/>
-      <c r="HT1" s="28"/>
-      <c r="HU1" s="28"/>
-      <c r="HV1" s="28"/>
-      <c r="HW1" s="28"/>
-      <c r="HX1" s="28"/>
-      <c r="HY1" s="28"/>
-      <c r="HZ1" s="28"/>
-      <c r="IA1" s="28"/>
-      <c r="IB1" s="28"/>
-      <c r="IC1" s="28"/>
-      <c r="ID1" s="28"/>
-      <c r="IE1" s="28"/>
-      <c r="IF1" s="28"/>
-      <c r="IG1" s="28"/>
-      <c r="IH1" s="28"/>
-      <c r="II1" s="28"/>
-      <c r="IJ1" s="28"/>
-      <c r="IK1" s="28"/>
-      <c r="IL1" s="28"/>
-      <c r="IM1" s="28"/>
-      <c r="IN1" s="28"/>
-      <c r="IO1" s="28"/>
-      <c r="IP1" s="28"/>
-      <c r="IQ1" s="28"/>
-      <c r="IR1" s="28"/>
-      <c r="IS1" s="28"/>
-      <c r="IT1" s="28"/>
-      <c r="IU1" s="28"/>
-      <c r="IV1" s="28"/>
-      <c r="IW1" s="28"/>
-      <c r="IX1" s="28"/>
-      <c r="IY1" s="28"/>
-      <c r="IZ1" s="28"/>
-      <c r="JA1" s="28"/>
-      <c r="JB1" s="28"/>
-      <c r="JC1" s="28"/>
-      <c r="JD1" s="28"/>
-      <c r="JE1" s="28"/>
-      <c r="JF1" s="28"/>
-      <c r="JG1" s="28"/>
-      <c r="JH1" s="28"/>
-      <c r="JI1" s="28"/>
-      <c r="JJ1" s="28"/>
-      <c r="JK1" s="28"/>
-      <c r="JL1" s="28"/>
-      <c r="JM1" s="28"/>
-      <c r="JN1" s="28"/>
-      <c r="JO1" s="28"/>
-      <c r="JP1" s="28"/>
-      <c r="JQ1" s="28"/>
-      <c r="JR1" s="28"/>
+    <row r="1" spans="1:282" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="36"/>
+      <c r="AR1" s="36"/>
+      <c r="AS1" s="36"/>
+      <c r="AT1" s="36"/>
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
+      <c r="AY1" s="36"/>
+      <c r="AZ1" s="36"/>
+      <c r="BA1" s="36"/>
+      <c r="BB1" s="36"/>
+      <c r="BC1" s="36"/>
+      <c r="BD1" s="36"/>
+      <c r="BE1" s="36"/>
+      <c r="BF1" s="36"/>
+      <c r="BG1" s="36"/>
+      <c r="BH1" s="36"/>
+      <c r="BI1" s="36"/>
+      <c r="BJ1" s="36"/>
+      <c r="BK1" s="36"/>
+      <c r="BL1" s="36"/>
+      <c r="BM1" s="36"/>
+      <c r="BN1" s="36"/>
+      <c r="BO1" s="36"/>
+      <c r="BP1" s="36"/>
+      <c r="BQ1" s="36"/>
+      <c r="BR1" s="36"/>
+      <c r="BS1" s="36"/>
+      <c r="BT1" s="36"/>
+      <c r="BU1" s="36"/>
+      <c r="BV1" s="36"/>
+      <c r="BW1" s="36"/>
+      <c r="BX1" s="36"/>
+      <c r="BY1" s="36"/>
+      <c r="BZ1" s="36"/>
+      <c r="CA1" s="36"/>
+      <c r="CB1" s="36"/>
+      <c r="CC1" s="36"/>
+      <c r="CD1" s="36"/>
+      <c r="CE1" s="36"/>
+      <c r="CF1" s="36"/>
+      <c r="CG1" s="36"/>
+      <c r="CH1" s="36"/>
+      <c r="CI1" s="36"/>
+      <c r="CJ1" s="36"/>
+      <c r="CK1" s="36"/>
+      <c r="CL1" s="36"/>
+      <c r="CM1" s="36"/>
+      <c r="CN1" s="36"/>
+      <c r="CO1" s="36"/>
+      <c r="CP1" s="36"/>
+      <c r="CQ1" s="36"/>
+      <c r="CR1" s="36"/>
+      <c r="CS1" s="36"/>
+      <c r="CT1" s="36"/>
+      <c r="CU1" s="36"/>
+      <c r="CV1" s="36"/>
+      <c r="CW1" s="36"/>
+      <c r="CX1" s="36"/>
+      <c r="CY1" s="36"/>
+      <c r="CZ1" s="36"/>
+      <c r="DA1" s="36"/>
+      <c r="DB1" s="36"/>
+      <c r="DC1" s="36"/>
+      <c r="DD1" s="36"/>
+      <c r="DE1" s="36"/>
+      <c r="DF1" s="36"/>
+      <c r="DG1" s="36"/>
+      <c r="DH1" s="36"/>
+      <c r="DI1" s="36"/>
+      <c r="DJ1" s="36"/>
+      <c r="DK1" s="36"/>
+      <c r="DL1" s="36"/>
+      <c r="DM1" s="36"/>
+      <c r="DN1" s="36"/>
+      <c r="DO1" s="36"/>
+      <c r="DP1" s="36"/>
+      <c r="DQ1" s="36"/>
+      <c r="DR1" s="36"/>
+      <c r="DS1" s="36"/>
+      <c r="DT1" s="36"/>
+      <c r="DU1" s="36"/>
+      <c r="DV1" s="36"/>
+      <c r="DW1" s="36"/>
+      <c r="DX1" s="36"/>
+      <c r="DY1" s="36"/>
+      <c r="DZ1" s="36"/>
+      <c r="EA1" s="36"/>
+      <c r="EB1" s="36"/>
+      <c r="EC1" s="36"/>
+      <c r="ED1" s="36"/>
+      <c r="EE1" s="36"/>
+      <c r="EF1" s="36"/>
+      <c r="EG1" s="36"/>
+      <c r="EH1" s="36"/>
+      <c r="EI1" s="36"/>
+      <c r="EJ1" s="36"/>
+      <c r="EK1" s="36"/>
+      <c r="EL1" s="36"/>
+      <c r="EM1" s="36"/>
+      <c r="EN1" s="36"/>
+      <c r="EO1" s="36"/>
+      <c r="EP1" s="36"/>
+      <c r="EQ1" s="36"/>
+      <c r="ER1" s="36"/>
+      <c r="ES1" s="36"/>
+      <c r="ET1" s="36"/>
+      <c r="EU1" s="36"/>
+      <c r="EV1" s="36"/>
+      <c r="EW1" s="36"/>
+      <c r="EX1" s="36"/>
+      <c r="EY1" s="36"/>
+      <c r="EZ1" s="36"/>
+      <c r="FA1" s="36"/>
+      <c r="FB1" s="36"/>
+      <c r="FC1" s="36"/>
+      <c r="FD1" s="36"/>
+      <c r="FE1" s="36"/>
+      <c r="FF1" s="36"/>
+      <c r="FG1" s="36"/>
+      <c r="FH1" s="36"/>
+      <c r="FI1" s="36"/>
+      <c r="FJ1" s="36"/>
+      <c r="FK1" s="36"/>
+      <c r="FL1" s="36"/>
+      <c r="FM1" s="36"/>
+      <c r="FN1" s="36"/>
+      <c r="FO1" s="36"/>
+      <c r="FP1" s="36"/>
+      <c r="FQ1" s="36"/>
+      <c r="FR1" s="36"/>
+      <c r="FS1" s="36"/>
+      <c r="FT1" s="36"/>
+      <c r="FU1" s="36"/>
+      <c r="FV1" s="36"/>
+      <c r="FW1" s="36"/>
+      <c r="FX1" s="36"/>
+      <c r="FY1" s="36"/>
+      <c r="FZ1" s="36"/>
+      <c r="GA1" s="36"/>
+      <c r="GB1" s="36"/>
+      <c r="GC1" s="36"/>
+      <c r="GD1" s="36"/>
+      <c r="GE1" s="36"/>
+      <c r="GF1" s="36"/>
+      <c r="GG1" s="36"/>
+      <c r="GH1" s="36"/>
+      <c r="GI1" s="36"/>
+      <c r="GJ1" s="36"/>
+      <c r="GK1" s="36"/>
+      <c r="GL1" s="36"/>
+      <c r="GM1" s="36"/>
+      <c r="GN1" s="36"/>
+      <c r="GO1" s="36"/>
+      <c r="GP1" s="36"/>
+      <c r="GQ1" s="36"/>
+      <c r="GR1" s="36"/>
+      <c r="GS1" s="36"/>
+      <c r="GT1" s="36"/>
+      <c r="GU1" s="36"/>
+      <c r="GV1" s="36"/>
+      <c r="GW1" s="36"/>
+      <c r="GX1" s="36"/>
+      <c r="GY1" s="36"/>
+      <c r="GZ1" s="36"/>
+      <c r="HA1" s="36"/>
+      <c r="HB1" s="36"/>
+      <c r="HC1" s="36"/>
+      <c r="HD1" s="36"/>
+      <c r="HE1" s="36"/>
+      <c r="HF1" s="36"/>
+      <c r="HG1" s="36"/>
+      <c r="HH1" s="36"/>
+      <c r="HI1" s="36"/>
+      <c r="HJ1" s="36"/>
+      <c r="HK1" s="36"/>
+      <c r="HL1" s="36"/>
+      <c r="HM1" s="36"/>
+      <c r="HN1" s="36"/>
+      <c r="HO1" s="36"/>
+      <c r="HP1" s="36"/>
+      <c r="HQ1" s="36"/>
+      <c r="HR1" s="36"/>
+      <c r="HS1" s="36"/>
+      <c r="HT1" s="36"/>
+      <c r="HU1" s="36"/>
+      <c r="HV1" s="36"/>
+      <c r="HW1" s="36"/>
+      <c r="HX1" s="36"/>
+      <c r="HY1" s="36"/>
+      <c r="HZ1" s="36"/>
+      <c r="IA1" s="36"/>
+      <c r="IB1" s="36"/>
+      <c r="IC1" s="36"/>
+      <c r="ID1" s="36"/>
+      <c r="IE1" s="36"/>
+      <c r="IF1" s="36"/>
+      <c r="IG1" s="36"/>
+      <c r="IH1" s="36"/>
+      <c r="II1" s="36"/>
+      <c r="IJ1" s="36"/>
+      <c r="IK1" s="36"/>
+      <c r="IL1" s="36"/>
+      <c r="IM1" s="36"/>
+      <c r="IN1" s="36"/>
+      <c r="IO1" s="36"/>
+      <c r="IP1" s="36"/>
+      <c r="IQ1" s="36"/>
+      <c r="IR1" s="36"/>
+      <c r="IS1" s="36"/>
+      <c r="IT1" s="36"/>
+      <c r="IU1" s="36"/>
+      <c r="IV1" s="36"/>
+      <c r="IW1" s="36"/>
+      <c r="IX1" s="36"/>
+      <c r="IY1" s="36"/>
+      <c r="IZ1" s="36"/>
+      <c r="JA1" s="36"/>
+      <c r="JB1" s="36"/>
+      <c r="JC1" s="36"/>
+      <c r="JD1" s="36"/>
+      <c r="JE1" s="36"/>
+      <c r="JF1" s="36"/>
+      <c r="JG1" s="36"/>
+      <c r="JH1" s="36"/>
+      <c r="JI1" s="36"/>
+      <c r="JJ1" s="36"/>
+      <c r="JK1" s="36"/>
+      <c r="JL1" s="36"/>
+      <c r="JM1" s="36"/>
+      <c r="JN1" s="36"/>
+      <c r="JO1" s="36"/>
+      <c r="JP1" s="36"/>
+      <c r="JQ1" s="36"/>
+      <c r="JR1" s="36"/>
       <c r="JS1" s="10"/>
       <c r="JT1" s="10"/>
       <c r="JU1" s="10"/>
+      <c r="JV1" s="1"/>
     </row>
-    <row r="2" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:282" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
-      <c r="BX2" s="28"/>
-      <c r="BY2" s="28"/>
-      <c r="BZ2" s="28"/>
-      <c r="CA2" s="28"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="28"/>
-      <c r="CG2" s="28"/>
-      <c r="CH2" s="28"/>
-      <c r="CI2" s="28"/>
-      <c r="CJ2" s="28"/>
-      <c r="CK2" s="28"/>
-      <c r="CL2" s="28"/>
-      <c r="CM2" s="28"/>
-      <c r="CN2" s="28"/>
-      <c r="CO2" s="28"/>
-      <c r="CP2" s="28"/>
-      <c r="CQ2" s="28"/>
-      <c r="CR2" s="28"/>
-      <c r="CS2" s="28"/>
-      <c r="CT2" s="28"/>
-      <c r="CU2" s="28"/>
-      <c r="CV2" s="28"/>
-      <c r="CW2" s="28"/>
-      <c r="CX2" s="28"/>
-      <c r="CY2" s="28"/>
-      <c r="CZ2" s="28"/>
-      <c r="DA2" s="28"/>
-      <c r="DB2" s="28"/>
-      <c r="DC2" s="28"/>
-      <c r="DD2" s="28"/>
-      <c r="DE2" s="28"/>
-      <c r="DF2" s="28"/>
-      <c r="DG2" s="28"/>
-      <c r="DH2" s="28"/>
-      <c r="DI2" s="28"/>
-      <c r="DJ2" s="28"/>
-      <c r="DK2" s="28"/>
-      <c r="DL2" s="28"/>
-      <c r="DM2" s="28"/>
-      <c r="DN2" s="28"/>
-      <c r="DO2" s="28"/>
-      <c r="DP2" s="28"/>
-      <c r="DQ2" s="28"/>
-      <c r="DR2" s="28"/>
-      <c r="DS2" s="28"/>
-      <c r="DT2" s="28"/>
-      <c r="DU2" s="28"/>
-      <c r="DV2" s="28"/>
-      <c r="DW2" s="28"/>
-      <c r="DX2" s="28"/>
-      <c r="DY2" s="28"/>
-      <c r="DZ2" s="28"/>
-      <c r="EA2" s="28"/>
-      <c r="EB2" s="28"/>
-      <c r="EC2" s="28"/>
-      <c r="ED2" s="28"/>
-      <c r="EE2" s="28"/>
-      <c r="EF2" s="28"/>
-      <c r="EG2" s="28"/>
-      <c r="EH2" s="28"/>
-      <c r="EI2" s="28"/>
-      <c r="EJ2" s="28"/>
-      <c r="EK2" s="28"/>
-      <c r="EL2" s="28"/>
-      <c r="EM2" s="28"/>
-      <c r="EN2" s="28"/>
-      <c r="EO2" s="28"/>
-      <c r="EP2" s="28"/>
-      <c r="EQ2" s="28"/>
-      <c r="ER2" s="28"/>
-      <c r="ES2" s="28"/>
-      <c r="ET2" s="28"/>
-      <c r="EU2" s="28"/>
-      <c r="EV2" s="28"/>
-      <c r="EW2" s="28"/>
-      <c r="EX2" s="28"/>
-      <c r="EY2" s="28"/>
-      <c r="EZ2" s="28"/>
-      <c r="FA2" s="28"/>
-      <c r="FB2" s="28"/>
-      <c r="FC2" s="28"/>
-      <c r="FD2" s="28"/>
-      <c r="FE2" s="28"/>
-      <c r="FF2" s="28"/>
-      <c r="FG2" s="28"/>
-      <c r="FH2" s="28"/>
-      <c r="FI2" s="28"/>
-      <c r="FJ2" s="28"/>
-      <c r="FK2" s="28"/>
-      <c r="FL2" s="28"/>
-      <c r="FM2" s="28"/>
-      <c r="FN2" s="28"/>
-      <c r="FO2" s="28"/>
-      <c r="FP2" s="28"/>
-      <c r="FQ2" s="28"/>
-      <c r="FR2" s="28"/>
-      <c r="FS2" s="28"/>
-      <c r="FT2" s="28"/>
-      <c r="FU2" s="28"/>
-      <c r="FV2" s="28"/>
-      <c r="FW2" s="28"/>
-      <c r="FX2" s="28"/>
-      <c r="FY2" s="28"/>
-      <c r="FZ2" s="28"/>
-      <c r="GA2" s="28"/>
-      <c r="GB2" s="28"/>
-      <c r="GC2" s="28"/>
-      <c r="GD2" s="28"/>
-      <c r="GE2" s="28"/>
-      <c r="GF2" s="28"/>
-      <c r="GG2" s="28"/>
-      <c r="GH2" s="28"/>
-      <c r="GI2" s="28"/>
-      <c r="GJ2" s="28"/>
-      <c r="GK2" s="28"/>
-      <c r="GL2" s="28"/>
-      <c r="GM2" s="28"/>
-      <c r="GN2" s="28"/>
-      <c r="GO2" s="28"/>
-      <c r="GP2" s="28"/>
-      <c r="GQ2" s="28"/>
-      <c r="GR2" s="28"/>
-      <c r="GS2" s="28"/>
-      <c r="GT2" s="28"/>
-      <c r="GU2" s="28"/>
-      <c r="GV2" s="28"/>
-      <c r="GW2" s="28"/>
-      <c r="GX2" s="28"/>
-      <c r="GY2" s="28"/>
-      <c r="GZ2" s="28"/>
-      <c r="HA2" s="28"/>
-      <c r="HB2" s="28"/>
-      <c r="HC2" s="28"/>
-      <c r="HD2" s="28"/>
-      <c r="HE2" s="28"/>
-      <c r="HF2" s="28"/>
-      <c r="HG2" s="28"/>
-      <c r="HH2" s="28"/>
-      <c r="HI2" s="28"/>
-      <c r="HJ2" s="28"/>
-      <c r="HK2" s="28"/>
-      <c r="HL2" s="28"/>
-      <c r="HM2" s="28"/>
-      <c r="HN2" s="28"/>
-      <c r="HO2" s="28"/>
-      <c r="HP2" s="28"/>
-      <c r="HQ2" s="28"/>
-      <c r="HR2" s="28"/>
-      <c r="HS2" s="28"/>
-      <c r="HT2" s="28"/>
-      <c r="HU2" s="28"/>
-      <c r="HV2" s="28"/>
-      <c r="HW2" s="28"/>
-      <c r="HX2" s="28"/>
-      <c r="HY2" s="28"/>
-      <c r="HZ2" s="28"/>
-      <c r="IA2" s="28"/>
-      <c r="IB2" s="28"/>
-      <c r="IC2" s="28"/>
-      <c r="ID2" s="28"/>
-      <c r="IE2" s="28"/>
-      <c r="IF2" s="28"/>
-      <c r="IG2" s="28"/>
-      <c r="IH2" s="28"/>
-      <c r="II2" s="28"/>
-      <c r="IJ2" s="28"/>
-      <c r="IK2" s="28"/>
-      <c r="IL2" s="28"/>
-      <c r="IM2" s="28"/>
-      <c r="IN2" s="28"/>
-      <c r="IO2" s="28"/>
-      <c r="IP2" s="28"/>
-      <c r="IQ2" s="28"/>
-      <c r="IR2" s="28"/>
-      <c r="IS2" s="28"/>
-      <c r="IT2" s="28"/>
-      <c r="IU2" s="28"/>
-      <c r="IV2" s="28"/>
-      <c r="IW2" s="28"/>
-      <c r="IX2" s="28"/>
-      <c r="IY2" s="28"/>
-      <c r="IZ2" s="28"/>
-      <c r="JA2" s="28"/>
-      <c r="JB2" s="28"/>
-      <c r="JC2" s="28"/>
-      <c r="JD2" s="28"/>
-      <c r="JE2" s="28"/>
-      <c r="JF2" s="28"/>
-      <c r="JG2" s="28"/>
-      <c r="JH2" s="28"/>
-      <c r="JI2" s="28"/>
-      <c r="JJ2" s="28"/>
-      <c r="JK2" s="28"/>
-      <c r="JL2" s="28"/>
-      <c r="JM2" s="28"/>
-      <c r="JN2" s="28"/>
-      <c r="JO2" s="28"/>
-      <c r="JP2" s="28"/>
-      <c r="JQ2" s="28"/>
-      <c r="JR2" s="28"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="36"/>
+      <c r="AR2" s="36"/>
+      <c r="AS2" s="36"/>
+      <c r="AT2" s="36"/>
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="36"/>
+      <c r="BB2" s="36"/>
+      <c r="BC2" s="36"/>
+      <c r="BD2" s="36"/>
+      <c r="BE2" s="36"/>
+      <c r="BF2" s="36"/>
+      <c r="BG2" s="36"/>
+      <c r="BH2" s="36"/>
+      <c r="BI2" s="36"/>
+      <c r="BJ2" s="36"/>
+      <c r="BK2" s="36"/>
+      <c r="BL2" s="36"/>
+      <c r="BM2" s="36"/>
+      <c r="BN2" s="36"/>
+      <c r="BO2" s="36"/>
+      <c r="BP2" s="36"/>
+      <c r="BQ2" s="36"/>
+      <c r="BR2" s="36"/>
+      <c r="BS2" s="36"/>
+      <c r="BT2" s="36"/>
+      <c r="BU2" s="36"/>
+      <c r="BV2" s="36"/>
+      <c r="BW2" s="36"/>
+      <c r="BX2" s="36"/>
+      <c r="BY2" s="36"/>
+      <c r="BZ2" s="36"/>
+      <c r="CA2" s="36"/>
+      <c r="CB2" s="36"/>
+      <c r="CC2" s="36"/>
+      <c r="CD2" s="36"/>
+      <c r="CE2" s="36"/>
+      <c r="CF2" s="36"/>
+      <c r="CG2" s="36"/>
+      <c r="CH2" s="36"/>
+      <c r="CI2" s="36"/>
+      <c r="CJ2" s="36"/>
+      <c r="CK2" s="36"/>
+      <c r="CL2" s="36"/>
+      <c r="CM2" s="36"/>
+      <c r="CN2" s="36"/>
+      <c r="CO2" s="36"/>
+      <c r="CP2" s="36"/>
+      <c r="CQ2" s="36"/>
+      <c r="CR2" s="36"/>
+      <c r="CS2" s="36"/>
+      <c r="CT2" s="36"/>
+      <c r="CU2" s="36"/>
+      <c r="CV2" s="36"/>
+      <c r="CW2" s="36"/>
+      <c r="CX2" s="36"/>
+      <c r="CY2" s="36"/>
+      <c r="CZ2" s="36"/>
+      <c r="DA2" s="36"/>
+      <c r="DB2" s="36"/>
+      <c r="DC2" s="36"/>
+      <c r="DD2" s="36"/>
+      <c r="DE2" s="36"/>
+      <c r="DF2" s="36"/>
+      <c r="DG2" s="36"/>
+      <c r="DH2" s="36"/>
+      <c r="DI2" s="36"/>
+      <c r="DJ2" s="36"/>
+      <c r="DK2" s="36"/>
+      <c r="DL2" s="36"/>
+      <c r="DM2" s="36"/>
+      <c r="DN2" s="36"/>
+      <c r="DO2" s="36"/>
+      <c r="DP2" s="36"/>
+      <c r="DQ2" s="36"/>
+      <c r="DR2" s="36"/>
+      <c r="DS2" s="36"/>
+      <c r="DT2" s="36"/>
+      <c r="DU2" s="36"/>
+      <c r="DV2" s="36"/>
+      <c r="DW2" s="36"/>
+      <c r="DX2" s="36"/>
+      <c r="DY2" s="36"/>
+      <c r="DZ2" s="36"/>
+      <c r="EA2" s="36"/>
+      <c r="EB2" s="36"/>
+      <c r="EC2" s="36"/>
+      <c r="ED2" s="36"/>
+      <c r="EE2" s="36"/>
+      <c r="EF2" s="36"/>
+      <c r="EG2" s="36"/>
+      <c r="EH2" s="36"/>
+      <c r="EI2" s="36"/>
+      <c r="EJ2" s="36"/>
+      <c r="EK2" s="36"/>
+      <c r="EL2" s="36"/>
+      <c r="EM2" s="36"/>
+      <c r="EN2" s="36"/>
+      <c r="EO2" s="36"/>
+      <c r="EP2" s="36"/>
+      <c r="EQ2" s="36"/>
+      <c r="ER2" s="36"/>
+      <c r="ES2" s="36"/>
+      <c r="ET2" s="36"/>
+      <c r="EU2" s="36"/>
+      <c r="EV2" s="36"/>
+      <c r="EW2" s="36"/>
+      <c r="EX2" s="36"/>
+      <c r="EY2" s="36"/>
+      <c r="EZ2" s="36"/>
+      <c r="FA2" s="36"/>
+      <c r="FB2" s="36"/>
+      <c r="FC2" s="36"/>
+      <c r="FD2" s="36"/>
+      <c r="FE2" s="36"/>
+      <c r="FF2" s="36"/>
+      <c r="FG2" s="36"/>
+      <c r="FH2" s="36"/>
+      <c r="FI2" s="36"/>
+      <c r="FJ2" s="36"/>
+      <c r="FK2" s="36"/>
+      <c r="FL2" s="36"/>
+      <c r="FM2" s="36"/>
+      <c r="FN2" s="36"/>
+      <c r="FO2" s="36"/>
+      <c r="FP2" s="36"/>
+      <c r="FQ2" s="36"/>
+      <c r="FR2" s="36"/>
+      <c r="FS2" s="36"/>
+      <c r="FT2" s="36"/>
+      <c r="FU2" s="36"/>
+      <c r="FV2" s="36"/>
+      <c r="FW2" s="36"/>
+      <c r="FX2" s="36"/>
+      <c r="FY2" s="36"/>
+      <c r="FZ2" s="36"/>
+      <c r="GA2" s="36"/>
+      <c r="GB2" s="36"/>
+      <c r="GC2" s="36"/>
+      <c r="GD2" s="36"/>
+      <c r="GE2" s="36"/>
+      <c r="GF2" s="36"/>
+      <c r="GG2" s="36"/>
+      <c r="GH2" s="36"/>
+      <c r="GI2" s="36"/>
+      <c r="GJ2" s="36"/>
+      <c r="GK2" s="36"/>
+      <c r="GL2" s="36"/>
+      <c r="GM2" s="36"/>
+      <c r="GN2" s="36"/>
+      <c r="GO2" s="36"/>
+      <c r="GP2" s="36"/>
+      <c r="GQ2" s="36"/>
+      <c r="GR2" s="36"/>
+      <c r="GS2" s="36"/>
+      <c r="GT2" s="36"/>
+      <c r="GU2" s="36"/>
+      <c r="GV2" s="36"/>
+      <c r="GW2" s="36"/>
+      <c r="GX2" s="36"/>
+      <c r="GY2" s="36"/>
+      <c r="GZ2" s="36"/>
+      <c r="HA2" s="36"/>
+      <c r="HB2" s="36"/>
+      <c r="HC2" s="36"/>
+      <c r="HD2" s="36"/>
+      <c r="HE2" s="36"/>
+      <c r="HF2" s="36"/>
+      <c r="HG2" s="36"/>
+      <c r="HH2" s="36"/>
+      <c r="HI2" s="36"/>
+      <c r="HJ2" s="36"/>
+      <c r="HK2" s="36"/>
+      <c r="HL2" s="36"/>
+      <c r="HM2" s="36"/>
+      <c r="HN2" s="36"/>
+      <c r="HO2" s="36"/>
+      <c r="HP2" s="36"/>
+      <c r="HQ2" s="36"/>
+      <c r="HR2" s="36"/>
+      <c r="HS2" s="36"/>
+      <c r="HT2" s="36"/>
+      <c r="HU2" s="36"/>
+      <c r="HV2" s="36"/>
+      <c r="HW2" s="36"/>
+      <c r="HX2" s="36"/>
+      <c r="HY2" s="36"/>
+      <c r="HZ2" s="36"/>
+      <c r="IA2" s="36"/>
+      <c r="IB2" s="36"/>
+      <c r="IC2" s="36"/>
+      <c r="ID2" s="36"/>
+      <c r="IE2" s="36"/>
+      <c r="IF2" s="36"/>
+      <c r="IG2" s="36"/>
+      <c r="IH2" s="36"/>
+      <c r="II2" s="36"/>
+      <c r="IJ2" s="36"/>
+      <c r="IK2" s="36"/>
+      <c r="IL2" s="36"/>
+      <c r="IM2" s="36"/>
+      <c r="IN2" s="36"/>
+      <c r="IO2" s="36"/>
+      <c r="IP2" s="36"/>
+      <c r="IQ2" s="36"/>
+      <c r="IR2" s="36"/>
+      <c r="IS2" s="36"/>
+      <c r="IT2" s="36"/>
+      <c r="IU2" s="36"/>
+      <c r="IV2" s="36"/>
+      <c r="IW2" s="36"/>
+      <c r="IX2" s="36"/>
+      <c r="IY2" s="36"/>
+      <c r="IZ2" s="36"/>
+      <c r="JA2" s="36"/>
+      <c r="JB2" s="36"/>
+      <c r="JC2" s="36"/>
+      <c r="JD2" s="36"/>
+      <c r="JE2" s="36"/>
+      <c r="JF2" s="36"/>
+      <c r="JG2" s="36"/>
+      <c r="JH2" s="36"/>
+      <c r="JI2" s="36"/>
+      <c r="JJ2" s="36"/>
+      <c r="JK2" s="36"/>
+      <c r="JL2" s="36"/>
+      <c r="JM2" s="36"/>
+      <c r="JN2" s="36"/>
+      <c r="JO2" s="36"/>
+      <c r="JP2" s="36"/>
+      <c r="JQ2" s="36"/>
+      <c r="JR2" s="36"/>
       <c r="JS2" s="10"/>
       <c r="JT2" s="10"/>
       <c r="JU2" s="10"/>
+      <c r="JV2" s="1"/>
     </row>
-    <row r="4" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:282" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="30">
+      <c r="B4" s="28">
         <v>2003</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30">
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28">
         <v>2004</v>
       </c>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30">
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28">
         <v>2005</v>
       </c>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
-      <c r="AL4" s="30">
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28">
         <v>2006</v>
       </c>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
-      <c r="AU4" s="30"/>
-      <c r="AV4" s="30"/>
-      <c r="AW4" s="30"/>
-      <c r="AX4" s="30">
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28">
         <v>2007</v>
       </c>
-      <c r="AY4" s="30"/>
-      <c r="AZ4" s="30"/>
-      <c r="BA4" s="30"/>
-      <c r="BB4" s="30"/>
-      <c r="BC4" s="30"/>
-      <c r="BD4" s="30"/>
-      <c r="BE4" s="30"/>
-      <c r="BF4" s="30"/>
-      <c r="BG4" s="30"/>
-      <c r="BH4" s="30"/>
-      <c r="BI4" s="30"/>
-      <c r="BJ4" s="30">
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28">
         <v>2008</v>
       </c>
-      <c r="BK4" s="30"/>
-      <c r="BL4" s="30"/>
-      <c r="BM4" s="30"/>
-      <c r="BN4" s="30"/>
-      <c r="BO4" s="30"/>
-      <c r="BP4" s="30"/>
-      <c r="BQ4" s="30"/>
-      <c r="BR4" s="30"/>
-      <c r="BS4" s="30"/>
-      <c r="BT4" s="30"/>
-      <c r="BU4" s="30"/>
-      <c r="BV4" s="30">
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28">
         <v>2009</v>
       </c>
-      <c r="BW4" s="30"/>
-      <c r="BX4" s="30"/>
-      <c r="BY4" s="30"/>
-      <c r="BZ4" s="30"/>
-      <c r="CA4" s="30"/>
-      <c r="CB4" s="30"/>
-      <c r="CC4" s="30"/>
-      <c r="CD4" s="30"/>
-      <c r="CE4" s="30"/>
-      <c r="CF4" s="30"/>
-      <c r="CG4" s="30"/>
-      <c r="CH4" s="30">
+      <c r="BW4" s="28"/>
+      <c r="BX4" s="28"/>
+      <c r="BY4" s="28"/>
+      <c r="BZ4" s="28"/>
+      <c r="CA4" s="28"/>
+      <c r="CB4" s="28"/>
+      <c r="CC4" s="28"/>
+      <c r="CD4" s="28"/>
+      <c r="CE4" s="28"/>
+      <c r="CF4" s="28"/>
+      <c r="CG4" s="28"/>
+      <c r="CH4" s="28">
         <v>2010</v>
       </c>
-      <c r="CI4" s="30"/>
-      <c r="CJ4" s="30"/>
-      <c r="CK4" s="30"/>
-      <c r="CL4" s="30"/>
-      <c r="CM4" s="30"/>
-      <c r="CN4" s="30"/>
-      <c r="CO4" s="30"/>
-      <c r="CP4" s="30"/>
-      <c r="CQ4" s="30"/>
-      <c r="CR4" s="30"/>
-      <c r="CS4" s="30"/>
-      <c r="CT4" s="30">
+      <c r="CI4" s="28"/>
+      <c r="CJ4" s="28"/>
+      <c r="CK4" s="28"/>
+      <c r="CL4" s="28"/>
+      <c r="CM4" s="28"/>
+      <c r="CN4" s="28"/>
+      <c r="CO4" s="28"/>
+      <c r="CP4" s="28"/>
+      <c r="CQ4" s="28"/>
+      <c r="CR4" s="28"/>
+      <c r="CS4" s="28"/>
+      <c r="CT4" s="28">
         <v>2011</v>
       </c>
-      <c r="CU4" s="30"/>
-      <c r="CV4" s="30"/>
-      <c r="CW4" s="30"/>
-      <c r="CX4" s="30"/>
-      <c r="CY4" s="30"/>
-      <c r="CZ4" s="30"/>
-      <c r="DA4" s="30"/>
-      <c r="DB4" s="30"/>
-      <c r="DC4" s="30"/>
-      <c r="DD4" s="30"/>
-      <c r="DE4" s="30"/>
-      <c r="DF4" s="30">
+      <c r="CU4" s="28"/>
+      <c r="CV4" s="28"/>
+      <c r="CW4" s="28"/>
+      <c r="CX4" s="28"/>
+      <c r="CY4" s="28"/>
+      <c r="CZ4" s="28"/>
+      <c r="DA4" s="28"/>
+      <c r="DB4" s="28"/>
+      <c r="DC4" s="28"/>
+      <c r="DD4" s="28"/>
+      <c r="DE4" s="28"/>
+      <c r="DF4" s="28">
         <v>2012</v>
       </c>
-      <c r="DG4" s="30"/>
-      <c r="DH4" s="30"/>
-      <c r="DI4" s="30"/>
-      <c r="DJ4" s="30"/>
-      <c r="DK4" s="30"/>
-      <c r="DL4" s="30"/>
-      <c r="DM4" s="30"/>
-      <c r="DN4" s="30"/>
-      <c r="DO4" s="30"/>
-      <c r="DP4" s="30"/>
-      <c r="DQ4" s="30"/>
-      <c r="DR4" s="30">
+      <c r="DG4" s="28"/>
+      <c r="DH4" s="28"/>
+      <c r="DI4" s="28"/>
+      <c r="DJ4" s="28"/>
+      <c r="DK4" s="28"/>
+      <c r="DL4" s="28"/>
+      <c r="DM4" s="28"/>
+      <c r="DN4" s="28"/>
+      <c r="DO4" s="28"/>
+      <c r="DP4" s="28"/>
+      <c r="DQ4" s="28"/>
+      <c r="DR4" s="28">
         <v>2013</v>
       </c>
-      <c r="DS4" s="30"/>
-      <c r="DT4" s="30"/>
-      <c r="DU4" s="30"/>
-      <c r="DV4" s="30"/>
-      <c r="DW4" s="30"/>
-      <c r="DX4" s="30"/>
-      <c r="DY4" s="30"/>
-      <c r="DZ4" s="30"/>
-      <c r="EA4" s="30"/>
-      <c r="EB4" s="30"/>
-      <c r="EC4" s="30"/>
-      <c r="ED4" s="30">
+      <c r="DS4" s="28"/>
+      <c r="DT4" s="28"/>
+      <c r="DU4" s="28"/>
+      <c r="DV4" s="28"/>
+      <c r="DW4" s="28"/>
+      <c r="DX4" s="28"/>
+      <c r="DY4" s="28"/>
+      <c r="DZ4" s="28"/>
+      <c r="EA4" s="28"/>
+      <c r="EB4" s="28"/>
+      <c r="EC4" s="28"/>
+      <c r="ED4" s="28">
         <v>2014</v>
       </c>
-      <c r="EE4" s="30"/>
-      <c r="EF4" s="30"/>
-      <c r="EG4" s="30"/>
-      <c r="EH4" s="30"/>
-      <c r="EI4" s="30"/>
-      <c r="EJ4" s="30"/>
-      <c r="EK4" s="30"/>
-      <c r="EL4" s="30"/>
-      <c r="EM4" s="30"/>
-      <c r="EN4" s="30"/>
-      <c r="EO4" s="30"/>
-      <c r="EP4" s="30">
+      <c r="EE4" s="28"/>
+      <c r="EF4" s="28"/>
+      <c r="EG4" s="28"/>
+      <c r="EH4" s="28"/>
+      <c r="EI4" s="28"/>
+      <c r="EJ4" s="28"/>
+      <c r="EK4" s="28"/>
+      <c r="EL4" s="28"/>
+      <c r="EM4" s="28"/>
+      <c r="EN4" s="28"/>
+      <c r="EO4" s="28"/>
+      <c r="EP4" s="28">
         <v>2015</v>
       </c>
-      <c r="EQ4" s="30"/>
-      <c r="ER4" s="30"/>
-      <c r="ES4" s="30"/>
-      <c r="ET4" s="30"/>
-      <c r="EU4" s="30"/>
-      <c r="EV4" s="30"/>
-      <c r="EW4" s="30"/>
-      <c r="EX4" s="30"/>
-      <c r="EY4" s="30"/>
-      <c r="EZ4" s="30"/>
-      <c r="FA4" s="30"/>
-      <c r="FB4" s="30">
+      <c r="EQ4" s="28"/>
+      <c r="ER4" s="28"/>
+      <c r="ES4" s="28"/>
+      <c r="ET4" s="28"/>
+      <c r="EU4" s="28"/>
+      <c r="EV4" s="28"/>
+      <c r="EW4" s="28"/>
+      <c r="EX4" s="28"/>
+      <c r="EY4" s="28"/>
+      <c r="EZ4" s="28"/>
+      <c r="FA4" s="28"/>
+      <c r="FB4" s="28">
         <v>2016</v>
       </c>
-      <c r="FC4" s="30"/>
-      <c r="FD4" s="30"/>
-      <c r="FE4" s="30"/>
-      <c r="FF4" s="30"/>
-      <c r="FG4" s="30"/>
-      <c r="FH4" s="30"/>
-      <c r="FI4" s="30"/>
-      <c r="FJ4" s="30"/>
-      <c r="FK4" s="30"/>
-      <c r="FL4" s="30"/>
-      <c r="FM4" s="30"/>
-      <c r="FN4" s="30">
+      <c r="FC4" s="28"/>
+      <c r="FD4" s="28"/>
+      <c r="FE4" s="28"/>
+      <c r="FF4" s="28"/>
+      <c r="FG4" s="28"/>
+      <c r="FH4" s="28"/>
+      <c r="FI4" s="28"/>
+      <c r="FJ4" s="28"/>
+      <c r="FK4" s="28"/>
+      <c r="FL4" s="28"/>
+      <c r="FM4" s="28"/>
+      <c r="FN4" s="28">
         <v>2017</v>
       </c>
-      <c r="FO4" s="30"/>
-      <c r="FP4" s="30"/>
-      <c r="FQ4" s="30"/>
-      <c r="FR4" s="30"/>
-      <c r="FS4" s="30"/>
-      <c r="FT4" s="30"/>
-      <c r="FU4" s="30"/>
-      <c r="FV4" s="30"/>
-      <c r="FW4" s="30"/>
-      <c r="FX4" s="30"/>
-      <c r="FY4" s="30"/>
-      <c r="FZ4" s="30">
+      <c r="FO4" s="28"/>
+      <c r="FP4" s="28"/>
+      <c r="FQ4" s="28"/>
+      <c r="FR4" s="28"/>
+      <c r="FS4" s="28"/>
+      <c r="FT4" s="28"/>
+      <c r="FU4" s="28"/>
+      <c r="FV4" s="28"/>
+      <c r="FW4" s="28"/>
+      <c r="FX4" s="28"/>
+      <c r="FY4" s="28"/>
+      <c r="FZ4" s="28">
         <v>2018</v>
       </c>
-      <c r="GA4" s="30"/>
-      <c r="GB4" s="30"/>
-      <c r="GC4" s="30"/>
-      <c r="GD4" s="30"/>
-      <c r="GE4" s="30"/>
-      <c r="GF4" s="30"/>
-      <c r="GG4" s="30"/>
-      <c r="GH4" s="30"/>
-      <c r="GI4" s="30"/>
-      <c r="GJ4" s="30"/>
-      <c r="GK4" s="30"/>
-      <c r="GL4" s="30">
+      <c r="GA4" s="28"/>
+      <c r="GB4" s="28"/>
+      <c r="GC4" s="28"/>
+      <c r="GD4" s="28"/>
+      <c r="GE4" s="28"/>
+      <c r="GF4" s="28"/>
+      <c r="GG4" s="28"/>
+      <c r="GH4" s="28"/>
+      <c r="GI4" s="28"/>
+      <c r="GJ4" s="28"/>
+      <c r="GK4" s="28"/>
+      <c r="GL4" s="28">
         <v>2019</v>
       </c>
-      <c r="GM4" s="30"/>
-      <c r="GN4" s="30"/>
-      <c r="GO4" s="30"/>
-      <c r="GP4" s="30"/>
-      <c r="GQ4" s="30"/>
-      <c r="GR4" s="30"/>
-      <c r="GS4" s="30"/>
-      <c r="GT4" s="30"/>
-      <c r="GU4" s="30"/>
-      <c r="GV4" s="30"/>
-      <c r="GW4" s="30"/>
-      <c r="GX4" s="30">
+      <c r="GM4" s="28"/>
+      <c r="GN4" s="28"/>
+      <c r="GO4" s="28"/>
+      <c r="GP4" s="28"/>
+      <c r="GQ4" s="28"/>
+      <c r="GR4" s="28"/>
+      <c r="GS4" s="28"/>
+      <c r="GT4" s="28"/>
+      <c r="GU4" s="28"/>
+      <c r="GV4" s="28"/>
+      <c r="GW4" s="28"/>
+      <c r="GX4" s="28">
         <v>2020</v>
       </c>
-      <c r="GY4" s="30"/>
-      <c r="GZ4" s="30"/>
-      <c r="HA4" s="30"/>
-      <c r="HB4" s="30"/>
-      <c r="HC4" s="30"/>
-      <c r="HD4" s="30"/>
-      <c r="HE4" s="30"/>
-      <c r="HF4" s="30"/>
-      <c r="HG4" s="30"/>
-      <c r="HH4" s="30"/>
-      <c r="HI4" s="30"/>
-      <c r="HJ4" s="30">
+      <c r="GY4" s="28"/>
+      <c r="GZ4" s="28"/>
+      <c r="HA4" s="28"/>
+      <c r="HB4" s="28"/>
+      <c r="HC4" s="28"/>
+      <c r="HD4" s="28"/>
+      <c r="HE4" s="28"/>
+      <c r="HF4" s="28"/>
+      <c r="HG4" s="28"/>
+      <c r="HH4" s="28"/>
+      <c r="HI4" s="28"/>
+      <c r="HJ4" s="28">
         <v>2021</v>
       </c>
-      <c r="HK4" s="30"/>
-      <c r="HL4" s="30"/>
-      <c r="HM4" s="30"/>
-      <c r="HN4" s="30"/>
-      <c r="HO4" s="30"/>
-      <c r="HP4" s="30"/>
-      <c r="HQ4" s="30"/>
-      <c r="HR4" s="30"/>
-      <c r="HS4" s="30"/>
-      <c r="HT4" s="30"/>
-      <c r="HU4" s="30"/>
-      <c r="HV4" s="30">
+      <c r="HK4" s="28"/>
+      <c r="HL4" s="28"/>
+      <c r="HM4" s="28"/>
+      <c r="HN4" s="28"/>
+      <c r="HO4" s="28"/>
+      <c r="HP4" s="28"/>
+      <c r="HQ4" s="28"/>
+      <c r="HR4" s="28"/>
+      <c r="HS4" s="28"/>
+      <c r="HT4" s="28"/>
+      <c r="HU4" s="28"/>
+      <c r="HV4" s="28">
         <v>2022</v>
       </c>
-      <c r="HW4" s="30"/>
-      <c r="HX4" s="30"/>
-      <c r="HY4" s="30"/>
-      <c r="HZ4" s="30"/>
-      <c r="IA4" s="30"/>
-      <c r="IB4" s="30"/>
-      <c r="IC4" s="30"/>
-      <c r="ID4" s="30"/>
-      <c r="IE4" s="30"/>
-      <c r="IF4" s="30"/>
-      <c r="IG4" s="30"/>
-      <c r="IH4" s="30">
+      <c r="HW4" s="28"/>
+      <c r="HX4" s="28"/>
+      <c r="HY4" s="28"/>
+      <c r="HZ4" s="28"/>
+      <c r="IA4" s="28"/>
+      <c r="IB4" s="28"/>
+      <c r="IC4" s="28"/>
+      <c r="ID4" s="28"/>
+      <c r="IE4" s="28"/>
+      <c r="IF4" s="28"/>
+      <c r="IG4" s="28"/>
+      <c r="IH4" s="28">
         <v>2023</v>
       </c>
-      <c r="II4" s="30"/>
-      <c r="IJ4" s="30"/>
-      <c r="IK4" s="30"/>
-      <c r="IL4" s="30"/>
-      <c r="IM4" s="30"/>
-      <c r="IN4" s="30"/>
-      <c r="IO4" s="30"/>
-      <c r="IP4" s="30"/>
-      <c r="IQ4" s="30"/>
-      <c r="IR4" s="30"/>
-      <c r="IS4" s="30"/>
-      <c r="IT4" s="30">
+      <c r="II4" s="28"/>
+      <c r="IJ4" s="28"/>
+      <c r="IK4" s="28"/>
+      <c r="IL4" s="28"/>
+      <c r="IM4" s="28"/>
+      <c r="IN4" s="28"/>
+      <c r="IO4" s="28"/>
+      <c r="IP4" s="28"/>
+      <c r="IQ4" s="28"/>
+      <c r="IR4" s="28"/>
+      <c r="IS4" s="28"/>
+      <c r="IT4" s="28">
         <v>2024</v>
       </c>
-      <c r="IU4" s="30"/>
-      <c r="IV4" s="30"/>
-      <c r="IW4" s="30"/>
-      <c r="IX4" s="30"/>
-      <c r="IY4" s="30"/>
-      <c r="IZ4" s="30"/>
-      <c r="JA4" s="30"/>
-      <c r="JB4" s="30"/>
-      <c r="JC4" s="30"/>
-      <c r="JD4" s="30"/>
-      <c r="JE4" s="30"/>
-      <c r="JF4" s="30">
+      <c r="IU4" s="28"/>
+      <c r="IV4" s="28"/>
+      <c r="IW4" s="28"/>
+      <c r="IX4" s="28"/>
+      <c r="IY4" s="28"/>
+      <c r="IZ4" s="28"/>
+      <c r="JA4" s="28"/>
+      <c r="JB4" s="28"/>
+      <c r="JC4" s="28"/>
+      <c r="JD4" s="28"/>
+      <c r="JE4" s="28"/>
+      <c r="JF4" s="28">
         <v>2025</v>
       </c>
-      <c r="JG4" s="30"/>
-      <c r="JH4" s="30"/>
-      <c r="JI4" s="30"/>
-      <c r="JJ4" s="30"/>
-      <c r="JK4" s="30"/>
-      <c r="JL4" s="30"/>
-      <c r="JM4" s="30"/>
-      <c r="JN4" s="30"/>
-      <c r="JO4" s="30"/>
-      <c r="JP4" s="30"/>
-      <c r="JQ4" s="32"/>
-      <c r="JR4" s="35">
+      <c r="JG4" s="28"/>
+      <c r="JH4" s="28"/>
+      <c r="JI4" s="28"/>
+      <c r="JJ4" s="28"/>
+      <c r="JK4" s="28"/>
+      <c r="JL4" s="28"/>
+      <c r="JM4" s="28"/>
+      <c r="JN4" s="28"/>
+      <c r="JO4" s="28"/>
+      <c r="JP4" s="28"/>
+      <c r="JQ4" s="29"/>
+      <c r="JR4" s="32">
         <v>2026</v>
       </c>
-      <c r="JS4" s="36"/>
-      <c r="JT4" s="36"/>
-      <c r="JU4" s="37"/>
+      <c r="JS4" s="33"/>
+      <c r="JT4" s="33"/>
+      <c r="JU4" s="33"/>
+      <c r="JV4" s="34"/>
     </row>
-    <row r="5" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:282" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2580,8 +2593,11 @@
       <c r="JU5" s="12" t="s">
         <v>6</v>
       </c>
+      <c r="JV5" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -3425,8 +3441,11 @@
       <c r="JU6" s="13">
         <v>-4410.93432889</v>
       </c>
+      <c r="JV6" s="13">
+        <v>-4100.0262555334002</v>
+      </c>
     </row>
-    <row r="7" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -4270,8 +4289,11 @@
       <c r="JU7" s="13">
         <v>-1209.8447660776999</v>
       </c>
+      <c r="JV7" s="13">
+        <v>2341.6261947909102</v>
+      </c>
     </row>
-    <row r="8" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -5115,8 +5137,11 @@
       <c r="JU8" s="13">
         <v>3201.0895628122898</v>
       </c>
+      <c r="JV8" s="13">
+        <v>6441.6524503243099</v>
+      </c>
     </row>
-    <row r="9" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -5960,8 +5985,11 @@
       <c r="JU9" s="13">
         <v>-1567.1094068355001</v>
       </c>
+      <c r="JV9" s="13">
+        <v>-1532.9750433586</v>
+      </c>
     </row>
-    <row r="10" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
@@ -6805,8 +6833,11 @@
       <c r="JU10" s="14">
         <v>667.98608566245503</v>
       </c>
+      <c r="JV10" s="14">
+        <v>636.15970238395801</v>
+      </c>
     </row>
-    <row r="11" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
@@ -7650,8 +7681,11 @@
       <c r="JU11" s="14">
         <v>259.44713658627001</v>
       </c>
+      <c r="JV11" s="14">
+        <v>223.239213639572</v>
+      </c>
     </row>
-    <row r="12" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
@@ -8495,8 +8529,11 @@
       <c r="JU12" s="14">
         <v>-87.706030654960003</v>
       </c>
+      <c r="JV12" s="14">
+        <v>179.896436717532</v>
+      </c>
     </row>
-    <row r="13" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
@@ -9340,8 +9377,11 @@
       <c r="JU13" s="14">
         <v>496.24497973114501</v>
       </c>
+      <c r="JV13" s="14">
+        <v>233.02405202685401</v>
+      </c>
     </row>
-    <row r="14" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -10185,8 +10225,11 @@
       <c r="JU14" s="14">
         <v>2235.0954924979101</v>
       </c>
+      <c r="JV14" s="14">
+        <v>2169.13474574255</v>
+      </c>
     </row>
-    <row r="15" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -11030,8 +11073,11 @@
       <c r="JU15" s="14">
         <v>223.850637124803</v>
       </c>
+      <c r="JV15" s="14">
+        <v>447.17540655481503</v>
+      </c>
     </row>
-    <row r="16" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
@@ -11875,8 +11921,11 @@
       <c r="JU16" s="14">
         <v>428.33030543049301</v>
       </c>
+      <c r="JV16" s="14">
+        <v>80.914109687737394</v>
+      </c>
     </row>
-    <row r="17" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
@@ -12720,8 +12769,11 @@
       <c r="JU17" s="14">
         <v>1582.9145499426099</v>
       </c>
+      <c r="JV17" s="14">
+        <v>1641.0452295</v>
+      </c>
     </row>
-    <row r="18" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -13565,8 +13617,11 @@
       <c r="JU18" s="13">
         <v>-1207.6794680788</v>
       </c>
+      <c r="JV18" s="13">
+        <v>-2166.0881867496</v>
+      </c>
     </row>
-    <row r="19" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
@@ -14410,8 +14465,11 @@
       <c r="JU19" s="14">
         <v>960.678971485484</v>
       </c>
+      <c r="JV19" s="14">
+        <v>364.47093860325799</v>
+      </c>
     </row>
-    <row r="20" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>25</v>
       </c>
@@ -15255,8 +15313,11 @@
       <c r="JU20" s="14">
         <v>417.09790611430401</v>
       </c>
+      <c r="JV20" s="14">
+        <v>-106.28999876332</v>
+      </c>
     </row>
-    <row r="21" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>26</v>
       </c>
@@ -16100,8 +16161,11 @@
       <c r="JU21" s="14">
         <v>543.58106537117999</v>
       </c>
+      <c r="JV21" s="14">
+        <v>470.76093736657401</v>
+      </c>
     </row>
-    <row r="22" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>27</v>
       </c>
@@ -16945,8 +17009,11 @@
       <c r="JU22" s="14">
         <v>189.24332829689101</v>
       </c>
+      <c r="JV22" s="14">
+        <v>397.69321830242899</v>
+      </c>
     </row>
-    <row r="23" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
@@ -17790,8 +17857,11 @@
       <c r="JU23" s="14">
         <v>354.33773707428901</v>
       </c>
+      <c r="JV23" s="14">
+        <v>73.067719064144597</v>
+      </c>
     </row>
-    <row r="24" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
@@ -18635,8 +18705,11 @@
       <c r="JU24" s="14">
         <v>2168.3584395643102</v>
       </c>
+      <c r="JV24" s="14">
+        <v>2530.5591253528601</v>
+      </c>
     </row>
-    <row r="25" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
@@ -19480,8 +19553,11 @@
       <c r="JU25" s="14">
         <v>127.803024629465</v>
       </c>
+      <c r="JV25" s="14">
+        <v>-398.73028860762003</v>
+      </c>
     </row>
-    <row r="26" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -20325,8 +20401,11 @@
       <c r="JU26" s="14">
         <v>2040.55541493484</v>
       </c>
+      <c r="JV26" s="14">
+        <v>2929.28941396049</v>
+      </c>
     </row>
-    <row r="27" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
@@ -21170,8 +21249,11 @@
       <c r="JU27" s="14">
         <v>2105.5442797692999</v>
       </c>
+      <c r="JV27" s="14">
+        <v>2499.5431149633</v>
+      </c>
     </row>
-    <row r="28" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -22015,8 +22097,11 @@
       <c r="JU28" s="14">
         <v>-64.988864834460998</v>
       </c>
+      <c r="JV28" s="14">
+        <v>429.74629899718502</v>
+      </c>
     </row>
-    <row r="29" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>30</v>
       </c>
@@ -22860,8 +22945,11 @@
       <c r="JU29" s="13">
         <v>-148.15686460025</v>
       </c>
+      <c r="JV29" s="13">
+        <v>-129.46076684694</v>
+      </c>
     </row>
-    <row r="30" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -23705,8 +23793,11 @@
       <c r="JU30" s="13">
         <v>-1756.5338596747999</v>
       </c>
+      <c r="JV30" s="13">
+        <v>-954.80629231703006</v>
+      </c>
     </row>
-    <row r="31" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>19</v>
       </c>
@@ -24550,8 +24641,11 @@
       <c r="JU31" s="14">
         <v>-971.18770325715002</v>
       </c>
+      <c r="JV31" s="14">
+        <v>2336.74736794929</v>
+      </c>
     </row>
-    <row r="32" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>32</v>
       </c>
@@ -25395,8 +25489,11 @@
       <c r="JU32" s="14">
         <v>0</v>
       </c>
+      <c r="JV32" s="14">
+        <v>32.546967219999999</v>
+      </c>
     </row>
-    <row r="33" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>33</v>
       </c>
@@ -26240,8 +26337,11 @@
       <c r="JU33" s="14">
         <v>-671.56428628590004</v>
       </c>
+      <c r="JV33" s="14">
+        <v>259.685421131135</v>
+      </c>
     </row>
-    <row r="34" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
@@ -27085,8 +27185,11 @@
       <c r="JU34" s="14">
         <v>139.919355204916</v>
       </c>
+      <c r="JV34" s="14">
+        <v>-947.68589708695004</v>
+      </c>
     </row>
-    <row r="35" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>35</v>
       </c>
@@ -27930,8 +28033,11 @@
       <c r="JU35" s="14">
         <v>-436.55846836137999</v>
       </c>
+      <c r="JV35" s="14">
+        <v>2995.1892430324501</v>
+      </c>
     </row>
-    <row r="36" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>36</v>
       </c>
@@ -28775,8 +28881,11 @@
       <c r="JU36" s="14">
         <v>-2.9843038147938001</v>
       </c>
+      <c r="JV36" s="14">
+        <v>-2.9883663473469002</v>
+      </c>
     </row>
-    <row r="37" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>23</v>
       </c>
@@ -29620,8 +29729,11 @@
       <c r="JU37" s="14">
         <v>785.346156417673</v>
       </c>
+      <c r="JV37" s="14">
+        <v>3291.5536602663201</v>
+      </c>
     </row>
-    <row r="38" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>33</v>
       </c>
@@ -30465,8 +30577,11 @@
       <c r="JU38" s="14">
         <v>432.722011012834</v>
       </c>
+      <c r="JV38" s="14">
+        <v>-239.39536842384001</v>
+      </c>
     </row>
-    <row r="39" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>34</v>
       </c>
@@ -31310,8 +31425,11 @@
       <c r="JU39" s="14">
         <v>253.444768609097</v>
       </c>
+      <c r="JV39" s="14">
+        <v>1965.1191477923501</v>
+      </c>
     </row>
-    <row r="40" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>35</v>
       </c>
@@ -32155,8 +32273,11 @@
       <c r="JU40" s="14">
         <v>91.483759025203298</v>
       </c>
+      <c r="JV40" s="14">
+        <v>1580.49689118167</v>
+      </c>
     </row>
-    <row r="41" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>37</v>
       </c>
@@ -33000,8 +33121,11 @@
       <c r="JU41" s="14">
         <v>4.5069000000000001E-4</v>
       </c>
+      <c r="JV41" s="14">
+        <v>-7.4927400000000003E-3</v>
+      </c>
     </row>
-    <row r="42" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>38</v>
       </c>
@@ -33845,8 +33969,11 @@
       <c r="JU42" s="14">
         <v>7.6951670805388801</v>
       </c>
+      <c r="JV42" s="14">
+        <v>-14.65951754386</v>
+      </c>
     </row>
-    <row r="43" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>39</v>
       </c>
@@ -34690,293 +34817,297 @@
       <c r="JU43" s="15">
         <v>268.54527029939601</v>
       </c>
+      <c r="JV43" s="15">
+        <v>683.30403373876095</v>
+      </c>
     </row>
-    <row r="44" spans="1:281" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="33" t="s">
+    <row r="44" spans="1:282" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="34"/>
-      <c r="N44" s="34"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="34"/>
-      <c r="W44" s="34"/>
-      <c r="X44" s="34"/>
-      <c r="Y44" s="34"/>
-      <c r="Z44" s="34"/>
-      <c r="AA44" s="34"/>
-      <c r="AB44" s="34"/>
-      <c r="AC44" s="34"/>
-      <c r="AD44" s="34"/>
-      <c r="AE44" s="34"/>
-      <c r="AF44" s="34"/>
-      <c r="AG44" s="34"/>
-      <c r="AH44" s="34"/>
-      <c r="AI44" s="34"/>
-      <c r="AJ44" s="34"/>
-      <c r="AK44" s="34"/>
-      <c r="AL44" s="34"/>
-      <c r="AM44" s="34"/>
-      <c r="AN44" s="34"/>
-      <c r="AO44" s="34"/>
-      <c r="AP44" s="34"/>
-      <c r="AQ44" s="34"/>
-      <c r="AR44" s="34"/>
-      <c r="AS44" s="34"/>
-      <c r="AT44" s="34"/>
-      <c r="AU44" s="34"/>
-      <c r="AV44" s="34"/>
-      <c r="AW44" s="34"/>
-      <c r="AX44" s="34"/>
-      <c r="AY44" s="34"/>
-      <c r="AZ44" s="34"/>
-      <c r="BA44" s="34"/>
-      <c r="BB44" s="34"/>
-      <c r="BC44" s="34"/>
-      <c r="BD44" s="34"/>
-      <c r="BE44" s="34"/>
-      <c r="BF44" s="34"/>
-      <c r="BG44" s="34"/>
-      <c r="BH44" s="34"/>
-      <c r="BI44" s="34"/>
-      <c r="BJ44" s="34"/>
-      <c r="BK44" s="34"/>
-      <c r="BL44" s="34"/>
-      <c r="BM44" s="34"/>
-      <c r="BN44" s="34"/>
-      <c r="BO44" s="34"/>
-      <c r="BP44" s="34"/>
-      <c r="BQ44" s="34"/>
-      <c r="BR44" s="34"/>
-      <c r="BS44" s="34"/>
-      <c r="BT44" s="34"/>
-      <c r="BU44" s="34"/>
-      <c r="BV44" s="34"/>
-      <c r="BW44" s="34"/>
-      <c r="BX44" s="34"/>
-      <c r="BY44" s="34"/>
-      <c r="BZ44" s="34"/>
-      <c r="CA44" s="34"/>
-      <c r="CB44" s="34"/>
-      <c r="CC44" s="34"/>
-      <c r="CD44" s="34"/>
-      <c r="CE44" s="34"/>
-      <c r="CF44" s="34"/>
-      <c r="CG44" s="34"/>
-      <c r="CH44" s="34"/>
-      <c r="CI44" s="34"/>
-      <c r="CJ44" s="34"/>
-      <c r="CK44" s="34"/>
-      <c r="CL44" s="34"/>
-      <c r="CM44" s="34"/>
-      <c r="CN44" s="34"/>
-      <c r="CO44" s="34"/>
-      <c r="CP44" s="34"/>
-      <c r="CQ44" s="34"/>
-      <c r="CR44" s="34"/>
-      <c r="CS44" s="34"/>
-      <c r="CT44" s="34"/>
-      <c r="CU44" s="34"/>
-      <c r="CV44" s="34"/>
-      <c r="CW44" s="34"/>
-      <c r="CX44" s="34"/>
-      <c r="CY44" s="34"/>
-      <c r="CZ44" s="34"/>
-      <c r="DA44" s="34"/>
-      <c r="DB44" s="34"/>
-      <c r="DC44" s="34"/>
-      <c r="DD44" s="34"/>
-      <c r="DE44" s="34"/>
-      <c r="DF44" s="34"/>
-      <c r="DG44" s="34"/>
-      <c r="DH44" s="34"/>
-      <c r="DI44" s="34"/>
-      <c r="DJ44" s="34"/>
-      <c r="DK44" s="34"/>
-      <c r="DL44" s="34"/>
-      <c r="DM44" s="34"/>
-      <c r="DN44" s="34"/>
-      <c r="DO44" s="34"/>
-      <c r="DP44" s="34"/>
-      <c r="DQ44" s="34"/>
-      <c r="DR44" s="34"/>
-      <c r="DS44" s="34"/>
-      <c r="DT44" s="34"/>
-      <c r="DU44" s="34"/>
-      <c r="DV44" s="34"/>
-      <c r="DW44" s="34"/>
-      <c r="DX44" s="34"/>
-      <c r="DY44" s="34"/>
-      <c r="DZ44" s="34"/>
-      <c r="EA44" s="34"/>
-      <c r="EB44" s="34"/>
-      <c r="EC44" s="34"/>
-      <c r="ED44" s="34"/>
-      <c r="EE44" s="34"/>
-      <c r="EF44" s="34"/>
-      <c r="EG44" s="34"/>
-      <c r="EH44" s="34"/>
-      <c r="EI44" s="34"/>
-      <c r="EJ44" s="34"/>
-      <c r="EK44" s="34"/>
-      <c r="EL44" s="34"/>
-      <c r="EM44" s="34"/>
-      <c r="EN44" s="34"/>
-      <c r="EO44" s="34"/>
-      <c r="EP44" s="34"/>
-      <c r="EQ44" s="34"/>
-      <c r="ER44" s="34"/>
-      <c r="ES44" s="34"/>
-      <c r="ET44" s="34"/>
-      <c r="EU44" s="34"/>
-      <c r="EV44" s="34"/>
-      <c r="EW44" s="34"/>
-      <c r="EX44" s="34"/>
-      <c r="EY44" s="34"/>
-      <c r="EZ44" s="34"/>
-      <c r="FA44" s="34"/>
-      <c r="FB44" s="34"/>
-      <c r="FC44" s="34"/>
-      <c r="FD44" s="34"/>
-      <c r="FE44" s="34"/>
-      <c r="FF44" s="34"/>
-      <c r="FG44" s="34"/>
-      <c r="FH44" s="34"/>
-      <c r="FI44" s="34"/>
-      <c r="FJ44" s="34"/>
-      <c r="FK44" s="34"/>
-      <c r="FL44" s="34"/>
-      <c r="FM44" s="34"/>
-      <c r="FN44" s="34"/>
-      <c r="FO44" s="34"/>
-      <c r="FP44" s="34"/>
-      <c r="FQ44" s="34"/>
-      <c r="FR44" s="34"/>
-      <c r="FS44" s="34"/>
-      <c r="FT44" s="34"/>
-      <c r="FU44" s="34"/>
-      <c r="FV44" s="34"/>
-      <c r="FW44" s="34"/>
-      <c r="FX44" s="34"/>
-      <c r="FY44" s="34"/>
-      <c r="FZ44" s="34"/>
-      <c r="GA44" s="34"/>
-      <c r="GB44" s="34"/>
-      <c r="GC44" s="34"/>
-      <c r="GD44" s="34"/>
-      <c r="GE44" s="34"/>
-      <c r="GF44" s="34"/>
-      <c r="GG44" s="34"/>
-      <c r="GH44" s="34"/>
-      <c r="GI44" s="34"/>
-      <c r="GJ44" s="34"/>
-      <c r="GK44" s="34"/>
-      <c r="GL44" s="34"/>
-      <c r="GM44" s="34"/>
-      <c r="GN44" s="34"/>
-      <c r="GO44" s="34"/>
-      <c r="GP44" s="34"/>
-      <c r="GQ44" s="34"/>
-      <c r="GR44" s="34"/>
-      <c r="GS44" s="34"/>
-      <c r="GT44" s="34"/>
-      <c r="GU44" s="34"/>
-      <c r="GV44" s="34"/>
-      <c r="GW44" s="34"/>
-      <c r="GX44" s="34"/>
-      <c r="GY44" s="34"/>
-      <c r="GZ44" s="34"/>
-      <c r="HA44" s="34"/>
-      <c r="HB44" s="34"/>
-      <c r="HC44" s="34"/>
-      <c r="HD44" s="34"/>
-      <c r="HE44" s="34"/>
-      <c r="HF44" s="34"/>
-      <c r="HG44" s="34"/>
-      <c r="HH44" s="34"/>
-      <c r="HI44" s="34"/>
-      <c r="HJ44" s="34"/>
-      <c r="HK44" s="34"/>
-      <c r="HL44" s="34"/>
-      <c r="HM44" s="34"/>
-      <c r="HN44" s="34"/>
-      <c r="HO44" s="34"/>
-      <c r="HP44" s="34"/>
-      <c r="HQ44" s="34"/>
-      <c r="HR44" s="34"/>
-      <c r="HS44" s="34"/>
-      <c r="HT44" s="34"/>
-      <c r="HU44" s="34"/>
-      <c r="HV44" s="34"/>
-      <c r="HW44" s="34"/>
-      <c r="HX44" s="34"/>
-      <c r="HY44" s="34"/>
-      <c r="HZ44" s="34"/>
-      <c r="IA44" s="34"/>
-      <c r="IB44" s="34"/>
-      <c r="IC44" s="34"/>
-      <c r="ID44" s="34"/>
-      <c r="IE44" s="34"/>
-      <c r="IF44" s="34"/>
-      <c r="IG44" s="34"/>
-      <c r="IH44" s="34"/>
-      <c r="II44" s="34"/>
-      <c r="IJ44" s="34"/>
-      <c r="IK44" s="34"/>
-      <c r="IL44" s="34"/>
-      <c r="IM44" s="34"/>
-      <c r="IN44" s="34"/>
-      <c r="IO44" s="34"/>
-      <c r="IP44" s="34"/>
-      <c r="IQ44" s="34"/>
-      <c r="IR44" s="34"/>
-      <c r="IS44" s="34"/>
-      <c r="IT44" s="34"/>
-      <c r="IU44" s="34"/>
-      <c r="IV44" s="34"/>
-      <c r="IW44" s="34"/>
-      <c r="IX44" s="34"/>
-      <c r="IY44" s="34"/>
-      <c r="IZ44" s="34"/>
-      <c r="JA44" s="34"/>
-      <c r="JB44" s="34"/>
-      <c r="JC44" s="34"/>
-      <c r="JD44" s="34"/>
-      <c r="JE44" s="34"/>
-      <c r="JF44" s="34"/>
-      <c r="JG44" s="34"/>
-      <c r="JH44" s="34"/>
-      <c r="JI44" s="34"/>
-      <c r="JJ44" s="34"/>
-      <c r="JK44" s="34"/>
-      <c r="JL44" s="34"/>
-      <c r="JM44" s="34"/>
-      <c r="JN44" s="34"/>
-      <c r="JO44" s="34"/>
-      <c r="JP44" s="34"/>
-      <c r="JQ44" s="34"/>
-      <c r="JR44" s="34"/>
-      <c r="JS44" s="34"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="31"/>
+      <c r="S44" s="31"/>
+      <c r="T44" s="31"/>
+      <c r="U44" s="31"/>
+      <c r="V44" s="31"/>
+      <c r="W44" s="31"/>
+      <c r="X44" s="31"/>
+      <c r="Y44" s="31"/>
+      <c r="Z44" s="31"/>
+      <c r="AA44" s="31"/>
+      <c r="AB44" s="31"/>
+      <c r="AC44" s="31"/>
+      <c r="AD44" s="31"/>
+      <c r="AE44" s="31"/>
+      <c r="AF44" s="31"/>
+      <c r="AG44" s="31"/>
+      <c r="AH44" s="31"/>
+      <c r="AI44" s="31"/>
+      <c r="AJ44" s="31"/>
+      <c r="AK44" s="31"/>
+      <c r="AL44" s="31"/>
+      <c r="AM44" s="31"/>
+      <c r="AN44" s="31"/>
+      <c r="AO44" s="31"/>
+      <c r="AP44" s="31"/>
+      <c r="AQ44" s="31"/>
+      <c r="AR44" s="31"/>
+      <c r="AS44" s="31"/>
+      <c r="AT44" s="31"/>
+      <c r="AU44" s="31"/>
+      <c r="AV44" s="31"/>
+      <c r="AW44" s="31"/>
+      <c r="AX44" s="31"/>
+      <c r="AY44" s="31"/>
+      <c r="AZ44" s="31"/>
+      <c r="BA44" s="31"/>
+      <c r="BB44" s="31"/>
+      <c r="BC44" s="31"/>
+      <c r="BD44" s="31"/>
+      <c r="BE44" s="31"/>
+      <c r="BF44" s="31"/>
+      <c r="BG44" s="31"/>
+      <c r="BH44" s="31"/>
+      <c r="BI44" s="31"/>
+      <c r="BJ44" s="31"/>
+      <c r="BK44" s="31"/>
+      <c r="BL44" s="31"/>
+      <c r="BM44" s="31"/>
+      <c r="BN44" s="31"/>
+      <c r="BO44" s="31"/>
+      <c r="BP44" s="31"/>
+      <c r="BQ44" s="31"/>
+      <c r="BR44" s="31"/>
+      <c r="BS44" s="31"/>
+      <c r="BT44" s="31"/>
+      <c r="BU44" s="31"/>
+      <c r="BV44" s="31"/>
+      <c r="BW44" s="31"/>
+      <c r="BX44" s="31"/>
+      <c r="BY44" s="31"/>
+      <c r="BZ44" s="31"/>
+      <c r="CA44" s="31"/>
+      <c r="CB44" s="31"/>
+      <c r="CC44" s="31"/>
+      <c r="CD44" s="31"/>
+      <c r="CE44" s="31"/>
+      <c r="CF44" s="31"/>
+      <c r="CG44" s="31"/>
+      <c r="CH44" s="31"/>
+      <c r="CI44" s="31"/>
+      <c r="CJ44" s="31"/>
+      <c r="CK44" s="31"/>
+      <c r="CL44" s="31"/>
+      <c r="CM44" s="31"/>
+      <c r="CN44" s="31"/>
+      <c r="CO44" s="31"/>
+      <c r="CP44" s="31"/>
+      <c r="CQ44" s="31"/>
+      <c r="CR44" s="31"/>
+      <c r="CS44" s="31"/>
+      <c r="CT44" s="31"/>
+      <c r="CU44" s="31"/>
+      <c r="CV44" s="31"/>
+      <c r="CW44" s="31"/>
+      <c r="CX44" s="31"/>
+      <c r="CY44" s="31"/>
+      <c r="CZ44" s="31"/>
+      <c r="DA44" s="31"/>
+      <c r="DB44" s="31"/>
+      <c r="DC44" s="31"/>
+      <c r="DD44" s="31"/>
+      <c r="DE44" s="31"/>
+      <c r="DF44" s="31"/>
+      <c r="DG44" s="31"/>
+      <c r="DH44" s="31"/>
+      <c r="DI44" s="31"/>
+      <c r="DJ44" s="31"/>
+      <c r="DK44" s="31"/>
+      <c r="DL44" s="31"/>
+      <c r="DM44" s="31"/>
+      <c r="DN44" s="31"/>
+      <c r="DO44" s="31"/>
+      <c r="DP44" s="31"/>
+      <c r="DQ44" s="31"/>
+      <c r="DR44" s="31"/>
+      <c r="DS44" s="31"/>
+      <c r="DT44" s="31"/>
+      <c r="DU44" s="31"/>
+      <c r="DV44" s="31"/>
+      <c r="DW44" s="31"/>
+      <c r="DX44" s="31"/>
+      <c r="DY44" s="31"/>
+      <c r="DZ44" s="31"/>
+      <c r="EA44" s="31"/>
+      <c r="EB44" s="31"/>
+      <c r="EC44" s="31"/>
+      <c r="ED44" s="31"/>
+      <c r="EE44" s="31"/>
+      <c r="EF44" s="31"/>
+      <c r="EG44" s="31"/>
+      <c r="EH44" s="31"/>
+      <c r="EI44" s="31"/>
+      <c r="EJ44" s="31"/>
+      <c r="EK44" s="31"/>
+      <c r="EL44" s="31"/>
+      <c r="EM44" s="31"/>
+      <c r="EN44" s="31"/>
+      <c r="EO44" s="31"/>
+      <c r="EP44" s="31"/>
+      <c r="EQ44" s="31"/>
+      <c r="ER44" s="31"/>
+      <c r="ES44" s="31"/>
+      <c r="ET44" s="31"/>
+      <c r="EU44" s="31"/>
+      <c r="EV44" s="31"/>
+      <c r="EW44" s="31"/>
+      <c r="EX44" s="31"/>
+      <c r="EY44" s="31"/>
+      <c r="EZ44" s="31"/>
+      <c r="FA44" s="31"/>
+      <c r="FB44" s="31"/>
+      <c r="FC44" s="31"/>
+      <c r="FD44" s="31"/>
+      <c r="FE44" s="31"/>
+      <c r="FF44" s="31"/>
+      <c r="FG44" s="31"/>
+      <c r="FH44" s="31"/>
+      <c r="FI44" s="31"/>
+      <c r="FJ44" s="31"/>
+      <c r="FK44" s="31"/>
+      <c r="FL44" s="31"/>
+      <c r="FM44" s="31"/>
+      <c r="FN44" s="31"/>
+      <c r="FO44" s="31"/>
+      <c r="FP44" s="31"/>
+      <c r="FQ44" s="31"/>
+      <c r="FR44" s="31"/>
+      <c r="FS44" s="31"/>
+      <c r="FT44" s="31"/>
+      <c r="FU44" s="31"/>
+      <c r="FV44" s="31"/>
+      <c r="FW44" s="31"/>
+      <c r="FX44" s="31"/>
+      <c r="FY44" s="31"/>
+      <c r="FZ44" s="31"/>
+      <c r="GA44" s="31"/>
+      <c r="GB44" s="31"/>
+      <c r="GC44" s="31"/>
+      <c r="GD44" s="31"/>
+      <c r="GE44" s="31"/>
+      <c r="GF44" s="31"/>
+      <c r="GG44" s="31"/>
+      <c r="GH44" s="31"/>
+      <c r="GI44" s="31"/>
+      <c r="GJ44" s="31"/>
+      <c r="GK44" s="31"/>
+      <c r="GL44" s="31"/>
+      <c r="GM44" s="31"/>
+      <c r="GN44" s="31"/>
+      <c r="GO44" s="31"/>
+      <c r="GP44" s="31"/>
+      <c r="GQ44" s="31"/>
+      <c r="GR44" s="31"/>
+      <c r="GS44" s="31"/>
+      <c r="GT44" s="31"/>
+      <c r="GU44" s="31"/>
+      <c r="GV44" s="31"/>
+      <c r="GW44" s="31"/>
+      <c r="GX44" s="31"/>
+      <c r="GY44" s="31"/>
+      <c r="GZ44" s="31"/>
+      <c r="HA44" s="31"/>
+      <c r="HB44" s="31"/>
+      <c r="HC44" s="31"/>
+      <c r="HD44" s="31"/>
+      <c r="HE44" s="31"/>
+      <c r="HF44" s="31"/>
+      <c r="HG44" s="31"/>
+      <c r="HH44" s="31"/>
+      <c r="HI44" s="31"/>
+      <c r="HJ44" s="31"/>
+      <c r="HK44" s="31"/>
+      <c r="HL44" s="31"/>
+      <c r="HM44" s="31"/>
+      <c r="HN44" s="31"/>
+      <c r="HO44" s="31"/>
+      <c r="HP44" s="31"/>
+      <c r="HQ44" s="31"/>
+      <c r="HR44" s="31"/>
+      <c r="HS44" s="31"/>
+      <c r="HT44" s="31"/>
+      <c r="HU44" s="31"/>
+      <c r="HV44" s="31"/>
+      <c r="HW44" s="31"/>
+      <c r="HX44" s="31"/>
+      <c r="HY44" s="31"/>
+      <c r="HZ44" s="31"/>
+      <c r="IA44" s="31"/>
+      <c r="IB44" s="31"/>
+      <c r="IC44" s="31"/>
+      <c r="ID44" s="31"/>
+      <c r="IE44" s="31"/>
+      <c r="IF44" s="31"/>
+      <c r="IG44" s="31"/>
+      <c r="IH44" s="31"/>
+      <c r="II44" s="31"/>
+      <c r="IJ44" s="31"/>
+      <c r="IK44" s="31"/>
+      <c r="IL44" s="31"/>
+      <c r="IM44" s="31"/>
+      <c r="IN44" s="31"/>
+      <c r="IO44" s="31"/>
+      <c r="IP44" s="31"/>
+      <c r="IQ44" s="31"/>
+      <c r="IR44" s="31"/>
+      <c r="IS44" s="31"/>
+      <c r="IT44" s="31"/>
+      <c r="IU44" s="31"/>
+      <c r="IV44" s="31"/>
+      <c r="IW44" s="31"/>
+      <c r="IX44" s="31"/>
+      <c r="IY44" s="31"/>
+      <c r="IZ44" s="31"/>
+      <c r="JA44" s="31"/>
+      <c r="JB44" s="31"/>
+      <c r="JC44" s="31"/>
+      <c r="JD44" s="31"/>
+      <c r="JE44" s="31"/>
+      <c r="JF44" s="31"/>
+      <c r="JG44" s="31"/>
+      <c r="JH44" s="31"/>
+      <c r="JI44" s="31"/>
+      <c r="JJ44" s="31"/>
+      <c r="JK44" s="31"/>
+      <c r="JL44" s="31"/>
+      <c r="JM44" s="31"/>
+      <c r="JN44" s="31"/>
+      <c r="JO44" s="31"/>
+      <c r="JP44" s="31"/>
+      <c r="JQ44" s="31"/>
+      <c r="JR44" s="31"/>
+      <c r="JS44" s="31"/>
       <c r="JT44" s="1"/>
       <c r="JU44" s="26"/>
+      <c r="JV44" s="1"/>
     </row>
-    <row r="45" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="21" t="s">
         <v>41</v>
       </c>
@@ -35820,8 +35951,11 @@
       <c r="JU45" s="16">
         <v>-4679.4795991893998</v>
       </c>
+      <c r="JV45" s="16">
+        <v>-4783.3302892722004</v>
+      </c>
     </row>
-    <row r="46" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="23" t="s">
         <v>42</v>
       </c>
@@ -36665,8 +36799,11 @@
       <c r="JU46" s="17">
         <v>2168.3584395643102</v>
       </c>
+      <c r="JV46" s="17">
+        <v>2530.5591253528601</v>
+      </c>
     </row>
-    <row r="47" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="23" t="s">
         <v>26</v>
       </c>
@@ -37510,8 +37647,11 @@
       <c r="JU47" s="17">
         <v>2040.55541493484</v>
       </c>
+      <c r="JV47" s="17">
+        <v>2929.28941396049</v>
+      </c>
     </row>
-    <row r="48" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="23" t="s">
         <v>43</v>
       </c>
@@ -38355,8 +38495,11 @@
       <c r="JU48" s="17">
         <v>1529.6102030053501</v>
       </c>
+      <c r="JV48" s="17">
+        <v>230.34358916908499</v>
+      </c>
     </row>
-    <row r="49" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="23" t="s">
         <v>45</v>
       </c>
@@ -39200,8 +39343,11 @@
       <c r="JU49" s="17">
         <v>510.94521192949298</v>
       </c>
+      <c r="JV49" s="17">
+        <v>2698.9458247913999</v>
+      </c>
     </row>
-    <row r="50" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="23" t="s">
         <v>25</v>
       </c>
@@ -40045,8 +40191,11 @@
       <c r="JU50" s="17">
         <v>127.803024629465</v>
       </c>
+      <c r="JV50" s="17">
+        <v>-398.73028860762003</v>
+      </c>
     </row>
-    <row r="51" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="23" t="s">
         <v>46</v>
       </c>
@@ -40890,8 +41039,11 @@
       <c r="JU51" s="17">
         <v>24.918333942348401</v>
       </c>
+      <c r="JV51" s="17">
+        <v>-177.81079379556999</v>
+      </c>
     </row>
-    <row r="52" spans="1:281" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:282" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="24" t="s">
         <v>47</v>
       </c>
@@ -41735,306 +41887,298 @@
       <c r="JU52" s="18">
         <v>102.884690687117</v>
       </c>
+      <c r="JV52" s="18">
+        <v>-220.91949481206001</v>
+      </c>
     </row>
-    <row r="54" spans="1:281" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="31" t="s">
+    <row r="54" spans="1:282" ht="9.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
-      <c r="N54" s="31"/>
-      <c r="O54" s="31"/>
-      <c r="P54" s="31"/>
-      <c r="Q54" s="31"/>
-      <c r="R54" s="31"/>
-      <c r="S54" s="31"/>
-      <c r="T54" s="31"/>
-      <c r="U54" s="31"/>
-      <c r="V54" s="31"/>
-      <c r="W54" s="31"/>
-      <c r="X54" s="31"/>
-      <c r="Y54" s="31"/>
-      <c r="Z54" s="31"/>
-      <c r="AA54" s="31"/>
-      <c r="AB54" s="31"/>
-      <c r="AC54" s="31"/>
-      <c r="AD54" s="31"/>
-      <c r="AE54" s="31"/>
-      <c r="AF54" s="31"/>
-      <c r="AG54" s="31"/>
-      <c r="AH54" s="31"/>
-      <c r="AI54" s="31"/>
-      <c r="AJ54" s="31"/>
-      <c r="AK54" s="31"/>
-      <c r="AL54" s="31"/>
-      <c r="AM54" s="31"/>
-      <c r="AN54" s="31"/>
-      <c r="AO54" s="31"/>
-      <c r="AP54" s="31"/>
-      <c r="AQ54" s="31"/>
-      <c r="AR54" s="31"/>
-      <c r="AS54" s="31"/>
-      <c r="AT54" s="31"/>
-      <c r="AU54" s="31"/>
-      <c r="AV54" s="31"/>
-      <c r="AW54" s="31"/>
-      <c r="AX54" s="31"/>
-      <c r="AY54" s="31"/>
-      <c r="AZ54" s="31"/>
-      <c r="BA54" s="31"/>
-      <c r="BB54" s="31"/>
-      <c r="BC54" s="31"/>
-      <c r="BD54" s="31"/>
-      <c r="BE54" s="31"/>
-      <c r="BF54" s="31"/>
-      <c r="BG54" s="31"/>
-      <c r="BH54" s="31"/>
-      <c r="BI54" s="31"/>
-      <c r="BJ54" s="31"/>
-      <c r="BK54" s="31"/>
-      <c r="BL54" s="31"/>
-      <c r="BM54" s="31"/>
-      <c r="BN54" s="31"/>
-      <c r="BO54" s="31"/>
-      <c r="BP54" s="31"/>
-      <c r="BQ54" s="31"/>
-      <c r="BR54" s="31"/>
-      <c r="BS54" s="31"/>
-      <c r="BT54" s="31"/>
-      <c r="BU54" s="31"/>
-      <c r="BV54" s="31"/>
-      <c r="BW54" s="31"/>
-      <c r="BX54" s="31"/>
-      <c r="BY54" s="31"/>
-      <c r="BZ54" s="31"/>
-      <c r="CA54" s="31"/>
-      <c r="CB54" s="31"/>
-      <c r="CC54" s="31"/>
-      <c r="CD54" s="31"/>
-      <c r="CE54" s="31"/>
-      <c r="CF54" s="31"/>
-      <c r="CG54" s="31"/>
-      <c r="CH54" s="31"/>
-      <c r="CI54" s="31"/>
-      <c r="CJ54" s="31"/>
-      <c r="CK54" s="31"/>
-      <c r="CL54" s="31"/>
-      <c r="CM54" s="31"/>
-      <c r="CN54" s="31"/>
-      <c r="CO54" s="31"/>
-      <c r="CP54" s="31"/>
-      <c r="CQ54" s="31"/>
-      <c r="CR54" s="31"/>
-      <c r="CS54" s="31"/>
-      <c r="CT54" s="31"/>
-      <c r="CU54" s="31"/>
-      <c r="CV54" s="31"/>
-      <c r="CW54" s="31"/>
-      <c r="CX54" s="31"/>
-      <c r="CY54" s="31"/>
-      <c r="CZ54" s="31"/>
-      <c r="DA54" s="31"/>
-      <c r="DB54" s="31"/>
-      <c r="DC54" s="31"/>
-      <c r="DD54" s="31"/>
-      <c r="DE54" s="31"/>
-      <c r="DF54" s="31"/>
-      <c r="DG54" s="31"/>
-      <c r="DH54" s="31"/>
-      <c r="DI54" s="31"/>
-      <c r="DJ54" s="31"/>
-      <c r="DK54" s="31"/>
-      <c r="DL54" s="31"/>
-      <c r="DM54" s="31"/>
-      <c r="DN54" s="31"/>
-      <c r="DO54" s="31"/>
-      <c r="DP54" s="31"/>
-      <c r="DQ54" s="31"/>
-      <c r="DR54" s="31"/>
-      <c r="DS54" s="31"/>
-      <c r="DT54" s="31"/>
-      <c r="DU54" s="31"/>
-      <c r="DV54" s="31"/>
-      <c r="DW54" s="31"/>
-      <c r="DX54" s="31"/>
-      <c r="DY54" s="31"/>
-      <c r="DZ54" s="31"/>
-      <c r="EA54" s="31"/>
-      <c r="EB54" s="31"/>
-      <c r="EC54" s="31"/>
-      <c r="ED54" s="31"/>
-      <c r="EE54" s="31"/>
-      <c r="EF54" s="31"/>
-      <c r="EG54" s="31"/>
-      <c r="EH54" s="31"/>
-      <c r="EI54" s="31"/>
-      <c r="EJ54" s="31"/>
-      <c r="EK54" s="31"/>
-      <c r="EL54" s="31"/>
-      <c r="EM54" s="31"/>
-      <c r="EN54" s="31"/>
-      <c r="EO54" s="31"/>
-      <c r="EP54" s="31"/>
-      <c r="EQ54" s="31"/>
-      <c r="ER54" s="31"/>
-      <c r="ES54" s="31"/>
-      <c r="ET54" s="31"/>
-      <c r="EU54" s="31"/>
-      <c r="EV54" s="31"/>
-      <c r="EW54" s="31"/>
-      <c r="EX54" s="31"/>
-      <c r="EY54" s="31"/>
-      <c r="EZ54" s="31"/>
-      <c r="FA54" s="31"/>
-      <c r="FB54" s="31"/>
-      <c r="FC54" s="31"/>
-      <c r="FD54" s="31"/>
-      <c r="FE54" s="31"/>
-      <c r="FF54" s="31"/>
-      <c r="FG54" s="31"/>
-      <c r="FH54" s="31"/>
-      <c r="FI54" s="31"/>
-      <c r="FJ54" s="31"/>
-      <c r="FK54" s="31"/>
-      <c r="FL54" s="31"/>
-      <c r="FM54" s="31"/>
-      <c r="FN54" s="31"/>
-      <c r="FO54" s="31"/>
-      <c r="FP54" s="31"/>
-      <c r="FQ54" s="31"/>
-      <c r="FR54" s="31"/>
-      <c r="FS54" s="31"/>
-      <c r="FT54" s="31"/>
-      <c r="FU54" s="31"/>
-      <c r="FV54" s="31"/>
-      <c r="FW54" s="31"/>
-      <c r="FX54" s="31"/>
-      <c r="FY54" s="31"/>
-      <c r="FZ54" s="31"/>
-      <c r="GA54" s="31"/>
-      <c r="GB54" s="31"/>
-      <c r="GC54" s="31"/>
-      <c r="GD54" s="31"/>
-      <c r="GE54" s="31"/>
-      <c r="GF54" s="31"/>
-      <c r="GG54" s="31"/>
-      <c r="GH54" s="31"/>
-      <c r="GI54" s="31"/>
-      <c r="GJ54" s="31"/>
-      <c r="GK54" s="31"/>
-      <c r="GL54" s="31"/>
-      <c r="GM54" s="31"/>
-      <c r="GN54" s="31"/>
-      <c r="GO54" s="31"/>
-      <c r="GP54" s="31"/>
-      <c r="GQ54" s="31"/>
-      <c r="GR54" s="31"/>
-      <c r="GS54" s="31"/>
-      <c r="GT54" s="31"/>
-      <c r="GU54" s="31"/>
-      <c r="GV54" s="31"/>
-      <c r="GW54" s="31"/>
-      <c r="GX54" s="31"/>
-      <c r="GY54" s="31"/>
-      <c r="GZ54" s="31"/>
-      <c r="HA54" s="31"/>
-      <c r="HB54" s="31"/>
-      <c r="HC54" s="31"/>
-      <c r="HD54" s="31"/>
-      <c r="HE54" s="31"/>
-      <c r="HF54" s="31"/>
-      <c r="HG54" s="31"/>
-      <c r="HH54" s="31"/>
-      <c r="HI54" s="31"/>
-      <c r="HJ54" s="31"/>
-      <c r="HK54" s="31"/>
-      <c r="HL54" s="31"/>
-      <c r="HM54" s="31"/>
-      <c r="HN54" s="31"/>
-      <c r="HO54" s="31"/>
-      <c r="HP54" s="31"/>
-      <c r="HQ54" s="31"/>
-      <c r="HR54" s="31"/>
-      <c r="HS54" s="31"/>
-      <c r="HT54" s="31"/>
-      <c r="HU54" s="31"/>
-      <c r="HV54" s="31"/>
-      <c r="HW54" s="31"/>
-      <c r="HX54" s="31"/>
-      <c r="HY54" s="31"/>
-      <c r="HZ54" s="31"/>
-      <c r="IA54" s="31"/>
-      <c r="IB54" s="31"/>
-      <c r="IC54" s="31"/>
-      <c r="ID54" s="31"/>
-      <c r="IE54" s="31"/>
-      <c r="IF54" s="31"/>
-      <c r="IG54" s="31"/>
-      <c r="IH54" s="31"/>
-      <c r="II54" s="31"/>
-      <c r="IJ54" s="31"/>
-      <c r="IK54" s="31"/>
-      <c r="IL54" s="31"/>
-      <c r="IM54" s="31"/>
-      <c r="IN54" s="31"/>
-      <c r="IO54" s="31"/>
-      <c r="IP54" s="31"/>
-      <c r="IQ54" s="31"/>
-      <c r="IR54" s="31"/>
-      <c r="IS54" s="31"/>
-      <c r="IT54" s="31"/>
-      <c r="IU54" s="31"/>
-      <c r="IV54" s="31"/>
-      <c r="IW54" s="31"/>
-      <c r="IX54" s="31"/>
-      <c r="IY54" s="31"/>
-      <c r="IZ54" s="31"/>
-      <c r="JA54" s="31"/>
-      <c r="JB54" s="31"/>
-      <c r="JC54" s="31"/>
-      <c r="JD54" s="31"/>
-      <c r="JE54" s="31"/>
-      <c r="JF54" s="31"/>
-      <c r="JG54" s="31"/>
-      <c r="JH54" s="31"/>
-      <c r="JI54" s="31"/>
-      <c r="JJ54" s="31"/>
-      <c r="JK54" s="31"/>
-      <c r="JL54" s="31"/>
-      <c r="JM54" s="31"/>
-      <c r="JN54" s="31"/>
-      <c r="JO54" s="31"/>
-      <c r="JP54" s="31"/>
-      <c r="JQ54" s="31"/>
-      <c r="JR54" s="31"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="27"/>
+      <c r="K54" s="27"/>
+      <c r="L54" s="27"/>
+      <c r="M54" s="27"/>
+      <c r="N54" s="27"/>
+      <c r="O54" s="27"/>
+      <c r="P54" s="27"/>
+      <c r="Q54" s="27"/>
+      <c r="R54" s="27"/>
+      <c r="S54" s="27"/>
+      <c r="T54" s="27"/>
+      <c r="U54" s="27"/>
+      <c r="V54" s="27"/>
+      <c r="W54" s="27"/>
+      <c r="X54" s="27"/>
+      <c r="Y54" s="27"/>
+      <c r="Z54" s="27"/>
+      <c r="AA54" s="27"/>
+      <c r="AB54" s="27"/>
+      <c r="AC54" s="27"/>
+      <c r="AD54" s="27"/>
+      <c r="AE54" s="27"/>
+      <c r="AF54" s="27"/>
+      <c r="AG54" s="27"/>
+      <c r="AH54" s="27"/>
+      <c r="AI54" s="27"/>
+      <c r="AJ54" s="27"/>
+      <c r="AK54" s="27"/>
+      <c r="AL54" s="27"/>
+      <c r="AM54" s="27"/>
+      <c r="AN54" s="27"/>
+      <c r="AO54" s="27"/>
+      <c r="AP54" s="27"/>
+      <c r="AQ54" s="27"/>
+      <c r="AR54" s="27"/>
+      <c r="AS54" s="27"/>
+      <c r="AT54" s="27"/>
+      <c r="AU54" s="27"/>
+      <c r="AV54" s="27"/>
+      <c r="AW54" s="27"/>
+      <c r="AX54" s="27"/>
+      <c r="AY54" s="27"/>
+      <c r="AZ54" s="27"/>
+      <c r="BA54" s="27"/>
+      <c r="BB54" s="27"/>
+      <c r="BC54" s="27"/>
+      <c r="BD54" s="27"/>
+      <c r="BE54" s="27"/>
+      <c r="BF54" s="27"/>
+      <c r="BG54" s="27"/>
+      <c r="BH54" s="27"/>
+      <c r="BI54" s="27"/>
+      <c r="BJ54" s="27"/>
+      <c r="BK54" s="27"/>
+      <c r="BL54" s="27"/>
+      <c r="BM54" s="27"/>
+      <c r="BN54" s="27"/>
+      <c r="BO54" s="27"/>
+      <c r="BP54" s="27"/>
+      <c r="BQ54" s="27"/>
+      <c r="BR54" s="27"/>
+      <c r="BS54" s="27"/>
+      <c r="BT54" s="27"/>
+      <c r="BU54" s="27"/>
+      <c r="BV54" s="27"/>
+      <c r="BW54" s="27"/>
+      <c r="BX54" s="27"/>
+      <c r="BY54" s="27"/>
+      <c r="BZ54" s="27"/>
+      <c r="CA54" s="27"/>
+      <c r="CB54" s="27"/>
+      <c r="CC54" s="27"/>
+      <c r="CD54" s="27"/>
+      <c r="CE54" s="27"/>
+      <c r="CF54" s="27"/>
+      <c r="CG54" s="27"/>
+      <c r="CH54" s="27"/>
+      <c r="CI54" s="27"/>
+      <c r="CJ54" s="27"/>
+      <c r="CK54" s="27"/>
+      <c r="CL54" s="27"/>
+      <c r="CM54" s="27"/>
+      <c r="CN54" s="27"/>
+      <c r="CO54" s="27"/>
+      <c r="CP54" s="27"/>
+      <c r="CQ54" s="27"/>
+      <c r="CR54" s="27"/>
+      <c r="CS54" s="27"/>
+      <c r="CT54" s="27"/>
+      <c r="CU54" s="27"/>
+      <c r="CV54" s="27"/>
+      <c r="CW54" s="27"/>
+      <c r="CX54" s="27"/>
+      <c r="CY54" s="27"/>
+      <c r="CZ54" s="27"/>
+      <c r="DA54" s="27"/>
+      <c r="DB54" s="27"/>
+      <c r="DC54" s="27"/>
+      <c r="DD54" s="27"/>
+      <c r="DE54" s="27"/>
+      <c r="DF54" s="27"/>
+      <c r="DG54" s="27"/>
+      <c r="DH54" s="27"/>
+      <c r="DI54" s="27"/>
+      <c r="DJ54" s="27"/>
+      <c r="DK54" s="27"/>
+      <c r="DL54" s="27"/>
+      <c r="DM54" s="27"/>
+      <c r="DN54" s="27"/>
+      <c r="DO54" s="27"/>
+      <c r="DP54" s="27"/>
+      <c r="DQ54" s="27"/>
+      <c r="DR54" s="27"/>
+      <c r="DS54" s="27"/>
+      <c r="DT54" s="27"/>
+      <c r="DU54" s="27"/>
+      <c r="DV54" s="27"/>
+      <c r="DW54" s="27"/>
+      <c r="DX54" s="27"/>
+      <c r="DY54" s="27"/>
+      <c r="DZ54" s="27"/>
+      <c r="EA54" s="27"/>
+      <c r="EB54" s="27"/>
+      <c r="EC54" s="27"/>
+      <c r="ED54" s="27"/>
+      <c r="EE54" s="27"/>
+      <c r="EF54" s="27"/>
+      <c r="EG54" s="27"/>
+      <c r="EH54" s="27"/>
+      <c r="EI54" s="27"/>
+      <c r="EJ54" s="27"/>
+      <c r="EK54" s="27"/>
+      <c r="EL54" s="27"/>
+      <c r="EM54" s="27"/>
+      <c r="EN54" s="27"/>
+      <c r="EO54" s="27"/>
+      <c r="EP54" s="27"/>
+      <c r="EQ54" s="27"/>
+      <c r="ER54" s="27"/>
+      <c r="ES54" s="27"/>
+      <c r="ET54" s="27"/>
+      <c r="EU54" s="27"/>
+      <c r="EV54" s="27"/>
+      <c r="EW54" s="27"/>
+      <c r="EX54" s="27"/>
+      <c r="EY54" s="27"/>
+      <c r="EZ54" s="27"/>
+      <c r="FA54" s="27"/>
+      <c r="FB54" s="27"/>
+      <c r="FC54" s="27"/>
+      <c r="FD54" s="27"/>
+      <c r="FE54" s="27"/>
+      <c r="FF54" s="27"/>
+      <c r="FG54" s="27"/>
+      <c r="FH54" s="27"/>
+      <c r="FI54" s="27"/>
+      <c r="FJ54" s="27"/>
+      <c r="FK54" s="27"/>
+      <c r="FL54" s="27"/>
+      <c r="FM54" s="27"/>
+      <c r="FN54" s="27"/>
+      <c r="FO54" s="27"/>
+      <c r="FP54" s="27"/>
+      <c r="FQ54" s="27"/>
+      <c r="FR54" s="27"/>
+      <c r="FS54" s="27"/>
+      <c r="FT54" s="27"/>
+      <c r="FU54" s="27"/>
+      <c r="FV54" s="27"/>
+      <c r="FW54" s="27"/>
+      <c r="FX54" s="27"/>
+      <c r="FY54" s="27"/>
+      <c r="FZ54" s="27"/>
+      <c r="GA54" s="27"/>
+      <c r="GB54" s="27"/>
+      <c r="GC54" s="27"/>
+      <c r="GD54" s="27"/>
+      <c r="GE54" s="27"/>
+      <c r="GF54" s="27"/>
+      <c r="GG54" s="27"/>
+      <c r="GH54" s="27"/>
+      <c r="GI54" s="27"/>
+      <c r="GJ54" s="27"/>
+      <c r="GK54" s="27"/>
+      <c r="GL54" s="27"/>
+      <c r="GM54" s="27"/>
+      <c r="GN54" s="27"/>
+      <c r="GO54" s="27"/>
+      <c r="GP54" s="27"/>
+      <c r="GQ54" s="27"/>
+      <c r="GR54" s="27"/>
+      <c r="GS54" s="27"/>
+      <c r="GT54" s="27"/>
+      <c r="GU54" s="27"/>
+      <c r="GV54" s="27"/>
+      <c r="GW54" s="27"/>
+      <c r="GX54" s="27"/>
+      <c r="GY54" s="27"/>
+      <c r="GZ54" s="27"/>
+      <c r="HA54" s="27"/>
+      <c r="HB54" s="27"/>
+      <c r="HC54" s="27"/>
+      <c r="HD54" s="27"/>
+      <c r="HE54" s="27"/>
+      <c r="HF54" s="27"/>
+      <c r="HG54" s="27"/>
+      <c r="HH54" s="27"/>
+      <c r="HI54" s="27"/>
+      <c r="HJ54" s="27"/>
+      <c r="HK54" s="27"/>
+      <c r="HL54" s="27"/>
+      <c r="HM54" s="27"/>
+      <c r="HN54" s="27"/>
+      <c r="HO54" s="27"/>
+      <c r="HP54" s="27"/>
+      <c r="HQ54" s="27"/>
+      <c r="HR54" s="27"/>
+      <c r="HS54" s="27"/>
+      <c r="HT54" s="27"/>
+      <c r="HU54" s="27"/>
+      <c r="HV54" s="27"/>
+      <c r="HW54" s="27"/>
+      <c r="HX54" s="27"/>
+      <c r="HY54" s="27"/>
+      <c r="HZ54" s="27"/>
+      <c r="IA54" s="27"/>
+      <c r="IB54" s="27"/>
+      <c r="IC54" s="27"/>
+      <c r="ID54" s="27"/>
+      <c r="IE54" s="27"/>
+      <c r="IF54" s="27"/>
+      <c r="IG54" s="27"/>
+      <c r="IH54" s="27"/>
+      <c r="II54" s="27"/>
+      <c r="IJ54" s="27"/>
+      <c r="IK54" s="27"/>
+      <c r="IL54" s="27"/>
+      <c r="IM54" s="27"/>
+      <c r="IN54" s="27"/>
+      <c r="IO54" s="27"/>
+      <c r="IP54" s="27"/>
+      <c r="IQ54" s="27"/>
+      <c r="IR54" s="27"/>
+      <c r="IS54" s="27"/>
+      <c r="IT54" s="27"/>
+      <c r="IU54" s="27"/>
+      <c r="IV54" s="27"/>
+      <c r="IW54" s="27"/>
+      <c r="IX54" s="27"/>
+      <c r="IY54" s="27"/>
+      <c r="IZ54" s="27"/>
+      <c r="JA54" s="27"/>
+      <c r="JB54" s="27"/>
+      <c r="JC54" s="27"/>
+      <c r="JD54" s="27"/>
+      <c r="JE54" s="27"/>
+      <c r="JF54" s="27"/>
+      <c r="JG54" s="27"/>
+      <c r="JH54" s="27"/>
+      <c r="JI54" s="27"/>
+      <c r="JJ54" s="27"/>
+      <c r="JK54" s="27"/>
+      <c r="JL54" s="27"/>
+      <c r="JM54" s="27"/>
+      <c r="JN54" s="27"/>
+      <c r="JO54" s="27"/>
+      <c r="JP54" s="27"/>
+      <c r="JQ54" s="27"/>
+      <c r="JR54" s="27"/>
       <c r="JS54" s="10"/>
       <c r="JT54" s="10"/>
       <c r="JU54" s="10"/>
+      <c r="JV54" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A54:JR54"/>
-    <mergeCell ref="IH4:IS4"/>
-    <mergeCell ref="IT4:JE4"/>
-    <mergeCell ref="JF4:JQ4"/>
-    <mergeCell ref="DF4:DQ4"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="N4:Y4"/>
-    <mergeCell ref="Z4:AK4"/>
-    <mergeCell ref="AL4:AW4"/>
-    <mergeCell ref="AX4:BI4"/>
-    <mergeCell ref="A44:JS44"/>
-    <mergeCell ref="JR4:JU4"/>
     <mergeCell ref="A1:JR1"/>
     <mergeCell ref="A2:JR2"/>
     <mergeCell ref="FZ4:GK4"/>
@@ -42051,6 +42195,18 @@
     <mergeCell ref="BV4:CG4"/>
     <mergeCell ref="CH4:CS4"/>
     <mergeCell ref="CT4:DE4"/>
+    <mergeCell ref="A54:JR54"/>
+    <mergeCell ref="IH4:IS4"/>
+    <mergeCell ref="IT4:JE4"/>
+    <mergeCell ref="JF4:JQ4"/>
+    <mergeCell ref="DF4:DQ4"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="Z4:AK4"/>
+    <mergeCell ref="AL4:AW4"/>
+    <mergeCell ref="AX4:BI4"/>
+    <mergeCell ref="A44:JS44"/>
+    <mergeCell ref="JR4:JV4"/>
   </mergeCells>
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -42060,74 +42216,74 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="23" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="23" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
     </row>
     <row r="2" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
     </row>
     <row r="4" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -42203,7 +42359,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -42277,7 +42433,7 @@
         <v>-6159.5439456127997</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -42351,7 +42507,7 @@
         <v>12270.3555343112</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -42425,7 +42581,7 @@
         <v>18429.899479923999</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -42499,7 +42655,7 @@
         <v>-5828.3895526892002</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
@@ -42573,7 +42729,7 @@
         <v>8684.9766038396901</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
@@ -42647,7 +42803,7 @@
         <v>3216.6225401582901</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
@@ -42721,7 +42877,7 @@
         <v>1763.9043727999899</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
@@ -42795,7 +42951,7 @@
         <v>3704.4496908814099</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
@@ -42869,7 +43025,7 @@
         <v>14513.3661565289</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>20</v>
       </c>
@@ -42943,7 +43099,7 @@
         <v>5772.6302372380196</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
@@ -43017,7 +43173,7 @@
         <v>-214.03675571743</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
@@ -43091,7 +43247,7 @@
         <v>8954.7726750082802</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
@@ -43165,7 +43321,7 @@
         <v>7360.6255679371698</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
@@ -43239,7 +43395,7 @@
         <v>18935.920760703699</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>25</v>
       </c>
@@ -43313,7 +43469,7 @@
         <v>17528.508047856401</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>26</v>
       </c>
@@ -43387,7 +43543,7 @@
         <v>1407.4127128472601</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
@@ -43461,7 +43617,7 @@
         <v>2599.8237492879398</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>28</v>
       </c>
@@ -43535,7 +43691,7 @@
         <v>-1192.4110364406999</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>29</v>
       </c>
@@ -43609,7 +43765,7 @@
         <v>11575.2951927665</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>25</v>
       </c>
@@ -43683,7 +43839,7 @@
         <v>-3139.6740043131999</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -43757,7 +43913,7 @@
         <v>14714.969197079699</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>27</v>
       </c>
@@ -43831,7 +43987,7 @@
         <v>13064.9731012144</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
@@ -43905,7 +44061,7 @@
         <v>1649.9960958653601</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
@@ -43979,7 +44135,7 @@
         <v>-1788.7804503911</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -44053,7 +44209,7 @@
         <v>-8093.6553195649003</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>19</v>
       </c>
@@ -44127,7 +44283,7 @@
         <v>1189.27149510036</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -44201,7 +44357,7 @@
         <v>26.77760129</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>33</v>
       </c>
@@ -44275,7 +44431,7 @@
         <v>3397.8787344247298</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>34</v>
       </c>
@@ -44349,7 +44505,7 @@
         <v>609.74727354836602</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -44423,7 +44579,7 @@
         <v>-2845.9392607711002</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>36</v>
       </c>
@@ -44497,7 +44653,7 @@
         <v>0.80714660841174002</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>23</v>
       </c>
@@ -44571,7 +44727,7 @@
         <v>9282.9268146652703</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>33</v>
       </c>
@@ -44645,7 +44801,7 @@
         <v>879.16120243558396</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>34</v>
       </c>
@@ -44719,7 +44875,7 @@
         <v>7500.1491590853602</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>35</v>
       </c>
@@ -44793,7 +44949,7 @@
         <v>906.68678319476805</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>37</v>
       </c>
@@ -44867,7 +45023,7 @@
         <v>-1.09066E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>38</v>
       </c>
@@ -44941,7 +45097,7 @@
         <v>-3.0692393904466999</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
@@ -45043,7 +45199,7 @@
       <c r="W43" s="38"/>
       <c r="X43" s="38"/>
     </row>
-    <row r="44" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>41</v>
       </c>
@@ -45117,7 +45273,7 @@
         <v>-8350.1997547079991</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>42</v>
       </c>
@@ -45191,7 +45347,7 @@
         <v>11575.2951927665</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -45265,7 +45421,7 @@
         <v>14714.969197079699</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>43</v>
       </c>
@@ -45339,7 +45495,7 @@
         <v>7402.7653546656602</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>45</v>
       </c>
@@ -45413,7 +45569,7 @@
         <v>7312.2038424140801</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>25</v>
       </c>
@@ -45487,7 +45643,7 @@
         <v>-3139.6740043131999</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>46</v>
       </c>
@@ -45561,7 +45717,7 @@
         <v>-1718.8849996723</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>47</v>
       </c>
@@ -45635,33 +45791,33 @@
         <v>-1420.7890046409</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="31" t="s">
+    <row r="53" spans="1:24" ht="9.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
-      <c r="X53" s="31"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="27"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27"/>
+      <c r="O53" s="27"/>
+      <c r="P53" s="27"/>
+      <c r="Q53" s="27"/>
+      <c r="R53" s="27"/>
+      <c r="S53" s="27"/>
+      <c r="T53" s="27"/>
+      <c r="U53" s="27"/>
+      <c r="V53" s="27"/>
+      <c r="W53" s="27"/>
+      <c r="X53" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">
